--- a/Ebooks/Plan.xlsx
+++ b/Ebooks/Plan.xlsx
@@ -1117,9 +1117,18 @@
       <c r="B10" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
+      <c r="C10" s="12">
+        <f>E10-D10</f>
+        <v>4</v>
+      </c>
+      <c r="D10" s="10">
+        <f>MIN(D11:D13)</f>
+        <v>46215</v>
+      </c>
+      <c r="E10" s="10">
+        <f>MAX(E11:E13)</f>
+        <v>46219</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1158,9 +1167,16 @@
       <c r="B11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="C11" s="15">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>46215</v>
+      </c>
+      <c r="E11" s="7">
+        <f>D11+C11</f>
+        <v>46216</v>
+      </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1199,9 +1215,16 @@
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
+      <c r="C12" s="15">
+        <v>2</v>
+      </c>
+      <c r="D12" s="7">
+        <v>46216</v>
+      </c>
+      <c r="E12" s="7">
+        <f>D12+C12</f>
+        <v>46218</v>
+      </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1240,9 +1263,16 @@
       <c r="B13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
+      <c r="C13" s="15">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>46218</v>
+      </c>
+      <c r="E13" s="7">
+        <f>D13+C13</f>
+        <v>46219</v>
+      </c>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="6"/>
@@ -1281,9 +1311,16 @@
       <c r="B14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
+      <c r="C14" s="15">
+        <v>5</v>
+      </c>
+      <c r="D14" s="7">
+        <v>46218</v>
+      </c>
+      <c r="E14" s="7">
+        <f>D14+C14</f>
+        <v>46223</v>
+      </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
@@ -1322,9 +1359,18 @@
       <c r="B15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
+      <c r="C15" s="12">
+        <f>E15-D15</f>
+        <v>27</v>
+      </c>
+      <c r="D15" s="10">
+        <f>MIN(D16:D23)</f>
+        <v>46223</v>
+      </c>
+      <c r="E15" s="10">
+        <f>MAX(E16:E23)</f>
+        <v>46250</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1363,9 +1409,16 @@
       <c r="B16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
+      <c r="C16" s="15">
+        <v>3</v>
+      </c>
+      <c r="D16" s="7">
+        <v>46223</v>
+      </c>
+      <c r="E16" s="7">
+        <f>D16+C16</f>
+        <v>46226</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
@@ -1404,9 +1457,16 @@
       <c r="B17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
+      <c r="C17" s="15">
+        <v>2</v>
+      </c>
+      <c r="D17" s="7">
+        <v>46226</v>
+      </c>
+      <c r="E17" s="7">
+        <f>D17+C17</f>
+        <v>46228</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
@@ -1445,9 +1505,16 @@
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
+      <c r="C18" s="15">
+        <v>4</v>
+      </c>
+      <c r="D18" s="7">
+        <v>46228</v>
+      </c>
+      <c r="E18" s="7">
+        <f>D18+C18</f>
+        <v>46232</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1486,9 +1553,16 @@
       <c r="B19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
+      <c r="C19" s="15">
+        <v>5</v>
+      </c>
+      <c r="D19" s="7">
+        <v>46228</v>
+      </c>
+      <c r="E19" s="7">
+        <f>D19+C19</f>
+        <v>46233</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1527,9 +1601,16 @@
       <c r="B20" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C20" s="15"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
+      <c r="C20" s="15">
+        <v>11</v>
+      </c>
+      <c r="D20" s="7">
+        <v>46233</v>
+      </c>
+      <c r="E20" s="7">
+        <f>D20+C20</f>
+        <v>46244</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -1568,9 +1649,16 @@
       <c r="B21" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="15"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
+      <c r="C21" s="15">
+        <v>4</v>
+      </c>
+      <c r="D21" s="7">
+        <v>46244</v>
+      </c>
+      <c r="E21" s="7">
+        <f>D21+C21</f>
+        <v>46248</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1609,9 +1697,16 @@
       <c r="B22" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
+      <c r="C22" s="15">
+        <v>3</v>
+      </c>
+      <c r="D22" s="7">
+        <v>46245</v>
+      </c>
+      <c r="E22" s="7">
+        <f>D22+C22</f>
+        <v>46248</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1650,9 +1745,16 @@
       <c r="B23" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="C23" s="15">
+        <v>2</v>
+      </c>
+      <c r="D23" s="7">
+        <v>46248</v>
+      </c>
+      <c r="E23" s="7">
+        <f>D23+C23</f>
+        <v>46250</v>
+      </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
@@ -1691,9 +1793,16 @@
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="15"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
+      <c r="C24" s="15">
+        <v>35</v>
+      </c>
+      <c r="D24" s="7">
+        <v>46215</v>
+      </c>
+      <c r="E24" s="7">
+        <f>D24+C24</f>
+        <v>46250</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1732,9 +1841,16 @@
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
+      <c r="C25" s="15">
+        <v>3</v>
+      </c>
+      <c r="D25" s="7">
+        <v>46247</v>
+      </c>
+      <c r="E25" s="7">
+        <f>D25+C25</f>
+        <v>46250</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>

--- a/Ebooks/Plan.xlsx
+++ b/Ebooks/Plan.xlsx
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>Task Name</t>
   </si>
@@ -168,6 +168,33 @@
   </si>
   <si>
     <t>CLOSING</t>
+  </si>
+  <si>
+    <t>w7</t>
+  </si>
+  <si>
+    <t>w8</t>
+  </si>
+  <si>
+    <t>w9</t>
+  </si>
+  <si>
+    <t>w10</t>
+  </si>
+  <si>
+    <t>w11</t>
+  </si>
+  <si>
+    <t>w12</t>
+  </si>
+  <si>
+    <t>w13</t>
+  </si>
+  <si>
+    <t>w14</t>
+  </si>
+  <si>
+    <t>w15</t>
   </si>
 </sst>
 </file>
@@ -649,7 +676,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F7F5B0-1B8D-4819-819D-6A9F41E72B54}">
-  <dimension ref="A2:AI25"/>
+  <dimension ref="A2:CB25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -657,7 +684,7 @@
     <col min="3" max="3" width="8" style="16" customWidth="1"/>
     <col min="4" max="4" width="11.44140625" customWidth="1"/>
     <col min="5" max="5" width="12.77734375" customWidth="1"/>
-    <col min="6" max="35" width="4" customWidth="1"/>
+    <col min="6" max="80" width="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -718,6 +745,69 @@
       <c r="AG2" s="14"/>
       <c r="AH2" s="14"/>
       <c r="AI2" s="14"/>
+      <c r="AJ2" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK2" s="14"/>
+      <c r="AL2" s="14"/>
+      <c r="AM2" s="14"/>
+      <c r="AN2" s="14"/>
+      <c r="AO2" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP2" s="14"/>
+      <c r="AQ2" s="14"/>
+      <c r="AR2" s="14"/>
+      <c r="AS2" s="14"/>
+      <c r="AT2" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="AU2" s="14"/>
+      <c r="AV2" s="14"/>
+      <c r="AW2" s="14"/>
+      <c r="AX2" s="14"/>
+      <c r="AY2" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="AZ2" s="14"/>
+      <c r="BA2" s="14"/>
+      <c r="BB2" s="14"/>
+      <c r="BC2" s="14"/>
+      <c r="BD2" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="BE2" s="14"/>
+      <c r="BF2" s="14"/>
+      <c r="BG2" s="14"/>
+      <c r="BH2" s="14"/>
+      <c r="BI2" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="BJ2" s="14"/>
+      <c r="BK2" s="14"/>
+      <c r="BL2" s="14"/>
+      <c r="BM2" s="14"/>
+      <c r="BN2" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="BO2" s="14"/>
+      <c r="BP2" s="14"/>
+      <c r="BQ2" s="14"/>
+      <c r="BR2" s="14"/>
+      <c r="BS2" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="BT2" s="14"/>
+      <c r="BU2" s="14"/>
+      <c r="BV2" s="14"/>
+      <c r="BW2" s="14"/>
+      <c r="BX2" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="BY2" s="14"/>
+      <c r="BZ2" s="14"/>
+      <c r="CA2" s="14"/>
+      <c r="CB2" s="14"/>
     </row>
     <row r="3" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
@@ -727,92 +817,302 @@
       <c r="E3" s="13"/>
       <c r="F3" s="2" t="s">
         <v>10</v>
+        <v>46216</v>
       </c>
       <c r="G3" s="2" t="s">
+        <f>F3+1</f>
         <v>11</v>
       </c>
       <c r="H3" s="2" t="s">
+        <f>G3+1</f>
         <v>12</v>
       </c>
       <c r="I3" s="2" t="s">
+        <f>H3+1</f>
         <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
+        <f>I3+1</f>
         <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
+        <f>J3+3</f>
         <v>10</v>
       </c>
       <c r="L3" s="2" t="s">
+        <f>K3+1</f>
         <v>11</v>
       </c>
       <c r="M3" s="2" t="s">
+        <f>L3+1</f>
         <v>12</v>
       </c>
       <c r="N3" s="2" t="s">
+        <f>M3+1</f>
         <v>13</v>
       </c>
       <c r="O3" s="2" t="s">
+        <f>N3+1</f>
         <v>14</v>
       </c>
       <c r="P3" s="2" t="s">
+        <f>O3+3</f>
         <v>10</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <f>P3+1</f>
         <v>11</v>
       </c>
       <c r="R3" s="2" t="s">
+        <f>Q3+1</f>
         <v>12</v>
       </c>
       <c r="S3" s="2" t="s">
+        <f>R3+1</f>
         <v>13</v>
       </c>
       <c r="T3" s="2" t="s">
+        <f>S3+1</f>
         <v>14</v>
       </c>
       <c r="U3" s="2" t="s">
+        <f>T3+3</f>
         <v>10</v>
       </c>
       <c r="V3" s="2" t="s">
+        <f>U3+1</f>
         <v>11</v>
       </c>
       <c r="W3" s="2" t="s">
+        <f>V3+1</f>
         <v>12</v>
       </c>
       <c r="X3" s="2" t="s">
+        <f>W3+1</f>
         <v>13</v>
       </c>
       <c r="Y3" s="2" t="s">
+        <f>X3+1</f>
         <v>14</v>
       </c>
       <c r="Z3" s="2" t="s">
+        <f>Y3+3</f>
         <v>10</v>
       </c>
       <c r="AA3" s="2" t="s">
+        <f>Z3+1</f>
         <v>11</v>
       </c>
       <c r="AB3" s="2" t="s">
+        <f>AA3+1</f>
         <v>12</v>
       </c>
       <c r="AC3" s="2" t="s">
+        <f>AB3+1</f>
         <v>13</v>
       </c>
       <c r="AD3" s="2" t="s">
+        <f>AC3+1</f>
         <v>14</v>
       </c>
       <c r="AE3" s="2" t="s">
+        <f>AD3+3</f>
         <v>10</v>
       </c>
       <c r="AF3" s="2" t="s">
+        <f>AE3+1</f>
         <v>11</v>
       </c>
       <c r="AG3" s="2" t="s">
+        <f>AF3+1</f>
         <v>12</v>
       </c>
       <c r="AH3" s="2" t="s">
+        <f>AG3+1</f>
         <v>13</v>
       </c>
       <c r="AI3" s="2" t="s">
+        <f>AH3+1</f>
+        <v>14</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <f>AI3+3</f>
+        <v>10</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <f>AJ3+1</f>
+        <v>11</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <f>AK3+1</f>
+        <v>12</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <f>AL3+1</f>
+        <v>13</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <f>AM3+1</f>
+        <v>14</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <f>AN3+3</f>
+        <v>10</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <f>AO3+1</f>
+        <v>11</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <f>AP3+1</f>
+        <v>12</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <f>AQ3+1</f>
+        <v>13</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <f>AR3+1</f>
+        <v>14</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <f>AS3+3</f>
+        <v>10</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <f>AT3+1</f>
+        <v>11</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <f>AU3+1</f>
+        <v>12</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <f>AV3+1</f>
+        <v>13</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <f>AW3+1</f>
+        <v>14</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <f>AX3+3</f>
+        <v>10</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <f>AY3+1</f>
+        <v>11</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <f>AZ3+1</f>
+        <v>12</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <f>BA3+1</f>
+        <v>13</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <f>BB3+1</f>
+        <v>14</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <f>BC3+3</f>
+        <v>10</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <f>BD3+1</f>
+        <v>11</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <f>BE3+1</f>
+        <v>12</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <f>BF3+1</f>
+        <v>13</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <f>BG3+1</f>
+        <v>14</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <f>BH3+3</f>
+        <v>10</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <f>BI3+1</f>
+        <v>11</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <f>BJ3+1</f>
+        <v>12</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <f>BK3+1</f>
+        <v>13</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <f>BL3+1</f>
+        <v>14</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <f>BM3+3</f>
+        <v>10</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <f>BN3+1</f>
+        <v>11</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <f>BO3+1</f>
+        <v>12</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <f>BP3+1</f>
+        <v>13</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <f>BQ3+1</f>
+        <v>14</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <f>BR3+3</f>
+        <v>10</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <f>BS3+1</f>
+        <v>11</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <f>BT3+1</f>
+        <v>12</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <f>BU3+1</f>
+        <v>13</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <f>BV3+1</f>
+        <v>14</v>
+      </c>
+      <c r="BX3" s="2" t="s">
+        <f>BW3+3</f>
+        <v>10</v>
+      </c>
+      <c r="BY3" s="2" t="s">
+        <f>BX3+1</f>
+        <v>11</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <f>BY3+1</f>
+        <v>12</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <f>BZ3+1</f>
+        <v>13</v>
+      </c>
+      <c r="CB3" s="2" t="s">
+        <f>CA3+1</f>
         <v>14</v>
       </c>
     </row>
@@ -835,36 +1135,231 @@
         <f>MAX(E5:E9)</f>
         <v>46234</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="8"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="1"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="1"/>
-      <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="1"/>
-      <c r="AC4" s="1"/>
-      <c r="AD4" s="1"/>
-      <c r="AE4" s="1"/>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="1"/>
-      <c r="AI4" s="1"/>
+      <c r="F4" s="1">
+        <f>IF(AND(F$3&gt;=$D4,F$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="G4" s="1">
+        <f>IF(AND(G$3&gt;=$D4,G$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="H4" s="1">
+        <f>IF(AND(H$3&gt;=$D4,H$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="I4" s="1">
+        <f>IF(AND(I$3&gt;=$D4,I$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="J4" s="1">
+        <f>IF(AND(J$3&gt;=$D4,J$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="K4" s="1">
+        <f>IF(AND(K$3&gt;=$D4,K$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="L4" s="1">
+        <f>IF(AND(L$3&gt;=$D4,L$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="M4" s="1">
+        <f>IF(AND(M$3&gt;=$D4,M$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="N4" s="1">
+        <f>IF(AND(N$3&gt;=$D4,N$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="O4" s="1">
+        <f>IF(AND(O$3&gt;=$D4,O$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="P4" s="1">
+        <f>IF(AND(P$3&gt;=$D4,P$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="Q4" s="1">
+        <f>IF(AND(Q$3&gt;=$D4,Q$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="R4" s="1">
+        <f>IF(AND(R$3&gt;=$D4,R$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="S4" s="1">
+        <f>IF(AND(S$3&gt;=$D4,S$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="T4" s="1">
+        <f>IF(AND(T$3&gt;=$D4,T$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="U4" s="1">
+        <f>IF(AND(U$3&gt;=$D4,U$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="V4" s="1">
+        <f>IF(AND(V$3&gt;=$D4,V$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="W4" s="1">
+        <f>IF(AND(W$3&gt;=$D4,W$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="X4" s="1">
+        <f>IF(AND(X$3&gt;=$D4,X$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="Y4" s="1">
+        <f>IF(AND(Y$3&gt;=$D4,Y$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="Z4" s="1">
+        <f>IF(AND(Z$3&gt;=$D4,Z$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AA4" s="1">
+        <f>IF(AND(AA$3&gt;=$D4,AA$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AB4" s="1">
+        <f>IF(AND(AB$3&gt;=$D4,AB$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AC4" s="1">
+        <f>IF(AND(AC$3&gt;=$D4,AC$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AD4" s="1">
+        <f>IF(AND(AD$3&gt;=$D4,AD$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AE4" s="1">
+        <f>IF(AND(AE$3&gt;=$D4,AE$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AF4" s="1">
+        <f>IF(AND(AF$3&gt;=$D4,AF$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AG4" s="1">
+        <f>IF(AND(AG$3&gt;=$D4,AG$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AH4" s="1">
+        <f>IF(AND(AH$3&gt;=$D4,AH$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AI4" s="1">
+        <f>IF(AND(AI$3&gt;=$D4,AI$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AJ4" s="1">
+        <f>IF(AND(AJ$3&gt;=$D4,AJ$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AK4" s="1">
+        <f>IF(AND(AK$3&gt;=$D4,AK$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AL4" s="1">
+        <f>IF(AND(AL$3&gt;=$D4,AL$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AM4" s="1">
+        <f>IF(AND(AM$3&gt;=$D4,AM$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AN4" s="1">
+        <f>IF(AND(AN$3&gt;=$D4,AN$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AO4" s="1">
+        <f>IF(AND(AO$3&gt;=$D4,AO$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AP4" s="1">
+        <f>IF(AND(AP$3&gt;=$D4,AP$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AQ4" s="1">
+        <f>IF(AND(AQ$3&gt;=$D4,AQ$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AR4" s="1">
+        <f>IF(AND(AR$3&gt;=$D4,AR$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AS4" s="1">
+        <f>IF(AND(AS$3&gt;=$D4,AS$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AT4" s="1">
+        <f>IF(AND(AT$3&gt;=$D4,AT$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AU4" s="1">
+        <f>IF(AND(AU$3&gt;=$D4,AU$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AV4" s="1">
+        <f>IF(AND(AV$3&gt;=$D4,AV$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AW4" s="1">
+        <f>IF(AND(AW$3&gt;=$D4,AW$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AX4" s="1">
+        <f>IF(AND(AX$3&gt;=$D4,AX$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AY4" s="1">
+        <f>IF(AND(AY$3&gt;=$D4,AY$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="AZ4" s="1">
+        <f>IF(AND(AZ$3&gt;=$D4,AZ$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BA4" s="1">
+        <f>IF(AND(BA$3&gt;=$D4,BA$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BB4" s="1">
+        <f>IF(AND(BB$3&gt;=$D4,BB$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BC4" s="1">
+        <f>IF(AND(BC$3&gt;=$D4,BC$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BD4" s="1">
+        <f>IF(AND(BD$3&gt;=$D4,BD$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BE4" s="1">
+        <f>IF(AND(BE$3&gt;=$D4,BE$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BF4" s="1">
+        <f>IF(AND(BF$3&gt;=$D4,BF$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BG4" s="1">
+        <f>IF(AND(BG$3&gt;=$D4,BG$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BH4" s="1">
+        <f>IF(AND(BH$3&gt;=$D4,BH$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BI4" s="1">
+        <f>IF(AND(BI$3&gt;=$D4,BI$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BJ4" s="1">
+        <f>IF(AND(BJ$3&gt;=$D4,BJ$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BK4" s="1">
+        <f>IF(AND(BK$3&gt;=$D4,BK$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BL4" s="1">
+        <f>IF(AND(BL$3&gt;=$D4,BL$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BM4" s="1">
+        <f>IF(AND(BM$3&gt;=$D4,BM$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BN4" s="1">
+        <f>IF(AND(BN$3&gt;=$D4,BN$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BO4" s="1">
+        <f>IF(AND(BO$3&gt;=$D4,BO$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BP4" s="1">
+        <f>IF(AND(BP$3&gt;=$D4,BP$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BQ4" s="1">
+        <f>IF(AND(BQ$3&gt;=$D4,BQ$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BR4" s="1">
+        <f>IF(AND(BR$3&gt;=$D4,BR$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BS4" s="1">
+        <f>IF(AND(BS$3&gt;=$D4,BS$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BT4" s="1">
+        <f>IF(AND(BT$3&gt;=$D4,BT$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BU4" s="1">
+        <f>IF(AND(BU$3&gt;=$D4,BU$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BV4" s="1">
+        <f>IF(AND(BV$3&gt;=$D4,BV$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BW4" s="1">
+        <f>IF(AND(BW$3&gt;=$D4,BW$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BX4" s="1">
+        <f>IF(AND(BX$3&gt;=$D4,BX$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BY4" s="1">
+        <f>IF(AND(BY$3&gt;=$D4,BY$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="BZ4" s="1">
+        <f>IF(AND(BZ$3&gt;=$D4,BZ$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="CA4" s="1">
+        <f>IF(AND(CA$3&gt;=$D4,CA$3&lt;=$E4),"█","")</f>
+      </c>
+      <c r="CB4" s="1">
+        <f>IF(AND(CB$3&gt;=$D4,CB$3&lt;=$E4),"█","")</f>
+      </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="17">
@@ -883,36 +1378,231 @@
         <f>D5+C5</f>
         <v>46227</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
-      <c r="AB5" s="1"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="1"/>
-      <c r="AE5" s="1"/>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
-      <c r="AH5" s="1"/>
-      <c r="AI5" s="1"/>
+      <c r="F5" s="1">
+        <f>IF(AND(F$3&gt;=$D5,F$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="G5" s="1">
+        <f>IF(AND(G$3&gt;=$D5,G$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="H5" s="1">
+        <f>IF(AND(H$3&gt;=$D5,H$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="I5" s="1">
+        <f>IF(AND(I$3&gt;=$D5,I$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="J5" s="1">
+        <f>IF(AND(J$3&gt;=$D5,J$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="K5" s="1">
+        <f>IF(AND(K$3&gt;=$D5,K$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="L5" s="1">
+        <f>IF(AND(L$3&gt;=$D5,L$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="M5" s="1">
+        <f>IF(AND(M$3&gt;=$D5,M$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="N5" s="1">
+        <f>IF(AND(N$3&gt;=$D5,N$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="O5" s="1">
+        <f>IF(AND(O$3&gt;=$D5,O$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="P5" s="1">
+        <f>IF(AND(P$3&gt;=$D5,P$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="Q5" s="1">
+        <f>IF(AND(Q$3&gt;=$D5,Q$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="R5" s="1">
+        <f>IF(AND(R$3&gt;=$D5,R$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="S5" s="1">
+        <f>IF(AND(S$3&gt;=$D5,S$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="T5" s="1">
+        <f>IF(AND(T$3&gt;=$D5,T$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="U5" s="1">
+        <f>IF(AND(U$3&gt;=$D5,U$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="V5" s="1">
+        <f>IF(AND(V$3&gt;=$D5,V$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="W5" s="1">
+        <f>IF(AND(W$3&gt;=$D5,W$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="X5" s="1">
+        <f>IF(AND(X$3&gt;=$D5,X$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="Y5" s="1">
+        <f>IF(AND(Y$3&gt;=$D5,Y$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="Z5" s="1">
+        <f>IF(AND(Z$3&gt;=$D5,Z$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AA5" s="1">
+        <f>IF(AND(AA$3&gt;=$D5,AA$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AB5" s="1">
+        <f>IF(AND(AB$3&gt;=$D5,AB$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AC5" s="1">
+        <f>IF(AND(AC$3&gt;=$D5,AC$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AD5" s="1">
+        <f>IF(AND(AD$3&gt;=$D5,AD$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AE5" s="1">
+        <f>IF(AND(AE$3&gt;=$D5,AE$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AF5" s="1">
+        <f>IF(AND(AF$3&gt;=$D5,AF$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AG5" s="1">
+        <f>IF(AND(AG$3&gt;=$D5,AG$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AH5" s="1">
+        <f>IF(AND(AH$3&gt;=$D5,AH$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AI5" s="1">
+        <f>IF(AND(AI$3&gt;=$D5,AI$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AJ5" s="1">
+        <f>IF(AND(AJ$3&gt;=$D5,AJ$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AK5" s="1">
+        <f>IF(AND(AK$3&gt;=$D5,AK$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AL5" s="1">
+        <f>IF(AND(AL$3&gt;=$D5,AL$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AM5" s="1">
+        <f>IF(AND(AM$3&gt;=$D5,AM$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AN5" s="1">
+        <f>IF(AND(AN$3&gt;=$D5,AN$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AO5" s="1">
+        <f>IF(AND(AO$3&gt;=$D5,AO$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AP5" s="1">
+        <f>IF(AND(AP$3&gt;=$D5,AP$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AQ5" s="1">
+        <f>IF(AND(AQ$3&gt;=$D5,AQ$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AR5" s="1">
+        <f>IF(AND(AR$3&gt;=$D5,AR$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AS5" s="1">
+        <f>IF(AND(AS$3&gt;=$D5,AS$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AT5" s="1">
+        <f>IF(AND(AT$3&gt;=$D5,AT$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AU5" s="1">
+        <f>IF(AND(AU$3&gt;=$D5,AU$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AV5" s="1">
+        <f>IF(AND(AV$3&gt;=$D5,AV$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AW5" s="1">
+        <f>IF(AND(AW$3&gt;=$D5,AW$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AX5" s="1">
+        <f>IF(AND(AX$3&gt;=$D5,AX$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AY5" s="1">
+        <f>IF(AND(AY$3&gt;=$D5,AY$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="AZ5" s="1">
+        <f>IF(AND(AZ$3&gt;=$D5,AZ$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BA5" s="1">
+        <f>IF(AND(BA$3&gt;=$D5,BA$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BB5" s="1">
+        <f>IF(AND(BB$3&gt;=$D5,BB$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BC5" s="1">
+        <f>IF(AND(BC$3&gt;=$D5,BC$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BD5" s="1">
+        <f>IF(AND(BD$3&gt;=$D5,BD$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BE5" s="1">
+        <f>IF(AND(BE$3&gt;=$D5,BE$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BF5" s="1">
+        <f>IF(AND(BF$3&gt;=$D5,BF$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BG5" s="1">
+        <f>IF(AND(BG$3&gt;=$D5,BG$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BH5" s="1">
+        <f>IF(AND(BH$3&gt;=$D5,BH$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BI5" s="1">
+        <f>IF(AND(BI$3&gt;=$D5,BI$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BJ5" s="1">
+        <f>IF(AND(BJ$3&gt;=$D5,BJ$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BK5" s="1">
+        <f>IF(AND(BK$3&gt;=$D5,BK$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BL5" s="1">
+        <f>IF(AND(BL$3&gt;=$D5,BL$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BM5" s="1">
+        <f>IF(AND(BM$3&gt;=$D5,BM$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BN5" s="1">
+        <f>IF(AND(BN$3&gt;=$D5,BN$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BO5" s="1">
+        <f>IF(AND(BO$3&gt;=$D5,BO$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BP5" s="1">
+        <f>IF(AND(BP$3&gt;=$D5,BP$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BQ5" s="1">
+        <f>IF(AND(BQ$3&gt;=$D5,BQ$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BR5" s="1">
+        <f>IF(AND(BR$3&gt;=$D5,BR$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BS5" s="1">
+        <f>IF(AND(BS$3&gt;=$D5,BS$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BT5" s="1">
+        <f>IF(AND(BT$3&gt;=$D5,BT$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BU5" s="1">
+        <f>IF(AND(BU$3&gt;=$D5,BU$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BV5" s="1">
+        <f>IF(AND(BV$3&gt;=$D5,BV$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BW5" s="1">
+        <f>IF(AND(BW$3&gt;=$D5,BW$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BX5" s="1">
+        <f>IF(AND(BX$3&gt;=$D5,BX$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BY5" s="1">
+        <f>IF(AND(BY$3&gt;=$D5,BY$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="BZ5" s="1">
+        <f>IF(AND(BZ$3&gt;=$D5,BZ$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="CA5" s="1">
+        <f>IF(AND(CA$3&gt;=$D5,CA$3&lt;=$E5),"█","")</f>
+      </c>
+      <c r="CB5" s="1">
+        <f>IF(AND(CB$3&gt;=$D5,CB$3&lt;=$E5),"█","")</f>
+      </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="17">
@@ -932,36 +1622,231 @@
         <f t="shared" ref="E6:E9" si="0">D6+C6</f>
         <v>46229</v>
       </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="1"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-      <c r="AE6" s="1"/>
-      <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="1"/>
-      <c r="AI6" s="1"/>
+      <c r="F6" s="1">
+        <f>IF(AND(F$3&gt;=$D6,F$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="G6" s="1">
+        <f>IF(AND(G$3&gt;=$D6,G$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="H6" s="1">
+        <f>IF(AND(H$3&gt;=$D6,H$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="I6" s="1">
+        <f>IF(AND(I$3&gt;=$D6,I$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="J6" s="1">
+        <f>IF(AND(J$3&gt;=$D6,J$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="K6" s="1">
+        <f>IF(AND(K$3&gt;=$D6,K$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="L6" s="1">
+        <f>IF(AND(L$3&gt;=$D6,L$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="M6" s="1">
+        <f>IF(AND(M$3&gt;=$D6,M$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="N6" s="1">
+        <f>IF(AND(N$3&gt;=$D6,N$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="O6" s="1">
+        <f>IF(AND(O$3&gt;=$D6,O$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="P6" s="1">
+        <f>IF(AND(P$3&gt;=$D6,P$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="Q6" s="1">
+        <f>IF(AND(Q$3&gt;=$D6,Q$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="R6" s="1">
+        <f>IF(AND(R$3&gt;=$D6,R$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="S6" s="1">
+        <f>IF(AND(S$3&gt;=$D6,S$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="T6" s="1">
+        <f>IF(AND(T$3&gt;=$D6,T$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="U6" s="1">
+        <f>IF(AND(U$3&gt;=$D6,U$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="V6" s="1">
+        <f>IF(AND(V$3&gt;=$D6,V$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="W6" s="1">
+        <f>IF(AND(W$3&gt;=$D6,W$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="X6" s="1">
+        <f>IF(AND(X$3&gt;=$D6,X$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="Y6" s="1">
+        <f>IF(AND(Y$3&gt;=$D6,Y$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="Z6" s="1">
+        <f>IF(AND(Z$3&gt;=$D6,Z$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AA6" s="1">
+        <f>IF(AND(AA$3&gt;=$D6,AA$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AB6" s="1">
+        <f>IF(AND(AB$3&gt;=$D6,AB$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AC6" s="1">
+        <f>IF(AND(AC$3&gt;=$D6,AC$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AD6" s="1">
+        <f>IF(AND(AD$3&gt;=$D6,AD$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AE6" s="1">
+        <f>IF(AND(AE$3&gt;=$D6,AE$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AF6" s="1">
+        <f>IF(AND(AF$3&gt;=$D6,AF$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AG6" s="1">
+        <f>IF(AND(AG$3&gt;=$D6,AG$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AH6" s="1">
+        <f>IF(AND(AH$3&gt;=$D6,AH$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AI6" s="1">
+        <f>IF(AND(AI$3&gt;=$D6,AI$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AJ6" s="1">
+        <f>IF(AND(AJ$3&gt;=$D6,AJ$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AK6" s="1">
+        <f>IF(AND(AK$3&gt;=$D6,AK$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AL6" s="1">
+        <f>IF(AND(AL$3&gt;=$D6,AL$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AM6" s="1">
+        <f>IF(AND(AM$3&gt;=$D6,AM$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AN6" s="1">
+        <f>IF(AND(AN$3&gt;=$D6,AN$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AO6" s="1">
+        <f>IF(AND(AO$3&gt;=$D6,AO$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AP6" s="1">
+        <f>IF(AND(AP$3&gt;=$D6,AP$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AQ6" s="1">
+        <f>IF(AND(AQ$3&gt;=$D6,AQ$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AR6" s="1">
+        <f>IF(AND(AR$3&gt;=$D6,AR$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AS6" s="1">
+        <f>IF(AND(AS$3&gt;=$D6,AS$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AT6" s="1">
+        <f>IF(AND(AT$3&gt;=$D6,AT$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AU6" s="1">
+        <f>IF(AND(AU$3&gt;=$D6,AU$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AV6" s="1">
+        <f>IF(AND(AV$3&gt;=$D6,AV$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AW6" s="1">
+        <f>IF(AND(AW$3&gt;=$D6,AW$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AX6" s="1">
+        <f>IF(AND(AX$3&gt;=$D6,AX$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AY6" s="1">
+        <f>IF(AND(AY$3&gt;=$D6,AY$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="AZ6" s="1">
+        <f>IF(AND(AZ$3&gt;=$D6,AZ$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BA6" s="1">
+        <f>IF(AND(BA$3&gt;=$D6,BA$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BB6" s="1">
+        <f>IF(AND(BB$3&gt;=$D6,BB$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BC6" s="1">
+        <f>IF(AND(BC$3&gt;=$D6,BC$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BD6" s="1">
+        <f>IF(AND(BD$3&gt;=$D6,BD$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BE6" s="1">
+        <f>IF(AND(BE$3&gt;=$D6,BE$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BF6" s="1">
+        <f>IF(AND(BF$3&gt;=$D6,BF$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BG6" s="1">
+        <f>IF(AND(BG$3&gt;=$D6,BG$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BH6" s="1">
+        <f>IF(AND(BH$3&gt;=$D6,BH$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BI6" s="1">
+        <f>IF(AND(BI$3&gt;=$D6,BI$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BJ6" s="1">
+        <f>IF(AND(BJ$3&gt;=$D6,BJ$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BK6" s="1">
+        <f>IF(AND(BK$3&gt;=$D6,BK$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BL6" s="1">
+        <f>IF(AND(BL$3&gt;=$D6,BL$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BM6" s="1">
+        <f>IF(AND(BM$3&gt;=$D6,BM$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BN6" s="1">
+        <f>IF(AND(BN$3&gt;=$D6,BN$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BO6" s="1">
+        <f>IF(AND(BO$3&gt;=$D6,BO$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BP6" s="1">
+        <f>IF(AND(BP$3&gt;=$D6,BP$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BQ6" s="1">
+        <f>IF(AND(BQ$3&gt;=$D6,BQ$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BR6" s="1">
+        <f>IF(AND(BR$3&gt;=$D6,BR$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BS6" s="1">
+        <f>IF(AND(BS$3&gt;=$D6,BS$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BT6" s="1">
+        <f>IF(AND(BT$3&gt;=$D6,BT$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BU6" s="1">
+        <f>IF(AND(BU$3&gt;=$D6,BU$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BV6" s="1">
+        <f>IF(AND(BV$3&gt;=$D6,BV$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BW6" s="1">
+        <f>IF(AND(BW$3&gt;=$D6,BW$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BX6" s="1">
+        <f>IF(AND(BX$3&gt;=$D6,BX$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BY6" s="1">
+        <f>IF(AND(BY$3&gt;=$D6,BY$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="BZ6" s="1">
+        <f>IF(AND(BZ$3&gt;=$D6,BZ$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="CA6" s="1">
+        <f>IF(AND(CA$3&gt;=$D6,CA$3&lt;=$E6),"█","")</f>
+      </c>
+      <c r="CB6" s="1">
+        <f>IF(AND(CB$3&gt;=$D6,CB$3&lt;=$E6),"█","")</f>
+      </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="17">
@@ -977,40 +1862,232 @@
         <f>E6+1</f>
         <v>46230</v>
       </c>
-      <c r="E7" s="7">
-        <f t="shared" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="9"/>
-      <c r="J7" s="9"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="1"/>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="1"/>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-      <c r="AE7" s="1"/>
-      <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="1"/>
-      <c r="AI7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1">
+        <f>IF(AND(F$3&gt;=$D7,F$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="G7" s="1">
+        <f>IF(AND(G$3&gt;=$D7,G$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="H7" s="1">
+        <f>IF(AND(H$3&gt;=$D7,H$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="I7" s="1">
+        <f>IF(AND(I$3&gt;=$D7,I$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="J7" s="1">
+        <f>IF(AND(J$3&gt;=$D7,J$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="K7" s="1">
+        <f>IF(AND(K$3&gt;=$D7,K$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="L7" s="1">
+        <f>IF(AND(L$3&gt;=$D7,L$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="M7" s="1">
+        <f>IF(AND(M$3&gt;=$D7,M$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="N7" s="1">
+        <f>IF(AND(N$3&gt;=$D7,N$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="O7" s="1">
+        <f>IF(AND(O$3&gt;=$D7,O$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="P7" s="1">
+        <f>IF(AND(P$3&gt;=$D7,P$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="Q7" s="1">
+        <f>IF(AND(Q$3&gt;=$D7,Q$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="R7" s="1">
+        <f>IF(AND(R$3&gt;=$D7,R$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="S7" s="1">
+        <f>IF(AND(S$3&gt;=$D7,S$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="T7" s="1">
+        <f>IF(AND(T$3&gt;=$D7,T$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="U7" s="1">
+        <f>IF(AND(U$3&gt;=$D7,U$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="V7" s="1">
+        <f>IF(AND(V$3&gt;=$D7,V$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="W7" s="1">
+        <f>IF(AND(W$3&gt;=$D7,W$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="X7" s="1">
+        <f>IF(AND(X$3&gt;=$D7,X$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="Y7" s="1">
+        <f>IF(AND(Y$3&gt;=$D7,Y$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="Z7" s="1">
+        <f>IF(AND(Z$3&gt;=$D7,Z$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AA7" s="1">
+        <f>IF(AND(AA$3&gt;=$D7,AA$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AB7" s="1">
+        <f>IF(AND(AB$3&gt;=$D7,AB$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AC7" s="1">
+        <f>IF(AND(AC$3&gt;=$D7,AC$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AD7" s="1">
+        <f>IF(AND(AD$3&gt;=$D7,AD$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AE7" s="1">
+        <f>IF(AND(AE$3&gt;=$D7,AE$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AF7" s="1">
+        <f>IF(AND(AF$3&gt;=$D7,AF$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AG7" s="1">
+        <f>IF(AND(AG$3&gt;=$D7,AG$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AH7" s="1">
+        <f>IF(AND(AH$3&gt;=$D7,AH$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AI7" s="1">
+        <f>IF(AND(AI$3&gt;=$D7,AI$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AJ7" s="1">
+        <f>IF(AND(AJ$3&gt;=$D7,AJ$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AK7" s="1">
+        <f>IF(AND(AK$3&gt;=$D7,AK$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AL7" s="1">
+        <f>IF(AND(AL$3&gt;=$D7,AL$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AM7" s="1">
+        <f>IF(AND(AM$3&gt;=$D7,AM$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AN7" s="1">
+        <f>IF(AND(AN$3&gt;=$D7,AN$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AO7" s="1">
+        <f>IF(AND(AO$3&gt;=$D7,AO$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AP7" s="1">
+        <f>IF(AND(AP$3&gt;=$D7,AP$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AQ7" s="1">
+        <f>IF(AND(AQ$3&gt;=$D7,AQ$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AR7" s="1">
+        <f>IF(AND(AR$3&gt;=$D7,AR$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AS7" s="1">
+        <f>IF(AND(AS$3&gt;=$D7,AS$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AT7" s="1">
+        <f>IF(AND(AT$3&gt;=$D7,AT$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AU7" s="1">
+        <f>IF(AND(AU$3&gt;=$D7,AU$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AV7" s="1">
+        <f>IF(AND(AV$3&gt;=$D7,AV$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AW7" s="1">
+        <f>IF(AND(AW$3&gt;=$D7,AW$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AX7" s="1">
+        <f>IF(AND(AX$3&gt;=$D7,AX$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AY7" s="1">
+        <f>IF(AND(AY$3&gt;=$D7,AY$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="AZ7" s="1">
+        <f>IF(AND(AZ$3&gt;=$D7,AZ$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BA7" s="1">
+        <f>IF(AND(BA$3&gt;=$D7,BA$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BB7" s="1">
+        <f>IF(AND(BB$3&gt;=$D7,BB$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BC7" s="1">
+        <f>IF(AND(BC$3&gt;=$D7,BC$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BD7" s="1">
+        <f>IF(AND(BD$3&gt;=$D7,BD$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BE7" s="1">
+        <f>IF(AND(BE$3&gt;=$D7,BE$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BF7" s="1">
+        <f>IF(AND(BF$3&gt;=$D7,BF$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BG7" s="1">
+        <f>IF(AND(BG$3&gt;=$D7,BG$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BH7" s="1">
+        <f>IF(AND(BH$3&gt;=$D7,BH$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BI7" s="1">
+        <f>IF(AND(BI$3&gt;=$D7,BI$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BJ7" s="1">
+        <f>IF(AND(BJ$3&gt;=$D7,BJ$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BK7" s="1">
+        <f>IF(AND(BK$3&gt;=$D7,BK$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BL7" s="1">
+        <f>IF(AND(BL$3&gt;=$D7,BL$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BM7" s="1">
+        <f>IF(AND(BM$3&gt;=$D7,BM$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BN7" s="1">
+        <f>IF(AND(BN$3&gt;=$D7,BN$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BO7" s="1">
+        <f>IF(AND(BO$3&gt;=$D7,BO$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BP7" s="1">
+        <f>IF(AND(BP$3&gt;=$D7,BP$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BQ7" s="1">
+        <f>IF(AND(BQ$3&gt;=$D7,BQ$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BR7" s="1">
+        <f>IF(AND(BR$3&gt;=$D7,BR$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BS7" s="1">
+        <f>IF(AND(BS$3&gt;=$D7,BS$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BT7" s="1">
+        <f>IF(AND(BT$3&gt;=$D7,BT$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BU7" s="1">
+        <f>IF(AND(BU$3&gt;=$D7,BU$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BV7" s="1">
+        <f>IF(AND(BV$3&gt;=$D7,BV$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BW7" s="1">
+        <f>IF(AND(BW$3&gt;=$D7,BW$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BX7" s="1">
+        <f>IF(AND(BX$3&gt;=$D7,BX$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BY7" s="1">
+        <f>IF(AND(BY$3&gt;=$D7,BY$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="BZ7" s="1">
+        <f>IF(AND(BZ$3&gt;=$D7,BZ$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="CA7" s="1">
+        <f>IF(AND(CA$3&gt;=$D7,CA$3&lt;=$E7),"█","")</f>
+      </c>
+      <c r="CB7" s="1">
+        <f>IF(AND(CB$3&gt;=$D7,CB$3&lt;=$E7),"█","")</f>
+      </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="17">
@@ -1026,40 +2103,232 @@
         <f>E7+1</f>
         <v>46233</v>
       </c>
-      <c r="E8" s="7">
-        <f t="shared" si="0"/>
-        <v>46234</v>
-      </c>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="1"/>
-      <c r="W8" s="1"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="1"/>
-      <c r="AI8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1">
+        <f>IF(AND(F$3&gt;=$D8,F$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="G8" s="1">
+        <f>IF(AND(G$3&gt;=$D8,G$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="H8" s="1">
+        <f>IF(AND(H$3&gt;=$D8,H$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="I8" s="1">
+        <f>IF(AND(I$3&gt;=$D8,I$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="J8" s="1">
+        <f>IF(AND(J$3&gt;=$D8,J$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="K8" s="1">
+        <f>IF(AND(K$3&gt;=$D8,K$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="L8" s="1">
+        <f>IF(AND(L$3&gt;=$D8,L$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="M8" s="1">
+        <f>IF(AND(M$3&gt;=$D8,M$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="N8" s="1">
+        <f>IF(AND(N$3&gt;=$D8,N$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="O8" s="1">
+        <f>IF(AND(O$3&gt;=$D8,O$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="P8" s="1">
+        <f>IF(AND(P$3&gt;=$D8,P$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="Q8" s="1">
+        <f>IF(AND(Q$3&gt;=$D8,Q$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="R8" s="1">
+        <f>IF(AND(R$3&gt;=$D8,R$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="S8" s="1">
+        <f>IF(AND(S$3&gt;=$D8,S$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="T8" s="1">
+        <f>IF(AND(T$3&gt;=$D8,T$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="U8" s="1">
+        <f>IF(AND(U$3&gt;=$D8,U$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="V8" s="1">
+        <f>IF(AND(V$3&gt;=$D8,V$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="W8" s="1">
+        <f>IF(AND(W$3&gt;=$D8,W$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="X8" s="1">
+        <f>IF(AND(X$3&gt;=$D8,X$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="Y8" s="1">
+        <f>IF(AND(Y$3&gt;=$D8,Y$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="Z8" s="1">
+        <f>IF(AND(Z$3&gt;=$D8,Z$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AA8" s="1">
+        <f>IF(AND(AA$3&gt;=$D8,AA$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AB8" s="1">
+        <f>IF(AND(AB$3&gt;=$D8,AB$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AC8" s="1">
+        <f>IF(AND(AC$3&gt;=$D8,AC$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AD8" s="1">
+        <f>IF(AND(AD$3&gt;=$D8,AD$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AE8" s="1">
+        <f>IF(AND(AE$3&gt;=$D8,AE$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AF8" s="1">
+        <f>IF(AND(AF$3&gt;=$D8,AF$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AG8" s="1">
+        <f>IF(AND(AG$3&gt;=$D8,AG$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AH8" s="1">
+        <f>IF(AND(AH$3&gt;=$D8,AH$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AI8" s="1">
+        <f>IF(AND(AI$3&gt;=$D8,AI$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AJ8" s="1">
+        <f>IF(AND(AJ$3&gt;=$D8,AJ$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AK8" s="1">
+        <f>IF(AND(AK$3&gt;=$D8,AK$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AL8" s="1">
+        <f>IF(AND(AL$3&gt;=$D8,AL$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AM8" s="1">
+        <f>IF(AND(AM$3&gt;=$D8,AM$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AN8" s="1">
+        <f>IF(AND(AN$3&gt;=$D8,AN$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AO8" s="1">
+        <f>IF(AND(AO$3&gt;=$D8,AO$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AP8" s="1">
+        <f>IF(AND(AP$3&gt;=$D8,AP$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AQ8" s="1">
+        <f>IF(AND(AQ$3&gt;=$D8,AQ$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AR8" s="1">
+        <f>IF(AND(AR$3&gt;=$D8,AR$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AS8" s="1">
+        <f>IF(AND(AS$3&gt;=$D8,AS$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AT8" s="1">
+        <f>IF(AND(AT$3&gt;=$D8,AT$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AU8" s="1">
+        <f>IF(AND(AU$3&gt;=$D8,AU$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AV8" s="1">
+        <f>IF(AND(AV$3&gt;=$D8,AV$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AW8" s="1">
+        <f>IF(AND(AW$3&gt;=$D8,AW$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AX8" s="1">
+        <f>IF(AND(AX$3&gt;=$D8,AX$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AY8" s="1">
+        <f>IF(AND(AY$3&gt;=$D8,AY$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="AZ8" s="1">
+        <f>IF(AND(AZ$3&gt;=$D8,AZ$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BA8" s="1">
+        <f>IF(AND(BA$3&gt;=$D8,BA$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BB8" s="1">
+        <f>IF(AND(BB$3&gt;=$D8,BB$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BC8" s="1">
+        <f>IF(AND(BC$3&gt;=$D8,BC$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BD8" s="1">
+        <f>IF(AND(BD$3&gt;=$D8,BD$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BE8" s="1">
+        <f>IF(AND(BE$3&gt;=$D8,BE$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BF8" s="1">
+        <f>IF(AND(BF$3&gt;=$D8,BF$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BG8" s="1">
+        <f>IF(AND(BG$3&gt;=$D8,BG$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BH8" s="1">
+        <f>IF(AND(BH$3&gt;=$D8,BH$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BI8" s="1">
+        <f>IF(AND(BI$3&gt;=$D8,BI$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BJ8" s="1">
+        <f>IF(AND(BJ$3&gt;=$D8,BJ$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BK8" s="1">
+        <f>IF(AND(BK$3&gt;=$D8,BK$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BL8" s="1">
+        <f>IF(AND(BL$3&gt;=$D8,BL$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BM8" s="1">
+        <f>IF(AND(BM$3&gt;=$D8,BM$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BN8" s="1">
+        <f>IF(AND(BN$3&gt;=$D8,BN$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BO8" s="1">
+        <f>IF(AND(BO$3&gt;=$D8,BO$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BP8" s="1">
+        <f>IF(AND(BP$3&gt;=$D8,BP$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BQ8" s="1">
+        <f>IF(AND(BQ$3&gt;=$D8,BQ$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BR8" s="1">
+        <f>IF(AND(BR$3&gt;=$D8,BR$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BS8" s="1">
+        <f>IF(AND(BS$3&gt;=$D8,BS$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BT8" s="1">
+        <f>IF(AND(BT$3&gt;=$D8,BT$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BU8" s="1">
+        <f>IF(AND(BU$3&gt;=$D8,BU$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BV8" s="1">
+        <f>IF(AND(BV$3&gt;=$D8,BV$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BW8" s="1">
+        <f>IF(AND(BW$3&gt;=$D8,BW$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BX8" s="1">
+        <f>IF(AND(BX$3&gt;=$D8,BX$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BY8" s="1">
+        <f>IF(AND(BY$3&gt;=$D8,BY$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="BZ8" s="1">
+        <f>IF(AND(BZ$3&gt;=$D8,BZ$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="CA8" s="1">
+        <f>IF(AND(CA$3&gt;=$D8,CA$3&lt;=$E8),"█","")</f>
+      </c>
+      <c r="CB8" s="1">
+        <f>IF(AND(CB$3&gt;=$D8,CB$3&lt;=$E8),"█","")</f>
+      </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="17">
@@ -1075,40 +2344,232 @@
         <f>D7</f>
         <v>46230</v>
       </c>
-      <c r="E9" s="7">
-        <f t="shared" si="0"/>
-        <v>46233</v>
-      </c>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="1"/>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="1"/>
-      <c r="AC9" s="1"/>
-      <c r="AD9" s="1"/>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="1"/>
-      <c r="AI9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1">
+        <f>IF(AND(F$3&gt;=$D9,F$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="G9" s="1">
+        <f>IF(AND(G$3&gt;=$D9,G$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="H9" s="1">
+        <f>IF(AND(H$3&gt;=$D9,H$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="I9" s="1">
+        <f>IF(AND(I$3&gt;=$D9,I$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="J9" s="1">
+        <f>IF(AND(J$3&gt;=$D9,J$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="K9" s="1">
+        <f>IF(AND(K$3&gt;=$D9,K$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="L9" s="1">
+        <f>IF(AND(L$3&gt;=$D9,L$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="M9" s="1">
+        <f>IF(AND(M$3&gt;=$D9,M$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="N9" s="1">
+        <f>IF(AND(N$3&gt;=$D9,N$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="O9" s="1">
+        <f>IF(AND(O$3&gt;=$D9,O$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="P9" s="1">
+        <f>IF(AND(P$3&gt;=$D9,P$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="Q9" s="1">
+        <f>IF(AND(Q$3&gt;=$D9,Q$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="R9" s="1">
+        <f>IF(AND(R$3&gt;=$D9,R$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="S9" s="1">
+        <f>IF(AND(S$3&gt;=$D9,S$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="T9" s="1">
+        <f>IF(AND(T$3&gt;=$D9,T$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="U9" s="1">
+        <f>IF(AND(U$3&gt;=$D9,U$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="V9" s="1">
+        <f>IF(AND(V$3&gt;=$D9,V$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="W9" s="1">
+        <f>IF(AND(W$3&gt;=$D9,W$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="X9" s="1">
+        <f>IF(AND(X$3&gt;=$D9,X$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="Y9" s="1">
+        <f>IF(AND(Y$3&gt;=$D9,Y$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="Z9" s="1">
+        <f>IF(AND(Z$3&gt;=$D9,Z$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AA9" s="1">
+        <f>IF(AND(AA$3&gt;=$D9,AA$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AB9" s="1">
+        <f>IF(AND(AB$3&gt;=$D9,AB$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AC9" s="1">
+        <f>IF(AND(AC$3&gt;=$D9,AC$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AD9" s="1">
+        <f>IF(AND(AD$3&gt;=$D9,AD$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AE9" s="1">
+        <f>IF(AND(AE$3&gt;=$D9,AE$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AF9" s="1">
+        <f>IF(AND(AF$3&gt;=$D9,AF$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AG9" s="1">
+        <f>IF(AND(AG$3&gt;=$D9,AG$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AH9" s="1">
+        <f>IF(AND(AH$3&gt;=$D9,AH$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AI9" s="1">
+        <f>IF(AND(AI$3&gt;=$D9,AI$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AJ9" s="1">
+        <f>IF(AND(AJ$3&gt;=$D9,AJ$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AK9" s="1">
+        <f>IF(AND(AK$3&gt;=$D9,AK$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AL9" s="1">
+        <f>IF(AND(AL$3&gt;=$D9,AL$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AM9" s="1">
+        <f>IF(AND(AM$3&gt;=$D9,AM$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AN9" s="1">
+        <f>IF(AND(AN$3&gt;=$D9,AN$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AO9" s="1">
+        <f>IF(AND(AO$3&gt;=$D9,AO$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AP9" s="1">
+        <f>IF(AND(AP$3&gt;=$D9,AP$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AQ9" s="1">
+        <f>IF(AND(AQ$3&gt;=$D9,AQ$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AR9" s="1">
+        <f>IF(AND(AR$3&gt;=$D9,AR$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AS9" s="1">
+        <f>IF(AND(AS$3&gt;=$D9,AS$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AT9" s="1">
+        <f>IF(AND(AT$3&gt;=$D9,AT$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AU9" s="1">
+        <f>IF(AND(AU$3&gt;=$D9,AU$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AV9" s="1">
+        <f>IF(AND(AV$3&gt;=$D9,AV$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AW9" s="1">
+        <f>IF(AND(AW$3&gt;=$D9,AW$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AX9" s="1">
+        <f>IF(AND(AX$3&gt;=$D9,AX$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AY9" s="1">
+        <f>IF(AND(AY$3&gt;=$D9,AY$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="AZ9" s="1">
+        <f>IF(AND(AZ$3&gt;=$D9,AZ$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BA9" s="1">
+        <f>IF(AND(BA$3&gt;=$D9,BA$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BB9" s="1">
+        <f>IF(AND(BB$3&gt;=$D9,BB$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BC9" s="1">
+        <f>IF(AND(BC$3&gt;=$D9,BC$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BD9" s="1">
+        <f>IF(AND(BD$3&gt;=$D9,BD$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BE9" s="1">
+        <f>IF(AND(BE$3&gt;=$D9,BE$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BF9" s="1">
+        <f>IF(AND(BF$3&gt;=$D9,BF$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BG9" s="1">
+        <f>IF(AND(BG$3&gt;=$D9,BG$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BH9" s="1">
+        <f>IF(AND(BH$3&gt;=$D9,BH$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BI9" s="1">
+        <f>IF(AND(BI$3&gt;=$D9,BI$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BJ9" s="1">
+        <f>IF(AND(BJ$3&gt;=$D9,BJ$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BK9" s="1">
+        <f>IF(AND(BK$3&gt;=$D9,BK$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BL9" s="1">
+        <f>IF(AND(BL$3&gt;=$D9,BL$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BM9" s="1">
+        <f>IF(AND(BM$3&gt;=$D9,BM$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BN9" s="1">
+        <f>IF(AND(BN$3&gt;=$D9,BN$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BO9" s="1">
+        <f>IF(AND(BO$3&gt;=$D9,BO$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BP9" s="1">
+        <f>IF(AND(BP$3&gt;=$D9,BP$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BQ9" s="1">
+        <f>IF(AND(BQ$3&gt;=$D9,BQ$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BR9" s="1">
+        <f>IF(AND(BR$3&gt;=$D9,BR$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BS9" s="1">
+        <f>IF(AND(BS$3&gt;=$D9,BS$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BT9" s="1">
+        <f>IF(AND(BT$3&gt;=$D9,BT$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BU9" s="1">
+        <f>IF(AND(BU$3&gt;=$D9,BU$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BV9" s="1">
+        <f>IF(AND(BV$3&gt;=$D9,BV$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BW9" s="1">
+        <f>IF(AND(BW$3&gt;=$D9,BW$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BX9" s="1">
+        <f>IF(AND(BX$3&gt;=$D9,BX$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BY9" s="1">
+        <f>IF(AND(BY$3&gt;=$D9,BY$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="BZ9" s="1">
+        <f>IF(AND(BZ$3&gt;=$D9,BZ$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="CA9" s="1">
+        <f>IF(AND(CA$3&gt;=$D9,CA$3&lt;=$E9),"█","")</f>
+      </c>
+      <c r="CB9" s="1">
+        <f>IF(AND(CB$3&gt;=$D9,CB$3&lt;=$E9),"█","")</f>
+      </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="11">
@@ -1129,36 +2590,231 @@
         <f>MAX(E11:E13)</f>
         <v>46219</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
-      <c r="V10" s="1"/>
-      <c r="W10" s="1"/>
-      <c r="X10" s="1"/>
-      <c r="Y10" s="1"/>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
-      <c r="AB10" s="1"/>
-      <c r="AC10" s="1"/>
-      <c r="AD10" s="1"/>
-      <c r="AE10" s="1"/>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1"/>
-      <c r="AH10" s="1"/>
-      <c r="AI10" s="1"/>
+      <c r="F10" s="1">
+        <f>IF(AND(F$3&gt;=$D10,F$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="G10" s="1">
+        <f>IF(AND(G$3&gt;=$D10,G$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="H10" s="1">
+        <f>IF(AND(H$3&gt;=$D10,H$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="I10" s="1">
+        <f>IF(AND(I$3&gt;=$D10,I$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="J10" s="1">
+        <f>IF(AND(J$3&gt;=$D10,J$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="K10" s="1">
+        <f>IF(AND(K$3&gt;=$D10,K$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="L10" s="1">
+        <f>IF(AND(L$3&gt;=$D10,L$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="M10" s="1">
+        <f>IF(AND(M$3&gt;=$D10,M$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="N10" s="1">
+        <f>IF(AND(N$3&gt;=$D10,N$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="O10" s="1">
+        <f>IF(AND(O$3&gt;=$D10,O$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="P10" s="1">
+        <f>IF(AND(P$3&gt;=$D10,P$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="Q10" s="1">
+        <f>IF(AND(Q$3&gt;=$D10,Q$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="R10" s="1">
+        <f>IF(AND(R$3&gt;=$D10,R$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="S10" s="1">
+        <f>IF(AND(S$3&gt;=$D10,S$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="T10" s="1">
+        <f>IF(AND(T$3&gt;=$D10,T$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="U10" s="1">
+        <f>IF(AND(U$3&gt;=$D10,U$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="V10" s="1">
+        <f>IF(AND(V$3&gt;=$D10,V$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="W10" s="1">
+        <f>IF(AND(W$3&gt;=$D10,W$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="X10" s="1">
+        <f>IF(AND(X$3&gt;=$D10,X$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="Y10" s="1">
+        <f>IF(AND(Y$3&gt;=$D10,Y$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="Z10" s="1">
+        <f>IF(AND(Z$3&gt;=$D10,Z$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AA10" s="1">
+        <f>IF(AND(AA$3&gt;=$D10,AA$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AB10" s="1">
+        <f>IF(AND(AB$3&gt;=$D10,AB$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AC10" s="1">
+        <f>IF(AND(AC$3&gt;=$D10,AC$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AD10" s="1">
+        <f>IF(AND(AD$3&gt;=$D10,AD$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AE10" s="1">
+        <f>IF(AND(AE$3&gt;=$D10,AE$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AF10" s="1">
+        <f>IF(AND(AF$3&gt;=$D10,AF$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AG10" s="1">
+        <f>IF(AND(AG$3&gt;=$D10,AG$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AH10" s="1">
+        <f>IF(AND(AH$3&gt;=$D10,AH$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AI10" s="1">
+        <f>IF(AND(AI$3&gt;=$D10,AI$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AJ10" s="1">
+        <f>IF(AND(AJ$3&gt;=$D10,AJ$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AK10" s="1">
+        <f>IF(AND(AK$3&gt;=$D10,AK$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AL10" s="1">
+        <f>IF(AND(AL$3&gt;=$D10,AL$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AM10" s="1">
+        <f>IF(AND(AM$3&gt;=$D10,AM$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AN10" s="1">
+        <f>IF(AND(AN$3&gt;=$D10,AN$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AO10" s="1">
+        <f>IF(AND(AO$3&gt;=$D10,AO$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AP10" s="1">
+        <f>IF(AND(AP$3&gt;=$D10,AP$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AQ10" s="1">
+        <f>IF(AND(AQ$3&gt;=$D10,AQ$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AR10" s="1">
+        <f>IF(AND(AR$3&gt;=$D10,AR$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AS10" s="1">
+        <f>IF(AND(AS$3&gt;=$D10,AS$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AT10" s="1">
+        <f>IF(AND(AT$3&gt;=$D10,AT$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AU10" s="1">
+        <f>IF(AND(AU$3&gt;=$D10,AU$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AV10" s="1">
+        <f>IF(AND(AV$3&gt;=$D10,AV$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AW10" s="1">
+        <f>IF(AND(AW$3&gt;=$D10,AW$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AX10" s="1">
+        <f>IF(AND(AX$3&gt;=$D10,AX$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AY10" s="1">
+        <f>IF(AND(AY$3&gt;=$D10,AY$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="AZ10" s="1">
+        <f>IF(AND(AZ$3&gt;=$D10,AZ$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BA10" s="1">
+        <f>IF(AND(BA$3&gt;=$D10,BA$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BB10" s="1">
+        <f>IF(AND(BB$3&gt;=$D10,BB$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BC10" s="1">
+        <f>IF(AND(BC$3&gt;=$D10,BC$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BD10" s="1">
+        <f>IF(AND(BD$3&gt;=$D10,BD$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BE10" s="1">
+        <f>IF(AND(BE$3&gt;=$D10,BE$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BF10" s="1">
+        <f>IF(AND(BF$3&gt;=$D10,BF$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BG10" s="1">
+        <f>IF(AND(BG$3&gt;=$D10,BG$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BH10" s="1">
+        <f>IF(AND(BH$3&gt;=$D10,BH$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BI10" s="1">
+        <f>IF(AND(BI$3&gt;=$D10,BI$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BJ10" s="1">
+        <f>IF(AND(BJ$3&gt;=$D10,BJ$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BK10" s="1">
+        <f>IF(AND(BK$3&gt;=$D10,BK$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BL10" s="1">
+        <f>IF(AND(BL$3&gt;=$D10,BL$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BM10" s="1">
+        <f>IF(AND(BM$3&gt;=$D10,BM$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BN10" s="1">
+        <f>IF(AND(BN$3&gt;=$D10,BN$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BO10" s="1">
+        <f>IF(AND(BO$3&gt;=$D10,BO$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BP10" s="1">
+        <f>IF(AND(BP$3&gt;=$D10,BP$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BQ10" s="1">
+        <f>IF(AND(BQ$3&gt;=$D10,BQ$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BR10" s="1">
+        <f>IF(AND(BR$3&gt;=$D10,BR$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BS10" s="1">
+        <f>IF(AND(BS$3&gt;=$D10,BS$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BT10" s="1">
+        <f>IF(AND(BT$3&gt;=$D10,BT$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BU10" s="1">
+        <f>IF(AND(BU$3&gt;=$D10,BU$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BV10" s="1">
+        <f>IF(AND(BV$3&gt;=$D10,BV$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BW10" s="1">
+        <f>IF(AND(BW$3&gt;=$D10,BW$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BX10" s="1">
+        <f>IF(AND(BX$3&gt;=$D10,BX$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BY10" s="1">
+        <f>IF(AND(BY$3&gt;=$D10,BY$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="BZ10" s="1">
+        <f>IF(AND(BZ$3&gt;=$D10,BZ$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="CA10" s="1">
+        <f>IF(AND(CA$3&gt;=$D10,CA$3&lt;=$E10),"█","")</f>
+      </c>
+      <c r="CB10" s="1">
+        <f>IF(AND(CB$3&gt;=$D10,CB$3&lt;=$E10),"█","")</f>
+      </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="17">
@@ -1177,36 +2833,231 @@
         <f>D11+C11</f>
         <v>46216</v>
       </c>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="1"/>
-      <c r="Y11" s="1"/>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
-      <c r="AB11" s="1"/>
-      <c r="AC11" s="1"/>
-      <c r="AD11" s="1"/>
-      <c r="AE11" s="1"/>
-      <c r="AF11" s="1"/>
-      <c r="AG11" s="1"/>
-      <c r="AH11" s="1"/>
-      <c r="AI11" s="1"/>
+      <c r="F11" s="1">
+        <f>IF(AND(F$3&gt;=$D11,F$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="G11" s="1">
+        <f>IF(AND(G$3&gt;=$D11,G$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="H11" s="1">
+        <f>IF(AND(H$3&gt;=$D11,H$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="I11" s="1">
+        <f>IF(AND(I$3&gt;=$D11,I$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="J11" s="1">
+        <f>IF(AND(J$3&gt;=$D11,J$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="K11" s="1">
+        <f>IF(AND(K$3&gt;=$D11,K$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="L11" s="1">
+        <f>IF(AND(L$3&gt;=$D11,L$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="M11" s="1">
+        <f>IF(AND(M$3&gt;=$D11,M$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="N11" s="1">
+        <f>IF(AND(N$3&gt;=$D11,N$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="O11" s="1">
+        <f>IF(AND(O$3&gt;=$D11,O$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="P11" s="1">
+        <f>IF(AND(P$3&gt;=$D11,P$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="Q11" s="1">
+        <f>IF(AND(Q$3&gt;=$D11,Q$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="R11" s="1">
+        <f>IF(AND(R$3&gt;=$D11,R$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="S11" s="1">
+        <f>IF(AND(S$3&gt;=$D11,S$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="T11" s="1">
+        <f>IF(AND(T$3&gt;=$D11,T$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="U11" s="1">
+        <f>IF(AND(U$3&gt;=$D11,U$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="V11" s="1">
+        <f>IF(AND(V$3&gt;=$D11,V$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="W11" s="1">
+        <f>IF(AND(W$3&gt;=$D11,W$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="X11" s="1">
+        <f>IF(AND(X$3&gt;=$D11,X$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="Y11" s="1">
+        <f>IF(AND(Y$3&gt;=$D11,Y$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="Z11" s="1">
+        <f>IF(AND(Z$3&gt;=$D11,Z$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AA11" s="1">
+        <f>IF(AND(AA$3&gt;=$D11,AA$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AB11" s="1">
+        <f>IF(AND(AB$3&gt;=$D11,AB$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AC11" s="1">
+        <f>IF(AND(AC$3&gt;=$D11,AC$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AD11" s="1">
+        <f>IF(AND(AD$3&gt;=$D11,AD$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AE11" s="1">
+        <f>IF(AND(AE$3&gt;=$D11,AE$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AF11" s="1">
+        <f>IF(AND(AF$3&gt;=$D11,AF$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AG11" s="1">
+        <f>IF(AND(AG$3&gt;=$D11,AG$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AH11" s="1">
+        <f>IF(AND(AH$3&gt;=$D11,AH$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AI11" s="1">
+        <f>IF(AND(AI$3&gt;=$D11,AI$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AJ11" s="1">
+        <f>IF(AND(AJ$3&gt;=$D11,AJ$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AK11" s="1">
+        <f>IF(AND(AK$3&gt;=$D11,AK$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AL11" s="1">
+        <f>IF(AND(AL$3&gt;=$D11,AL$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AM11" s="1">
+        <f>IF(AND(AM$3&gt;=$D11,AM$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AN11" s="1">
+        <f>IF(AND(AN$3&gt;=$D11,AN$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AO11" s="1">
+        <f>IF(AND(AO$3&gt;=$D11,AO$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AP11" s="1">
+        <f>IF(AND(AP$3&gt;=$D11,AP$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AQ11" s="1">
+        <f>IF(AND(AQ$3&gt;=$D11,AQ$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AR11" s="1">
+        <f>IF(AND(AR$3&gt;=$D11,AR$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AS11" s="1">
+        <f>IF(AND(AS$3&gt;=$D11,AS$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AT11" s="1">
+        <f>IF(AND(AT$3&gt;=$D11,AT$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AU11" s="1">
+        <f>IF(AND(AU$3&gt;=$D11,AU$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AV11" s="1">
+        <f>IF(AND(AV$3&gt;=$D11,AV$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AW11" s="1">
+        <f>IF(AND(AW$3&gt;=$D11,AW$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AX11" s="1">
+        <f>IF(AND(AX$3&gt;=$D11,AX$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AY11" s="1">
+        <f>IF(AND(AY$3&gt;=$D11,AY$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="AZ11" s="1">
+        <f>IF(AND(AZ$3&gt;=$D11,AZ$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BA11" s="1">
+        <f>IF(AND(BA$3&gt;=$D11,BA$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BB11" s="1">
+        <f>IF(AND(BB$3&gt;=$D11,BB$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BC11" s="1">
+        <f>IF(AND(BC$3&gt;=$D11,BC$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BD11" s="1">
+        <f>IF(AND(BD$3&gt;=$D11,BD$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BE11" s="1">
+        <f>IF(AND(BE$3&gt;=$D11,BE$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BF11" s="1">
+        <f>IF(AND(BF$3&gt;=$D11,BF$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BG11" s="1">
+        <f>IF(AND(BG$3&gt;=$D11,BG$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BH11" s="1">
+        <f>IF(AND(BH$3&gt;=$D11,BH$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BI11" s="1">
+        <f>IF(AND(BI$3&gt;=$D11,BI$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BJ11" s="1">
+        <f>IF(AND(BJ$3&gt;=$D11,BJ$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BK11" s="1">
+        <f>IF(AND(BK$3&gt;=$D11,BK$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BL11" s="1">
+        <f>IF(AND(BL$3&gt;=$D11,BL$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BM11" s="1">
+        <f>IF(AND(BM$3&gt;=$D11,BM$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BN11" s="1">
+        <f>IF(AND(BN$3&gt;=$D11,BN$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BO11" s="1">
+        <f>IF(AND(BO$3&gt;=$D11,BO$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BP11" s="1">
+        <f>IF(AND(BP$3&gt;=$D11,BP$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BQ11" s="1">
+        <f>IF(AND(BQ$3&gt;=$D11,BQ$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BR11" s="1">
+        <f>IF(AND(BR$3&gt;=$D11,BR$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BS11" s="1">
+        <f>IF(AND(BS$3&gt;=$D11,BS$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BT11" s="1">
+        <f>IF(AND(BT$3&gt;=$D11,BT$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BU11" s="1">
+        <f>IF(AND(BU$3&gt;=$D11,BU$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BV11" s="1">
+        <f>IF(AND(BV$3&gt;=$D11,BV$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BW11" s="1">
+        <f>IF(AND(BW$3&gt;=$D11,BW$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BX11" s="1">
+        <f>IF(AND(BX$3&gt;=$D11,BX$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BY11" s="1">
+        <f>IF(AND(BY$3&gt;=$D11,BY$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="BZ11" s="1">
+        <f>IF(AND(BZ$3&gt;=$D11,BZ$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="CA11" s="1">
+        <f>IF(AND(CA$3&gt;=$D11,CA$3&lt;=$E11),"█","")</f>
+      </c>
+      <c r="CB11" s="1">
+        <f>IF(AND(CB$3&gt;=$D11,CB$3&lt;=$E11),"█","")</f>
+      </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="17">
@@ -1225,36 +3076,231 @@
         <f>D12+C12</f>
         <v>46218</v>
       </c>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="1"/>
-      <c r="X12" s="1"/>
-      <c r="Y12" s="1"/>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
-      <c r="AB12" s="1"/>
-      <c r="AC12" s="1"/>
-      <c r="AD12" s="1"/>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1"/>
-      <c r="AH12" s="1"/>
-      <c r="AI12" s="1"/>
+      <c r="F12" s="1">
+        <f>IF(AND(F$3&gt;=$D12,F$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="G12" s="1">
+        <f>IF(AND(G$3&gt;=$D12,G$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="H12" s="1">
+        <f>IF(AND(H$3&gt;=$D12,H$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="I12" s="1">
+        <f>IF(AND(I$3&gt;=$D12,I$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="J12" s="1">
+        <f>IF(AND(J$3&gt;=$D12,J$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="K12" s="1">
+        <f>IF(AND(K$3&gt;=$D12,K$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="L12" s="1">
+        <f>IF(AND(L$3&gt;=$D12,L$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="M12" s="1">
+        <f>IF(AND(M$3&gt;=$D12,M$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="N12" s="1">
+        <f>IF(AND(N$3&gt;=$D12,N$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="O12" s="1">
+        <f>IF(AND(O$3&gt;=$D12,O$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="P12" s="1">
+        <f>IF(AND(P$3&gt;=$D12,P$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="Q12" s="1">
+        <f>IF(AND(Q$3&gt;=$D12,Q$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="R12" s="1">
+        <f>IF(AND(R$3&gt;=$D12,R$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="S12" s="1">
+        <f>IF(AND(S$3&gt;=$D12,S$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="T12" s="1">
+        <f>IF(AND(T$3&gt;=$D12,T$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="U12" s="1">
+        <f>IF(AND(U$3&gt;=$D12,U$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="V12" s="1">
+        <f>IF(AND(V$3&gt;=$D12,V$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="W12" s="1">
+        <f>IF(AND(W$3&gt;=$D12,W$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="X12" s="1">
+        <f>IF(AND(X$3&gt;=$D12,X$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="Y12" s="1">
+        <f>IF(AND(Y$3&gt;=$D12,Y$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="Z12" s="1">
+        <f>IF(AND(Z$3&gt;=$D12,Z$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AA12" s="1">
+        <f>IF(AND(AA$3&gt;=$D12,AA$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AB12" s="1">
+        <f>IF(AND(AB$3&gt;=$D12,AB$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AC12" s="1">
+        <f>IF(AND(AC$3&gt;=$D12,AC$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AD12" s="1">
+        <f>IF(AND(AD$3&gt;=$D12,AD$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AE12" s="1">
+        <f>IF(AND(AE$3&gt;=$D12,AE$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AF12" s="1">
+        <f>IF(AND(AF$3&gt;=$D12,AF$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AG12" s="1">
+        <f>IF(AND(AG$3&gt;=$D12,AG$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AH12" s="1">
+        <f>IF(AND(AH$3&gt;=$D12,AH$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AI12" s="1">
+        <f>IF(AND(AI$3&gt;=$D12,AI$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AJ12" s="1">
+        <f>IF(AND(AJ$3&gt;=$D12,AJ$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AK12" s="1">
+        <f>IF(AND(AK$3&gt;=$D12,AK$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AL12" s="1">
+        <f>IF(AND(AL$3&gt;=$D12,AL$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AM12" s="1">
+        <f>IF(AND(AM$3&gt;=$D12,AM$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AN12" s="1">
+        <f>IF(AND(AN$3&gt;=$D12,AN$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AO12" s="1">
+        <f>IF(AND(AO$3&gt;=$D12,AO$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AP12" s="1">
+        <f>IF(AND(AP$3&gt;=$D12,AP$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AQ12" s="1">
+        <f>IF(AND(AQ$3&gt;=$D12,AQ$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AR12" s="1">
+        <f>IF(AND(AR$3&gt;=$D12,AR$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AS12" s="1">
+        <f>IF(AND(AS$3&gt;=$D12,AS$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AT12" s="1">
+        <f>IF(AND(AT$3&gt;=$D12,AT$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AU12" s="1">
+        <f>IF(AND(AU$3&gt;=$D12,AU$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AV12" s="1">
+        <f>IF(AND(AV$3&gt;=$D12,AV$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AW12" s="1">
+        <f>IF(AND(AW$3&gt;=$D12,AW$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AX12" s="1">
+        <f>IF(AND(AX$3&gt;=$D12,AX$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AY12" s="1">
+        <f>IF(AND(AY$3&gt;=$D12,AY$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="AZ12" s="1">
+        <f>IF(AND(AZ$3&gt;=$D12,AZ$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BA12" s="1">
+        <f>IF(AND(BA$3&gt;=$D12,BA$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BB12" s="1">
+        <f>IF(AND(BB$3&gt;=$D12,BB$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BC12" s="1">
+        <f>IF(AND(BC$3&gt;=$D12,BC$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BD12" s="1">
+        <f>IF(AND(BD$3&gt;=$D12,BD$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BE12" s="1">
+        <f>IF(AND(BE$3&gt;=$D12,BE$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BF12" s="1">
+        <f>IF(AND(BF$3&gt;=$D12,BF$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BG12" s="1">
+        <f>IF(AND(BG$3&gt;=$D12,BG$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BH12" s="1">
+        <f>IF(AND(BH$3&gt;=$D12,BH$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BI12" s="1">
+        <f>IF(AND(BI$3&gt;=$D12,BI$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BJ12" s="1">
+        <f>IF(AND(BJ$3&gt;=$D12,BJ$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BK12" s="1">
+        <f>IF(AND(BK$3&gt;=$D12,BK$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BL12" s="1">
+        <f>IF(AND(BL$3&gt;=$D12,BL$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BM12" s="1">
+        <f>IF(AND(BM$3&gt;=$D12,BM$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BN12" s="1">
+        <f>IF(AND(BN$3&gt;=$D12,BN$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BO12" s="1">
+        <f>IF(AND(BO$3&gt;=$D12,BO$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BP12" s="1">
+        <f>IF(AND(BP$3&gt;=$D12,BP$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BQ12" s="1">
+        <f>IF(AND(BQ$3&gt;=$D12,BQ$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BR12" s="1">
+        <f>IF(AND(BR$3&gt;=$D12,BR$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BS12" s="1">
+        <f>IF(AND(BS$3&gt;=$D12,BS$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BT12" s="1">
+        <f>IF(AND(BT$3&gt;=$D12,BT$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BU12" s="1">
+        <f>IF(AND(BU$3&gt;=$D12,BU$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BV12" s="1">
+        <f>IF(AND(BV$3&gt;=$D12,BV$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BW12" s="1">
+        <f>IF(AND(BW$3&gt;=$D12,BW$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BX12" s="1">
+        <f>IF(AND(BX$3&gt;=$D12,BX$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BY12" s="1">
+        <f>IF(AND(BY$3&gt;=$D12,BY$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="BZ12" s="1">
+        <f>IF(AND(BZ$3&gt;=$D12,BZ$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="CA12" s="1">
+        <f>IF(AND(CA$3&gt;=$D12,CA$3&lt;=$E12),"█","")</f>
+      </c>
+      <c r="CB12" s="1">
+        <f>IF(AND(CB$3&gt;=$D12,CB$3&lt;=$E12),"█","")</f>
+      </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="18">
@@ -1273,36 +3319,231 @@
         <f>D13+C13</f>
         <v>46219</v>
       </c>
-      <c r="F13" s="6"/>
-      <c r="G13" s="6"/>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="6"/>
-      <c r="Q13" s="6"/>
-      <c r="R13" s="6"/>
-      <c r="S13" s="6"/>
-      <c r="T13" s="6"/>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6"/>
-      <c r="W13" s="6"/>
-      <c r="X13" s="6"/>
-      <c r="Y13" s="6"/>
-      <c r="Z13" s="6"/>
-      <c r="AA13" s="6"/>
-      <c r="AB13" s="6"/>
-      <c r="AC13" s="6"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
+      <c r="F13" s="1">
+        <f>IF(AND(F$3&gt;=$D13,F$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="G13" s="1">
+        <f>IF(AND(G$3&gt;=$D13,G$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="H13" s="1">
+        <f>IF(AND(H$3&gt;=$D13,H$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="I13" s="1">
+        <f>IF(AND(I$3&gt;=$D13,I$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="J13" s="1">
+        <f>IF(AND(J$3&gt;=$D13,J$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="K13" s="1">
+        <f>IF(AND(K$3&gt;=$D13,K$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="L13" s="1">
+        <f>IF(AND(L$3&gt;=$D13,L$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="M13" s="1">
+        <f>IF(AND(M$3&gt;=$D13,M$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="N13" s="1">
+        <f>IF(AND(N$3&gt;=$D13,N$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="O13" s="1">
+        <f>IF(AND(O$3&gt;=$D13,O$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="P13" s="1">
+        <f>IF(AND(P$3&gt;=$D13,P$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="Q13" s="1">
+        <f>IF(AND(Q$3&gt;=$D13,Q$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="R13" s="1">
+        <f>IF(AND(R$3&gt;=$D13,R$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="S13" s="1">
+        <f>IF(AND(S$3&gt;=$D13,S$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="T13" s="1">
+        <f>IF(AND(T$3&gt;=$D13,T$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="U13" s="1">
+        <f>IF(AND(U$3&gt;=$D13,U$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="V13" s="1">
+        <f>IF(AND(V$3&gt;=$D13,V$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="W13" s="1">
+        <f>IF(AND(W$3&gt;=$D13,W$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="X13" s="1">
+        <f>IF(AND(X$3&gt;=$D13,X$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="Y13" s="1">
+        <f>IF(AND(Y$3&gt;=$D13,Y$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="Z13" s="1">
+        <f>IF(AND(Z$3&gt;=$D13,Z$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AA13" s="1">
+        <f>IF(AND(AA$3&gt;=$D13,AA$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AB13" s="1">
+        <f>IF(AND(AB$3&gt;=$D13,AB$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AC13" s="1">
+        <f>IF(AND(AC$3&gt;=$D13,AC$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AD13" s="1">
+        <f>IF(AND(AD$3&gt;=$D13,AD$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AE13" s="1">
+        <f>IF(AND(AE$3&gt;=$D13,AE$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AF13" s="1">
+        <f>IF(AND(AF$3&gt;=$D13,AF$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AG13" s="1">
+        <f>IF(AND(AG$3&gt;=$D13,AG$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AH13" s="1">
+        <f>IF(AND(AH$3&gt;=$D13,AH$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AI13" s="1">
+        <f>IF(AND(AI$3&gt;=$D13,AI$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AJ13" s="1">
+        <f>IF(AND(AJ$3&gt;=$D13,AJ$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AK13" s="1">
+        <f>IF(AND(AK$3&gt;=$D13,AK$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AL13" s="1">
+        <f>IF(AND(AL$3&gt;=$D13,AL$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AM13" s="1">
+        <f>IF(AND(AM$3&gt;=$D13,AM$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AN13" s="1">
+        <f>IF(AND(AN$3&gt;=$D13,AN$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AO13" s="1">
+        <f>IF(AND(AO$3&gt;=$D13,AO$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AP13" s="1">
+        <f>IF(AND(AP$3&gt;=$D13,AP$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AQ13" s="1">
+        <f>IF(AND(AQ$3&gt;=$D13,AQ$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AR13" s="1">
+        <f>IF(AND(AR$3&gt;=$D13,AR$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AS13" s="1">
+        <f>IF(AND(AS$3&gt;=$D13,AS$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AT13" s="1">
+        <f>IF(AND(AT$3&gt;=$D13,AT$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AU13" s="1">
+        <f>IF(AND(AU$3&gt;=$D13,AU$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AV13" s="1">
+        <f>IF(AND(AV$3&gt;=$D13,AV$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AW13" s="1">
+        <f>IF(AND(AW$3&gt;=$D13,AW$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AX13" s="1">
+        <f>IF(AND(AX$3&gt;=$D13,AX$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AY13" s="1">
+        <f>IF(AND(AY$3&gt;=$D13,AY$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="AZ13" s="1">
+        <f>IF(AND(AZ$3&gt;=$D13,AZ$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BA13" s="1">
+        <f>IF(AND(BA$3&gt;=$D13,BA$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BB13" s="1">
+        <f>IF(AND(BB$3&gt;=$D13,BB$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BC13" s="1">
+        <f>IF(AND(BC$3&gt;=$D13,BC$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BD13" s="1">
+        <f>IF(AND(BD$3&gt;=$D13,BD$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BE13" s="1">
+        <f>IF(AND(BE$3&gt;=$D13,BE$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BF13" s="1">
+        <f>IF(AND(BF$3&gt;=$D13,BF$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BG13" s="1">
+        <f>IF(AND(BG$3&gt;=$D13,BG$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BH13" s="1">
+        <f>IF(AND(BH$3&gt;=$D13,BH$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BI13" s="1">
+        <f>IF(AND(BI$3&gt;=$D13,BI$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BJ13" s="1">
+        <f>IF(AND(BJ$3&gt;=$D13,BJ$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BK13" s="1">
+        <f>IF(AND(BK$3&gt;=$D13,BK$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BL13" s="1">
+        <f>IF(AND(BL$3&gt;=$D13,BL$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BM13" s="1">
+        <f>IF(AND(BM$3&gt;=$D13,BM$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BN13" s="1">
+        <f>IF(AND(BN$3&gt;=$D13,BN$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BO13" s="1">
+        <f>IF(AND(BO$3&gt;=$D13,BO$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BP13" s="1">
+        <f>IF(AND(BP$3&gt;=$D13,BP$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BQ13" s="1">
+        <f>IF(AND(BQ$3&gt;=$D13,BQ$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BR13" s="1">
+        <f>IF(AND(BR$3&gt;=$D13,BR$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BS13" s="1">
+        <f>IF(AND(BS$3&gt;=$D13,BS$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BT13" s="1">
+        <f>IF(AND(BT$3&gt;=$D13,BT$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BU13" s="1">
+        <f>IF(AND(BU$3&gt;=$D13,BU$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BV13" s="1">
+        <f>IF(AND(BV$3&gt;=$D13,BV$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BW13" s="1">
+        <f>IF(AND(BW$3&gt;=$D13,BW$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BX13" s="1">
+        <f>IF(AND(BX$3&gt;=$D13,BX$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BY13" s="1">
+        <f>IF(AND(BY$3&gt;=$D13,BY$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="BZ13" s="1">
+        <f>IF(AND(BZ$3&gt;=$D13,BZ$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="CA13" s="1">
+        <f>IF(AND(CA$3&gt;=$D13,CA$3&lt;=$E13),"█","")</f>
+      </c>
+      <c r="CB13" s="1">
+        <f>IF(AND(CB$3&gt;=$D13,CB$3&lt;=$E13),"█","")</f>
+      </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -1321,36 +3562,231 @@
         <f>D14+C14</f>
         <v>46223</v>
       </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="X14" s="1"/>
-      <c r="Y14" s="1"/>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
-      <c r="AB14" s="1"/>
-      <c r="AC14" s="1"/>
-      <c r="AD14" s="1"/>
-      <c r="AE14" s="1"/>
-      <c r="AF14" s="1"/>
-      <c r="AG14" s="1"/>
-      <c r="AH14" s="1"/>
-      <c r="AI14" s="1"/>
+      <c r="F14" s="1">
+        <f>IF(AND(F$3&gt;=$D14,F$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="G14" s="1">
+        <f>IF(AND(G$3&gt;=$D14,G$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="H14" s="1">
+        <f>IF(AND(H$3&gt;=$D14,H$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="I14" s="1">
+        <f>IF(AND(I$3&gt;=$D14,I$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="J14" s="1">
+        <f>IF(AND(J$3&gt;=$D14,J$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="K14" s="1">
+        <f>IF(AND(K$3&gt;=$D14,K$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="L14" s="1">
+        <f>IF(AND(L$3&gt;=$D14,L$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="M14" s="1">
+        <f>IF(AND(M$3&gt;=$D14,M$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="N14" s="1">
+        <f>IF(AND(N$3&gt;=$D14,N$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="O14" s="1">
+        <f>IF(AND(O$3&gt;=$D14,O$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="P14" s="1">
+        <f>IF(AND(P$3&gt;=$D14,P$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="Q14" s="1">
+        <f>IF(AND(Q$3&gt;=$D14,Q$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="R14" s="1">
+        <f>IF(AND(R$3&gt;=$D14,R$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="S14" s="1">
+        <f>IF(AND(S$3&gt;=$D14,S$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="T14" s="1">
+        <f>IF(AND(T$3&gt;=$D14,T$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="U14" s="1">
+        <f>IF(AND(U$3&gt;=$D14,U$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="V14" s="1">
+        <f>IF(AND(V$3&gt;=$D14,V$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="W14" s="1">
+        <f>IF(AND(W$3&gt;=$D14,W$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="X14" s="1">
+        <f>IF(AND(X$3&gt;=$D14,X$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="Y14" s="1">
+        <f>IF(AND(Y$3&gt;=$D14,Y$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="Z14" s="1">
+        <f>IF(AND(Z$3&gt;=$D14,Z$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AA14" s="1">
+        <f>IF(AND(AA$3&gt;=$D14,AA$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AB14" s="1">
+        <f>IF(AND(AB$3&gt;=$D14,AB$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AC14" s="1">
+        <f>IF(AND(AC$3&gt;=$D14,AC$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AD14" s="1">
+        <f>IF(AND(AD$3&gt;=$D14,AD$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AE14" s="1">
+        <f>IF(AND(AE$3&gt;=$D14,AE$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AF14" s="1">
+        <f>IF(AND(AF$3&gt;=$D14,AF$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AG14" s="1">
+        <f>IF(AND(AG$3&gt;=$D14,AG$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AH14" s="1">
+        <f>IF(AND(AH$3&gt;=$D14,AH$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AI14" s="1">
+        <f>IF(AND(AI$3&gt;=$D14,AI$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AJ14" s="1">
+        <f>IF(AND(AJ$3&gt;=$D14,AJ$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AK14" s="1">
+        <f>IF(AND(AK$3&gt;=$D14,AK$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AL14" s="1">
+        <f>IF(AND(AL$3&gt;=$D14,AL$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AM14" s="1">
+        <f>IF(AND(AM$3&gt;=$D14,AM$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AN14" s="1">
+        <f>IF(AND(AN$3&gt;=$D14,AN$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AO14" s="1">
+        <f>IF(AND(AO$3&gt;=$D14,AO$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AP14" s="1">
+        <f>IF(AND(AP$3&gt;=$D14,AP$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AQ14" s="1">
+        <f>IF(AND(AQ$3&gt;=$D14,AQ$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AR14" s="1">
+        <f>IF(AND(AR$3&gt;=$D14,AR$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AS14" s="1">
+        <f>IF(AND(AS$3&gt;=$D14,AS$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AT14" s="1">
+        <f>IF(AND(AT$3&gt;=$D14,AT$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AU14" s="1">
+        <f>IF(AND(AU$3&gt;=$D14,AU$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AV14" s="1">
+        <f>IF(AND(AV$3&gt;=$D14,AV$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AW14" s="1">
+        <f>IF(AND(AW$3&gt;=$D14,AW$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AX14" s="1">
+        <f>IF(AND(AX$3&gt;=$D14,AX$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AY14" s="1">
+        <f>IF(AND(AY$3&gt;=$D14,AY$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="AZ14" s="1">
+        <f>IF(AND(AZ$3&gt;=$D14,AZ$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BA14" s="1">
+        <f>IF(AND(BA$3&gt;=$D14,BA$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BB14" s="1">
+        <f>IF(AND(BB$3&gt;=$D14,BB$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BC14" s="1">
+        <f>IF(AND(BC$3&gt;=$D14,BC$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BD14" s="1">
+        <f>IF(AND(BD$3&gt;=$D14,BD$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BE14" s="1">
+        <f>IF(AND(BE$3&gt;=$D14,BE$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BF14" s="1">
+        <f>IF(AND(BF$3&gt;=$D14,BF$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BG14" s="1">
+        <f>IF(AND(BG$3&gt;=$D14,BG$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BH14" s="1">
+        <f>IF(AND(BH$3&gt;=$D14,BH$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BI14" s="1">
+        <f>IF(AND(BI$3&gt;=$D14,BI$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BJ14" s="1">
+        <f>IF(AND(BJ$3&gt;=$D14,BJ$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BK14" s="1">
+        <f>IF(AND(BK$3&gt;=$D14,BK$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BL14" s="1">
+        <f>IF(AND(BL$3&gt;=$D14,BL$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BM14" s="1">
+        <f>IF(AND(BM$3&gt;=$D14,BM$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BN14" s="1">
+        <f>IF(AND(BN$3&gt;=$D14,BN$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BO14" s="1">
+        <f>IF(AND(BO$3&gt;=$D14,BO$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BP14" s="1">
+        <f>IF(AND(BP$3&gt;=$D14,BP$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BQ14" s="1">
+        <f>IF(AND(BQ$3&gt;=$D14,BQ$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BR14" s="1">
+        <f>IF(AND(BR$3&gt;=$D14,BR$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BS14" s="1">
+        <f>IF(AND(BS$3&gt;=$D14,BS$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BT14" s="1">
+        <f>IF(AND(BT$3&gt;=$D14,BT$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BU14" s="1">
+        <f>IF(AND(BU$3&gt;=$D14,BU$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BV14" s="1">
+        <f>IF(AND(BV$3&gt;=$D14,BV$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BW14" s="1">
+        <f>IF(AND(BW$3&gt;=$D14,BW$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BX14" s="1">
+        <f>IF(AND(BX$3&gt;=$D14,BX$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BY14" s="1">
+        <f>IF(AND(BY$3&gt;=$D14,BY$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="BZ14" s="1">
+        <f>IF(AND(BZ$3&gt;=$D14,BZ$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="CA14" s="1">
+        <f>IF(AND(CA$3&gt;=$D14,CA$3&lt;=$E14),"█","")</f>
+      </c>
+      <c r="CB14" s="1">
+        <f>IF(AND(CB$3&gt;=$D14,CB$3&lt;=$E14),"█","")</f>
+      </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
@@ -1371,36 +3807,231 @@
         <f>MAX(E16:E23)</f>
         <v>46250</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
-      <c r="V15" s="1"/>
-      <c r="W15" s="1"/>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1"/>
-      <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
-      <c r="AB15" s="1"/>
-      <c r="AC15" s="1"/>
-      <c r="AD15" s="1"/>
-      <c r="AE15" s="1"/>
-      <c r="AF15" s="1"/>
-      <c r="AG15" s="1"/>
-      <c r="AH15" s="1"/>
-      <c r="AI15" s="1"/>
+      <c r="F15" s="1">
+        <f>IF(AND(F$3&gt;=$D15,F$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="G15" s="1">
+        <f>IF(AND(G$3&gt;=$D15,G$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="H15" s="1">
+        <f>IF(AND(H$3&gt;=$D15,H$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="I15" s="1">
+        <f>IF(AND(I$3&gt;=$D15,I$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="J15" s="1">
+        <f>IF(AND(J$3&gt;=$D15,J$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="K15" s="1">
+        <f>IF(AND(K$3&gt;=$D15,K$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="L15" s="1">
+        <f>IF(AND(L$3&gt;=$D15,L$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="M15" s="1">
+        <f>IF(AND(M$3&gt;=$D15,M$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="N15" s="1">
+        <f>IF(AND(N$3&gt;=$D15,N$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="O15" s="1">
+        <f>IF(AND(O$3&gt;=$D15,O$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="P15" s="1">
+        <f>IF(AND(P$3&gt;=$D15,P$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="Q15" s="1">
+        <f>IF(AND(Q$3&gt;=$D15,Q$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="R15" s="1">
+        <f>IF(AND(R$3&gt;=$D15,R$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="S15" s="1">
+        <f>IF(AND(S$3&gt;=$D15,S$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="T15" s="1">
+        <f>IF(AND(T$3&gt;=$D15,T$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="U15" s="1">
+        <f>IF(AND(U$3&gt;=$D15,U$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="V15" s="1">
+        <f>IF(AND(V$3&gt;=$D15,V$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="W15" s="1">
+        <f>IF(AND(W$3&gt;=$D15,W$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="X15" s="1">
+        <f>IF(AND(X$3&gt;=$D15,X$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="Y15" s="1">
+        <f>IF(AND(Y$3&gt;=$D15,Y$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="Z15" s="1">
+        <f>IF(AND(Z$3&gt;=$D15,Z$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AA15" s="1">
+        <f>IF(AND(AA$3&gt;=$D15,AA$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AB15" s="1">
+        <f>IF(AND(AB$3&gt;=$D15,AB$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AC15" s="1">
+        <f>IF(AND(AC$3&gt;=$D15,AC$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AD15" s="1">
+        <f>IF(AND(AD$3&gt;=$D15,AD$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AE15" s="1">
+        <f>IF(AND(AE$3&gt;=$D15,AE$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AF15" s="1">
+        <f>IF(AND(AF$3&gt;=$D15,AF$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AG15" s="1">
+        <f>IF(AND(AG$3&gt;=$D15,AG$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AH15" s="1">
+        <f>IF(AND(AH$3&gt;=$D15,AH$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AI15" s="1">
+        <f>IF(AND(AI$3&gt;=$D15,AI$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AJ15" s="1">
+        <f>IF(AND(AJ$3&gt;=$D15,AJ$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AK15" s="1">
+        <f>IF(AND(AK$3&gt;=$D15,AK$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AL15" s="1">
+        <f>IF(AND(AL$3&gt;=$D15,AL$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AM15" s="1">
+        <f>IF(AND(AM$3&gt;=$D15,AM$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AN15" s="1">
+        <f>IF(AND(AN$3&gt;=$D15,AN$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AO15" s="1">
+        <f>IF(AND(AO$3&gt;=$D15,AO$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AP15" s="1">
+        <f>IF(AND(AP$3&gt;=$D15,AP$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AQ15" s="1">
+        <f>IF(AND(AQ$3&gt;=$D15,AQ$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AR15" s="1">
+        <f>IF(AND(AR$3&gt;=$D15,AR$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AS15" s="1">
+        <f>IF(AND(AS$3&gt;=$D15,AS$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AT15" s="1">
+        <f>IF(AND(AT$3&gt;=$D15,AT$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AU15" s="1">
+        <f>IF(AND(AU$3&gt;=$D15,AU$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AV15" s="1">
+        <f>IF(AND(AV$3&gt;=$D15,AV$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AW15" s="1">
+        <f>IF(AND(AW$3&gt;=$D15,AW$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AX15" s="1">
+        <f>IF(AND(AX$3&gt;=$D15,AX$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AY15" s="1">
+        <f>IF(AND(AY$3&gt;=$D15,AY$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="AZ15" s="1">
+        <f>IF(AND(AZ$3&gt;=$D15,AZ$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BA15" s="1">
+        <f>IF(AND(BA$3&gt;=$D15,BA$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BB15" s="1">
+        <f>IF(AND(BB$3&gt;=$D15,BB$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BC15" s="1">
+        <f>IF(AND(BC$3&gt;=$D15,BC$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BD15" s="1">
+        <f>IF(AND(BD$3&gt;=$D15,BD$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BE15" s="1">
+        <f>IF(AND(BE$3&gt;=$D15,BE$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BF15" s="1">
+        <f>IF(AND(BF$3&gt;=$D15,BF$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BG15" s="1">
+        <f>IF(AND(BG$3&gt;=$D15,BG$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BH15" s="1">
+        <f>IF(AND(BH$3&gt;=$D15,BH$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BI15" s="1">
+        <f>IF(AND(BI$3&gt;=$D15,BI$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BJ15" s="1">
+        <f>IF(AND(BJ$3&gt;=$D15,BJ$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BK15" s="1">
+        <f>IF(AND(BK$3&gt;=$D15,BK$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BL15" s="1">
+        <f>IF(AND(BL$3&gt;=$D15,BL$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BM15" s="1">
+        <f>IF(AND(BM$3&gt;=$D15,BM$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BN15" s="1">
+        <f>IF(AND(BN$3&gt;=$D15,BN$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BO15" s="1">
+        <f>IF(AND(BO$3&gt;=$D15,BO$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BP15" s="1">
+        <f>IF(AND(BP$3&gt;=$D15,BP$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BQ15" s="1">
+        <f>IF(AND(BQ$3&gt;=$D15,BQ$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BR15" s="1">
+        <f>IF(AND(BR$3&gt;=$D15,BR$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BS15" s="1">
+        <f>IF(AND(BS$3&gt;=$D15,BS$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BT15" s="1">
+        <f>IF(AND(BT$3&gt;=$D15,BT$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BU15" s="1">
+        <f>IF(AND(BU$3&gt;=$D15,BU$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BV15" s="1">
+        <f>IF(AND(BV$3&gt;=$D15,BV$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BW15" s="1">
+        <f>IF(AND(BW$3&gt;=$D15,BW$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BX15" s="1">
+        <f>IF(AND(BX$3&gt;=$D15,BX$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BY15" s="1">
+        <f>IF(AND(BY$3&gt;=$D15,BY$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="BZ15" s="1">
+        <f>IF(AND(BZ$3&gt;=$D15,BZ$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="CA15" s="1">
+        <f>IF(AND(CA$3&gt;=$D15,CA$3&lt;=$E15),"█","")</f>
+      </c>
+      <c r="CB15" s="1">
+        <f>IF(AND(CB$3&gt;=$D15,CB$3&lt;=$E15),"█","")</f>
+      </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A16" s="17">
@@ -1419,36 +4050,231 @@
         <f>D16+C16</f>
         <v>46226</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
-      <c r="V16" s="1"/>
-      <c r="W16" s="1"/>
-      <c r="X16" s="1"/>
-      <c r="Y16" s="1"/>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
-      <c r="AB16" s="1"/>
-      <c r="AC16" s="1"/>
-      <c r="AD16" s="1"/>
-      <c r="AE16" s="1"/>
-      <c r="AF16" s="1"/>
-      <c r="AG16" s="1"/>
-      <c r="AH16" s="1"/>
-      <c r="AI16" s="1"/>
+      <c r="F16" s="1">
+        <f>IF(AND(F$3&gt;=$D16,F$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="G16" s="1">
+        <f>IF(AND(G$3&gt;=$D16,G$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="H16" s="1">
+        <f>IF(AND(H$3&gt;=$D16,H$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="I16" s="1">
+        <f>IF(AND(I$3&gt;=$D16,I$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="J16" s="1">
+        <f>IF(AND(J$3&gt;=$D16,J$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="K16" s="1">
+        <f>IF(AND(K$3&gt;=$D16,K$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="L16" s="1">
+        <f>IF(AND(L$3&gt;=$D16,L$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="M16" s="1">
+        <f>IF(AND(M$3&gt;=$D16,M$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="N16" s="1">
+        <f>IF(AND(N$3&gt;=$D16,N$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="O16" s="1">
+        <f>IF(AND(O$3&gt;=$D16,O$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="P16" s="1">
+        <f>IF(AND(P$3&gt;=$D16,P$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="Q16" s="1">
+        <f>IF(AND(Q$3&gt;=$D16,Q$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="R16" s="1">
+        <f>IF(AND(R$3&gt;=$D16,R$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="S16" s="1">
+        <f>IF(AND(S$3&gt;=$D16,S$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="T16" s="1">
+        <f>IF(AND(T$3&gt;=$D16,T$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="U16" s="1">
+        <f>IF(AND(U$3&gt;=$D16,U$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="V16" s="1">
+        <f>IF(AND(V$3&gt;=$D16,V$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="W16" s="1">
+        <f>IF(AND(W$3&gt;=$D16,W$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="X16" s="1">
+        <f>IF(AND(X$3&gt;=$D16,X$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="Y16" s="1">
+        <f>IF(AND(Y$3&gt;=$D16,Y$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="Z16" s="1">
+        <f>IF(AND(Z$3&gt;=$D16,Z$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AA16" s="1">
+        <f>IF(AND(AA$3&gt;=$D16,AA$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AB16" s="1">
+        <f>IF(AND(AB$3&gt;=$D16,AB$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AC16" s="1">
+        <f>IF(AND(AC$3&gt;=$D16,AC$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AD16" s="1">
+        <f>IF(AND(AD$3&gt;=$D16,AD$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AE16" s="1">
+        <f>IF(AND(AE$3&gt;=$D16,AE$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AF16" s="1">
+        <f>IF(AND(AF$3&gt;=$D16,AF$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AG16" s="1">
+        <f>IF(AND(AG$3&gt;=$D16,AG$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AH16" s="1">
+        <f>IF(AND(AH$3&gt;=$D16,AH$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AI16" s="1">
+        <f>IF(AND(AI$3&gt;=$D16,AI$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AJ16" s="1">
+        <f>IF(AND(AJ$3&gt;=$D16,AJ$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AK16" s="1">
+        <f>IF(AND(AK$3&gt;=$D16,AK$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AL16" s="1">
+        <f>IF(AND(AL$3&gt;=$D16,AL$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AM16" s="1">
+        <f>IF(AND(AM$3&gt;=$D16,AM$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AN16" s="1">
+        <f>IF(AND(AN$3&gt;=$D16,AN$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AO16" s="1">
+        <f>IF(AND(AO$3&gt;=$D16,AO$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AP16" s="1">
+        <f>IF(AND(AP$3&gt;=$D16,AP$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AQ16" s="1">
+        <f>IF(AND(AQ$3&gt;=$D16,AQ$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AR16" s="1">
+        <f>IF(AND(AR$3&gt;=$D16,AR$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AS16" s="1">
+        <f>IF(AND(AS$3&gt;=$D16,AS$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AT16" s="1">
+        <f>IF(AND(AT$3&gt;=$D16,AT$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AU16" s="1">
+        <f>IF(AND(AU$3&gt;=$D16,AU$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AV16" s="1">
+        <f>IF(AND(AV$3&gt;=$D16,AV$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AW16" s="1">
+        <f>IF(AND(AW$3&gt;=$D16,AW$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AX16" s="1">
+        <f>IF(AND(AX$3&gt;=$D16,AX$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AY16" s="1">
+        <f>IF(AND(AY$3&gt;=$D16,AY$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="AZ16" s="1">
+        <f>IF(AND(AZ$3&gt;=$D16,AZ$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BA16" s="1">
+        <f>IF(AND(BA$3&gt;=$D16,BA$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BB16" s="1">
+        <f>IF(AND(BB$3&gt;=$D16,BB$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BC16" s="1">
+        <f>IF(AND(BC$3&gt;=$D16,BC$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BD16" s="1">
+        <f>IF(AND(BD$3&gt;=$D16,BD$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BE16" s="1">
+        <f>IF(AND(BE$3&gt;=$D16,BE$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BF16" s="1">
+        <f>IF(AND(BF$3&gt;=$D16,BF$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BG16" s="1">
+        <f>IF(AND(BG$3&gt;=$D16,BG$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BH16" s="1">
+        <f>IF(AND(BH$3&gt;=$D16,BH$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BI16" s="1">
+        <f>IF(AND(BI$3&gt;=$D16,BI$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BJ16" s="1">
+        <f>IF(AND(BJ$3&gt;=$D16,BJ$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BK16" s="1">
+        <f>IF(AND(BK$3&gt;=$D16,BK$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BL16" s="1">
+        <f>IF(AND(BL$3&gt;=$D16,BL$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BM16" s="1">
+        <f>IF(AND(BM$3&gt;=$D16,BM$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BN16" s="1">
+        <f>IF(AND(BN$3&gt;=$D16,BN$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BO16" s="1">
+        <f>IF(AND(BO$3&gt;=$D16,BO$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BP16" s="1">
+        <f>IF(AND(BP$3&gt;=$D16,BP$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BQ16" s="1">
+        <f>IF(AND(BQ$3&gt;=$D16,BQ$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BR16" s="1">
+        <f>IF(AND(BR$3&gt;=$D16,BR$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BS16" s="1">
+        <f>IF(AND(BS$3&gt;=$D16,BS$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BT16" s="1">
+        <f>IF(AND(BT$3&gt;=$D16,BT$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BU16" s="1">
+        <f>IF(AND(BU$3&gt;=$D16,BU$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BV16" s="1">
+        <f>IF(AND(BV$3&gt;=$D16,BV$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BW16" s="1">
+        <f>IF(AND(BW$3&gt;=$D16,BW$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BX16" s="1">
+        <f>IF(AND(BX$3&gt;=$D16,BX$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BY16" s="1">
+        <f>IF(AND(BY$3&gt;=$D16,BY$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="BZ16" s="1">
+        <f>IF(AND(BZ$3&gt;=$D16,BZ$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="CA16" s="1">
+        <f>IF(AND(CA$3&gt;=$D16,CA$3&lt;=$E16),"█","")</f>
+      </c>
+      <c r="CB16" s="1">
+        <f>IF(AND(CB$3&gt;=$D16,CB$3&lt;=$E16),"█","")</f>
+      </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A17" s="17">
@@ -1467,36 +4293,231 @@
         <f>D17+C17</f>
         <v>46228</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-      <c r="AD17" s="1"/>
-      <c r="AE17" s="1"/>
-      <c r="AF17" s="1"/>
-      <c r="AG17" s="1"/>
-      <c r="AH17" s="1"/>
-      <c r="AI17" s="1"/>
+      <c r="F17" s="1">
+        <f>IF(AND(F$3&gt;=$D17,F$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="G17" s="1">
+        <f>IF(AND(G$3&gt;=$D17,G$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="H17" s="1">
+        <f>IF(AND(H$3&gt;=$D17,H$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="I17" s="1">
+        <f>IF(AND(I$3&gt;=$D17,I$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="J17" s="1">
+        <f>IF(AND(J$3&gt;=$D17,J$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="K17" s="1">
+        <f>IF(AND(K$3&gt;=$D17,K$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="L17" s="1">
+        <f>IF(AND(L$3&gt;=$D17,L$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="M17" s="1">
+        <f>IF(AND(M$3&gt;=$D17,M$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="N17" s="1">
+        <f>IF(AND(N$3&gt;=$D17,N$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="O17" s="1">
+        <f>IF(AND(O$3&gt;=$D17,O$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="P17" s="1">
+        <f>IF(AND(P$3&gt;=$D17,P$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="Q17" s="1">
+        <f>IF(AND(Q$3&gt;=$D17,Q$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="R17" s="1">
+        <f>IF(AND(R$3&gt;=$D17,R$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="S17" s="1">
+        <f>IF(AND(S$3&gt;=$D17,S$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="T17" s="1">
+        <f>IF(AND(T$3&gt;=$D17,T$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="U17" s="1">
+        <f>IF(AND(U$3&gt;=$D17,U$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="V17" s="1">
+        <f>IF(AND(V$3&gt;=$D17,V$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="W17" s="1">
+        <f>IF(AND(W$3&gt;=$D17,W$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="X17" s="1">
+        <f>IF(AND(X$3&gt;=$D17,X$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="Y17" s="1">
+        <f>IF(AND(Y$3&gt;=$D17,Y$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="Z17" s="1">
+        <f>IF(AND(Z$3&gt;=$D17,Z$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AA17" s="1">
+        <f>IF(AND(AA$3&gt;=$D17,AA$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AB17" s="1">
+        <f>IF(AND(AB$3&gt;=$D17,AB$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AC17" s="1">
+        <f>IF(AND(AC$3&gt;=$D17,AC$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AD17" s="1">
+        <f>IF(AND(AD$3&gt;=$D17,AD$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AE17" s="1">
+        <f>IF(AND(AE$3&gt;=$D17,AE$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AF17" s="1">
+        <f>IF(AND(AF$3&gt;=$D17,AF$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AG17" s="1">
+        <f>IF(AND(AG$3&gt;=$D17,AG$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AH17" s="1">
+        <f>IF(AND(AH$3&gt;=$D17,AH$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AI17" s="1">
+        <f>IF(AND(AI$3&gt;=$D17,AI$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AJ17" s="1">
+        <f>IF(AND(AJ$3&gt;=$D17,AJ$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AK17" s="1">
+        <f>IF(AND(AK$3&gt;=$D17,AK$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AL17" s="1">
+        <f>IF(AND(AL$3&gt;=$D17,AL$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AM17" s="1">
+        <f>IF(AND(AM$3&gt;=$D17,AM$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AN17" s="1">
+        <f>IF(AND(AN$3&gt;=$D17,AN$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AO17" s="1">
+        <f>IF(AND(AO$3&gt;=$D17,AO$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AP17" s="1">
+        <f>IF(AND(AP$3&gt;=$D17,AP$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AQ17" s="1">
+        <f>IF(AND(AQ$3&gt;=$D17,AQ$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AR17" s="1">
+        <f>IF(AND(AR$3&gt;=$D17,AR$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AS17" s="1">
+        <f>IF(AND(AS$3&gt;=$D17,AS$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AT17" s="1">
+        <f>IF(AND(AT$3&gt;=$D17,AT$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AU17" s="1">
+        <f>IF(AND(AU$3&gt;=$D17,AU$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AV17" s="1">
+        <f>IF(AND(AV$3&gt;=$D17,AV$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AW17" s="1">
+        <f>IF(AND(AW$3&gt;=$D17,AW$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AX17" s="1">
+        <f>IF(AND(AX$3&gt;=$D17,AX$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AY17" s="1">
+        <f>IF(AND(AY$3&gt;=$D17,AY$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="AZ17" s="1">
+        <f>IF(AND(AZ$3&gt;=$D17,AZ$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BA17" s="1">
+        <f>IF(AND(BA$3&gt;=$D17,BA$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BB17" s="1">
+        <f>IF(AND(BB$3&gt;=$D17,BB$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BC17" s="1">
+        <f>IF(AND(BC$3&gt;=$D17,BC$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BD17" s="1">
+        <f>IF(AND(BD$3&gt;=$D17,BD$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BE17" s="1">
+        <f>IF(AND(BE$3&gt;=$D17,BE$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BF17" s="1">
+        <f>IF(AND(BF$3&gt;=$D17,BF$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BG17" s="1">
+        <f>IF(AND(BG$3&gt;=$D17,BG$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BH17" s="1">
+        <f>IF(AND(BH$3&gt;=$D17,BH$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BI17" s="1">
+        <f>IF(AND(BI$3&gt;=$D17,BI$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BJ17" s="1">
+        <f>IF(AND(BJ$3&gt;=$D17,BJ$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BK17" s="1">
+        <f>IF(AND(BK$3&gt;=$D17,BK$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BL17" s="1">
+        <f>IF(AND(BL$3&gt;=$D17,BL$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BM17" s="1">
+        <f>IF(AND(BM$3&gt;=$D17,BM$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BN17" s="1">
+        <f>IF(AND(BN$3&gt;=$D17,BN$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BO17" s="1">
+        <f>IF(AND(BO$3&gt;=$D17,BO$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BP17" s="1">
+        <f>IF(AND(BP$3&gt;=$D17,BP$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BQ17" s="1">
+        <f>IF(AND(BQ$3&gt;=$D17,BQ$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BR17" s="1">
+        <f>IF(AND(BR$3&gt;=$D17,BR$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BS17" s="1">
+        <f>IF(AND(BS$3&gt;=$D17,BS$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BT17" s="1">
+        <f>IF(AND(BT$3&gt;=$D17,BT$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BU17" s="1">
+        <f>IF(AND(BU$3&gt;=$D17,BU$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BV17" s="1">
+        <f>IF(AND(BV$3&gt;=$D17,BV$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BW17" s="1">
+        <f>IF(AND(BW$3&gt;=$D17,BW$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BX17" s="1">
+        <f>IF(AND(BX$3&gt;=$D17,BX$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BY17" s="1">
+        <f>IF(AND(BY$3&gt;=$D17,BY$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="BZ17" s="1">
+        <f>IF(AND(BZ$3&gt;=$D17,BZ$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="CA17" s="1">
+        <f>IF(AND(CA$3&gt;=$D17,CA$3&lt;=$E17),"█","")</f>
+      </c>
+      <c r="CB17" s="1">
+        <f>IF(AND(CB$3&gt;=$D17,CB$3&lt;=$E17),"█","")</f>
+      </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A18" s="17">
@@ -1515,36 +4536,231 @@
         <f>D18+C18</f>
         <v>46232</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-      <c r="AD18" s="1"/>
-      <c r="AE18" s="1"/>
-      <c r="AF18" s="1"/>
-      <c r="AG18" s="1"/>
-      <c r="AH18" s="1"/>
-      <c r="AI18" s="1"/>
+      <c r="F18" s="1">
+        <f>IF(AND(F$3&gt;=$D18,F$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="G18" s="1">
+        <f>IF(AND(G$3&gt;=$D18,G$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="H18" s="1">
+        <f>IF(AND(H$3&gt;=$D18,H$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="I18" s="1">
+        <f>IF(AND(I$3&gt;=$D18,I$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="J18" s="1">
+        <f>IF(AND(J$3&gt;=$D18,J$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="K18" s="1">
+        <f>IF(AND(K$3&gt;=$D18,K$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="L18" s="1">
+        <f>IF(AND(L$3&gt;=$D18,L$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="M18" s="1">
+        <f>IF(AND(M$3&gt;=$D18,M$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="N18" s="1">
+        <f>IF(AND(N$3&gt;=$D18,N$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="O18" s="1">
+        <f>IF(AND(O$3&gt;=$D18,O$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="P18" s="1">
+        <f>IF(AND(P$3&gt;=$D18,P$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="Q18" s="1">
+        <f>IF(AND(Q$3&gt;=$D18,Q$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="R18" s="1">
+        <f>IF(AND(R$3&gt;=$D18,R$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="S18" s="1">
+        <f>IF(AND(S$3&gt;=$D18,S$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="T18" s="1">
+        <f>IF(AND(T$3&gt;=$D18,T$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="U18" s="1">
+        <f>IF(AND(U$3&gt;=$D18,U$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="V18" s="1">
+        <f>IF(AND(V$3&gt;=$D18,V$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="W18" s="1">
+        <f>IF(AND(W$3&gt;=$D18,W$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="X18" s="1">
+        <f>IF(AND(X$3&gt;=$D18,X$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="Y18" s="1">
+        <f>IF(AND(Y$3&gt;=$D18,Y$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="Z18" s="1">
+        <f>IF(AND(Z$3&gt;=$D18,Z$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AA18" s="1">
+        <f>IF(AND(AA$3&gt;=$D18,AA$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AB18" s="1">
+        <f>IF(AND(AB$3&gt;=$D18,AB$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AC18" s="1">
+        <f>IF(AND(AC$3&gt;=$D18,AC$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AD18" s="1">
+        <f>IF(AND(AD$3&gt;=$D18,AD$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AE18" s="1">
+        <f>IF(AND(AE$3&gt;=$D18,AE$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AF18" s="1">
+        <f>IF(AND(AF$3&gt;=$D18,AF$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AG18" s="1">
+        <f>IF(AND(AG$3&gt;=$D18,AG$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AH18" s="1">
+        <f>IF(AND(AH$3&gt;=$D18,AH$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AI18" s="1">
+        <f>IF(AND(AI$3&gt;=$D18,AI$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AJ18" s="1">
+        <f>IF(AND(AJ$3&gt;=$D18,AJ$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AK18" s="1">
+        <f>IF(AND(AK$3&gt;=$D18,AK$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AL18" s="1">
+        <f>IF(AND(AL$3&gt;=$D18,AL$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AM18" s="1">
+        <f>IF(AND(AM$3&gt;=$D18,AM$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AN18" s="1">
+        <f>IF(AND(AN$3&gt;=$D18,AN$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AO18" s="1">
+        <f>IF(AND(AO$3&gt;=$D18,AO$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AP18" s="1">
+        <f>IF(AND(AP$3&gt;=$D18,AP$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AQ18" s="1">
+        <f>IF(AND(AQ$3&gt;=$D18,AQ$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AR18" s="1">
+        <f>IF(AND(AR$3&gt;=$D18,AR$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AS18" s="1">
+        <f>IF(AND(AS$3&gt;=$D18,AS$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AT18" s="1">
+        <f>IF(AND(AT$3&gt;=$D18,AT$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AU18" s="1">
+        <f>IF(AND(AU$3&gt;=$D18,AU$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AV18" s="1">
+        <f>IF(AND(AV$3&gt;=$D18,AV$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AW18" s="1">
+        <f>IF(AND(AW$3&gt;=$D18,AW$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AX18" s="1">
+        <f>IF(AND(AX$3&gt;=$D18,AX$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AY18" s="1">
+        <f>IF(AND(AY$3&gt;=$D18,AY$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="AZ18" s="1">
+        <f>IF(AND(AZ$3&gt;=$D18,AZ$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BA18" s="1">
+        <f>IF(AND(BA$3&gt;=$D18,BA$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BB18" s="1">
+        <f>IF(AND(BB$3&gt;=$D18,BB$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BC18" s="1">
+        <f>IF(AND(BC$3&gt;=$D18,BC$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BD18" s="1">
+        <f>IF(AND(BD$3&gt;=$D18,BD$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BE18" s="1">
+        <f>IF(AND(BE$3&gt;=$D18,BE$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BF18" s="1">
+        <f>IF(AND(BF$3&gt;=$D18,BF$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BG18" s="1">
+        <f>IF(AND(BG$3&gt;=$D18,BG$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BH18" s="1">
+        <f>IF(AND(BH$3&gt;=$D18,BH$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BI18" s="1">
+        <f>IF(AND(BI$3&gt;=$D18,BI$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BJ18" s="1">
+        <f>IF(AND(BJ$3&gt;=$D18,BJ$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BK18" s="1">
+        <f>IF(AND(BK$3&gt;=$D18,BK$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BL18" s="1">
+        <f>IF(AND(BL$3&gt;=$D18,BL$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BM18" s="1">
+        <f>IF(AND(BM$3&gt;=$D18,BM$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BN18" s="1">
+        <f>IF(AND(BN$3&gt;=$D18,BN$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BO18" s="1">
+        <f>IF(AND(BO$3&gt;=$D18,BO$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BP18" s="1">
+        <f>IF(AND(BP$3&gt;=$D18,BP$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BQ18" s="1">
+        <f>IF(AND(BQ$3&gt;=$D18,BQ$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BR18" s="1">
+        <f>IF(AND(BR$3&gt;=$D18,BR$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BS18" s="1">
+        <f>IF(AND(BS$3&gt;=$D18,BS$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BT18" s="1">
+        <f>IF(AND(BT$3&gt;=$D18,BT$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BU18" s="1">
+        <f>IF(AND(BU$3&gt;=$D18,BU$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BV18" s="1">
+        <f>IF(AND(BV$3&gt;=$D18,BV$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BW18" s="1">
+        <f>IF(AND(BW$3&gt;=$D18,BW$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BX18" s="1">
+        <f>IF(AND(BX$3&gt;=$D18,BX$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BY18" s="1">
+        <f>IF(AND(BY$3&gt;=$D18,BY$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="BZ18" s="1">
+        <f>IF(AND(BZ$3&gt;=$D18,BZ$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="CA18" s="1">
+        <f>IF(AND(CA$3&gt;=$D18,CA$3&lt;=$E18),"█","")</f>
+      </c>
+      <c r="CB18" s="1">
+        <f>IF(AND(CB$3&gt;=$D18,CB$3&lt;=$E18),"█","")</f>
+      </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A19" s="17">
@@ -1563,36 +4779,231 @@
         <f>D19+C19</f>
         <v>46233</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
-      <c r="W19" s="1"/>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-      <c r="AD19" s="1"/>
-      <c r="AE19" s="1"/>
-      <c r="AF19" s="1"/>
-      <c r="AG19" s="1"/>
-      <c r="AH19" s="1"/>
-      <c r="AI19" s="1"/>
+      <c r="F19" s="1">
+        <f>IF(AND(F$3&gt;=$D19,F$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="G19" s="1">
+        <f>IF(AND(G$3&gt;=$D19,G$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="H19" s="1">
+        <f>IF(AND(H$3&gt;=$D19,H$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="I19" s="1">
+        <f>IF(AND(I$3&gt;=$D19,I$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="J19" s="1">
+        <f>IF(AND(J$3&gt;=$D19,J$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="K19" s="1">
+        <f>IF(AND(K$3&gt;=$D19,K$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="L19" s="1">
+        <f>IF(AND(L$3&gt;=$D19,L$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="M19" s="1">
+        <f>IF(AND(M$3&gt;=$D19,M$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="N19" s="1">
+        <f>IF(AND(N$3&gt;=$D19,N$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="O19" s="1">
+        <f>IF(AND(O$3&gt;=$D19,O$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="P19" s="1">
+        <f>IF(AND(P$3&gt;=$D19,P$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="Q19" s="1">
+        <f>IF(AND(Q$3&gt;=$D19,Q$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="R19" s="1">
+        <f>IF(AND(R$3&gt;=$D19,R$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="S19" s="1">
+        <f>IF(AND(S$3&gt;=$D19,S$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="T19" s="1">
+        <f>IF(AND(T$3&gt;=$D19,T$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="U19" s="1">
+        <f>IF(AND(U$3&gt;=$D19,U$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="V19" s="1">
+        <f>IF(AND(V$3&gt;=$D19,V$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="W19" s="1">
+        <f>IF(AND(W$3&gt;=$D19,W$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="X19" s="1">
+        <f>IF(AND(X$3&gt;=$D19,X$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="Y19" s="1">
+        <f>IF(AND(Y$3&gt;=$D19,Y$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="Z19" s="1">
+        <f>IF(AND(Z$3&gt;=$D19,Z$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AA19" s="1">
+        <f>IF(AND(AA$3&gt;=$D19,AA$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AB19" s="1">
+        <f>IF(AND(AB$3&gt;=$D19,AB$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AC19" s="1">
+        <f>IF(AND(AC$3&gt;=$D19,AC$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AD19" s="1">
+        <f>IF(AND(AD$3&gt;=$D19,AD$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AE19" s="1">
+        <f>IF(AND(AE$3&gt;=$D19,AE$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AF19" s="1">
+        <f>IF(AND(AF$3&gt;=$D19,AF$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AG19" s="1">
+        <f>IF(AND(AG$3&gt;=$D19,AG$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AH19" s="1">
+        <f>IF(AND(AH$3&gt;=$D19,AH$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AI19" s="1">
+        <f>IF(AND(AI$3&gt;=$D19,AI$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AJ19" s="1">
+        <f>IF(AND(AJ$3&gt;=$D19,AJ$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AK19" s="1">
+        <f>IF(AND(AK$3&gt;=$D19,AK$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AL19" s="1">
+        <f>IF(AND(AL$3&gt;=$D19,AL$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AM19" s="1">
+        <f>IF(AND(AM$3&gt;=$D19,AM$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AN19" s="1">
+        <f>IF(AND(AN$3&gt;=$D19,AN$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AO19" s="1">
+        <f>IF(AND(AO$3&gt;=$D19,AO$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AP19" s="1">
+        <f>IF(AND(AP$3&gt;=$D19,AP$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AQ19" s="1">
+        <f>IF(AND(AQ$3&gt;=$D19,AQ$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AR19" s="1">
+        <f>IF(AND(AR$3&gt;=$D19,AR$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AS19" s="1">
+        <f>IF(AND(AS$3&gt;=$D19,AS$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AT19" s="1">
+        <f>IF(AND(AT$3&gt;=$D19,AT$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AU19" s="1">
+        <f>IF(AND(AU$3&gt;=$D19,AU$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AV19" s="1">
+        <f>IF(AND(AV$3&gt;=$D19,AV$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AW19" s="1">
+        <f>IF(AND(AW$3&gt;=$D19,AW$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AX19" s="1">
+        <f>IF(AND(AX$3&gt;=$D19,AX$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AY19" s="1">
+        <f>IF(AND(AY$3&gt;=$D19,AY$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="AZ19" s="1">
+        <f>IF(AND(AZ$3&gt;=$D19,AZ$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BA19" s="1">
+        <f>IF(AND(BA$3&gt;=$D19,BA$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BB19" s="1">
+        <f>IF(AND(BB$3&gt;=$D19,BB$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BC19" s="1">
+        <f>IF(AND(BC$3&gt;=$D19,BC$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BD19" s="1">
+        <f>IF(AND(BD$3&gt;=$D19,BD$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BE19" s="1">
+        <f>IF(AND(BE$3&gt;=$D19,BE$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BF19" s="1">
+        <f>IF(AND(BF$3&gt;=$D19,BF$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BG19" s="1">
+        <f>IF(AND(BG$3&gt;=$D19,BG$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BH19" s="1">
+        <f>IF(AND(BH$3&gt;=$D19,BH$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BI19" s="1">
+        <f>IF(AND(BI$3&gt;=$D19,BI$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BJ19" s="1">
+        <f>IF(AND(BJ$3&gt;=$D19,BJ$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BK19" s="1">
+        <f>IF(AND(BK$3&gt;=$D19,BK$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BL19" s="1">
+        <f>IF(AND(BL$3&gt;=$D19,BL$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BM19" s="1">
+        <f>IF(AND(BM$3&gt;=$D19,BM$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BN19" s="1">
+        <f>IF(AND(BN$3&gt;=$D19,BN$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BO19" s="1">
+        <f>IF(AND(BO$3&gt;=$D19,BO$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BP19" s="1">
+        <f>IF(AND(BP$3&gt;=$D19,BP$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BQ19" s="1">
+        <f>IF(AND(BQ$3&gt;=$D19,BQ$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BR19" s="1">
+        <f>IF(AND(BR$3&gt;=$D19,BR$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BS19" s="1">
+        <f>IF(AND(BS$3&gt;=$D19,BS$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BT19" s="1">
+        <f>IF(AND(BT$3&gt;=$D19,BT$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BU19" s="1">
+        <f>IF(AND(BU$3&gt;=$D19,BU$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BV19" s="1">
+        <f>IF(AND(BV$3&gt;=$D19,BV$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BW19" s="1">
+        <f>IF(AND(BW$3&gt;=$D19,BW$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BX19" s="1">
+        <f>IF(AND(BX$3&gt;=$D19,BX$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BY19" s="1">
+        <f>IF(AND(BY$3&gt;=$D19,BY$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="BZ19" s="1">
+        <f>IF(AND(BZ$3&gt;=$D19,BZ$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="CA19" s="1">
+        <f>IF(AND(CA$3&gt;=$D19,CA$3&lt;=$E19),"█","")</f>
+      </c>
+      <c r="CB19" s="1">
+        <f>IF(AND(CB$3&gt;=$D19,CB$3&lt;=$E19),"█","")</f>
+      </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A20" s="17">
@@ -1611,36 +5022,231 @@
         <f>D20+C20</f>
         <v>46244</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-      <c r="X20" s="1"/>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-      <c r="AD20" s="1"/>
-      <c r="AE20" s="1"/>
-      <c r="AF20" s="1"/>
-      <c r="AG20" s="1"/>
-      <c r="AH20" s="1"/>
-      <c r="AI20" s="1"/>
+      <c r="F20" s="1">
+        <f>IF(AND(F$3&gt;=$D20,F$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="G20" s="1">
+        <f>IF(AND(G$3&gt;=$D20,G$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="H20" s="1">
+        <f>IF(AND(H$3&gt;=$D20,H$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="I20" s="1">
+        <f>IF(AND(I$3&gt;=$D20,I$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="J20" s="1">
+        <f>IF(AND(J$3&gt;=$D20,J$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="K20" s="1">
+        <f>IF(AND(K$3&gt;=$D20,K$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="L20" s="1">
+        <f>IF(AND(L$3&gt;=$D20,L$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="M20" s="1">
+        <f>IF(AND(M$3&gt;=$D20,M$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="N20" s="1">
+        <f>IF(AND(N$3&gt;=$D20,N$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="O20" s="1">
+        <f>IF(AND(O$3&gt;=$D20,O$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="P20" s="1">
+        <f>IF(AND(P$3&gt;=$D20,P$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="Q20" s="1">
+        <f>IF(AND(Q$3&gt;=$D20,Q$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="R20" s="1">
+        <f>IF(AND(R$3&gt;=$D20,R$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="S20" s="1">
+        <f>IF(AND(S$3&gt;=$D20,S$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="T20" s="1">
+        <f>IF(AND(T$3&gt;=$D20,T$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="U20" s="1">
+        <f>IF(AND(U$3&gt;=$D20,U$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="V20" s="1">
+        <f>IF(AND(V$3&gt;=$D20,V$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="W20" s="1">
+        <f>IF(AND(W$3&gt;=$D20,W$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="X20" s="1">
+        <f>IF(AND(X$3&gt;=$D20,X$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="Y20" s="1">
+        <f>IF(AND(Y$3&gt;=$D20,Y$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="Z20" s="1">
+        <f>IF(AND(Z$3&gt;=$D20,Z$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AA20" s="1">
+        <f>IF(AND(AA$3&gt;=$D20,AA$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AB20" s="1">
+        <f>IF(AND(AB$3&gt;=$D20,AB$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AC20" s="1">
+        <f>IF(AND(AC$3&gt;=$D20,AC$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AD20" s="1">
+        <f>IF(AND(AD$3&gt;=$D20,AD$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AE20" s="1">
+        <f>IF(AND(AE$3&gt;=$D20,AE$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AF20" s="1">
+        <f>IF(AND(AF$3&gt;=$D20,AF$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AG20" s="1">
+        <f>IF(AND(AG$3&gt;=$D20,AG$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AH20" s="1">
+        <f>IF(AND(AH$3&gt;=$D20,AH$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AI20" s="1">
+        <f>IF(AND(AI$3&gt;=$D20,AI$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AJ20" s="1">
+        <f>IF(AND(AJ$3&gt;=$D20,AJ$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AK20" s="1">
+        <f>IF(AND(AK$3&gt;=$D20,AK$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AL20" s="1">
+        <f>IF(AND(AL$3&gt;=$D20,AL$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AM20" s="1">
+        <f>IF(AND(AM$3&gt;=$D20,AM$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AN20" s="1">
+        <f>IF(AND(AN$3&gt;=$D20,AN$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AO20" s="1">
+        <f>IF(AND(AO$3&gt;=$D20,AO$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AP20" s="1">
+        <f>IF(AND(AP$3&gt;=$D20,AP$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AQ20" s="1">
+        <f>IF(AND(AQ$3&gt;=$D20,AQ$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AR20" s="1">
+        <f>IF(AND(AR$3&gt;=$D20,AR$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AS20" s="1">
+        <f>IF(AND(AS$3&gt;=$D20,AS$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AT20" s="1">
+        <f>IF(AND(AT$3&gt;=$D20,AT$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AU20" s="1">
+        <f>IF(AND(AU$3&gt;=$D20,AU$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AV20" s="1">
+        <f>IF(AND(AV$3&gt;=$D20,AV$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AW20" s="1">
+        <f>IF(AND(AW$3&gt;=$D20,AW$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AX20" s="1">
+        <f>IF(AND(AX$3&gt;=$D20,AX$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AY20" s="1">
+        <f>IF(AND(AY$3&gt;=$D20,AY$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="AZ20" s="1">
+        <f>IF(AND(AZ$3&gt;=$D20,AZ$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BA20" s="1">
+        <f>IF(AND(BA$3&gt;=$D20,BA$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BB20" s="1">
+        <f>IF(AND(BB$3&gt;=$D20,BB$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BC20" s="1">
+        <f>IF(AND(BC$3&gt;=$D20,BC$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BD20" s="1">
+        <f>IF(AND(BD$3&gt;=$D20,BD$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BE20" s="1">
+        <f>IF(AND(BE$3&gt;=$D20,BE$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BF20" s="1">
+        <f>IF(AND(BF$3&gt;=$D20,BF$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BG20" s="1">
+        <f>IF(AND(BG$3&gt;=$D20,BG$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BH20" s="1">
+        <f>IF(AND(BH$3&gt;=$D20,BH$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BI20" s="1">
+        <f>IF(AND(BI$3&gt;=$D20,BI$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BJ20" s="1">
+        <f>IF(AND(BJ$3&gt;=$D20,BJ$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BK20" s="1">
+        <f>IF(AND(BK$3&gt;=$D20,BK$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BL20" s="1">
+        <f>IF(AND(BL$3&gt;=$D20,BL$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BM20" s="1">
+        <f>IF(AND(BM$3&gt;=$D20,BM$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BN20" s="1">
+        <f>IF(AND(BN$3&gt;=$D20,BN$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BO20" s="1">
+        <f>IF(AND(BO$3&gt;=$D20,BO$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BP20" s="1">
+        <f>IF(AND(BP$3&gt;=$D20,BP$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BQ20" s="1">
+        <f>IF(AND(BQ$3&gt;=$D20,BQ$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BR20" s="1">
+        <f>IF(AND(BR$3&gt;=$D20,BR$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BS20" s="1">
+        <f>IF(AND(BS$3&gt;=$D20,BS$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BT20" s="1">
+        <f>IF(AND(BT$3&gt;=$D20,BT$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BU20" s="1">
+        <f>IF(AND(BU$3&gt;=$D20,BU$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BV20" s="1">
+        <f>IF(AND(BV$3&gt;=$D20,BV$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BW20" s="1">
+        <f>IF(AND(BW$3&gt;=$D20,BW$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BX20" s="1">
+        <f>IF(AND(BX$3&gt;=$D20,BX$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BY20" s="1">
+        <f>IF(AND(BY$3&gt;=$D20,BY$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="BZ20" s="1">
+        <f>IF(AND(BZ$3&gt;=$D20,BZ$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="CA20" s="1">
+        <f>IF(AND(CA$3&gt;=$D20,CA$3&lt;=$E20),"█","")</f>
+      </c>
+      <c r="CB20" s="1">
+        <f>IF(AND(CB$3&gt;=$D20,CB$3&lt;=$E20),"█","")</f>
+      </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
@@ -1659,36 +5265,231 @@
         <f>D21+C21</f>
         <v>46248</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
-      <c r="V21" s="1"/>
-      <c r="W21" s="1"/>
-      <c r="X21" s="1"/>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-      <c r="AD21" s="1"/>
-      <c r="AE21" s="1"/>
-      <c r="AF21" s="1"/>
-      <c r="AG21" s="1"/>
-      <c r="AH21" s="1"/>
-      <c r="AI21" s="1"/>
+      <c r="F21" s="1">
+        <f>IF(AND(F$3&gt;=$D21,F$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="G21" s="1">
+        <f>IF(AND(G$3&gt;=$D21,G$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="H21" s="1">
+        <f>IF(AND(H$3&gt;=$D21,H$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="I21" s="1">
+        <f>IF(AND(I$3&gt;=$D21,I$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="J21" s="1">
+        <f>IF(AND(J$3&gt;=$D21,J$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="K21" s="1">
+        <f>IF(AND(K$3&gt;=$D21,K$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="L21" s="1">
+        <f>IF(AND(L$3&gt;=$D21,L$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="M21" s="1">
+        <f>IF(AND(M$3&gt;=$D21,M$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="N21" s="1">
+        <f>IF(AND(N$3&gt;=$D21,N$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="O21" s="1">
+        <f>IF(AND(O$3&gt;=$D21,O$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="P21" s="1">
+        <f>IF(AND(P$3&gt;=$D21,P$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="Q21" s="1">
+        <f>IF(AND(Q$3&gt;=$D21,Q$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="R21" s="1">
+        <f>IF(AND(R$3&gt;=$D21,R$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="S21" s="1">
+        <f>IF(AND(S$3&gt;=$D21,S$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="T21" s="1">
+        <f>IF(AND(T$3&gt;=$D21,T$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="U21" s="1">
+        <f>IF(AND(U$3&gt;=$D21,U$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="V21" s="1">
+        <f>IF(AND(V$3&gt;=$D21,V$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="W21" s="1">
+        <f>IF(AND(W$3&gt;=$D21,W$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="X21" s="1">
+        <f>IF(AND(X$3&gt;=$D21,X$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="Y21" s="1">
+        <f>IF(AND(Y$3&gt;=$D21,Y$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="Z21" s="1">
+        <f>IF(AND(Z$3&gt;=$D21,Z$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AA21" s="1">
+        <f>IF(AND(AA$3&gt;=$D21,AA$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AB21" s="1">
+        <f>IF(AND(AB$3&gt;=$D21,AB$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AC21" s="1">
+        <f>IF(AND(AC$3&gt;=$D21,AC$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AD21" s="1">
+        <f>IF(AND(AD$3&gt;=$D21,AD$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AE21" s="1">
+        <f>IF(AND(AE$3&gt;=$D21,AE$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AF21" s="1">
+        <f>IF(AND(AF$3&gt;=$D21,AF$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AG21" s="1">
+        <f>IF(AND(AG$3&gt;=$D21,AG$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AH21" s="1">
+        <f>IF(AND(AH$3&gt;=$D21,AH$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AI21" s="1">
+        <f>IF(AND(AI$3&gt;=$D21,AI$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AJ21" s="1">
+        <f>IF(AND(AJ$3&gt;=$D21,AJ$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AK21" s="1">
+        <f>IF(AND(AK$3&gt;=$D21,AK$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AL21" s="1">
+        <f>IF(AND(AL$3&gt;=$D21,AL$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AM21" s="1">
+        <f>IF(AND(AM$3&gt;=$D21,AM$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AN21" s="1">
+        <f>IF(AND(AN$3&gt;=$D21,AN$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AO21" s="1">
+        <f>IF(AND(AO$3&gt;=$D21,AO$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AP21" s="1">
+        <f>IF(AND(AP$3&gt;=$D21,AP$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AQ21" s="1">
+        <f>IF(AND(AQ$3&gt;=$D21,AQ$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AR21" s="1">
+        <f>IF(AND(AR$3&gt;=$D21,AR$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AS21" s="1">
+        <f>IF(AND(AS$3&gt;=$D21,AS$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AT21" s="1">
+        <f>IF(AND(AT$3&gt;=$D21,AT$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AU21" s="1">
+        <f>IF(AND(AU$3&gt;=$D21,AU$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AV21" s="1">
+        <f>IF(AND(AV$3&gt;=$D21,AV$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AW21" s="1">
+        <f>IF(AND(AW$3&gt;=$D21,AW$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AX21" s="1">
+        <f>IF(AND(AX$3&gt;=$D21,AX$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AY21" s="1">
+        <f>IF(AND(AY$3&gt;=$D21,AY$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="AZ21" s="1">
+        <f>IF(AND(AZ$3&gt;=$D21,AZ$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BA21" s="1">
+        <f>IF(AND(BA$3&gt;=$D21,BA$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BB21" s="1">
+        <f>IF(AND(BB$3&gt;=$D21,BB$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BC21" s="1">
+        <f>IF(AND(BC$3&gt;=$D21,BC$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BD21" s="1">
+        <f>IF(AND(BD$3&gt;=$D21,BD$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BE21" s="1">
+        <f>IF(AND(BE$3&gt;=$D21,BE$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BF21" s="1">
+        <f>IF(AND(BF$3&gt;=$D21,BF$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BG21" s="1">
+        <f>IF(AND(BG$3&gt;=$D21,BG$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BH21" s="1">
+        <f>IF(AND(BH$3&gt;=$D21,BH$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BI21" s="1">
+        <f>IF(AND(BI$3&gt;=$D21,BI$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BJ21" s="1">
+        <f>IF(AND(BJ$3&gt;=$D21,BJ$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BK21" s="1">
+        <f>IF(AND(BK$3&gt;=$D21,BK$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BL21" s="1">
+        <f>IF(AND(BL$3&gt;=$D21,BL$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BM21" s="1">
+        <f>IF(AND(BM$3&gt;=$D21,BM$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BN21" s="1">
+        <f>IF(AND(BN$3&gt;=$D21,BN$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BO21" s="1">
+        <f>IF(AND(BO$3&gt;=$D21,BO$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BP21" s="1">
+        <f>IF(AND(BP$3&gt;=$D21,BP$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BQ21" s="1">
+        <f>IF(AND(BQ$3&gt;=$D21,BQ$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BR21" s="1">
+        <f>IF(AND(BR$3&gt;=$D21,BR$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BS21" s="1">
+        <f>IF(AND(BS$3&gt;=$D21,BS$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BT21" s="1">
+        <f>IF(AND(BT$3&gt;=$D21,BT$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BU21" s="1">
+        <f>IF(AND(BU$3&gt;=$D21,BU$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BV21" s="1">
+        <f>IF(AND(BV$3&gt;=$D21,BV$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BW21" s="1">
+        <f>IF(AND(BW$3&gt;=$D21,BW$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BX21" s="1">
+        <f>IF(AND(BX$3&gt;=$D21,BX$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BY21" s="1">
+        <f>IF(AND(BY$3&gt;=$D21,BY$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="BZ21" s="1">
+        <f>IF(AND(BZ$3&gt;=$D21,BZ$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="CA21" s="1">
+        <f>IF(AND(CA$3&gt;=$D21,CA$3&lt;=$E21),"█","")</f>
+      </c>
+      <c r="CB21" s="1">
+        <f>IF(AND(CB$3&gt;=$D21,CB$3&lt;=$E21),"█","")</f>
+      </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A22" s="17">
@@ -1707,36 +5508,231 @@
         <f>D22+C22</f>
         <v>46248</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
-      <c r="U22" s="1"/>
-      <c r="V22" s="1"/>
-      <c r="W22" s="1"/>
-      <c r="X22" s="1"/>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
-      <c r="AD22" s="1"/>
-      <c r="AE22" s="1"/>
-      <c r="AF22" s="1"/>
-      <c r="AG22" s="1"/>
-      <c r="AH22" s="1"/>
-      <c r="AI22" s="1"/>
+      <c r="F22" s="1">
+        <f>IF(AND(F$3&gt;=$D22,F$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="G22" s="1">
+        <f>IF(AND(G$3&gt;=$D22,G$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="H22" s="1">
+        <f>IF(AND(H$3&gt;=$D22,H$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="I22" s="1">
+        <f>IF(AND(I$3&gt;=$D22,I$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="J22" s="1">
+        <f>IF(AND(J$3&gt;=$D22,J$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="K22" s="1">
+        <f>IF(AND(K$3&gt;=$D22,K$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="L22" s="1">
+        <f>IF(AND(L$3&gt;=$D22,L$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="M22" s="1">
+        <f>IF(AND(M$3&gt;=$D22,M$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="N22" s="1">
+        <f>IF(AND(N$3&gt;=$D22,N$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="O22" s="1">
+        <f>IF(AND(O$3&gt;=$D22,O$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="P22" s="1">
+        <f>IF(AND(P$3&gt;=$D22,P$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="Q22" s="1">
+        <f>IF(AND(Q$3&gt;=$D22,Q$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="R22" s="1">
+        <f>IF(AND(R$3&gt;=$D22,R$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="S22" s="1">
+        <f>IF(AND(S$3&gt;=$D22,S$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="T22" s="1">
+        <f>IF(AND(T$3&gt;=$D22,T$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="U22" s="1">
+        <f>IF(AND(U$3&gt;=$D22,U$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="V22" s="1">
+        <f>IF(AND(V$3&gt;=$D22,V$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="W22" s="1">
+        <f>IF(AND(W$3&gt;=$D22,W$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="X22" s="1">
+        <f>IF(AND(X$3&gt;=$D22,X$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="Y22" s="1">
+        <f>IF(AND(Y$3&gt;=$D22,Y$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="Z22" s="1">
+        <f>IF(AND(Z$3&gt;=$D22,Z$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AA22" s="1">
+        <f>IF(AND(AA$3&gt;=$D22,AA$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AB22" s="1">
+        <f>IF(AND(AB$3&gt;=$D22,AB$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AC22" s="1">
+        <f>IF(AND(AC$3&gt;=$D22,AC$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AD22" s="1">
+        <f>IF(AND(AD$3&gt;=$D22,AD$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AE22" s="1">
+        <f>IF(AND(AE$3&gt;=$D22,AE$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AF22" s="1">
+        <f>IF(AND(AF$3&gt;=$D22,AF$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AG22" s="1">
+        <f>IF(AND(AG$3&gt;=$D22,AG$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AH22" s="1">
+        <f>IF(AND(AH$3&gt;=$D22,AH$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AI22" s="1">
+        <f>IF(AND(AI$3&gt;=$D22,AI$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AJ22" s="1">
+        <f>IF(AND(AJ$3&gt;=$D22,AJ$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AK22" s="1">
+        <f>IF(AND(AK$3&gt;=$D22,AK$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AL22" s="1">
+        <f>IF(AND(AL$3&gt;=$D22,AL$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AM22" s="1">
+        <f>IF(AND(AM$3&gt;=$D22,AM$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AN22" s="1">
+        <f>IF(AND(AN$3&gt;=$D22,AN$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AO22" s="1">
+        <f>IF(AND(AO$3&gt;=$D22,AO$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AP22" s="1">
+        <f>IF(AND(AP$3&gt;=$D22,AP$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AQ22" s="1">
+        <f>IF(AND(AQ$3&gt;=$D22,AQ$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AR22" s="1">
+        <f>IF(AND(AR$3&gt;=$D22,AR$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AS22" s="1">
+        <f>IF(AND(AS$3&gt;=$D22,AS$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AT22" s="1">
+        <f>IF(AND(AT$3&gt;=$D22,AT$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AU22" s="1">
+        <f>IF(AND(AU$3&gt;=$D22,AU$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AV22" s="1">
+        <f>IF(AND(AV$3&gt;=$D22,AV$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AW22" s="1">
+        <f>IF(AND(AW$3&gt;=$D22,AW$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AX22" s="1">
+        <f>IF(AND(AX$3&gt;=$D22,AX$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AY22" s="1">
+        <f>IF(AND(AY$3&gt;=$D22,AY$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="AZ22" s="1">
+        <f>IF(AND(AZ$3&gt;=$D22,AZ$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BA22" s="1">
+        <f>IF(AND(BA$3&gt;=$D22,BA$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BB22" s="1">
+        <f>IF(AND(BB$3&gt;=$D22,BB$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BC22" s="1">
+        <f>IF(AND(BC$3&gt;=$D22,BC$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BD22" s="1">
+        <f>IF(AND(BD$3&gt;=$D22,BD$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BE22" s="1">
+        <f>IF(AND(BE$3&gt;=$D22,BE$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BF22" s="1">
+        <f>IF(AND(BF$3&gt;=$D22,BF$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BG22" s="1">
+        <f>IF(AND(BG$3&gt;=$D22,BG$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BH22" s="1">
+        <f>IF(AND(BH$3&gt;=$D22,BH$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BI22" s="1">
+        <f>IF(AND(BI$3&gt;=$D22,BI$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BJ22" s="1">
+        <f>IF(AND(BJ$3&gt;=$D22,BJ$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BK22" s="1">
+        <f>IF(AND(BK$3&gt;=$D22,BK$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BL22" s="1">
+        <f>IF(AND(BL$3&gt;=$D22,BL$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BM22" s="1">
+        <f>IF(AND(BM$3&gt;=$D22,BM$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BN22" s="1">
+        <f>IF(AND(BN$3&gt;=$D22,BN$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BO22" s="1">
+        <f>IF(AND(BO$3&gt;=$D22,BO$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BP22" s="1">
+        <f>IF(AND(BP$3&gt;=$D22,BP$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BQ22" s="1">
+        <f>IF(AND(BQ$3&gt;=$D22,BQ$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BR22" s="1">
+        <f>IF(AND(BR$3&gt;=$D22,BR$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BS22" s="1">
+        <f>IF(AND(BS$3&gt;=$D22,BS$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BT22" s="1">
+        <f>IF(AND(BT$3&gt;=$D22,BT$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BU22" s="1">
+        <f>IF(AND(BU$3&gt;=$D22,BU$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BV22" s="1">
+        <f>IF(AND(BV$3&gt;=$D22,BV$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BW22" s="1">
+        <f>IF(AND(BW$3&gt;=$D22,BW$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BX22" s="1">
+        <f>IF(AND(BX$3&gt;=$D22,BX$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BY22" s="1">
+        <f>IF(AND(BY$3&gt;=$D22,BY$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="BZ22" s="1">
+        <f>IF(AND(BZ$3&gt;=$D22,BZ$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="CA22" s="1">
+        <f>IF(AND(CA$3&gt;=$D22,CA$3&lt;=$E22),"█","")</f>
+      </c>
+      <c r="CB22" s="1">
+        <f>IF(AND(CB$3&gt;=$D22,CB$3&lt;=$E22),"█","")</f>
+      </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A23" s="17">
@@ -1755,36 +5751,231 @@
         <f>D23+C23</f>
         <v>46250</v>
       </c>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
-      <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="1"/>
-      <c r="AI23" s="1"/>
+      <c r="F23" s="1">
+        <f>IF(AND(F$3&gt;=$D23,F$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="G23" s="1">
+        <f>IF(AND(G$3&gt;=$D23,G$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="H23" s="1">
+        <f>IF(AND(H$3&gt;=$D23,H$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="I23" s="1">
+        <f>IF(AND(I$3&gt;=$D23,I$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="J23" s="1">
+        <f>IF(AND(J$3&gt;=$D23,J$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="K23" s="1">
+        <f>IF(AND(K$3&gt;=$D23,K$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="L23" s="1">
+        <f>IF(AND(L$3&gt;=$D23,L$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="M23" s="1">
+        <f>IF(AND(M$3&gt;=$D23,M$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="N23" s="1">
+        <f>IF(AND(N$3&gt;=$D23,N$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="O23" s="1">
+        <f>IF(AND(O$3&gt;=$D23,O$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="P23" s="1">
+        <f>IF(AND(P$3&gt;=$D23,P$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="Q23" s="1">
+        <f>IF(AND(Q$3&gt;=$D23,Q$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="R23" s="1">
+        <f>IF(AND(R$3&gt;=$D23,R$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="S23" s="1">
+        <f>IF(AND(S$3&gt;=$D23,S$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="T23" s="1">
+        <f>IF(AND(T$3&gt;=$D23,T$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="U23" s="1">
+        <f>IF(AND(U$3&gt;=$D23,U$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="V23" s="1">
+        <f>IF(AND(V$3&gt;=$D23,V$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="W23" s="1">
+        <f>IF(AND(W$3&gt;=$D23,W$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="X23" s="1">
+        <f>IF(AND(X$3&gt;=$D23,X$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="Y23" s="1">
+        <f>IF(AND(Y$3&gt;=$D23,Y$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="Z23" s="1">
+        <f>IF(AND(Z$3&gt;=$D23,Z$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AA23" s="1">
+        <f>IF(AND(AA$3&gt;=$D23,AA$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AB23" s="1">
+        <f>IF(AND(AB$3&gt;=$D23,AB$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AC23" s="1">
+        <f>IF(AND(AC$3&gt;=$D23,AC$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AD23" s="1">
+        <f>IF(AND(AD$3&gt;=$D23,AD$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AE23" s="1">
+        <f>IF(AND(AE$3&gt;=$D23,AE$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AF23" s="1">
+        <f>IF(AND(AF$3&gt;=$D23,AF$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AG23" s="1">
+        <f>IF(AND(AG$3&gt;=$D23,AG$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AH23" s="1">
+        <f>IF(AND(AH$3&gt;=$D23,AH$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AI23" s="1">
+        <f>IF(AND(AI$3&gt;=$D23,AI$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AJ23" s="1">
+        <f>IF(AND(AJ$3&gt;=$D23,AJ$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AK23" s="1">
+        <f>IF(AND(AK$3&gt;=$D23,AK$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AL23" s="1">
+        <f>IF(AND(AL$3&gt;=$D23,AL$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AM23" s="1">
+        <f>IF(AND(AM$3&gt;=$D23,AM$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AN23" s="1">
+        <f>IF(AND(AN$3&gt;=$D23,AN$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AO23" s="1">
+        <f>IF(AND(AO$3&gt;=$D23,AO$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AP23" s="1">
+        <f>IF(AND(AP$3&gt;=$D23,AP$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AQ23" s="1">
+        <f>IF(AND(AQ$3&gt;=$D23,AQ$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AR23" s="1">
+        <f>IF(AND(AR$3&gt;=$D23,AR$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AS23" s="1">
+        <f>IF(AND(AS$3&gt;=$D23,AS$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AT23" s="1">
+        <f>IF(AND(AT$3&gt;=$D23,AT$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AU23" s="1">
+        <f>IF(AND(AU$3&gt;=$D23,AU$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AV23" s="1">
+        <f>IF(AND(AV$3&gt;=$D23,AV$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AW23" s="1">
+        <f>IF(AND(AW$3&gt;=$D23,AW$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AX23" s="1">
+        <f>IF(AND(AX$3&gt;=$D23,AX$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AY23" s="1">
+        <f>IF(AND(AY$3&gt;=$D23,AY$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="AZ23" s="1">
+        <f>IF(AND(AZ$3&gt;=$D23,AZ$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BA23" s="1">
+        <f>IF(AND(BA$3&gt;=$D23,BA$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BB23" s="1">
+        <f>IF(AND(BB$3&gt;=$D23,BB$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BC23" s="1">
+        <f>IF(AND(BC$3&gt;=$D23,BC$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BD23" s="1">
+        <f>IF(AND(BD$3&gt;=$D23,BD$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BE23" s="1">
+        <f>IF(AND(BE$3&gt;=$D23,BE$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BF23" s="1">
+        <f>IF(AND(BF$3&gt;=$D23,BF$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BG23" s="1">
+        <f>IF(AND(BG$3&gt;=$D23,BG$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BH23" s="1">
+        <f>IF(AND(BH$3&gt;=$D23,BH$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BI23" s="1">
+        <f>IF(AND(BI$3&gt;=$D23,BI$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BJ23" s="1">
+        <f>IF(AND(BJ$3&gt;=$D23,BJ$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BK23" s="1">
+        <f>IF(AND(BK$3&gt;=$D23,BK$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BL23" s="1">
+        <f>IF(AND(BL$3&gt;=$D23,BL$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BM23" s="1">
+        <f>IF(AND(BM$3&gt;=$D23,BM$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BN23" s="1">
+        <f>IF(AND(BN$3&gt;=$D23,BN$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BO23" s="1">
+        <f>IF(AND(BO$3&gt;=$D23,BO$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BP23" s="1">
+        <f>IF(AND(BP$3&gt;=$D23,BP$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BQ23" s="1">
+        <f>IF(AND(BQ$3&gt;=$D23,BQ$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BR23" s="1">
+        <f>IF(AND(BR$3&gt;=$D23,BR$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BS23" s="1">
+        <f>IF(AND(BS$3&gt;=$D23,BS$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BT23" s="1">
+        <f>IF(AND(BT$3&gt;=$D23,BT$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BU23" s="1">
+        <f>IF(AND(BU$3&gt;=$D23,BU$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BV23" s="1">
+        <f>IF(AND(BV$3&gt;=$D23,BV$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BW23" s="1">
+        <f>IF(AND(BW$3&gt;=$D23,BW$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BX23" s="1">
+        <f>IF(AND(BX$3&gt;=$D23,BX$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BY23" s="1">
+        <f>IF(AND(BY$3&gt;=$D23,BY$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="BZ23" s="1">
+        <f>IF(AND(BZ$3&gt;=$D23,BZ$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="CA23" s="1">
+        <f>IF(AND(CA$3&gt;=$D23,CA$3&lt;=$E23),"█","")</f>
+      </c>
+      <c r="CB23" s="1">
+        <f>IF(AND(CB$3&gt;=$D23,CB$3&lt;=$E23),"█","")</f>
+      </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
@@ -1803,36 +5994,231 @@
         <f>D24+C24</f>
         <v>46250</v>
       </c>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
-      <c r="V24" s="1"/>
-      <c r="W24" s="1"/>
-      <c r="X24" s="1"/>
-      <c r="Y24" s="1"/>
-      <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
-      <c r="AB24" s="1"/>
-      <c r="AC24" s="1"/>
-      <c r="AD24" s="1"/>
-      <c r="AE24" s="1"/>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1"/>
-      <c r="AH24" s="1"/>
-      <c r="AI24" s="1"/>
+      <c r="F24" s="1">
+        <f>IF(AND(F$3&gt;=$D24,F$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="G24" s="1">
+        <f>IF(AND(G$3&gt;=$D24,G$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="H24" s="1">
+        <f>IF(AND(H$3&gt;=$D24,H$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="I24" s="1">
+        <f>IF(AND(I$3&gt;=$D24,I$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="J24" s="1">
+        <f>IF(AND(J$3&gt;=$D24,J$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="K24" s="1">
+        <f>IF(AND(K$3&gt;=$D24,K$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="L24" s="1">
+        <f>IF(AND(L$3&gt;=$D24,L$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="M24" s="1">
+        <f>IF(AND(M$3&gt;=$D24,M$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="N24" s="1">
+        <f>IF(AND(N$3&gt;=$D24,N$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="O24" s="1">
+        <f>IF(AND(O$3&gt;=$D24,O$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="P24" s="1">
+        <f>IF(AND(P$3&gt;=$D24,P$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="Q24" s="1">
+        <f>IF(AND(Q$3&gt;=$D24,Q$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="R24" s="1">
+        <f>IF(AND(R$3&gt;=$D24,R$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="S24" s="1">
+        <f>IF(AND(S$3&gt;=$D24,S$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="T24" s="1">
+        <f>IF(AND(T$3&gt;=$D24,T$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="U24" s="1">
+        <f>IF(AND(U$3&gt;=$D24,U$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="V24" s="1">
+        <f>IF(AND(V$3&gt;=$D24,V$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="W24" s="1">
+        <f>IF(AND(W$3&gt;=$D24,W$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="X24" s="1">
+        <f>IF(AND(X$3&gt;=$D24,X$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="Y24" s="1">
+        <f>IF(AND(Y$3&gt;=$D24,Y$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="Z24" s="1">
+        <f>IF(AND(Z$3&gt;=$D24,Z$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AA24" s="1">
+        <f>IF(AND(AA$3&gt;=$D24,AA$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AB24" s="1">
+        <f>IF(AND(AB$3&gt;=$D24,AB$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AC24" s="1">
+        <f>IF(AND(AC$3&gt;=$D24,AC$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AD24" s="1">
+        <f>IF(AND(AD$3&gt;=$D24,AD$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AE24" s="1">
+        <f>IF(AND(AE$3&gt;=$D24,AE$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AF24" s="1">
+        <f>IF(AND(AF$3&gt;=$D24,AF$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AG24" s="1">
+        <f>IF(AND(AG$3&gt;=$D24,AG$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AH24" s="1">
+        <f>IF(AND(AH$3&gt;=$D24,AH$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AI24" s="1">
+        <f>IF(AND(AI$3&gt;=$D24,AI$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AJ24" s="1">
+        <f>IF(AND(AJ$3&gt;=$D24,AJ$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AK24" s="1">
+        <f>IF(AND(AK$3&gt;=$D24,AK$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AL24" s="1">
+        <f>IF(AND(AL$3&gt;=$D24,AL$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AM24" s="1">
+        <f>IF(AND(AM$3&gt;=$D24,AM$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AN24" s="1">
+        <f>IF(AND(AN$3&gt;=$D24,AN$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AO24" s="1">
+        <f>IF(AND(AO$3&gt;=$D24,AO$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AP24" s="1">
+        <f>IF(AND(AP$3&gt;=$D24,AP$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AQ24" s="1">
+        <f>IF(AND(AQ$3&gt;=$D24,AQ$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AR24" s="1">
+        <f>IF(AND(AR$3&gt;=$D24,AR$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AS24" s="1">
+        <f>IF(AND(AS$3&gt;=$D24,AS$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AT24" s="1">
+        <f>IF(AND(AT$3&gt;=$D24,AT$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AU24" s="1">
+        <f>IF(AND(AU$3&gt;=$D24,AU$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AV24" s="1">
+        <f>IF(AND(AV$3&gt;=$D24,AV$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AW24" s="1">
+        <f>IF(AND(AW$3&gt;=$D24,AW$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AX24" s="1">
+        <f>IF(AND(AX$3&gt;=$D24,AX$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AY24" s="1">
+        <f>IF(AND(AY$3&gt;=$D24,AY$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="AZ24" s="1">
+        <f>IF(AND(AZ$3&gt;=$D24,AZ$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BA24" s="1">
+        <f>IF(AND(BA$3&gt;=$D24,BA$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BB24" s="1">
+        <f>IF(AND(BB$3&gt;=$D24,BB$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BC24" s="1">
+        <f>IF(AND(BC$3&gt;=$D24,BC$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BD24" s="1">
+        <f>IF(AND(BD$3&gt;=$D24,BD$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BE24" s="1">
+        <f>IF(AND(BE$3&gt;=$D24,BE$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BF24" s="1">
+        <f>IF(AND(BF$3&gt;=$D24,BF$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BG24" s="1">
+        <f>IF(AND(BG$3&gt;=$D24,BG$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BH24" s="1">
+        <f>IF(AND(BH$3&gt;=$D24,BH$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BI24" s="1">
+        <f>IF(AND(BI$3&gt;=$D24,BI$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BJ24" s="1">
+        <f>IF(AND(BJ$3&gt;=$D24,BJ$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BK24" s="1">
+        <f>IF(AND(BK$3&gt;=$D24,BK$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BL24" s="1">
+        <f>IF(AND(BL$3&gt;=$D24,BL$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BM24" s="1">
+        <f>IF(AND(BM$3&gt;=$D24,BM$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BN24" s="1">
+        <f>IF(AND(BN$3&gt;=$D24,BN$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BO24" s="1">
+        <f>IF(AND(BO$3&gt;=$D24,BO$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BP24" s="1">
+        <f>IF(AND(BP$3&gt;=$D24,BP$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BQ24" s="1">
+        <f>IF(AND(BQ$3&gt;=$D24,BQ$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BR24" s="1">
+        <f>IF(AND(BR$3&gt;=$D24,BR$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BS24" s="1">
+        <f>IF(AND(BS$3&gt;=$D24,BS$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BT24" s="1">
+        <f>IF(AND(BT$3&gt;=$D24,BT$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BU24" s="1">
+        <f>IF(AND(BU$3&gt;=$D24,BU$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BV24" s="1">
+        <f>IF(AND(BV$3&gt;=$D24,BV$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BW24" s="1">
+        <f>IF(AND(BW$3&gt;=$D24,BW$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BX24" s="1">
+        <f>IF(AND(BX$3&gt;=$D24,BX$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BY24" s="1">
+        <f>IF(AND(BY$3&gt;=$D24,BY$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="BZ24" s="1">
+        <f>IF(AND(BZ$3&gt;=$D24,BZ$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="CA24" s="1">
+        <f>IF(AND(CA$3&gt;=$D24,CA$3&lt;=$E24),"█","")</f>
+      </c>
+      <c r="CB24" s="1">
+        <f>IF(AND(CB$3&gt;=$D24,CB$3&lt;=$E24),"█","")</f>
+      </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
@@ -1851,50 +6237,254 @@
         <f>D25+C25</f>
         <v>46250</v>
       </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
-      <c r="AG25" s="1"/>
-      <c r="AH25" s="1"/>
-      <c r="AI25" s="1"/>
+      <c r="F25" s="1">
+        <f>IF(AND(F$3&gt;=$D25,F$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="G25" s="1">
+        <f>IF(AND(G$3&gt;=$D25,G$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="H25" s="1">
+        <f>IF(AND(H$3&gt;=$D25,H$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="I25" s="1">
+        <f>IF(AND(I$3&gt;=$D25,I$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="J25" s="1">
+        <f>IF(AND(J$3&gt;=$D25,J$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="K25" s="1">
+        <f>IF(AND(K$3&gt;=$D25,K$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="L25" s="1">
+        <f>IF(AND(L$3&gt;=$D25,L$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="M25" s="1">
+        <f>IF(AND(M$3&gt;=$D25,M$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="N25" s="1">
+        <f>IF(AND(N$3&gt;=$D25,N$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="O25" s="1">
+        <f>IF(AND(O$3&gt;=$D25,O$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="P25" s="1">
+        <f>IF(AND(P$3&gt;=$D25,P$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="Q25" s="1">
+        <f>IF(AND(Q$3&gt;=$D25,Q$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="R25" s="1">
+        <f>IF(AND(R$3&gt;=$D25,R$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="S25" s="1">
+        <f>IF(AND(S$3&gt;=$D25,S$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="T25" s="1">
+        <f>IF(AND(T$3&gt;=$D25,T$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="U25" s="1">
+        <f>IF(AND(U$3&gt;=$D25,U$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="V25" s="1">
+        <f>IF(AND(V$3&gt;=$D25,V$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="W25" s="1">
+        <f>IF(AND(W$3&gt;=$D25,W$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="X25" s="1">
+        <f>IF(AND(X$3&gt;=$D25,X$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="Y25" s="1">
+        <f>IF(AND(Y$3&gt;=$D25,Y$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="Z25" s="1">
+        <f>IF(AND(Z$3&gt;=$D25,Z$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AA25" s="1">
+        <f>IF(AND(AA$3&gt;=$D25,AA$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AB25" s="1">
+        <f>IF(AND(AB$3&gt;=$D25,AB$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AC25" s="1">
+        <f>IF(AND(AC$3&gt;=$D25,AC$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AD25" s="1">
+        <f>IF(AND(AD$3&gt;=$D25,AD$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AE25" s="1">
+        <f>IF(AND(AE$3&gt;=$D25,AE$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AF25" s="1">
+        <f>IF(AND(AF$3&gt;=$D25,AF$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AG25" s="1">
+        <f>IF(AND(AG$3&gt;=$D25,AG$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AH25" s="1">
+        <f>IF(AND(AH$3&gt;=$D25,AH$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AI25" s="1">
+        <f>IF(AND(AI$3&gt;=$D25,AI$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AJ25" s="1">
+        <f>IF(AND(AJ$3&gt;=$D25,AJ$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AK25" s="1">
+        <f>IF(AND(AK$3&gt;=$D25,AK$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AL25" s="1">
+        <f>IF(AND(AL$3&gt;=$D25,AL$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AM25" s="1">
+        <f>IF(AND(AM$3&gt;=$D25,AM$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AN25" s="1">
+        <f>IF(AND(AN$3&gt;=$D25,AN$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AO25" s="1">
+        <f>IF(AND(AO$3&gt;=$D25,AO$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AP25" s="1">
+        <f>IF(AND(AP$3&gt;=$D25,AP$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AQ25" s="1">
+        <f>IF(AND(AQ$3&gt;=$D25,AQ$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AR25" s="1">
+        <f>IF(AND(AR$3&gt;=$D25,AR$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AS25" s="1">
+        <f>IF(AND(AS$3&gt;=$D25,AS$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AT25" s="1">
+        <f>IF(AND(AT$3&gt;=$D25,AT$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AU25" s="1">
+        <f>IF(AND(AU$3&gt;=$D25,AU$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AV25" s="1">
+        <f>IF(AND(AV$3&gt;=$D25,AV$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AW25" s="1">
+        <f>IF(AND(AW$3&gt;=$D25,AW$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AX25" s="1">
+        <f>IF(AND(AX$3&gt;=$D25,AX$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AY25" s="1">
+        <f>IF(AND(AY$3&gt;=$D25,AY$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="AZ25" s="1">
+        <f>IF(AND(AZ$3&gt;=$D25,AZ$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BA25" s="1">
+        <f>IF(AND(BA$3&gt;=$D25,BA$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BB25" s="1">
+        <f>IF(AND(BB$3&gt;=$D25,BB$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BC25" s="1">
+        <f>IF(AND(BC$3&gt;=$D25,BC$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BD25" s="1">
+        <f>IF(AND(BD$3&gt;=$D25,BD$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BE25" s="1">
+        <f>IF(AND(BE$3&gt;=$D25,BE$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BF25" s="1">
+        <f>IF(AND(BF$3&gt;=$D25,BF$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BG25" s="1">
+        <f>IF(AND(BG$3&gt;=$D25,BG$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BH25" s="1">
+        <f>IF(AND(BH$3&gt;=$D25,BH$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BI25" s="1">
+        <f>IF(AND(BI$3&gt;=$D25,BI$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BJ25" s="1">
+        <f>IF(AND(BJ$3&gt;=$D25,BJ$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BK25" s="1">
+        <f>IF(AND(BK$3&gt;=$D25,BK$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BL25" s="1">
+        <f>IF(AND(BL$3&gt;=$D25,BL$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BM25" s="1">
+        <f>IF(AND(BM$3&gt;=$D25,BM$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BN25" s="1">
+        <f>IF(AND(BN$3&gt;=$D25,BN$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BO25" s="1">
+        <f>IF(AND(BO$3&gt;=$D25,BO$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BP25" s="1">
+        <f>IF(AND(BP$3&gt;=$D25,BP$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BQ25" s="1">
+        <f>IF(AND(BQ$3&gt;=$D25,BQ$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BR25" s="1">
+        <f>IF(AND(BR$3&gt;=$D25,BR$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BS25" s="1">
+        <f>IF(AND(BS$3&gt;=$D25,BS$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BT25" s="1">
+        <f>IF(AND(BT$3&gt;=$D25,BT$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BU25" s="1">
+        <f>IF(AND(BU$3&gt;=$D25,BU$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BV25" s="1">
+        <f>IF(AND(BV$3&gt;=$D25,BV$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BW25" s="1">
+        <f>IF(AND(BW$3&gt;=$D25,BW$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BX25" s="1">
+        <f>IF(AND(BX$3&gt;=$D25,BX$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BY25" s="1">
+        <f>IF(AND(BY$3&gt;=$D25,BY$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="BZ25" s="1">
+        <f>IF(AND(BZ$3&gt;=$D25,BZ$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="CA25" s="1">
+        <f>IF(AND(CA$3&gt;=$D25,CA$3&lt;=$E25),"█","")</f>
+      </c>
+      <c r="CB25" s="1">
+        <f>IF(AND(CB$3&gt;=$D25,CB$3&lt;=$E25),"█","")</f>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="AE2:AI2"/>
+  <mergeCells count="20">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
     <mergeCell ref="F2:J2"/>
     <mergeCell ref="K2:O2"/>
     <mergeCell ref="P2:T2"/>
     <mergeCell ref="U2:Y2"/>
     <mergeCell ref="Z2:AD2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="AE2:AI2"/>
+    <mergeCell ref="AJ2:AN2"/>
+    <mergeCell ref="AO2:AS2"/>
+    <mergeCell ref="AT2:AX2"/>
+    <mergeCell ref="AY2:BC2"/>
+    <mergeCell ref="BD2:BH2"/>
+    <mergeCell ref="BI2:BM2"/>
+    <mergeCell ref="BN2:BR2"/>
+    <mergeCell ref="BS2:BW2"/>
+    <mergeCell ref="BX2:CB2"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Ebooks/Plan.xlsx
+++ b/Ebooks/Plan.xlsx
@@ -676,7 +676,7 @@
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84F7F5B0-1B8D-4819-819D-6A9F41E72B54}">
-  <dimension ref="A2:CB25"/>
+  <dimension ref="A1:CB25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.21875" customWidth="1"/>
@@ -687,7 +687,234 @@
     <col min="6" max="80" width="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:80" x14ac:dyDescent="0.3">
+      <c r="F1" s="1">
+        <v>46216</v>
+      </c>
+      <c r="G1" s="1">
+        <f>F1+1</f>
+      </c>
+      <c r="H1" s="1">
+        <f>G1+1</f>
+      </c>
+      <c r="I1" s="1">
+        <f>H1+1</f>
+      </c>
+      <c r="J1" s="1">
+        <f>I1+1</f>
+      </c>
+      <c r="K1" s="1">
+        <f>J1+3</f>
+      </c>
+      <c r="L1" s="1">
+        <f>K1+1</f>
+      </c>
+      <c r="M1" s="1">
+        <f>L1+1</f>
+      </c>
+      <c r="N1" s="1">
+        <f>M1+1</f>
+      </c>
+      <c r="O1" s="1">
+        <f>N1+1</f>
+      </c>
+      <c r="P1" s="1">
+        <f>O1+3</f>
+      </c>
+      <c r="Q1" s="1">
+        <f>P1+1</f>
+      </c>
+      <c r="R1" s="1">
+        <f>Q1+1</f>
+      </c>
+      <c r="S1" s="1">
+        <f>R1+1</f>
+      </c>
+      <c r="T1" s="1">
+        <f>S1+1</f>
+      </c>
+      <c r="U1" s="1">
+        <f>T1+3</f>
+      </c>
+      <c r="V1" s="1">
+        <f>U1+1</f>
+      </c>
+      <c r="W1" s="1">
+        <f>V1+1</f>
+      </c>
+      <c r="X1" s="1">
+        <f>W1+1</f>
+      </c>
+      <c r="Y1" s="1">
+        <f>X1+1</f>
+      </c>
+      <c r="Z1" s="1">
+        <f>Y1+3</f>
+      </c>
+      <c r="AA1" s="1">
+        <f>Z1+1</f>
+      </c>
+      <c r="AB1" s="1">
+        <f>AA1+1</f>
+      </c>
+      <c r="AC1" s="1">
+        <f>AB1+1</f>
+      </c>
+      <c r="AD1" s="1">
+        <f>AC1+1</f>
+      </c>
+      <c r="AE1" s="1">
+        <f>AD1+3</f>
+      </c>
+      <c r="AF1" s="1">
+        <f>AE1+1</f>
+      </c>
+      <c r="AG1" s="1">
+        <f>AF1+1</f>
+      </c>
+      <c r="AH1" s="1">
+        <f>AG1+1</f>
+      </c>
+      <c r="AI1" s="1">
+        <f>AH1+1</f>
+      </c>
+      <c r="AJ1" s="1">
+        <f>AI1+3</f>
+      </c>
+      <c r="AK1" s="1">
+        <f>AJ1+1</f>
+      </c>
+      <c r="AL1" s="1">
+        <f>AK1+1</f>
+      </c>
+      <c r="AM1" s="1">
+        <f>AL1+1</f>
+      </c>
+      <c r="AN1" s="1">
+        <f>AM1+1</f>
+      </c>
+      <c r="AO1" s="1">
+        <f>AN1+3</f>
+      </c>
+      <c r="AP1" s="1">
+        <f>AO1+1</f>
+      </c>
+      <c r="AQ1" s="1">
+        <f>AP1+1</f>
+      </c>
+      <c r="AR1" s="1">
+        <f>AQ1+1</f>
+      </c>
+      <c r="AS1" s="1">
+        <f>AR1+1</f>
+      </c>
+      <c r="AT1" s="1">
+        <f>AS1+3</f>
+      </c>
+      <c r="AU1" s="1">
+        <f>AT1+1</f>
+      </c>
+      <c r="AV1" s="1">
+        <f>AU1+1</f>
+      </c>
+      <c r="AW1" s="1">
+        <f>AV1+1</f>
+      </c>
+      <c r="AX1" s="1">
+        <f>AW1+1</f>
+      </c>
+      <c r="AY1" s="1">
+        <f>AX1+3</f>
+      </c>
+      <c r="AZ1" s="1">
+        <f>AY1+1</f>
+      </c>
+      <c r="BA1" s="1">
+        <f>AZ1+1</f>
+      </c>
+      <c r="BB1" s="1">
+        <f>BA1+1</f>
+      </c>
+      <c r="BC1" s="1">
+        <f>BB1+1</f>
+      </c>
+      <c r="BD1" s="1">
+        <f>BC1+3</f>
+      </c>
+      <c r="BE1" s="1">
+        <f>BD1+1</f>
+      </c>
+      <c r="BF1" s="1">
+        <f>BE1+1</f>
+      </c>
+      <c r="BG1" s="1">
+        <f>BF1+1</f>
+      </c>
+      <c r="BH1" s="1">
+        <f>BG1+1</f>
+      </c>
+      <c r="BI1" s="1">
+        <f>BH1+3</f>
+      </c>
+      <c r="BJ1" s="1">
+        <f>BI1+1</f>
+      </c>
+      <c r="BK1" s="1">
+        <f>BJ1+1</f>
+      </c>
+      <c r="BL1" s="1">
+        <f>BK1+1</f>
+      </c>
+      <c r="BM1" s="1">
+        <f>BL1+1</f>
+      </c>
+      <c r="BN1" s="1">
+        <f>BM1+3</f>
+      </c>
+      <c r="BO1" s="1">
+        <f>BN1+1</f>
+      </c>
+      <c r="BP1" s="1">
+        <f>BO1+1</f>
+      </c>
+      <c r="BQ1" s="1">
+        <f>BP1+1</f>
+      </c>
+      <c r="BR1" s="1">
+        <f>BQ1+1</f>
+      </c>
+      <c r="BS1" s="1">
+        <f>BR1+3</f>
+      </c>
+      <c r="BT1" s="1">
+        <f>BS1+1</f>
+      </c>
+      <c r="BU1" s="1">
+        <f>BT1+1</f>
+      </c>
+      <c r="BV1" s="1">
+        <f>BU1+1</f>
+      </c>
+      <c r="BW1" s="1">
+        <f>BV1+1</f>
+      </c>
+      <c r="BX1" s="1">
+        <f>BW1+3</f>
+      </c>
+      <c r="BY1" s="1">
+        <f>BX1+1</f>
+      </c>
+      <c r="BZ1" s="1">
+        <f>BY1+1</f>
+      </c>
+      <c r="CA1" s="1">
+        <f>BZ1+1</f>
+      </c>
+      <c r="CB1" s="1">
+        <f>CA1+1</f>
+      </c>
+    </row>
+    <row r="2" spans="1:80" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>22</v>
       </c>
@@ -809,7 +1036,7 @@
       <c r="CA2" s="14"/>
       <c r="CB2" s="14"/>
     </row>
-    <row r="3" spans="1:35" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:80" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -817,302 +1044,227 @@
       <c r="E3" s="13"/>
       <c r="F3" s="2" t="s">
         <v>10</v>
-        <v>46216</v>
       </c>
       <c r="G3" s="2" t="s">
-        <f>F3+1</f>
         <v>11</v>
       </c>
       <c r="H3" s="2" t="s">
-        <f>G3+1</f>
         <v>12</v>
       </c>
       <c r="I3" s="2" t="s">
-        <f>H3+1</f>
         <v>13</v>
       </c>
       <c r="J3" s="2" t="s">
-        <f>I3+1</f>
         <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
-        <f>J3+3</f>
         <v>10</v>
       </c>
       <c r="L3" s="2" t="s">
-        <f>K3+1</f>
         <v>11</v>
       </c>
       <c r="M3" s="2" t="s">
-        <f>L3+1</f>
         <v>12</v>
       </c>
       <c r="N3" s="2" t="s">
-        <f>M3+1</f>
         <v>13</v>
       </c>
       <c r="O3" s="2" t="s">
-        <f>N3+1</f>
         <v>14</v>
       </c>
       <c r="P3" s="2" t="s">
-        <f>O3+3</f>
         <v>10</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <f>P3+1</f>
         <v>11</v>
       </c>
       <c r="R3" s="2" t="s">
-        <f>Q3+1</f>
         <v>12</v>
       </c>
       <c r="S3" s="2" t="s">
-        <f>R3+1</f>
         <v>13</v>
       </c>
       <c r="T3" s="2" t="s">
-        <f>S3+1</f>
         <v>14</v>
       </c>
       <c r="U3" s="2" t="s">
-        <f>T3+3</f>
         <v>10</v>
       </c>
       <c r="V3" s="2" t="s">
-        <f>U3+1</f>
         <v>11</v>
       </c>
       <c r="W3" s="2" t="s">
-        <f>V3+1</f>
         <v>12</v>
       </c>
       <c r="X3" s="2" t="s">
-        <f>W3+1</f>
         <v>13</v>
       </c>
       <c r="Y3" s="2" t="s">
-        <f>X3+1</f>
         <v>14</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <f>Y3+3</f>
         <v>10</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <f>Z3+1</f>
         <v>11</v>
       </c>
       <c r="AB3" s="2" t="s">
-        <f>AA3+1</f>
         <v>12</v>
       </c>
       <c r="AC3" s="2" t="s">
-        <f>AB3+1</f>
         <v>13</v>
       </c>
       <c r="AD3" s="2" t="s">
-        <f>AC3+1</f>
         <v>14</v>
       </c>
       <c r="AE3" s="2" t="s">
-        <f>AD3+3</f>
         <v>10</v>
       </c>
       <c r="AF3" s="2" t="s">
-        <f>AE3+1</f>
         <v>11</v>
       </c>
       <c r="AG3" s="2" t="s">
-        <f>AF3+1</f>
         <v>12</v>
       </c>
       <c r="AH3" s="2" t="s">
-        <f>AG3+1</f>
         <v>13</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <f>AH3+1</f>
         <v>14</v>
       </c>
       <c r="AJ3" s="2" t="s">
-        <f>AI3+3</f>
         <v>10</v>
       </c>
       <c r="AK3" s="2" t="s">
-        <f>AJ3+1</f>
         <v>11</v>
       </c>
       <c r="AL3" s="2" t="s">
-        <f>AK3+1</f>
         <v>12</v>
       </c>
       <c r="AM3" s="2" t="s">
-        <f>AL3+1</f>
         <v>13</v>
       </c>
       <c r="AN3" s="2" t="s">
-        <f>AM3+1</f>
         <v>14</v>
       </c>
       <c r="AO3" s="2" t="s">
-        <f>AN3+3</f>
         <v>10</v>
       </c>
       <c r="AP3" s="2" t="s">
-        <f>AO3+1</f>
         <v>11</v>
       </c>
       <c r="AQ3" s="2" t="s">
-        <f>AP3+1</f>
         <v>12</v>
       </c>
       <c r="AR3" s="2" t="s">
-        <f>AQ3+1</f>
         <v>13</v>
       </c>
       <c r="AS3" s="2" t="s">
-        <f>AR3+1</f>
         <v>14</v>
       </c>
       <c r="AT3" s="2" t="s">
-        <f>AS3+3</f>
         <v>10</v>
       </c>
       <c r="AU3" s="2" t="s">
-        <f>AT3+1</f>
         <v>11</v>
       </c>
       <c r="AV3" s="2" t="s">
-        <f>AU3+1</f>
         <v>12</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <f>AV3+1</f>
         <v>13</v>
       </c>
       <c r="AX3" s="2" t="s">
-        <f>AW3+1</f>
         <v>14</v>
       </c>
       <c r="AY3" s="2" t="s">
-        <f>AX3+3</f>
         <v>10</v>
       </c>
       <c r="AZ3" s="2" t="s">
-        <f>AY3+1</f>
         <v>11</v>
       </c>
       <c r="BA3" s="2" t="s">
-        <f>AZ3+1</f>
         <v>12</v>
       </c>
       <c r="BB3" s="2" t="s">
-        <f>BA3+1</f>
         <v>13</v>
       </c>
       <c r="BC3" s="2" t="s">
-        <f>BB3+1</f>
         <v>14</v>
       </c>
       <c r="BD3" s="2" t="s">
-        <f>BC3+3</f>
         <v>10</v>
       </c>
       <c r="BE3" s="2" t="s">
-        <f>BD3+1</f>
         <v>11</v>
       </c>
       <c r="BF3" s="2" t="s">
-        <f>BE3+1</f>
         <v>12</v>
       </c>
       <c r="BG3" s="2" t="s">
-        <f>BF3+1</f>
         <v>13</v>
       </c>
       <c r="BH3" s="2" t="s">
-        <f>BG3+1</f>
         <v>14</v>
       </c>
       <c r="BI3" s="2" t="s">
-        <f>BH3+3</f>
         <v>10</v>
       </c>
       <c r="BJ3" s="2" t="s">
-        <f>BI3+1</f>
         <v>11</v>
       </c>
       <c r="BK3" s="2" t="s">
-        <f>BJ3+1</f>
         <v>12</v>
       </c>
       <c r="BL3" s="2" t="s">
-        <f>BK3+1</f>
         <v>13</v>
       </c>
       <c r="BM3" s="2" t="s">
-        <f>BL3+1</f>
         <v>14</v>
       </c>
       <c r="BN3" s="2" t="s">
-        <f>BM3+3</f>
         <v>10</v>
       </c>
       <c r="BO3" s="2" t="s">
-        <f>BN3+1</f>
         <v>11</v>
       </c>
       <c r="BP3" s="2" t="s">
-        <f>BO3+1</f>
         <v>12</v>
       </c>
       <c r="BQ3" s="2" t="s">
-        <f>BP3+1</f>
         <v>13</v>
       </c>
       <c r="BR3" s="2" t="s">
-        <f>BQ3+1</f>
         <v>14</v>
       </c>
       <c r="BS3" s="2" t="s">
-        <f>BR3+3</f>
         <v>10</v>
       </c>
       <c r="BT3" s="2" t="s">
-        <f>BS3+1</f>
         <v>11</v>
       </c>
       <c r="BU3" s="2" t="s">
-        <f>BT3+1</f>
         <v>12</v>
       </c>
       <c r="BV3" s="2" t="s">
-        <f>BU3+1</f>
         <v>13</v>
       </c>
       <c r="BW3" s="2" t="s">
-        <f>BV3+1</f>
         <v>14</v>
       </c>
       <c r="BX3" s="2" t="s">
-        <f>BW3+3</f>
         <v>10</v>
       </c>
       <c r="BY3" s="2" t="s">
-        <f>BX3+1</f>
         <v>11</v>
       </c>
       <c r="BZ3" s="2" t="s">
-        <f>BY3+1</f>
         <v>12</v>
       </c>
       <c r="CA3" s="2" t="s">
-        <f>BZ3+1</f>
         <v>13</v>
       </c>
       <c r="CB3" s="2" t="s">
-        <f>CA3+1</f>
         <v>14</v>
       </c>
     </row>
@@ -1136,229 +1288,229 @@
         <v>46234</v>
       </c>
       <c r="F4" s="1">
-        <f>IF(AND(F$3&gt;=$D4,F$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D4,F$1&lt;=$E4),"█","")</f>
       </c>
       <c r="G4" s="1">
-        <f>IF(AND(G$3&gt;=$D4,G$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D4,G$1&lt;=$E4),"█","")</f>
       </c>
       <c r="H4" s="1">
-        <f>IF(AND(H$3&gt;=$D4,H$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D4,H$1&lt;=$E4),"█","")</f>
       </c>
       <c r="I4" s="1">
-        <f>IF(AND(I$3&gt;=$D4,I$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D4,I$1&lt;=$E4),"█","")</f>
       </c>
       <c r="J4" s="1">
-        <f>IF(AND(J$3&gt;=$D4,J$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D4,J$1&lt;=$E4),"█","")</f>
       </c>
       <c r="K4" s="1">
-        <f>IF(AND(K$3&gt;=$D4,K$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D4,K$1&lt;=$E4),"█","")</f>
       </c>
       <c r="L4" s="1">
-        <f>IF(AND(L$3&gt;=$D4,L$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D4,L$1&lt;=$E4),"█","")</f>
       </c>
       <c r="M4" s="1">
-        <f>IF(AND(M$3&gt;=$D4,M$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D4,M$1&lt;=$E4),"█","")</f>
       </c>
       <c r="N4" s="1">
-        <f>IF(AND(N$3&gt;=$D4,N$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D4,N$1&lt;=$E4),"█","")</f>
       </c>
       <c r="O4" s="1">
-        <f>IF(AND(O$3&gt;=$D4,O$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D4,O$1&lt;=$E4),"█","")</f>
       </c>
       <c r="P4" s="1">
-        <f>IF(AND(P$3&gt;=$D4,P$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D4,P$1&lt;=$E4),"█","")</f>
       </c>
       <c r="Q4" s="1">
-        <f>IF(AND(Q$3&gt;=$D4,Q$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D4,Q$1&lt;=$E4),"█","")</f>
       </c>
       <c r="R4" s="1">
-        <f>IF(AND(R$3&gt;=$D4,R$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D4,R$1&lt;=$E4),"█","")</f>
       </c>
       <c r="S4" s="1">
-        <f>IF(AND(S$3&gt;=$D4,S$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D4,S$1&lt;=$E4),"█","")</f>
       </c>
       <c r="T4" s="1">
-        <f>IF(AND(T$3&gt;=$D4,T$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D4,T$1&lt;=$E4),"█","")</f>
       </c>
       <c r="U4" s="1">
-        <f>IF(AND(U$3&gt;=$D4,U$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D4,U$1&lt;=$E4),"█","")</f>
       </c>
       <c r="V4" s="1">
-        <f>IF(AND(V$3&gt;=$D4,V$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D4,V$1&lt;=$E4),"█","")</f>
       </c>
       <c r="W4" s="1">
-        <f>IF(AND(W$3&gt;=$D4,W$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D4,W$1&lt;=$E4),"█","")</f>
       </c>
       <c r="X4" s="1">
-        <f>IF(AND(X$3&gt;=$D4,X$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D4,X$1&lt;=$E4),"█","")</f>
       </c>
       <c r="Y4" s="1">
-        <f>IF(AND(Y$3&gt;=$D4,Y$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D4,Y$1&lt;=$E4),"█","")</f>
       </c>
       <c r="Z4" s="1">
-        <f>IF(AND(Z$3&gt;=$D4,Z$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D4,Z$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AA4" s="1">
-        <f>IF(AND(AA$3&gt;=$D4,AA$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D4,AA$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AB4" s="1">
-        <f>IF(AND(AB$3&gt;=$D4,AB$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D4,AB$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AC4" s="1">
-        <f>IF(AND(AC$3&gt;=$D4,AC$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D4,AC$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AD4" s="1">
-        <f>IF(AND(AD$3&gt;=$D4,AD$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D4,AD$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AE4" s="1">
-        <f>IF(AND(AE$3&gt;=$D4,AE$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D4,AE$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AF4" s="1">
-        <f>IF(AND(AF$3&gt;=$D4,AF$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D4,AF$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AG4" s="1">
-        <f>IF(AND(AG$3&gt;=$D4,AG$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D4,AG$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AH4" s="1">
-        <f>IF(AND(AH$3&gt;=$D4,AH$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D4,AH$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AI4" s="1">
-        <f>IF(AND(AI$3&gt;=$D4,AI$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D4,AI$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AJ4" s="1">
-        <f>IF(AND(AJ$3&gt;=$D4,AJ$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D4,AJ$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AK4" s="1">
-        <f>IF(AND(AK$3&gt;=$D4,AK$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D4,AK$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AL4" s="1">
-        <f>IF(AND(AL$3&gt;=$D4,AL$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D4,AL$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AM4" s="1">
-        <f>IF(AND(AM$3&gt;=$D4,AM$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D4,AM$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AN4" s="1">
-        <f>IF(AND(AN$3&gt;=$D4,AN$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D4,AN$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AO4" s="1">
-        <f>IF(AND(AO$3&gt;=$D4,AO$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D4,AO$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AP4" s="1">
-        <f>IF(AND(AP$3&gt;=$D4,AP$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D4,AP$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AQ4" s="1">
-        <f>IF(AND(AQ$3&gt;=$D4,AQ$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D4,AQ$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AR4" s="1">
-        <f>IF(AND(AR$3&gt;=$D4,AR$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D4,AR$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AS4" s="1">
-        <f>IF(AND(AS$3&gt;=$D4,AS$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D4,AS$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AT4" s="1">
-        <f>IF(AND(AT$3&gt;=$D4,AT$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D4,AT$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AU4" s="1">
-        <f>IF(AND(AU$3&gt;=$D4,AU$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D4,AU$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AV4" s="1">
-        <f>IF(AND(AV$3&gt;=$D4,AV$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D4,AV$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AW4" s="1">
-        <f>IF(AND(AW$3&gt;=$D4,AW$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D4,AW$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AX4" s="1">
-        <f>IF(AND(AX$3&gt;=$D4,AX$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D4,AX$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AY4" s="1">
-        <f>IF(AND(AY$3&gt;=$D4,AY$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D4,AY$1&lt;=$E4),"█","")</f>
       </c>
       <c r="AZ4" s="1">
-        <f>IF(AND(AZ$3&gt;=$D4,AZ$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D4,AZ$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BA4" s="1">
-        <f>IF(AND(BA$3&gt;=$D4,BA$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D4,BA$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BB4" s="1">
-        <f>IF(AND(BB$3&gt;=$D4,BB$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D4,BB$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BC4" s="1">
-        <f>IF(AND(BC$3&gt;=$D4,BC$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D4,BC$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BD4" s="1">
-        <f>IF(AND(BD$3&gt;=$D4,BD$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D4,BD$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BE4" s="1">
-        <f>IF(AND(BE$3&gt;=$D4,BE$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D4,BE$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BF4" s="1">
-        <f>IF(AND(BF$3&gt;=$D4,BF$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D4,BF$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BG4" s="1">
-        <f>IF(AND(BG$3&gt;=$D4,BG$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D4,BG$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BH4" s="1">
-        <f>IF(AND(BH$3&gt;=$D4,BH$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D4,BH$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BI4" s="1">
-        <f>IF(AND(BI$3&gt;=$D4,BI$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D4,BI$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BJ4" s="1">
-        <f>IF(AND(BJ$3&gt;=$D4,BJ$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D4,BJ$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BK4" s="1">
-        <f>IF(AND(BK$3&gt;=$D4,BK$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D4,BK$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BL4" s="1">
-        <f>IF(AND(BL$3&gt;=$D4,BL$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D4,BL$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BM4" s="1">
-        <f>IF(AND(BM$3&gt;=$D4,BM$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D4,BM$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BN4" s="1">
-        <f>IF(AND(BN$3&gt;=$D4,BN$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D4,BN$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BO4" s="1">
-        <f>IF(AND(BO$3&gt;=$D4,BO$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D4,BO$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BP4" s="1">
-        <f>IF(AND(BP$3&gt;=$D4,BP$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D4,BP$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BQ4" s="1">
-        <f>IF(AND(BQ$3&gt;=$D4,BQ$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D4,BQ$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BR4" s="1">
-        <f>IF(AND(BR$3&gt;=$D4,BR$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D4,BR$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BS4" s="1">
-        <f>IF(AND(BS$3&gt;=$D4,BS$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D4,BS$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BT4" s="1">
-        <f>IF(AND(BT$3&gt;=$D4,BT$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D4,BT$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BU4" s="1">
-        <f>IF(AND(BU$3&gt;=$D4,BU$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D4,BU$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BV4" s="1">
-        <f>IF(AND(BV$3&gt;=$D4,BV$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D4,BV$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BW4" s="1">
-        <f>IF(AND(BW$3&gt;=$D4,BW$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D4,BW$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BX4" s="1">
-        <f>IF(AND(BX$3&gt;=$D4,BX$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D4,BX$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BY4" s="1">
-        <f>IF(AND(BY$3&gt;=$D4,BY$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D4,BY$1&lt;=$E4),"█","")</f>
       </c>
       <c r="BZ4" s="1">
-        <f>IF(AND(BZ$3&gt;=$D4,BZ$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D4,BZ$1&lt;=$E4),"█","")</f>
       </c>
       <c r="CA4" s="1">
-        <f>IF(AND(CA$3&gt;=$D4,CA$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D4,CA$1&lt;=$E4),"█","")</f>
       </c>
       <c r="CB4" s="1">
-        <f>IF(AND(CB$3&gt;=$D4,CB$3&lt;=$E4),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D4,CB$1&lt;=$E4),"█","")</f>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.3">
@@ -1372,236 +1524,235 @@
         <v>2</v>
       </c>
       <c r="D5" s="7">
-        <v>46225</v>
+        <v>46213</v>
       </c>
       <c r="E5" s="7">
         <f>D5+C5</f>
-        <v>46227</v>
       </c>
       <c r="F5" s="1">
-        <f>IF(AND(F$3&gt;=$D5,F$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D5,F$1&lt;=$E5),"█","")</f>
       </c>
       <c r="G5" s="1">
-        <f>IF(AND(G$3&gt;=$D5,G$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D5,G$1&lt;=$E5),"█","")</f>
       </c>
       <c r="H5" s="1">
-        <f>IF(AND(H$3&gt;=$D5,H$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D5,H$1&lt;=$E5),"█","")</f>
       </c>
       <c r="I5" s="1">
-        <f>IF(AND(I$3&gt;=$D5,I$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D5,I$1&lt;=$E5),"█","")</f>
       </c>
       <c r="J5" s="1">
-        <f>IF(AND(J$3&gt;=$D5,J$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D5,J$1&lt;=$E5),"█","")</f>
       </c>
       <c r="K5" s="1">
-        <f>IF(AND(K$3&gt;=$D5,K$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D5,K$1&lt;=$E5),"█","")</f>
       </c>
       <c r="L5" s="1">
-        <f>IF(AND(L$3&gt;=$D5,L$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D5,L$1&lt;=$E5),"█","")</f>
       </c>
       <c r="M5" s="1">
-        <f>IF(AND(M$3&gt;=$D5,M$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D5,M$1&lt;=$E5),"█","")</f>
       </c>
       <c r="N5" s="1">
-        <f>IF(AND(N$3&gt;=$D5,N$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D5,N$1&lt;=$E5),"█","")</f>
       </c>
       <c r="O5" s="1">
-        <f>IF(AND(O$3&gt;=$D5,O$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D5,O$1&lt;=$E5),"█","")</f>
       </c>
       <c r="P5" s="1">
-        <f>IF(AND(P$3&gt;=$D5,P$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D5,P$1&lt;=$E5),"█","")</f>
       </c>
       <c r="Q5" s="1">
-        <f>IF(AND(Q$3&gt;=$D5,Q$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D5,Q$1&lt;=$E5),"█","")</f>
       </c>
       <c r="R5" s="1">
-        <f>IF(AND(R$3&gt;=$D5,R$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D5,R$1&lt;=$E5),"█","")</f>
       </c>
       <c r="S5" s="1">
-        <f>IF(AND(S$3&gt;=$D5,S$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D5,S$1&lt;=$E5),"█","")</f>
       </c>
       <c r="T5" s="1">
-        <f>IF(AND(T$3&gt;=$D5,T$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D5,T$1&lt;=$E5),"█","")</f>
       </c>
       <c r="U5" s="1">
-        <f>IF(AND(U$3&gt;=$D5,U$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D5,U$1&lt;=$E5),"█","")</f>
       </c>
       <c r="V5" s="1">
-        <f>IF(AND(V$3&gt;=$D5,V$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D5,V$1&lt;=$E5),"█","")</f>
       </c>
       <c r="W5" s="1">
-        <f>IF(AND(W$3&gt;=$D5,W$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D5,W$1&lt;=$E5),"█","")</f>
       </c>
       <c r="X5" s="1">
-        <f>IF(AND(X$3&gt;=$D5,X$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D5,X$1&lt;=$E5),"█","")</f>
       </c>
       <c r="Y5" s="1">
-        <f>IF(AND(Y$3&gt;=$D5,Y$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D5,Y$1&lt;=$E5),"█","")</f>
       </c>
       <c r="Z5" s="1">
-        <f>IF(AND(Z$3&gt;=$D5,Z$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D5,Z$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AA5" s="1">
-        <f>IF(AND(AA$3&gt;=$D5,AA$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D5,AA$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AB5" s="1">
-        <f>IF(AND(AB$3&gt;=$D5,AB$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D5,AB$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AC5" s="1">
-        <f>IF(AND(AC$3&gt;=$D5,AC$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D5,AC$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AD5" s="1">
-        <f>IF(AND(AD$3&gt;=$D5,AD$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D5,AD$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AE5" s="1">
-        <f>IF(AND(AE$3&gt;=$D5,AE$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D5,AE$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AF5" s="1">
-        <f>IF(AND(AF$3&gt;=$D5,AF$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D5,AF$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AG5" s="1">
-        <f>IF(AND(AG$3&gt;=$D5,AG$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D5,AG$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AH5" s="1">
-        <f>IF(AND(AH$3&gt;=$D5,AH$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D5,AH$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AI5" s="1">
-        <f>IF(AND(AI$3&gt;=$D5,AI$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D5,AI$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AJ5" s="1">
-        <f>IF(AND(AJ$3&gt;=$D5,AJ$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D5,AJ$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AK5" s="1">
-        <f>IF(AND(AK$3&gt;=$D5,AK$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D5,AK$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AL5" s="1">
-        <f>IF(AND(AL$3&gt;=$D5,AL$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D5,AL$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AM5" s="1">
-        <f>IF(AND(AM$3&gt;=$D5,AM$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D5,AM$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AN5" s="1">
-        <f>IF(AND(AN$3&gt;=$D5,AN$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D5,AN$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AO5" s="1">
-        <f>IF(AND(AO$3&gt;=$D5,AO$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D5,AO$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AP5" s="1">
-        <f>IF(AND(AP$3&gt;=$D5,AP$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D5,AP$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AQ5" s="1">
-        <f>IF(AND(AQ$3&gt;=$D5,AQ$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D5,AQ$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AR5" s="1">
-        <f>IF(AND(AR$3&gt;=$D5,AR$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D5,AR$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AS5" s="1">
-        <f>IF(AND(AS$3&gt;=$D5,AS$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D5,AS$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AT5" s="1">
-        <f>IF(AND(AT$3&gt;=$D5,AT$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D5,AT$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AU5" s="1">
-        <f>IF(AND(AU$3&gt;=$D5,AU$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D5,AU$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AV5" s="1">
-        <f>IF(AND(AV$3&gt;=$D5,AV$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D5,AV$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AW5" s="1">
-        <f>IF(AND(AW$3&gt;=$D5,AW$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D5,AW$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AX5" s="1">
-        <f>IF(AND(AX$3&gt;=$D5,AX$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D5,AX$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AY5" s="1">
-        <f>IF(AND(AY$3&gt;=$D5,AY$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D5,AY$1&lt;=$E5),"█","")</f>
       </c>
       <c r="AZ5" s="1">
-        <f>IF(AND(AZ$3&gt;=$D5,AZ$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D5,AZ$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BA5" s="1">
-        <f>IF(AND(BA$3&gt;=$D5,BA$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D5,BA$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BB5" s="1">
-        <f>IF(AND(BB$3&gt;=$D5,BB$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D5,BB$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BC5" s="1">
-        <f>IF(AND(BC$3&gt;=$D5,BC$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D5,BC$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BD5" s="1">
-        <f>IF(AND(BD$3&gt;=$D5,BD$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D5,BD$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BE5" s="1">
-        <f>IF(AND(BE$3&gt;=$D5,BE$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D5,BE$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BF5" s="1">
-        <f>IF(AND(BF$3&gt;=$D5,BF$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D5,BF$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BG5" s="1">
-        <f>IF(AND(BG$3&gt;=$D5,BG$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D5,BG$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BH5" s="1">
-        <f>IF(AND(BH$3&gt;=$D5,BH$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D5,BH$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BI5" s="1">
-        <f>IF(AND(BI$3&gt;=$D5,BI$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D5,BI$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BJ5" s="1">
-        <f>IF(AND(BJ$3&gt;=$D5,BJ$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D5,BJ$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BK5" s="1">
-        <f>IF(AND(BK$3&gt;=$D5,BK$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D5,BK$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BL5" s="1">
-        <f>IF(AND(BL$3&gt;=$D5,BL$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D5,BL$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BM5" s="1">
-        <f>IF(AND(BM$3&gt;=$D5,BM$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D5,BM$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BN5" s="1">
-        <f>IF(AND(BN$3&gt;=$D5,BN$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D5,BN$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BO5" s="1">
-        <f>IF(AND(BO$3&gt;=$D5,BO$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D5,BO$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BP5" s="1">
-        <f>IF(AND(BP$3&gt;=$D5,BP$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D5,BP$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BQ5" s="1">
-        <f>IF(AND(BQ$3&gt;=$D5,BQ$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D5,BQ$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BR5" s="1">
-        <f>IF(AND(BR$3&gt;=$D5,BR$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D5,BR$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BS5" s="1">
-        <f>IF(AND(BS$3&gt;=$D5,BS$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D5,BS$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BT5" s="1">
-        <f>IF(AND(BT$3&gt;=$D5,BT$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D5,BT$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BU5" s="1">
-        <f>IF(AND(BU$3&gt;=$D5,BU$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D5,BU$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BV5" s="1">
-        <f>IF(AND(BV$3&gt;=$D5,BV$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D5,BV$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BW5" s="1">
-        <f>IF(AND(BW$3&gt;=$D5,BW$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D5,BW$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BX5" s="1">
-        <f>IF(AND(BX$3&gt;=$D5,BX$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D5,BX$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BY5" s="1">
-        <f>IF(AND(BY$3&gt;=$D5,BY$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D5,BY$1&lt;=$E5),"█","")</f>
       </c>
       <c r="BZ5" s="1">
-        <f>IF(AND(BZ$3&gt;=$D5,BZ$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D5,BZ$1&lt;=$E5),"█","")</f>
       </c>
       <c r="CA5" s="1">
-        <f>IF(AND(CA$3&gt;=$D5,CA$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D5,CA$1&lt;=$E5),"█","")</f>
       </c>
       <c r="CB5" s="1">
-        <f>IF(AND(CB$3&gt;=$D5,CB$3&lt;=$E5),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D5,CB$1&lt;=$E5),"█","")</f>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.3">
@@ -1616,236 +1767,234 @@
       </c>
       <c r="D6" s="7">
         <f>E5+1</f>
-        <v>46228</v>
       </c>
       <c r="E6" s="7">
-        <f t="shared" ref="E6:E9" si="0">D6+C6</f>
-        <v>46229</v>
+        <f>D6+C6</f>
       </c>
       <c r="F6" s="1">
-        <f>IF(AND(F$3&gt;=$D6,F$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D6,F$1&lt;=$E6),"█","")</f>
       </c>
       <c r="G6" s="1">
-        <f>IF(AND(G$3&gt;=$D6,G$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D6,G$1&lt;=$E6),"█","")</f>
       </c>
       <c r="H6" s="1">
-        <f>IF(AND(H$3&gt;=$D6,H$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D6,H$1&lt;=$E6),"█","")</f>
       </c>
       <c r="I6" s="1">
-        <f>IF(AND(I$3&gt;=$D6,I$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D6,I$1&lt;=$E6),"█","")</f>
       </c>
       <c r="J6" s="1">
-        <f>IF(AND(J$3&gt;=$D6,J$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D6,J$1&lt;=$E6),"█","")</f>
       </c>
       <c r="K6" s="1">
-        <f>IF(AND(K$3&gt;=$D6,K$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D6,K$1&lt;=$E6),"█","")</f>
       </c>
       <c r="L6" s="1">
-        <f>IF(AND(L$3&gt;=$D6,L$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D6,L$1&lt;=$E6),"█","")</f>
       </c>
       <c r="M6" s="1">
-        <f>IF(AND(M$3&gt;=$D6,M$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D6,M$1&lt;=$E6),"█","")</f>
       </c>
       <c r="N6" s="1">
-        <f>IF(AND(N$3&gt;=$D6,N$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D6,N$1&lt;=$E6),"█","")</f>
       </c>
       <c r="O6" s="1">
-        <f>IF(AND(O$3&gt;=$D6,O$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D6,O$1&lt;=$E6),"█","")</f>
       </c>
       <c r="P6" s="1">
-        <f>IF(AND(P$3&gt;=$D6,P$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D6,P$1&lt;=$E6),"█","")</f>
       </c>
       <c r="Q6" s="1">
-        <f>IF(AND(Q$3&gt;=$D6,Q$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D6,Q$1&lt;=$E6),"█","")</f>
       </c>
       <c r="R6" s="1">
-        <f>IF(AND(R$3&gt;=$D6,R$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D6,R$1&lt;=$E6),"█","")</f>
       </c>
       <c r="S6" s="1">
-        <f>IF(AND(S$3&gt;=$D6,S$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D6,S$1&lt;=$E6),"█","")</f>
       </c>
       <c r="T6" s="1">
-        <f>IF(AND(T$3&gt;=$D6,T$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D6,T$1&lt;=$E6),"█","")</f>
       </c>
       <c r="U6" s="1">
-        <f>IF(AND(U$3&gt;=$D6,U$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D6,U$1&lt;=$E6),"█","")</f>
       </c>
       <c r="V6" s="1">
-        <f>IF(AND(V$3&gt;=$D6,V$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D6,V$1&lt;=$E6),"█","")</f>
       </c>
       <c r="W6" s="1">
-        <f>IF(AND(W$3&gt;=$D6,W$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D6,W$1&lt;=$E6),"█","")</f>
       </c>
       <c r="X6" s="1">
-        <f>IF(AND(X$3&gt;=$D6,X$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D6,X$1&lt;=$E6),"█","")</f>
       </c>
       <c r="Y6" s="1">
-        <f>IF(AND(Y$3&gt;=$D6,Y$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D6,Y$1&lt;=$E6),"█","")</f>
       </c>
       <c r="Z6" s="1">
-        <f>IF(AND(Z$3&gt;=$D6,Z$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D6,Z$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AA6" s="1">
-        <f>IF(AND(AA$3&gt;=$D6,AA$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D6,AA$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AB6" s="1">
-        <f>IF(AND(AB$3&gt;=$D6,AB$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D6,AB$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AC6" s="1">
-        <f>IF(AND(AC$3&gt;=$D6,AC$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D6,AC$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AD6" s="1">
-        <f>IF(AND(AD$3&gt;=$D6,AD$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D6,AD$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AE6" s="1">
-        <f>IF(AND(AE$3&gt;=$D6,AE$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D6,AE$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AF6" s="1">
-        <f>IF(AND(AF$3&gt;=$D6,AF$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D6,AF$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AG6" s="1">
-        <f>IF(AND(AG$3&gt;=$D6,AG$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D6,AG$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AH6" s="1">
-        <f>IF(AND(AH$3&gt;=$D6,AH$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D6,AH$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AI6" s="1">
-        <f>IF(AND(AI$3&gt;=$D6,AI$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D6,AI$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AJ6" s="1">
-        <f>IF(AND(AJ$3&gt;=$D6,AJ$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D6,AJ$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AK6" s="1">
-        <f>IF(AND(AK$3&gt;=$D6,AK$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D6,AK$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AL6" s="1">
-        <f>IF(AND(AL$3&gt;=$D6,AL$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D6,AL$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AM6" s="1">
-        <f>IF(AND(AM$3&gt;=$D6,AM$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D6,AM$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AN6" s="1">
-        <f>IF(AND(AN$3&gt;=$D6,AN$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D6,AN$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AO6" s="1">
-        <f>IF(AND(AO$3&gt;=$D6,AO$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D6,AO$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AP6" s="1">
-        <f>IF(AND(AP$3&gt;=$D6,AP$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D6,AP$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AQ6" s="1">
-        <f>IF(AND(AQ$3&gt;=$D6,AQ$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D6,AQ$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AR6" s="1">
-        <f>IF(AND(AR$3&gt;=$D6,AR$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D6,AR$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AS6" s="1">
-        <f>IF(AND(AS$3&gt;=$D6,AS$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D6,AS$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AT6" s="1">
-        <f>IF(AND(AT$3&gt;=$D6,AT$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D6,AT$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AU6" s="1">
-        <f>IF(AND(AU$3&gt;=$D6,AU$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D6,AU$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AV6" s="1">
-        <f>IF(AND(AV$3&gt;=$D6,AV$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D6,AV$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AW6" s="1">
-        <f>IF(AND(AW$3&gt;=$D6,AW$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D6,AW$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AX6" s="1">
-        <f>IF(AND(AX$3&gt;=$D6,AX$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D6,AX$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AY6" s="1">
-        <f>IF(AND(AY$3&gt;=$D6,AY$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D6,AY$1&lt;=$E6),"█","")</f>
       </c>
       <c r="AZ6" s="1">
-        <f>IF(AND(AZ$3&gt;=$D6,AZ$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D6,AZ$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BA6" s="1">
-        <f>IF(AND(BA$3&gt;=$D6,BA$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D6,BA$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BB6" s="1">
-        <f>IF(AND(BB$3&gt;=$D6,BB$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D6,BB$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BC6" s="1">
-        <f>IF(AND(BC$3&gt;=$D6,BC$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D6,BC$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BD6" s="1">
-        <f>IF(AND(BD$3&gt;=$D6,BD$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D6,BD$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BE6" s="1">
-        <f>IF(AND(BE$3&gt;=$D6,BE$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D6,BE$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BF6" s="1">
-        <f>IF(AND(BF$3&gt;=$D6,BF$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D6,BF$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BG6" s="1">
-        <f>IF(AND(BG$3&gt;=$D6,BG$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D6,BG$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BH6" s="1">
-        <f>IF(AND(BH$3&gt;=$D6,BH$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D6,BH$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BI6" s="1">
-        <f>IF(AND(BI$3&gt;=$D6,BI$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D6,BI$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BJ6" s="1">
-        <f>IF(AND(BJ$3&gt;=$D6,BJ$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D6,BJ$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BK6" s="1">
-        <f>IF(AND(BK$3&gt;=$D6,BK$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D6,BK$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BL6" s="1">
-        <f>IF(AND(BL$3&gt;=$D6,BL$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D6,BL$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BM6" s="1">
-        <f>IF(AND(BM$3&gt;=$D6,BM$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D6,BM$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BN6" s="1">
-        <f>IF(AND(BN$3&gt;=$D6,BN$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D6,BN$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BO6" s="1">
-        <f>IF(AND(BO$3&gt;=$D6,BO$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D6,BO$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BP6" s="1">
-        <f>IF(AND(BP$3&gt;=$D6,BP$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D6,BP$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BQ6" s="1">
-        <f>IF(AND(BQ$3&gt;=$D6,BQ$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D6,BQ$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BR6" s="1">
-        <f>IF(AND(BR$3&gt;=$D6,BR$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D6,BR$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BS6" s="1">
-        <f>IF(AND(BS$3&gt;=$D6,BS$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D6,BS$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BT6" s="1">
-        <f>IF(AND(BT$3&gt;=$D6,BT$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D6,BT$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BU6" s="1">
-        <f>IF(AND(BU$3&gt;=$D6,BU$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D6,BU$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BV6" s="1">
-        <f>IF(AND(BV$3&gt;=$D6,BV$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D6,BV$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BW6" s="1">
-        <f>IF(AND(BW$3&gt;=$D6,BW$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D6,BW$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BX6" s="1">
-        <f>IF(AND(BX$3&gt;=$D6,BX$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D6,BX$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BY6" s="1">
-        <f>IF(AND(BY$3&gt;=$D6,BY$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D6,BY$1&lt;=$E6),"█","")</f>
       </c>
       <c r="BZ6" s="1">
-        <f>IF(AND(BZ$3&gt;=$D6,BZ$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D6,BZ$1&lt;=$E6),"█","")</f>
       </c>
       <c r="CA6" s="1">
-        <f>IF(AND(CA$3&gt;=$D6,CA$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D6,CA$1&lt;=$E6),"█","")</f>
       </c>
       <c r="CB6" s="1">
-        <f>IF(AND(CB$3&gt;=$D6,CB$3&lt;=$E6),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D6,CB$1&lt;=$E6),"█","")</f>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.3">
@@ -1860,233 +2009,234 @@
       </c>
       <c r="D7" s="7">
         <f>E6+1</f>
-        <v>46230</v>
-      </c>
-      <c r="E7" s="1"/>
+      </c>
+      <c r="E7" s="7">
+        <f>D7+C7</f>
+      </c>
       <c r="F7" s="1">
-        <f>IF(AND(F$3&gt;=$D7,F$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D7,F$1&lt;=$E7),"█","")</f>
       </c>
       <c r="G7" s="1">
-        <f>IF(AND(G$3&gt;=$D7,G$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D7,G$1&lt;=$E7),"█","")</f>
       </c>
       <c r="H7" s="1">
-        <f>IF(AND(H$3&gt;=$D7,H$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D7,H$1&lt;=$E7),"█","")</f>
       </c>
       <c r="I7" s="1">
-        <f>IF(AND(I$3&gt;=$D7,I$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D7,I$1&lt;=$E7),"█","")</f>
       </c>
       <c r="J7" s="1">
-        <f>IF(AND(J$3&gt;=$D7,J$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D7,J$1&lt;=$E7),"█","")</f>
       </c>
       <c r="K7" s="1">
-        <f>IF(AND(K$3&gt;=$D7,K$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D7,K$1&lt;=$E7),"█","")</f>
       </c>
       <c r="L7" s="1">
-        <f>IF(AND(L$3&gt;=$D7,L$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D7,L$1&lt;=$E7),"█","")</f>
       </c>
       <c r="M7" s="1">
-        <f>IF(AND(M$3&gt;=$D7,M$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D7,M$1&lt;=$E7),"█","")</f>
       </c>
       <c r="N7" s="1">
-        <f>IF(AND(N$3&gt;=$D7,N$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D7,N$1&lt;=$E7),"█","")</f>
       </c>
       <c r="O7" s="1">
-        <f>IF(AND(O$3&gt;=$D7,O$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D7,O$1&lt;=$E7),"█","")</f>
       </c>
       <c r="P7" s="1">
-        <f>IF(AND(P$3&gt;=$D7,P$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D7,P$1&lt;=$E7),"█","")</f>
       </c>
       <c r="Q7" s="1">
-        <f>IF(AND(Q$3&gt;=$D7,Q$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D7,Q$1&lt;=$E7),"█","")</f>
       </c>
       <c r="R7" s="1">
-        <f>IF(AND(R$3&gt;=$D7,R$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D7,R$1&lt;=$E7),"█","")</f>
       </c>
       <c r="S7" s="1">
-        <f>IF(AND(S$3&gt;=$D7,S$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D7,S$1&lt;=$E7),"█","")</f>
       </c>
       <c r="T7" s="1">
-        <f>IF(AND(T$3&gt;=$D7,T$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D7,T$1&lt;=$E7),"█","")</f>
       </c>
       <c r="U7" s="1">
-        <f>IF(AND(U$3&gt;=$D7,U$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D7,U$1&lt;=$E7),"█","")</f>
       </c>
       <c r="V7" s="1">
-        <f>IF(AND(V$3&gt;=$D7,V$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D7,V$1&lt;=$E7),"█","")</f>
       </c>
       <c r="W7" s="1">
-        <f>IF(AND(W$3&gt;=$D7,W$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D7,W$1&lt;=$E7),"█","")</f>
       </c>
       <c r="X7" s="1">
-        <f>IF(AND(X$3&gt;=$D7,X$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D7,X$1&lt;=$E7),"█","")</f>
       </c>
       <c r="Y7" s="1">
-        <f>IF(AND(Y$3&gt;=$D7,Y$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D7,Y$1&lt;=$E7),"█","")</f>
       </c>
       <c r="Z7" s="1">
-        <f>IF(AND(Z$3&gt;=$D7,Z$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D7,Z$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AA7" s="1">
-        <f>IF(AND(AA$3&gt;=$D7,AA$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D7,AA$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AB7" s="1">
-        <f>IF(AND(AB$3&gt;=$D7,AB$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D7,AB$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AC7" s="1">
-        <f>IF(AND(AC$3&gt;=$D7,AC$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D7,AC$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AD7" s="1">
-        <f>IF(AND(AD$3&gt;=$D7,AD$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D7,AD$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AE7" s="1">
-        <f>IF(AND(AE$3&gt;=$D7,AE$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D7,AE$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AF7" s="1">
-        <f>IF(AND(AF$3&gt;=$D7,AF$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D7,AF$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AG7" s="1">
-        <f>IF(AND(AG$3&gt;=$D7,AG$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D7,AG$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AH7" s="1">
-        <f>IF(AND(AH$3&gt;=$D7,AH$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D7,AH$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AI7" s="1">
-        <f>IF(AND(AI$3&gt;=$D7,AI$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D7,AI$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AJ7" s="1">
-        <f>IF(AND(AJ$3&gt;=$D7,AJ$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D7,AJ$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AK7" s="1">
-        <f>IF(AND(AK$3&gt;=$D7,AK$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D7,AK$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AL7" s="1">
-        <f>IF(AND(AL$3&gt;=$D7,AL$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D7,AL$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AM7" s="1">
-        <f>IF(AND(AM$3&gt;=$D7,AM$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D7,AM$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AN7" s="1">
-        <f>IF(AND(AN$3&gt;=$D7,AN$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D7,AN$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AO7" s="1">
-        <f>IF(AND(AO$3&gt;=$D7,AO$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D7,AO$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AP7" s="1">
-        <f>IF(AND(AP$3&gt;=$D7,AP$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D7,AP$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AQ7" s="1">
-        <f>IF(AND(AQ$3&gt;=$D7,AQ$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D7,AQ$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AR7" s="1">
-        <f>IF(AND(AR$3&gt;=$D7,AR$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D7,AR$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AS7" s="1">
-        <f>IF(AND(AS$3&gt;=$D7,AS$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D7,AS$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AT7" s="1">
-        <f>IF(AND(AT$3&gt;=$D7,AT$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D7,AT$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AU7" s="1">
-        <f>IF(AND(AU$3&gt;=$D7,AU$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D7,AU$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AV7" s="1">
-        <f>IF(AND(AV$3&gt;=$D7,AV$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D7,AV$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AW7" s="1">
-        <f>IF(AND(AW$3&gt;=$D7,AW$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D7,AW$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AX7" s="1">
-        <f>IF(AND(AX$3&gt;=$D7,AX$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D7,AX$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AY7" s="1">
-        <f>IF(AND(AY$3&gt;=$D7,AY$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D7,AY$1&lt;=$E7),"█","")</f>
       </c>
       <c r="AZ7" s="1">
-        <f>IF(AND(AZ$3&gt;=$D7,AZ$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D7,AZ$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BA7" s="1">
-        <f>IF(AND(BA$3&gt;=$D7,BA$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D7,BA$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BB7" s="1">
-        <f>IF(AND(BB$3&gt;=$D7,BB$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D7,BB$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BC7" s="1">
-        <f>IF(AND(BC$3&gt;=$D7,BC$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D7,BC$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BD7" s="1">
-        <f>IF(AND(BD$3&gt;=$D7,BD$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D7,BD$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BE7" s="1">
-        <f>IF(AND(BE$3&gt;=$D7,BE$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D7,BE$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BF7" s="1">
-        <f>IF(AND(BF$3&gt;=$D7,BF$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D7,BF$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BG7" s="1">
-        <f>IF(AND(BG$3&gt;=$D7,BG$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D7,BG$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BH7" s="1">
-        <f>IF(AND(BH$3&gt;=$D7,BH$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D7,BH$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BI7" s="1">
-        <f>IF(AND(BI$3&gt;=$D7,BI$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D7,BI$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BJ7" s="1">
-        <f>IF(AND(BJ$3&gt;=$D7,BJ$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D7,BJ$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BK7" s="1">
-        <f>IF(AND(BK$3&gt;=$D7,BK$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D7,BK$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BL7" s="1">
-        <f>IF(AND(BL$3&gt;=$D7,BL$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D7,BL$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BM7" s="1">
-        <f>IF(AND(BM$3&gt;=$D7,BM$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D7,BM$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BN7" s="1">
-        <f>IF(AND(BN$3&gt;=$D7,BN$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D7,BN$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BO7" s="1">
-        <f>IF(AND(BO$3&gt;=$D7,BO$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D7,BO$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BP7" s="1">
-        <f>IF(AND(BP$3&gt;=$D7,BP$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D7,BP$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BQ7" s="1">
-        <f>IF(AND(BQ$3&gt;=$D7,BQ$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D7,BQ$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BR7" s="1">
-        <f>IF(AND(BR$3&gt;=$D7,BR$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D7,BR$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BS7" s="1">
-        <f>IF(AND(BS$3&gt;=$D7,BS$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D7,BS$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BT7" s="1">
-        <f>IF(AND(BT$3&gt;=$D7,BT$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D7,BT$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BU7" s="1">
-        <f>IF(AND(BU$3&gt;=$D7,BU$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D7,BU$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BV7" s="1">
-        <f>IF(AND(BV$3&gt;=$D7,BV$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D7,BV$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BW7" s="1">
-        <f>IF(AND(BW$3&gt;=$D7,BW$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D7,BW$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BX7" s="1">
-        <f>IF(AND(BX$3&gt;=$D7,BX$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D7,BX$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BY7" s="1">
-        <f>IF(AND(BY$3&gt;=$D7,BY$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D7,BY$1&lt;=$E7),"█","")</f>
       </c>
       <c r="BZ7" s="1">
-        <f>IF(AND(BZ$3&gt;=$D7,BZ$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D7,BZ$1&lt;=$E7),"█","")</f>
       </c>
       <c r="CA7" s="1">
-        <f>IF(AND(CA$3&gt;=$D7,CA$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D7,CA$1&lt;=$E7),"█","")</f>
       </c>
       <c r="CB7" s="1">
-        <f>IF(AND(CB$3&gt;=$D7,CB$3&lt;=$E7),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D7,CB$1&lt;=$E7),"█","")</f>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.3">
@@ -2101,233 +2251,234 @@
       </c>
       <c r="D8" s="7">
         <f>E7+1</f>
-        <v>46233</v>
-      </c>
-      <c r="E8" s="1"/>
+      </c>
+      <c r="E8" s="7">
+        <f>D8+C8</f>
+      </c>
       <c r="F8" s="1">
-        <f>IF(AND(F$3&gt;=$D8,F$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D8,F$1&lt;=$E8),"█","")</f>
       </c>
       <c r="G8" s="1">
-        <f>IF(AND(G$3&gt;=$D8,G$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D8,G$1&lt;=$E8),"█","")</f>
       </c>
       <c r="H8" s="1">
-        <f>IF(AND(H$3&gt;=$D8,H$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D8,H$1&lt;=$E8),"█","")</f>
       </c>
       <c r="I8" s="1">
-        <f>IF(AND(I$3&gt;=$D8,I$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D8,I$1&lt;=$E8),"█","")</f>
       </c>
       <c r="J8" s="1">
-        <f>IF(AND(J$3&gt;=$D8,J$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D8,J$1&lt;=$E8),"█","")</f>
       </c>
       <c r="K8" s="1">
-        <f>IF(AND(K$3&gt;=$D8,K$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D8,K$1&lt;=$E8),"█","")</f>
       </c>
       <c r="L8" s="1">
-        <f>IF(AND(L$3&gt;=$D8,L$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D8,L$1&lt;=$E8),"█","")</f>
       </c>
       <c r="M8" s="1">
-        <f>IF(AND(M$3&gt;=$D8,M$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D8,M$1&lt;=$E8),"█","")</f>
       </c>
       <c r="N8" s="1">
-        <f>IF(AND(N$3&gt;=$D8,N$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D8,N$1&lt;=$E8),"█","")</f>
       </c>
       <c r="O8" s="1">
-        <f>IF(AND(O$3&gt;=$D8,O$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D8,O$1&lt;=$E8),"█","")</f>
       </c>
       <c r="P8" s="1">
-        <f>IF(AND(P$3&gt;=$D8,P$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D8,P$1&lt;=$E8),"█","")</f>
       </c>
       <c r="Q8" s="1">
-        <f>IF(AND(Q$3&gt;=$D8,Q$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D8,Q$1&lt;=$E8),"█","")</f>
       </c>
       <c r="R8" s="1">
-        <f>IF(AND(R$3&gt;=$D8,R$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D8,R$1&lt;=$E8),"█","")</f>
       </c>
       <c r="S8" s="1">
-        <f>IF(AND(S$3&gt;=$D8,S$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D8,S$1&lt;=$E8),"█","")</f>
       </c>
       <c r="T8" s="1">
-        <f>IF(AND(T$3&gt;=$D8,T$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D8,T$1&lt;=$E8),"█","")</f>
       </c>
       <c r="U8" s="1">
-        <f>IF(AND(U$3&gt;=$D8,U$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D8,U$1&lt;=$E8),"█","")</f>
       </c>
       <c r="V8" s="1">
-        <f>IF(AND(V$3&gt;=$D8,V$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D8,V$1&lt;=$E8),"█","")</f>
       </c>
       <c r="W8" s="1">
-        <f>IF(AND(W$3&gt;=$D8,W$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D8,W$1&lt;=$E8),"█","")</f>
       </c>
       <c r="X8" s="1">
-        <f>IF(AND(X$3&gt;=$D8,X$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D8,X$1&lt;=$E8),"█","")</f>
       </c>
       <c r="Y8" s="1">
-        <f>IF(AND(Y$3&gt;=$D8,Y$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D8,Y$1&lt;=$E8),"█","")</f>
       </c>
       <c r="Z8" s="1">
-        <f>IF(AND(Z$3&gt;=$D8,Z$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D8,Z$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AA8" s="1">
-        <f>IF(AND(AA$3&gt;=$D8,AA$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D8,AA$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AB8" s="1">
-        <f>IF(AND(AB$3&gt;=$D8,AB$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D8,AB$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AC8" s="1">
-        <f>IF(AND(AC$3&gt;=$D8,AC$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D8,AC$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AD8" s="1">
-        <f>IF(AND(AD$3&gt;=$D8,AD$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D8,AD$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AE8" s="1">
-        <f>IF(AND(AE$3&gt;=$D8,AE$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D8,AE$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AF8" s="1">
-        <f>IF(AND(AF$3&gt;=$D8,AF$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D8,AF$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AG8" s="1">
-        <f>IF(AND(AG$3&gt;=$D8,AG$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D8,AG$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AH8" s="1">
-        <f>IF(AND(AH$3&gt;=$D8,AH$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D8,AH$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AI8" s="1">
-        <f>IF(AND(AI$3&gt;=$D8,AI$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D8,AI$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AJ8" s="1">
-        <f>IF(AND(AJ$3&gt;=$D8,AJ$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D8,AJ$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AK8" s="1">
-        <f>IF(AND(AK$3&gt;=$D8,AK$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D8,AK$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AL8" s="1">
-        <f>IF(AND(AL$3&gt;=$D8,AL$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D8,AL$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AM8" s="1">
-        <f>IF(AND(AM$3&gt;=$D8,AM$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D8,AM$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AN8" s="1">
-        <f>IF(AND(AN$3&gt;=$D8,AN$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D8,AN$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AO8" s="1">
-        <f>IF(AND(AO$3&gt;=$D8,AO$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D8,AO$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AP8" s="1">
-        <f>IF(AND(AP$3&gt;=$D8,AP$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D8,AP$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AQ8" s="1">
-        <f>IF(AND(AQ$3&gt;=$D8,AQ$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D8,AQ$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AR8" s="1">
-        <f>IF(AND(AR$3&gt;=$D8,AR$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D8,AR$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AS8" s="1">
-        <f>IF(AND(AS$3&gt;=$D8,AS$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D8,AS$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AT8" s="1">
-        <f>IF(AND(AT$3&gt;=$D8,AT$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D8,AT$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AU8" s="1">
-        <f>IF(AND(AU$3&gt;=$D8,AU$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D8,AU$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AV8" s="1">
-        <f>IF(AND(AV$3&gt;=$D8,AV$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D8,AV$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AW8" s="1">
-        <f>IF(AND(AW$3&gt;=$D8,AW$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D8,AW$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AX8" s="1">
-        <f>IF(AND(AX$3&gt;=$D8,AX$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D8,AX$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AY8" s="1">
-        <f>IF(AND(AY$3&gt;=$D8,AY$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D8,AY$1&lt;=$E8),"█","")</f>
       </c>
       <c r="AZ8" s="1">
-        <f>IF(AND(AZ$3&gt;=$D8,AZ$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D8,AZ$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BA8" s="1">
-        <f>IF(AND(BA$3&gt;=$D8,BA$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D8,BA$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BB8" s="1">
-        <f>IF(AND(BB$3&gt;=$D8,BB$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D8,BB$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BC8" s="1">
-        <f>IF(AND(BC$3&gt;=$D8,BC$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D8,BC$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BD8" s="1">
-        <f>IF(AND(BD$3&gt;=$D8,BD$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D8,BD$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BE8" s="1">
-        <f>IF(AND(BE$3&gt;=$D8,BE$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D8,BE$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BF8" s="1">
-        <f>IF(AND(BF$3&gt;=$D8,BF$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D8,BF$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BG8" s="1">
-        <f>IF(AND(BG$3&gt;=$D8,BG$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D8,BG$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BH8" s="1">
-        <f>IF(AND(BH$3&gt;=$D8,BH$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D8,BH$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BI8" s="1">
-        <f>IF(AND(BI$3&gt;=$D8,BI$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D8,BI$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BJ8" s="1">
-        <f>IF(AND(BJ$3&gt;=$D8,BJ$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D8,BJ$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BK8" s="1">
-        <f>IF(AND(BK$3&gt;=$D8,BK$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D8,BK$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BL8" s="1">
-        <f>IF(AND(BL$3&gt;=$D8,BL$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D8,BL$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BM8" s="1">
-        <f>IF(AND(BM$3&gt;=$D8,BM$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D8,BM$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BN8" s="1">
-        <f>IF(AND(BN$3&gt;=$D8,BN$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D8,BN$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BO8" s="1">
-        <f>IF(AND(BO$3&gt;=$D8,BO$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D8,BO$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BP8" s="1">
-        <f>IF(AND(BP$3&gt;=$D8,BP$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D8,BP$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BQ8" s="1">
-        <f>IF(AND(BQ$3&gt;=$D8,BQ$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D8,BQ$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BR8" s="1">
-        <f>IF(AND(BR$3&gt;=$D8,BR$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D8,BR$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BS8" s="1">
-        <f>IF(AND(BS$3&gt;=$D8,BS$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D8,BS$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BT8" s="1">
-        <f>IF(AND(BT$3&gt;=$D8,BT$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D8,BT$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BU8" s="1">
-        <f>IF(AND(BU$3&gt;=$D8,BU$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D8,BU$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BV8" s="1">
-        <f>IF(AND(BV$3&gt;=$D8,BV$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D8,BV$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BW8" s="1">
-        <f>IF(AND(BW$3&gt;=$D8,BW$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D8,BW$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BX8" s="1">
-        <f>IF(AND(BX$3&gt;=$D8,BX$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D8,BX$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BY8" s="1">
-        <f>IF(AND(BY$3&gt;=$D8,BY$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D8,BY$1&lt;=$E8),"█","")</f>
       </c>
       <c r="BZ8" s="1">
-        <f>IF(AND(BZ$3&gt;=$D8,BZ$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D8,BZ$1&lt;=$E8),"█","")</f>
       </c>
       <c r="CA8" s="1">
-        <f>IF(AND(CA$3&gt;=$D8,CA$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D8,CA$1&lt;=$E8),"█","")</f>
       </c>
       <c r="CB8" s="1">
-        <f>IF(AND(CB$3&gt;=$D8,CB$3&lt;=$E8),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D8,CB$1&lt;=$E8),"█","")</f>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.3">
@@ -2342,233 +2493,234 @@
       </c>
       <c r="D9" s="7">
         <f>D7</f>
-        <v>46230</v>
-      </c>
-      <c r="E9" s="1"/>
+      </c>
+      <c r="E9" s="7">
+        <f>D9+C9</f>
+      </c>
       <c r="F9" s="1">
-        <f>IF(AND(F$3&gt;=$D9,F$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D9,F$1&lt;=$E9),"█","")</f>
       </c>
       <c r="G9" s="1">
-        <f>IF(AND(G$3&gt;=$D9,G$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D9,G$1&lt;=$E9),"█","")</f>
       </c>
       <c r="H9" s="1">
-        <f>IF(AND(H$3&gt;=$D9,H$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D9,H$1&lt;=$E9),"█","")</f>
       </c>
       <c r="I9" s="1">
-        <f>IF(AND(I$3&gt;=$D9,I$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D9,I$1&lt;=$E9),"█","")</f>
       </c>
       <c r="J9" s="1">
-        <f>IF(AND(J$3&gt;=$D9,J$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D9,J$1&lt;=$E9),"█","")</f>
       </c>
       <c r="K9" s="1">
-        <f>IF(AND(K$3&gt;=$D9,K$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D9,K$1&lt;=$E9),"█","")</f>
       </c>
       <c r="L9" s="1">
-        <f>IF(AND(L$3&gt;=$D9,L$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D9,L$1&lt;=$E9),"█","")</f>
       </c>
       <c r="M9" s="1">
-        <f>IF(AND(M$3&gt;=$D9,M$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D9,M$1&lt;=$E9),"█","")</f>
       </c>
       <c r="N9" s="1">
-        <f>IF(AND(N$3&gt;=$D9,N$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D9,N$1&lt;=$E9),"█","")</f>
       </c>
       <c r="O9" s="1">
-        <f>IF(AND(O$3&gt;=$D9,O$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D9,O$1&lt;=$E9),"█","")</f>
       </c>
       <c r="P9" s="1">
-        <f>IF(AND(P$3&gt;=$D9,P$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D9,P$1&lt;=$E9),"█","")</f>
       </c>
       <c r="Q9" s="1">
-        <f>IF(AND(Q$3&gt;=$D9,Q$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D9,Q$1&lt;=$E9),"█","")</f>
       </c>
       <c r="R9" s="1">
-        <f>IF(AND(R$3&gt;=$D9,R$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D9,R$1&lt;=$E9),"█","")</f>
       </c>
       <c r="S9" s="1">
-        <f>IF(AND(S$3&gt;=$D9,S$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D9,S$1&lt;=$E9),"█","")</f>
       </c>
       <c r="T9" s="1">
-        <f>IF(AND(T$3&gt;=$D9,T$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D9,T$1&lt;=$E9),"█","")</f>
       </c>
       <c r="U9" s="1">
-        <f>IF(AND(U$3&gt;=$D9,U$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D9,U$1&lt;=$E9),"█","")</f>
       </c>
       <c r="V9" s="1">
-        <f>IF(AND(V$3&gt;=$D9,V$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D9,V$1&lt;=$E9),"█","")</f>
       </c>
       <c r="W9" s="1">
-        <f>IF(AND(W$3&gt;=$D9,W$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D9,W$1&lt;=$E9),"█","")</f>
       </c>
       <c r="X9" s="1">
-        <f>IF(AND(X$3&gt;=$D9,X$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D9,X$1&lt;=$E9),"█","")</f>
       </c>
       <c r="Y9" s="1">
-        <f>IF(AND(Y$3&gt;=$D9,Y$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D9,Y$1&lt;=$E9),"█","")</f>
       </c>
       <c r="Z9" s="1">
-        <f>IF(AND(Z$3&gt;=$D9,Z$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D9,Z$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AA9" s="1">
-        <f>IF(AND(AA$3&gt;=$D9,AA$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D9,AA$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AB9" s="1">
-        <f>IF(AND(AB$3&gt;=$D9,AB$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D9,AB$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AC9" s="1">
-        <f>IF(AND(AC$3&gt;=$D9,AC$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D9,AC$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AD9" s="1">
-        <f>IF(AND(AD$3&gt;=$D9,AD$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D9,AD$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AE9" s="1">
-        <f>IF(AND(AE$3&gt;=$D9,AE$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D9,AE$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AF9" s="1">
-        <f>IF(AND(AF$3&gt;=$D9,AF$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D9,AF$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AG9" s="1">
-        <f>IF(AND(AG$3&gt;=$D9,AG$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D9,AG$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AH9" s="1">
-        <f>IF(AND(AH$3&gt;=$D9,AH$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D9,AH$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AI9" s="1">
-        <f>IF(AND(AI$3&gt;=$D9,AI$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D9,AI$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AJ9" s="1">
-        <f>IF(AND(AJ$3&gt;=$D9,AJ$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D9,AJ$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AK9" s="1">
-        <f>IF(AND(AK$3&gt;=$D9,AK$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D9,AK$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AL9" s="1">
-        <f>IF(AND(AL$3&gt;=$D9,AL$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D9,AL$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AM9" s="1">
-        <f>IF(AND(AM$3&gt;=$D9,AM$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D9,AM$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AN9" s="1">
-        <f>IF(AND(AN$3&gt;=$D9,AN$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D9,AN$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AO9" s="1">
-        <f>IF(AND(AO$3&gt;=$D9,AO$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D9,AO$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AP9" s="1">
-        <f>IF(AND(AP$3&gt;=$D9,AP$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D9,AP$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AQ9" s="1">
-        <f>IF(AND(AQ$3&gt;=$D9,AQ$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D9,AQ$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AR9" s="1">
-        <f>IF(AND(AR$3&gt;=$D9,AR$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D9,AR$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AS9" s="1">
-        <f>IF(AND(AS$3&gt;=$D9,AS$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D9,AS$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AT9" s="1">
-        <f>IF(AND(AT$3&gt;=$D9,AT$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D9,AT$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AU9" s="1">
-        <f>IF(AND(AU$3&gt;=$D9,AU$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D9,AU$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AV9" s="1">
-        <f>IF(AND(AV$3&gt;=$D9,AV$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D9,AV$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AW9" s="1">
-        <f>IF(AND(AW$3&gt;=$D9,AW$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D9,AW$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AX9" s="1">
-        <f>IF(AND(AX$3&gt;=$D9,AX$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D9,AX$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AY9" s="1">
-        <f>IF(AND(AY$3&gt;=$D9,AY$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D9,AY$1&lt;=$E9),"█","")</f>
       </c>
       <c r="AZ9" s="1">
-        <f>IF(AND(AZ$3&gt;=$D9,AZ$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D9,AZ$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BA9" s="1">
-        <f>IF(AND(BA$3&gt;=$D9,BA$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D9,BA$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BB9" s="1">
-        <f>IF(AND(BB$3&gt;=$D9,BB$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D9,BB$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BC9" s="1">
-        <f>IF(AND(BC$3&gt;=$D9,BC$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D9,BC$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BD9" s="1">
-        <f>IF(AND(BD$3&gt;=$D9,BD$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D9,BD$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BE9" s="1">
-        <f>IF(AND(BE$3&gt;=$D9,BE$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D9,BE$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BF9" s="1">
-        <f>IF(AND(BF$3&gt;=$D9,BF$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D9,BF$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BG9" s="1">
-        <f>IF(AND(BG$3&gt;=$D9,BG$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D9,BG$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BH9" s="1">
-        <f>IF(AND(BH$3&gt;=$D9,BH$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D9,BH$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BI9" s="1">
-        <f>IF(AND(BI$3&gt;=$D9,BI$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D9,BI$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BJ9" s="1">
-        <f>IF(AND(BJ$3&gt;=$D9,BJ$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D9,BJ$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BK9" s="1">
-        <f>IF(AND(BK$3&gt;=$D9,BK$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D9,BK$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BL9" s="1">
-        <f>IF(AND(BL$3&gt;=$D9,BL$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D9,BL$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BM9" s="1">
-        <f>IF(AND(BM$3&gt;=$D9,BM$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D9,BM$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BN9" s="1">
-        <f>IF(AND(BN$3&gt;=$D9,BN$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D9,BN$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BO9" s="1">
-        <f>IF(AND(BO$3&gt;=$D9,BO$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D9,BO$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BP9" s="1">
-        <f>IF(AND(BP$3&gt;=$D9,BP$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D9,BP$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BQ9" s="1">
-        <f>IF(AND(BQ$3&gt;=$D9,BQ$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D9,BQ$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BR9" s="1">
-        <f>IF(AND(BR$3&gt;=$D9,BR$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D9,BR$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BS9" s="1">
-        <f>IF(AND(BS$3&gt;=$D9,BS$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D9,BS$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BT9" s="1">
-        <f>IF(AND(BT$3&gt;=$D9,BT$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D9,BT$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BU9" s="1">
-        <f>IF(AND(BU$3&gt;=$D9,BU$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D9,BU$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BV9" s="1">
-        <f>IF(AND(BV$3&gt;=$D9,BV$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D9,BV$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BW9" s="1">
-        <f>IF(AND(BW$3&gt;=$D9,BW$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D9,BW$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BX9" s="1">
-        <f>IF(AND(BX$3&gt;=$D9,BX$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D9,BX$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BY9" s="1">
-        <f>IF(AND(BY$3&gt;=$D9,BY$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D9,BY$1&lt;=$E9),"█","")</f>
       </c>
       <c r="BZ9" s="1">
-        <f>IF(AND(BZ$3&gt;=$D9,BZ$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D9,BZ$1&lt;=$E9),"█","")</f>
       </c>
       <c r="CA9" s="1">
-        <f>IF(AND(CA$3&gt;=$D9,CA$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D9,CA$1&lt;=$E9),"█","")</f>
       </c>
       <c r="CB9" s="1">
-        <f>IF(AND(CB$3&gt;=$D9,CB$3&lt;=$E9),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D9,CB$1&lt;=$E9),"█","")</f>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.3">
@@ -2591,229 +2743,229 @@
         <v>46219</v>
       </c>
       <c r="F10" s="1">
-        <f>IF(AND(F$3&gt;=$D10,F$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D10,F$1&lt;=$E10),"█","")</f>
       </c>
       <c r="G10" s="1">
-        <f>IF(AND(G$3&gt;=$D10,G$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D10,G$1&lt;=$E10),"█","")</f>
       </c>
       <c r="H10" s="1">
-        <f>IF(AND(H$3&gt;=$D10,H$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D10,H$1&lt;=$E10),"█","")</f>
       </c>
       <c r="I10" s="1">
-        <f>IF(AND(I$3&gt;=$D10,I$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D10,I$1&lt;=$E10),"█","")</f>
       </c>
       <c r="J10" s="1">
-        <f>IF(AND(J$3&gt;=$D10,J$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D10,J$1&lt;=$E10),"█","")</f>
       </c>
       <c r="K10" s="1">
-        <f>IF(AND(K$3&gt;=$D10,K$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D10,K$1&lt;=$E10),"█","")</f>
       </c>
       <c r="L10" s="1">
-        <f>IF(AND(L$3&gt;=$D10,L$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D10,L$1&lt;=$E10),"█","")</f>
       </c>
       <c r="M10" s="1">
-        <f>IF(AND(M$3&gt;=$D10,M$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D10,M$1&lt;=$E10),"█","")</f>
       </c>
       <c r="N10" s="1">
-        <f>IF(AND(N$3&gt;=$D10,N$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D10,N$1&lt;=$E10),"█","")</f>
       </c>
       <c r="O10" s="1">
-        <f>IF(AND(O$3&gt;=$D10,O$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D10,O$1&lt;=$E10),"█","")</f>
       </c>
       <c r="P10" s="1">
-        <f>IF(AND(P$3&gt;=$D10,P$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D10,P$1&lt;=$E10),"█","")</f>
       </c>
       <c r="Q10" s="1">
-        <f>IF(AND(Q$3&gt;=$D10,Q$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D10,Q$1&lt;=$E10),"█","")</f>
       </c>
       <c r="R10" s="1">
-        <f>IF(AND(R$3&gt;=$D10,R$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D10,R$1&lt;=$E10),"█","")</f>
       </c>
       <c r="S10" s="1">
-        <f>IF(AND(S$3&gt;=$D10,S$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D10,S$1&lt;=$E10),"█","")</f>
       </c>
       <c r="T10" s="1">
-        <f>IF(AND(T$3&gt;=$D10,T$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D10,T$1&lt;=$E10),"█","")</f>
       </c>
       <c r="U10" s="1">
-        <f>IF(AND(U$3&gt;=$D10,U$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D10,U$1&lt;=$E10),"█","")</f>
       </c>
       <c r="V10" s="1">
-        <f>IF(AND(V$3&gt;=$D10,V$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D10,V$1&lt;=$E10),"█","")</f>
       </c>
       <c r="W10" s="1">
-        <f>IF(AND(W$3&gt;=$D10,W$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D10,W$1&lt;=$E10),"█","")</f>
       </c>
       <c r="X10" s="1">
-        <f>IF(AND(X$3&gt;=$D10,X$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D10,X$1&lt;=$E10),"█","")</f>
       </c>
       <c r="Y10" s="1">
-        <f>IF(AND(Y$3&gt;=$D10,Y$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D10,Y$1&lt;=$E10),"█","")</f>
       </c>
       <c r="Z10" s="1">
-        <f>IF(AND(Z$3&gt;=$D10,Z$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D10,Z$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AA10" s="1">
-        <f>IF(AND(AA$3&gt;=$D10,AA$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D10,AA$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AB10" s="1">
-        <f>IF(AND(AB$3&gt;=$D10,AB$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D10,AB$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AC10" s="1">
-        <f>IF(AND(AC$3&gt;=$D10,AC$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D10,AC$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AD10" s="1">
-        <f>IF(AND(AD$3&gt;=$D10,AD$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D10,AD$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AE10" s="1">
-        <f>IF(AND(AE$3&gt;=$D10,AE$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D10,AE$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AF10" s="1">
-        <f>IF(AND(AF$3&gt;=$D10,AF$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D10,AF$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AG10" s="1">
-        <f>IF(AND(AG$3&gt;=$D10,AG$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D10,AG$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AH10" s="1">
-        <f>IF(AND(AH$3&gt;=$D10,AH$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D10,AH$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AI10" s="1">
-        <f>IF(AND(AI$3&gt;=$D10,AI$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D10,AI$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AJ10" s="1">
-        <f>IF(AND(AJ$3&gt;=$D10,AJ$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D10,AJ$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AK10" s="1">
-        <f>IF(AND(AK$3&gt;=$D10,AK$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D10,AK$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AL10" s="1">
-        <f>IF(AND(AL$3&gt;=$D10,AL$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D10,AL$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AM10" s="1">
-        <f>IF(AND(AM$3&gt;=$D10,AM$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D10,AM$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AN10" s="1">
-        <f>IF(AND(AN$3&gt;=$D10,AN$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D10,AN$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AO10" s="1">
-        <f>IF(AND(AO$3&gt;=$D10,AO$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D10,AO$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AP10" s="1">
-        <f>IF(AND(AP$3&gt;=$D10,AP$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D10,AP$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AQ10" s="1">
-        <f>IF(AND(AQ$3&gt;=$D10,AQ$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D10,AQ$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AR10" s="1">
-        <f>IF(AND(AR$3&gt;=$D10,AR$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D10,AR$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AS10" s="1">
-        <f>IF(AND(AS$3&gt;=$D10,AS$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D10,AS$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AT10" s="1">
-        <f>IF(AND(AT$3&gt;=$D10,AT$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D10,AT$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AU10" s="1">
-        <f>IF(AND(AU$3&gt;=$D10,AU$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D10,AU$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AV10" s="1">
-        <f>IF(AND(AV$3&gt;=$D10,AV$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D10,AV$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AW10" s="1">
-        <f>IF(AND(AW$3&gt;=$D10,AW$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D10,AW$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AX10" s="1">
-        <f>IF(AND(AX$3&gt;=$D10,AX$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D10,AX$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AY10" s="1">
-        <f>IF(AND(AY$3&gt;=$D10,AY$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D10,AY$1&lt;=$E10),"█","")</f>
       </c>
       <c r="AZ10" s="1">
-        <f>IF(AND(AZ$3&gt;=$D10,AZ$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D10,AZ$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BA10" s="1">
-        <f>IF(AND(BA$3&gt;=$D10,BA$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D10,BA$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BB10" s="1">
-        <f>IF(AND(BB$3&gt;=$D10,BB$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D10,BB$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BC10" s="1">
-        <f>IF(AND(BC$3&gt;=$D10,BC$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D10,BC$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BD10" s="1">
-        <f>IF(AND(BD$3&gt;=$D10,BD$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D10,BD$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BE10" s="1">
-        <f>IF(AND(BE$3&gt;=$D10,BE$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D10,BE$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BF10" s="1">
-        <f>IF(AND(BF$3&gt;=$D10,BF$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D10,BF$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BG10" s="1">
-        <f>IF(AND(BG$3&gt;=$D10,BG$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D10,BG$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BH10" s="1">
-        <f>IF(AND(BH$3&gt;=$D10,BH$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D10,BH$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BI10" s="1">
-        <f>IF(AND(BI$3&gt;=$D10,BI$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D10,BI$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BJ10" s="1">
-        <f>IF(AND(BJ$3&gt;=$D10,BJ$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D10,BJ$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BK10" s="1">
-        <f>IF(AND(BK$3&gt;=$D10,BK$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D10,BK$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BL10" s="1">
-        <f>IF(AND(BL$3&gt;=$D10,BL$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D10,BL$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BM10" s="1">
-        <f>IF(AND(BM$3&gt;=$D10,BM$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D10,BM$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BN10" s="1">
-        <f>IF(AND(BN$3&gt;=$D10,BN$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D10,BN$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BO10" s="1">
-        <f>IF(AND(BO$3&gt;=$D10,BO$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D10,BO$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BP10" s="1">
-        <f>IF(AND(BP$3&gt;=$D10,BP$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D10,BP$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BQ10" s="1">
-        <f>IF(AND(BQ$3&gt;=$D10,BQ$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D10,BQ$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BR10" s="1">
-        <f>IF(AND(BR$3&gt;=$D10,BR$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D10,BR$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BS10" s="1">
-        <f>IF(AND(BS$3&gt;=$D10,BS$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D10,BS$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BT10" s="1">
-        <f>IF(AND(BT$3&gt;=$D10,BT$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D10,BT$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BU10" s="1">
-        <f>IF(AND(BU$3&gt;=$D10,BU$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D10,BU$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BV10" s="1">
-        <f>IF(AND(BV$3&gt;=$D10,BV$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D10,BV$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BW10" s="1">
-        <f>IF(AND(BW$3&gt;=$D10,BW$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D10,BW$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BX10" s="1">
-        <f>IF(AND(BX$3&gt;=$D10,BX$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D10,BX$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BY10" s="1">
-        <f>IF(AND(BY$3&gt;=$D10,BY$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D10,BY$1&lt;=$E10),"█","")</f>
       </c>
       <c r="BZ10" s="1">
-        <f>IF(AND(BZ$3&gt;=$D10,BZ$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D10,BZ$1&lt;=$E10),"█","")</f>
       </c>
       <c r="CA10" s="1">
-        <f>IF(AND(CA$3&gt;=$D10,CA$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D10,CA$1&lt;=$E10),"█","")</f>
       </c>
       <c r="CB10" s="1">
-        <f>IF(AND(CB$3&gt;=$D10,CB$3&lt;=$E10),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D10,CB$1&lt;=$E10),"█","")</f>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.3">
@@ -2831,232 +2983,231 @@
       </c>
       <c r="E11" s="7">
         <f>D11+C11</f>
-        <v>46216</v>
       </c>
       <c r="F11" s="1">
-        <f>IF(AND(F$3&gt;=$D11,F$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D11,F$1&lt;=$E11),"█","")</f>
       </c>
       <c r="G11" s="1">
-        <f>IF(AND(G$3&gt;=$D11,G$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D11,G$1&lt;=$E11),"█","")</f>
       </c>
       <c r="H11" s="1">
-        <f>IF(AND(H$3&gt;=$D11,H$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D11,H$1&lt;=$E11),"█","")</f>
       </c>
       <c r="I11" s="1">
-        <f>IF(AND(I$3&gt;=$D11,I$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D11,I$1&lt;=$E11),"█","")</f>
       </c>
       <c r="J11" s="1">
-        <f>IF(AND(J$3&gt;=$D11,J$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D11,J$1&lt;=$E11),"█","")</f>
       </c>
       <c r="K11" s="1">
-        <f>IF(AND(K$3&gt;=$D11,K$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D11,K$1&lt;=$E11),"█","")</f>
       </c>
       <c r="L11" s="1">
-        <f>IF(AND(L$3&gt;=$D11,L$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D11,L$1&lt;=$E11),"█","")</f>
       </c>
       <c r="M11" s="1">
-        <f>IF(AND(M$3&gt;=$D11,M$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D11,M$1&lt;=$E11),"█","")</f>
       </c>
       <c r="N11" s="1">
-        <f>IF(AND(N$3&gt;=$D11,N$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D11,N$1&lt;=$E11),"█","")</f>
       </c>
       <c r="O11" s="1">
-        <f>IF(AND(O$3&gt;=$D11,O$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D11,O$1&lt;=$E11),"█","")</f>
       </c>
       <c r="P11" s="1">
-        <f>IF(AND(P$3&gt;=$D11,P$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D11,P$1&lt;=$E11),"█","")</f>
       </c>
       <c r="Q11" s="1">
-        <f>IF(AND(Q$3&gt;=$D11,Q$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D11,Q$1&lt;=$E11),"█","")</f>
       </c>
       <c r="R11" s="1">
-        <f>IF(AND(R$3&gt;=$D11,R$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D11,R$1&lt;=$E11),"█","")</f>
       </c>
       <c r="S11" s="1">
-        <f>IF(AND(S$3&gt;=$D11,S$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D11,S$1&lt;=$E11),"█","")</f>
       </c>
       <c r="T11" s="1">
-        <f>IF(AND(T$3&gt;=$D11,T$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D11,T$1&lt;=$E11),"█","")</f>
       </c>
       <c r="U11" s="1">
-        <f>IF(AND(U$3&gt;=$D11,U$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D11,U$1&lt;=$E11),"█","")</f>
       </c>
       <c r="V11" s="1">
-        <f>IF(AND(V$3&gt;=$D11,V$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D11,V$1&lt;=$E11),"█","")</f>
       </c>
       <c r="W11" s="1">
-        <f>IF(AND(W$3&gt;=$D11,W$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D11,W$1&lt;=$E11),"█","")</f>
       </c>
       <c r="X11" s="1">
-        <f>IF(AND(X$3&gt;=$D11,X$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D11,X$1&lt;=$E11),"█","")</f>
       </c>
       <c r="Y11" s="1">
-        <f>IF(AND(Y$3&gt;=$D11,Y$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D11,Y$1&lt;=$E11),"█","")</f>
       </c>
       <c r="Z11" s="1">
-        <f>IF(AND(Z$3&gt;=$D11,Z$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D11,Z$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AA11" s="1">
-        <f>IF(AND(AA$3&gt;=$D11,AA$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D11,AA$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AB11" s="1">
-        <f>IF(AND(AB$3&gt;=$D11,AB$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D11,AB$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AC11" s="1">
-        <f>IF(AND(AC$3&gt;=$D11,AC$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D11,AC$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AD11" s="1">
-        <f>IF(AND(AD$3&gt;=$D11,AD$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D11,AD$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AE11" s="1">
-        <f>IF(AND(AE$3&gt;=$D11,AE$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D11,AE$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AF11" s="1">
-        <f>IF(AND(AF$3&gt;=$D11,AF$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D11,AF$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AG11" s="1">
-        <f>IF(AND(AG$3&gt;=$D11,AG$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D11,AG$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AH11" s="1">
-        <f>IF(AND(AH$3&gt;=$D11,AH$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D11,AH$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AI11" s="1">
-        <f>IF(AND(AI$3&gt;=$D11,AI$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D11,AI$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AJ11" s="1">
-        <f>IF(AND(AJ$3&gt;=$D11,AJ$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D11,AJ$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AK11" s="1">
-        <f>IF(AND(AK$3&gt;=$D11,AK$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D11,AK$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AL11" s="1">
-        <f>IF(AND(AL$3&gt;=$D11,AL$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D11,AL$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AM11" s="1">
-        <f>IF(AND(AM$3&gt;=$D11,AM$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D11,AM$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AN11" s="1">
-        <f>IF(AND(AN$3&gt;=$D11,AN$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D11,AN$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AO11" s="1">
-        <f>IF(AND(AO$3&gt;=$D11,AO$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D11,AO$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AP11" s="1">
-        <f>IF(AND(AP$3&gt;=$D11,AP$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D11,AP$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AQ11" s="1">
-        <f>IF(AND(AQ$3&gt;=$D11,AQ$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D11,AQ$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AR11" s="1">
-        <f>IF(AND(AR$3&gt;=$D11,AR$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D11,AR$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AS11" s="1">
-        <f>IF(AND(AS$3&gt;=$D11,AS$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D11,AS$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AT11" s="1">
-        <f>IF(AND(AT$3&gt;=$D11,AT$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D11,AT$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AU11" s="1">
-        <f>IF(AND(AU$3&gt;=$D11,AU$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D11,AU$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AV11" s="1">
-        <f>IF(AND(AV$3&gt;=$D11,AV$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D11,AV$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AW11" s="1">
-        <f>IF(AND(AW$3&gt;=$D11,AW$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D11,AW$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AX11" s="1">
-        <f>IF(AND(AX$3&gt;=$D11,AX$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D11,AX$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AY11" s="1">
-        <f>IF(AND(AY$3&gt;=$D11,AY$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D11,AY$1&lt;=$E11),"█","")</f>
       </c>
       <c r="AZ11" s="1">
-        <f>IF(AND(AZ$3&gt;=$D11,AZ$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D11,AZ$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BA11" s="1">
-        <f>IF(AND(BA$3&gt;=$D11,BA$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D11,BA$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BB11" s="1">
-        <f>IF(AND(BB$3&gt;=$D11,BB$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D11,BB$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BC11" s="1">
-        <f>IF(AND(BC$3&gt;=$D11,BC$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D11,BC$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BD11" s="1">
-        <f>IF(AND(BD$3&gt;=$D11,BD$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D11,BD$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BE11" s="1">
-        <f>IF(AND(BE$3&gt;=$D11,BE$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D11,BE$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BF11" s="1">
-        <f>IF(AND(BF$3&gt;=$D11,BF$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D11,BF$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BG11" s="1">
-        <f>IF(AND(BG$3&gt;=$D11,BG$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D11,BG$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BH11" s="1">
-        <f>IF(AND(BH$3&gt;=$D11,BH$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D11,BH$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BI11" s="1">
-        <f>IF(AND(BI$3&gt;=$D11,BI$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D11,BI$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BJ11" s="1">
-        <f>IF(AND(BJ$3&gt;=$D11,BJ$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D11,BJ$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BK11" s="1">
-        <f>IF(AND(BK$3&gt;=$D11,BK$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D11,BK$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BL11" s="1">
-        <f>IF(AND(BL$3&gt;=$D11,BL$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D11,BL$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BM11" s="1">
-        <f>IF(AND(BM$3&gt;=$D11,BM$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D11,BM$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BN11" s="1">
-        <f>IF(AND(BN$3&gt;=$D11,BN$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D11,BN$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BO11" s="1">
-        <f>IF(AND(BO$3&gt;=$D11,BO$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D11,BO$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BP11" s="1">
-        <f>IF(AND(BP$3&gt;=$D11,BP$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D11,BP$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BQ11" s="1">
-        <f>IF(AND(BQ$3&gt;=$D11,BQ$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D11,BQ$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BR11" s="1">
-        <f>IF(AND(BR$3&gt;=$D11,BR$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D11,BR$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BS11" s="1">
-        <f>IF(AND(BS$3&gt;=$D11,BS$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D11,BS$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BT11" s="1">
-        <f>IF(AND(BT$3&gt;=$D11,BT$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D11,BT$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BU11" s="1">
-        <f>IF(AND(BU$3&gt;=$D11,BU$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D11,BU$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BV11" s="1">
-        <f>IF(AND(BV$3&gt;=$D11,BV$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D11,BV$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BW11" s="1">
-        <f>IF(AND(BW$3&gt;=$D11,BW$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D11,BW$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BX11" s="1">
-        <f>IF(AND(BX$3&gt;=$D11,BX$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D11,BX$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BY11" s="1">
-        <f>IF(AND(BY$3&gt;=$D11,BY$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D11,BY$1&lt;=$E11),"█","")</f>
       </c>
       <c r="BZ11" s="1">
-        <f>IF(AND(BZ$3&gt;=$D11,BZ$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D11,BZ$1&lt;=$E11),"█","")</f>
       </c>
       <c r="CA11" s="1">
-        <f>IF(AND(CA$3&gt;=$D11,CA$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D11,CA$1&lt;=$E11),"█","")</f>
       </c>
       <c r="CB11" s="1">
-        <f>IF(AND(CB$3&gt;=$D11,CB$3&lt;=$E11),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D11,CB$1&lt;=$E11),"█","")</f>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.3">
@@ -3070,236 +3221,235 @@
         <v>2</v>
       </c>
       <c r="D12" s="7">
-        <v>46216</v>
+        <f>E11+1</f>
       </c>
       <c r="E12" s="7">
         <f>D12+C12</f>
-        <v>46218</v>
       </c>
       <c r="F12" s="1">
-        <f>IF(AND(F$3&gt;=$D12,F$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D12,F$1&lt;=$E12),"█","")</f>
       </c>
       <c r="G12" s="1">
-        <f>IF(AND(G$3&gt;=$D12,G$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D12,G$1&lt;=$E12),"█","")</f>
       </c>
       <c r="H12" s="1">
-        <f>IF(AND(H$3&gt;=$D12,H$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D12,H$1&lt;=$E12),"█","")</f>
       </c>
       <c r="I12" s="1">
-        <f>IF(AND(I$3&gt;=$D12,I$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D12,I$1&lt;=$E12),"█","")</f>
       </c>
       <c r="J12" s="1">
-        <f>IF(AND(J$3&gt;=$D12,J$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D12,J$1&lt;=$E12),"█","")</f>
       </c>
       <c r="K12" s="1">
-        <f>IF(AND(K$3&gt;=$D12,K$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D12,K$1&lt;=$E12),"█","")</f>
       </c>
       <c r="L12" s="1">
-        <f>IF(AND(L$3&gt;=$D12,L$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D12,L$1&lt;=$E12),"█","")</f>
       </c>
       <c r="M12" s="1">
-        <f>IF(AND(M$3&gt;=$D12,M$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D12,M$1&lt;=$E12),"█","")</f>
       </c>
       <c r="N12" s="1">
-        <f>IF(AND(N$3&gt;=$D12,N$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D12,N$1&lt;=$E12),"█","")</f>
       </c>
       <c r="O12" s="1">
-        <f>IF(AND(O$3&gt;=$D12,O$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D12,O$1&lt;=$E12),"█","")</f>
       </c>
       <c r="P12" s="1">
-        <f>IF(AND(P$3&gt;=$D12,P$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D12,P$1&lt;=$E12),"█","")</f>
       </c>
       <c r="Q12" s="1">
-        <f>IF(AND(Q$3&gt;=$D12,Q$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D12,Q$1&lt;=$E12),"█","")</f>
       </c>
       <c r="R12" s="1">
-        <f>IF(AND(R$3&gt;=$D12,R$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D12,R$1&lt;=$E12),"█","")</f>
       </c>
       <c r="S12" s="1">
-        <f>IF(AND(S$3&gt;=$D12,S$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D12,S$1&lt;=$E12),"█","")</f>
       </c>
       <c r="T12" s="1">
-        <f>IF(AND(T$3&gt;=$D12,T$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D12,T$1&lt;=$E12),"█","")</f>
       </c>
       <c r="U12" s="1">
-        <f>IF(AND(U$3&gt;=$D12,U$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D12,U$1&lt;=$E12),"█","")</f>
       </c>
       <c r="V12" s="1">
-        <f>IF(AND(V$3&gt;=$D12,V$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D12,V$1&lt;=$E12),"█","")</f>
       </c>
       <c r="W12" s="1">
-        <f>IF(AND(W$3&gt;=$D12,W$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D12,W$1&lt;=$E12),"█","")</f>
       </c>
       <c r="X12" s="1">
-        <f>IF(AND(X$3&gt;=$D12,X$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D12,X$1&lt;=$E12),"█","")</f>
       </c>
       <c r="Y12" s="1">
-        <f>IF(AND(Y$3&gt;=$D12,Y$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D12,Y$1&lt;=$E12),"█","")</f>
       </c>
       <c r="Z12" s="1">
-        <f>IF(AND(Z$3&gt;=$D12,Z$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D12,Z$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AA12" s="1">
-        <f>IF(AND(AA$3&gt;=$D12,AA$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D12,AA$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AB12" s="1">
-        <f>IF(AND(AB$3&gt;=$D12,AB$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D12,AB$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AC12" s="1">
-        <f>IF(AND(AC$3&gt;=$D12,AC$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D12,AC$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AD12" s="1">
-        <f>IF(AND(AD$3&gt;=$D12,AD$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D12,AD$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AE12" s="1">
-        <f>IF(AND(AE$3&gt;=$D12,AE$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D12,AE$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AF12" s="1">
-        <f>IF(AND(AF$3&gt;=$D12,AF$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D12,AF$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AG12" s="1">
-        <f>IF(AND(AG$3&gt;=$D12,AG$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D12,AG$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AH12" s="1">
-        <f>IF(AND(AH$3&gt;=$D12,AH$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D12,AH$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AI12" s="1">
-        <f>IF(AND(AI$3&gt;=$D12,AI$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D12,AI$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AJ12" s="1">
-        <f>IF(AND(AJ$3&gt;=$D12,AJ$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D12,AJ$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AK12" s="1">
-        <f>IF(AND(AK$3&gt;=$D12,AK$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D12,AK$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AL12" s="1">
-        <f>IF(AND(AL$3&gt;=$D12,AL$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D12,AL$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AM12" s="1">
-        <f>IF(AND(AM$3&gt;=$D12,AM$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D12,AM$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AN12" s="1">
-        <f>IF(AND(AN$3&gt;=$D12,AN$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D12,AN$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AO12" s="1">
-        <f>IF(AND(AO$3&gt;=$D12,AO$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D12,AO$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AP12" s="1">
-        <f>IF(AND(AP$3&gt;=$D12,AP$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D12,AP$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AQ12" s="1">
-        <f>IF(AND(AQ$3&gt;=$D12,AQ$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D12,AQ$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AR12" s="1">
-        <f>IF(AND(AR$3&gt;=$D12,AR$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D12,AR$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AS12" s="1">
-        <f>IF(AND(AS$3&gt;=$D12,AS$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D12,AS$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AT12" s="1">
-        <f>IF(AND(AT$3&gt;=$D12,AT$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D12,AT$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AU12" s="1">
-        <f>IF(AND(AU$3&gt;=$D12,AU$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D12,AU$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AV12" s="1">
-        <f>IF(AND(AV$3&gt;=$D12,AV$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D12,AV$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AW12" s="1">
-        <f>IF(AND(AW$3&gt;=$D12,AW$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D12,AW$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AX12" s="1">
-        <f>IF(AND(AX$3&gt;=$D12,AX$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D12,AX$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AY12" s="1">
-        <f>IF(AND(AY$3&gt;=$D12,AY$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D12,AY$1&lt;=$E12),"█","")</f>
       </c>
       <c r="AZ12" s="1">
-        <f>IF(AND(AZ$3&gt;=$D12,AZ$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D12,AZ$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BA12" s="1">
-        <f>IF(AND(BA$3&gt;=$D12,BA$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D12,BA$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BB12" s="1">
-        <f>IF(AND(BB$3&gt;=$D12,BB$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D12,BB$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BC12" s="1">
-        <f>IF(AND(BC$3&gt;=$D12,BC$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D12,BC$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BD12" s="1">
-        <f>IF(AND(BD$3&gt;=$D12,BD$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D12,BD$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BE12" s="1">
-        <f>IF(AND(BE$3&gt;=$D12,BE$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D12,BE$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BF12" s="1">
-        <f>IF(AND(BF$3&gt;=$D12,BF$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D12,BF$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BG12" s="1">
-        <f>IF(AND(BG$3&gt;=$D12,BG$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D12,BG$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BH12" s="1">
-        <f>IF(AND(BH$3&gt;=$D12,BH$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D12,BH$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BI12" s="1">
-        <f>IF(AND(BI$3&gt;=$D12,BI$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D12,BI$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BJ12" s="1">
-        <f>IF(AND(BJ$3&gt;=$D12,BJ$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D12,BJ$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BK12" s="1">
-        <f>IF(AND(BK$3&gt;=$D12,BK$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D12,BK$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BL12" s="1">
-        <f>IF(AND(BL$3&gt;=$D12,BL$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D12,BL$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BM12" s="1">
-        <f>IF(AND(BM$3&gt;=$D12,BM$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D12,BM$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BN12" s="1">
-        <f>IF(AND(BN$3&gt;=$D12,BN$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D12,BN$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BO12" s="1">
-        <f>IF(AND(BO$3&gt;=$D12,BO$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D12,BO$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BP12" s="1">
-        <f>IF(AND(BP$3&gt;=$D12,BP$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D12,BP$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BQ12" s="1">
-        <f>IF(AND(BQ$3&gt;=$D12,BQ$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D12,BQ$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BR12" s="1">
-        <f>IF(AND(BR$3&gt;=$D12,BR$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D12,BR$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BS12" s="1">
-        <f>IF(AND(BS$3&gt;=$D12,BS$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D12,BS$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BT12" s="1">
-        <f>IF(AND(BT$3&gt;=$D12,BT$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D12,BT$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BU12" s="1">
-        <f>IF(AND(BU$3&gt;=$D12,BU$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D12,BU$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BV12" s="1">
-        <f>IF(AND(BV$3&gt;=$D12,BV$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D12,BV$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BW12" s="1">
-        <f>IF(AND(BW$3&gt;=$D12,BW$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D12,BW$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BX12" s="1">
-        <f>IF(AND(BX$3&gt;=$D12,BX$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D12,BX$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BY12" s="1">
-        <f>IF(AND(BY$3&gt;=$D12,BY$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D12,BY$1&lt;=$E12),"█","")</f>
       </c>
       <c r="BZ12" s="1">
-        <f>IF(AND(BZ$3&gt;=$D12,BZ$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D12,BZ$1&lt;=$E12),"█","")</f>
       </c>
       <c r="CA12" s="1">
-        <f>IF(AND(CA$3&gt;=$D12,CA$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D12,CA$1&lt;=$E12),"█","")</f>
       </c>
       <c r="CB12" s="1">
-        <f>IF(AND(CB$3&gt;=$D12,CB$3&lt;=$E12),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D12,CB$1&lt;=$E12),"█","")</f>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.3">
@@ -3313,236 +3463,235 @@
         <v>1</v>
       </c>
       <c r="D13" s="7">
-        <v>46218</v>
+        <f>E12+1</f>
       </c>
       <c r="E13" s="7">
         <f>D13+C13</f>
-        <v>46219</v>
       </c>
       <c r="F13" s="1">
-        <f>IF(AND(F$3&gt;=$D13,F$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D13,F$1&lt;=$E13),"█","")</f>
       </c>
       <c r="G13" s="1">
-        <f>IF(AND(G$3&gt;=$D13,G$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D13,G$1&lt;=$E13),"█","")</f>
       </c>
       <c r="H13" s="1">
-        <f>IF(AND(H$3&gt;=$D13,H$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D13,H$1&lt;=$E13),"█","")</f>
       </c>
       <c r="I13" s="1">
-        <f>IF(AND(I$3&gt;=$D13,I$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D13,I$1&lt;=$E13),"█","")</f>
       </c>
       <c r="J13" s="1">
-        <f>IF(AND(J$3&gt;=$D13,J$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D13,J$1&lt;=$E13),"█","")</f>
       </c>
       <c r="K13" s="1">
-        <f>IF(AND(K$3&gt;=$D13,K$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D13,K$1&lt;=$E13),"█","")</f>
       </c>
       <c r="L13" s="1">
-        <f>IF(AND(L$3&gt;=$D13,L$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D13,L$1&lt;=$E13),"█","")</f>
       </c>
       <c r="M13" s="1">
-        <f>IF(AND(M$3&gt;=$D13,M$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D13,M$1&lt;=$E13),"█","")</f>
       </c>
       <c r="N13" s="1">
-        <f>IF(AND(N$3&gt;=$D13,N$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D13,N$1&lt;=$E13),"█","")</f>
       </c>
       <c r="O13" s="1">
-        <f>IF(AND(O$3&gt;=$D13,O$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D13,O$1&lt;=$E13),"█","")</f>
       </c>
       <c r="P13" s="1">
-        <f>IF(AND(P$3&gt;=$D13,P$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D13,P$1&lt;=$E13),"█","")</f>
       </c>
       <c r="Q13" s="1">
-        <f>IF(AND(Q$3&gt;=$D13,Q$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D13,Q$1&lt;=$E13),"█","")</f>
       </c>
       <c r="R13" s="1">
-        <f>IF(AND(R$3&gt;=$D13,R$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D13,R$1&lt;=$E13),"█","")</f>
       </c>
       <c r="S13" s="1">
-        <f>IF(AND(S$3&gt;=$D13,S$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D13,S$1&lt;=$E13),"█","")</f>
       </c>
       <c r="T13" s="1">
-        <f>IF(AND(T$3&gt;=$D13,T$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D13,T$1&lt;=$E13),"█","")</f>
       </c>
       <c r="U13" s="1">
-        <f>IF(AND(U$3&gt;=$D13,U$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D13,U$1&lt;=$E13),"█","")</f>
       </c>
       <c r="V13" s="1">
-        <f>IF(AND(V$3&gt;=$D13,V$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D13,V$1&lt;=$E13),"█","")</f>
       </c>
       <c r="W13" s="1">
-        <f>IF(AND(W$3&gt;=$D13,W$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D13,W$1&lt;=$E13),"█","")</f>
       </c>
       <c r="X13" s="1">
-        <f>IF(AND(X$3&gt;=$D13,X$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D13,X$1&lt;=$E13),"█","")</f>
       </c>
       <c r="Y13" s="1">
-        <f>IF(AND(Y$3&gt;=$D13,Y$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D13,Y$1&lt;=$E13),"█","")</f>
       </c>
       <c r="Z13" s="1">
-        <f>IF(AND(Z$3&gt;=$D13,Z$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D13,Z$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AA13" s="1">
-        <f>IF(AND(AA$3&gt;=$D13,AA$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D13,AA$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AB13" s="1">
-        <f>IF(AND(AB$3&gt;=$D13,AB$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D13,AB$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AC13" s="1">
-        <f>IF(AND(AC$3&gt;=$D13,AC$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D13,AC$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AD13" s="1">
-        <f>IF(AND(AD$3&gt;=$D13,AD$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D13,AD$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AE13" s="1">
-        <f>IF(AND(AE$3&gt;=$D13,AE$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D13,AE$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AF13" s="1">
-        <f>IF(AND(AF$3&gt;=$D13,AF$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D13,AF$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AG13" s="1">
-        <f>IF(AND(AG$3&gt;=$D13,AG$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D13,AG$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AH13" s="1">
-        <f>IF(AND(AH$3&gt;=$D13,AH$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D13,AH$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AI13" s="1">
-        <f>IF(AND(AI$3&gt;=$D13,AI$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D13,AI$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AJ13" s="1">
-        <f>IF(AND(AJ$3&gt;=$D13,AJ$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D13,AJ$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AK13" s="1">
-        <f>IF(AND(AK$3&gt;=$D13,AK$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D13,AK$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AL13" s="1">
-        <f>IF(AND(AL$3&gt;=$D13,AL$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D13,AL$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AM13" s="1">
-        <f>IF(AND(AM$3&gt;=$D13,AM$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D13,AM$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AN13" s="1">
-        <f>IF(AND(AN$3&gt;=$D13,AN$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D13,AN$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AO13" s="1">
-        <f>IF(AND(AO$3&gt;=$D13,AO$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D13,AO$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AP13" s="1">
-        <f>IF(AND(AP$3&gt;=$D13,AP$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D13,AP$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AQ13" s="1">
-        <f>IF(AND(AQ$3&gt;=$D13,AQ$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D13,AQ$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AR13" s="1">
-        <f>IF(AND(AR$3&gt;=$D13,AR$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D13,AR$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AS13" s="1">
-        <f>IF(AND(AS$3&gt;=$D13,AS$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D13,AS$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AT13" s="1">
-        <f>IF(AND(AT$3&gt;=$D13,AT$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D13,AT$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AU13" s="1">
-        <f>IF(AND(AU$3&gt;=$D13,AU$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D13,AU$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AV13" s="1">
-        <f>IF(AND(AV$3&gt;=$D13,AV$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D13,AV$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AW13" s="1">
-        <f>IF(AND(AW$3&gt;=$D13,AW$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D13,AW$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AX13" s="1">
-        <f>IF(AND(AX$3&gt;=$D13,AX$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D13,AX$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AY13" s="1">
-        <f>IF(AND(AY$3&gt;=$D13,AY$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D13,AY$1&lt;=$E13),"█","")</f>
       </c>
       <c r="AZ13" s="1">
-        <f>IF(AND(AZ$3&gt;=$D13,AZ$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D13,AZ$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BA13" s="1">
-        <f>IF(AND(BA$3&gt;=$D13,BA$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D13,BA$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BB13" s="1">
-        <f>IF(AND(BB$3&gt;=$D13,BB$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D13,BB$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BC13" s="1">
-        <f>IF(AND(BC$3&gt;=$D13,BC$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D13,BC$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BD13" s="1">
-        <f>IF(AND(BD$3&gt;=$D13,BD$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D13,BD$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BE13" s="1">
-        <f>IF(AND(BE$3&gt;=$D13,BE$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D13,BE$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BF13" s="1">
-        <f>IF(AND(BF$3&gt;=$D13,BF$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D13,BF$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BG13" s="1">
-        <f>IF(AND(BG$3&gt;=$D13,BG$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D13,BG$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BH13" s="1">
-        <f>IF(AND(BH$3&gt;=$D13,BH$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D13,BH$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BI13" s="1">
-        <f>IF(AND(BI$3&gt;=$D13,BI$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D13,BI$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BJ13" s="1">
-        <f>IF(AND(BJ$3&gt;=$D13,BJ$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D13,BJ$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BK13" s="1">
-        <f>IF(AND(BK$3&gt;=$D13,BK$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D13,BK$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BL13" s="1">
-        <f>IF(AND(BL$3&gt;=$D13,BL$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D13,BL$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BM13" s="1">
-        <f>IF(AND(BM$3&gt;=$D13,BM$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D13,BM$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BN13" s="1">
-        <f>IF(AND(BN$3&gt;=$D13,BN$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D13,BN$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BO13" s="1">
-        <f>IF(AND(BO$3&gt;=$D13,BO$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D13,BO$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BP13" s="1">
-        <f>IF(AND(BP$3&gt;=$D13,BP$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D13,BP$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BQ13" s="1">
-        <f>IF(AND(BQ$3&gt;=$D13,BQ$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D13,BQ$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BR13" s="1">
-        <f>IF(AND(BR$3&gt;=$D13,BR$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D13,BR$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BS13" s="1">
-        <f>IF(AND(BS$3&gt;=$D13,BS$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D13,BS$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BT13" s="1">
-        <f>IF(AND(BT$3&gt;=$D13,BT$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D13,BT$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BU13" s="1">
-        <f>IF(AND(BU$3&gt;=$D13,BU$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D13,BU$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BV13" s="1">
-        <f>IF(AND(BV$3&gt;=$D13,BV$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D13,BV$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BW13" s="1">
-        <f>IF(AND(BW$3&gt;=$D13,BW$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D13,BW$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BX13" s="1">
-        <f>IF(AND(BX$3&gt;=$D13,BX$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D13,BX$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BY13" s="1">
-        <f>IF(AND(BY$3&gt;=$D13,BY$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D13,BY$1&lt;=$E13),"█","")</f>
       </c>
       <c r="BZ13" s="1">
-        <f>IF(AND(BZ$3&gt;=$D13,BZ$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D13,BZ$1&lt;=$E13),"█","")</f>
       </c>
       <c r="CA13" s="1">
-        <f>IF(AND(CA$3&gt;=$D13,CA$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D13,CA$1&lt;=$E13),"█","")</f>
       </c>
       <c r="CB13" s="1">
-        <f>IF(AND(CB$3&gt;=$D13,CB$3&lt;=$E13),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D13,CB$1&lt;=$E13),"█","")</f>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.3">
@@ -3556,236 +3705,235 @@
         <v>5</v>
       </c>
       <c r="D14" s="7">
-        <v>46218</v>
+        <f>E13+1</f>
       </c>
       <c r="E14" s="7">
         <f>D14+C14</f>
-        <v>46223</v>
       </c>
       <c r="F14" s="1">
-        <f>IF(AND(F$3&gt;=$D14,F$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D14,F$1&lt;=$E14),"█","")</f>
       </c>
       <c r="G14" s="1">
-        <f>IF(AND(G$3&gt;=$D14,G$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D14,G$1&lt;=$E14),"█","")</f>
       </c>
       <c r="H14" s="1">
-        <f>IF(AND(H$3&gt;=$D14,H$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D14,H$1&lt;=$E14),"█","")</f>
       </c>
       <c r="I14" s="1">
-        <f>IF(AND(I$3&gt;=$D14,I$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D14,I$1&lt;=$E14),"█","")</f>
       </c>
       <c r="J14" s="1">
-        <f>IF(AND(J$3&gt;=$D14,J$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D14,J$1&lt;=$E14),"█","")</f>
       </c>
       <c r="K14" s="1">
-        <f>IF(AND(K$3&gt;=$D14,K$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D14,K$1&lt;=$E14),"█","")</f>
       </c>
       <c r="L14" s="1">
-        <f>IF(AND(L$3&gt;=$D14,L$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D14,L$1&lt;=$E14),"█","")</f>
       </c>
       <c r="M14" s="1">
-        <f>IF(AND(M$3&gt;=$D14,M$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D14,M$1&lt;=$E14),"█","")</f>
       </c>
       <c r="N14" s="1">
-        <f>IF(AND(N$3&gt;=$D14,N$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D14,N$1&lt;=$E14),"█","")</f>
       </c>
       <c r="O14" s="1">
-        <f>IF(AND(O$3&gt;=$D14,O$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D14,O$1&lt;=$E14),"█","")</f>
       </c>
       <c r="P14" s="1">
-        <f>IF(AND(P$3&gt;=$D14,P$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D14,P$1&lt;=$E14),"█","")</f>
       </c>
       <c r="Q14" s="1">
-        <f>IF(AND(Q$3&gt;=$D14,Q$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D14,Q$1&lt;=$E14),"█","")</f>
       </c>
       <c r="R14" s="1">
-        <f>IF(AND(R$3&gt;=$D14,R$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D14,R$1&lt;=$E14),"█","")</f>
       </c>
       <c r="S14" s="1">
-        <f>IF(AND(S$3&gt;=$D14,S$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D14,S$1&lt;=$E14),"█","")</f>
       </c>
       <c r="T14" s="1">
-        <f>IF(AND(T$3&gt;=$D14,T$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D14,T$1&lt;=$E14),"█","")</f>
       </c>
       <c r="U14" s="1">
-        <f>IF(AND(U$3&gt;=$D14,U$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D14,U$1&lt;=$E14),"█","")</f>
       </c>
       <c r="V14" s="1">
-        <f>IF(AND(V$3&gt;=$D14,V$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D14,V$1&lt;=$E14),"█","")</f>
       </c>
       <c r="W14" s="1">
-        <f>IF(AND(W$3&gt;=$D14,W$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D14,W$1&lt;=$E14),"█","")</f>
       </c>
       <c r="X14" s="1">
-        <f>IF(AND(X$3&gt;=$D14,X$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D14,X$1&lt;=$E14),"█","")</f>
       </c>
       <c r="Y14" s="1">
-        <f>IF(AND(Y$3&gt;=$D14,Y$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D14,Y$1&lt;=$E14),"█","")</f>
       </c>
       <c r="Z14" s="1">
-        <f>IF(AND(Z$3&gt;=$D14,Z$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D14,Z$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AA14" s="1">
-        <f>IF(AND(AA$3&gt;=$D14,AA$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D14,AA$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AB14" s="1">
-        <f>IF(AND(AB$3&gt;=$D14,AB$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D14,AB$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AC14" s="1">
-        <f>IF(AND(AC$3&gt;=$D14,AC$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D14,AC$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AD14" s="1">
-        <f>IF(AND(AD$3&gt;=$D14,AD$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D14,AD$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AE14" s="1">
-        <f>IF(AND(AE$3&gt;=$D14,AE$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D14,AE$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AF14" s="1">
-        <f>IF(AND(AF$3&gt;=$D14,AF$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D14,AF$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AG14" s="1">
-        <f>IF(AND(AG$3&gt;=$D14,AG$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D14,AG$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AH14" s="1">
-        <f>IF(AND(AH$3&gt;=$D14,AH$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D14,AH$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AI14" s="1">
-        <f>IF(AND(AI$3&gt;=$D14,AI$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D14,AI$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AJ14" s="1">
-        <f>IF(AND(AJ$3&gt;=$D14,AJ$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D14,AJ$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AK14" s="1">
-        <f>IF(AND(AK$3&gt;=$D14,AK$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D14,AK$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AL14" s="1">
-        <f>IF(AND(AL$3&gt;=$D14,AL$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D14,AL$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AM14" s="1">
-        <f>IF(AND(AM$3&gt;=$D14,AM$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D14,AM$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AN14" s="1">
-        <f>IF(AND(AN$3&gt;=$D14,AN$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D14,AN$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AO14" s="1">
-        <f>IF(AND(AO$3&gt;=$D14,AO$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D14,AO$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AP14" s="1">
-        <f>IF(AND(AP$3&gt;=$D14,AP$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D14,AP$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AQ14" s="1">
-        <f>IF(AND(AQ$3&gt;=$D14,AQ$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D14,AQ$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AR14" s="1">
-        <f>IF(AND(AR$3&gt;=$D14,AR$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D14,AR$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AS14" s="1">
-        <f>IF(AND(AS$3&gt;=$D14,AS$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D14,AS$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AT14" s="1">
-        <f>IF(AND(AT$3&gt;=$D14,AT$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D14,AT$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AU14" s="1">
-        <f>IF(AND(AU$3&gt;=$D14,AU$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D14,AU$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AV14" s="1">
-        <f>IF(AND(AV$3&gt;=$D14,AV$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D14,AV$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AW14" s="1">
-        <f>IF(AND(AW$3&gt;=$D14,AW$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D14,AW$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AX14" s="1">
-        <f>IF(AND(AX$3&gt;=$D14,AX$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D14,AX$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AY14" s="1">
-        <f>IF(AND(AY$3&gt;=$D14,AY$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D14,AY$1&lt;=$E14),"█","")</f>
       </c>
       <c r="AZ14" s="1">
-        <f>IF(AND(AZ$3&gt;=$D14,AZ$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D14,AZ$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BA14" s="1">
-        <f>IF(AND(BA$3&gt;=$D14,BA$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D14,BA$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BB14" s="1">
-        <f>IF(AND(BB$3&gt;=$D14,BB$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D14,BB$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BC14" s="1">
-        <f>IF(AND(BC$3&gt;=$D14,BC$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D14,BC$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BD14" s="1">
-        <f>IF(AND(BD$3&gt;=$D14,BD$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D14,BD$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BE14" s="1">
-        <f>IF(AND(BE$3&gt;=$D14,BE$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D14,BE$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BF14" s="1">
-        <f>IF(AND(BF$3&gt;=$D14,BF$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D14,BF$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BG14" s="1">
-        <f>IF(AND(BG$3&gt;=$D14,BG$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D14,BG$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BH14" s="1">
-        <f>IF(AND(BH$3&gt;=$D14,BH$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D14,BH$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BI14" s="1">
-        <f>IF(AND(BI$3&gt;=$D14,BI$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D14,BI$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BJ14" s="1">
-        <f>IF(AND(BJ$3&gt;=$D14,BJ$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D14,BJ$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BK14" s="1">
-        <f>IF(AND(BK$3&gt;=$D14,BK$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D14,BK$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BL14" s="1">
-        <f>IF(AND(BL$3&gt;=$D14,BL$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D14,BL$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BM14" s="1">
-        <f>IF(AND(BM$3&gt;=$D14,BM$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D14,BM$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BN14" s="1">
-        <f>IF(AND(BN$3&gt;=$D14,BN$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D14,BN$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BO14" s="1">
-        <f>IF(AND(BO$3&gt;=$D14,BO$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D14,BO$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BP14" s="1">
-        <f>IF(AND(BP$3&gt;=$D14,BP$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D14,BP$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BQ14" s="1">
-        <f>IF(AND(BQ$3&gt;=$D14,BQ$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D14,BQ$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BR14" s="1">
-        <f>IF(AND(BR$3&gt;=$D14,BR$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D14,BR$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BS14" s="1">
-        <f>IF(AND(BS$3&gt;=$D14,BS$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D14,BS$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BT14" s="1">
-        <f>IF(AND(BT$3&gt;=$D14,BT$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D14,BT$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BU14" s="1">
-        <f>IF(AND(BU$3&gt;=$D14,BU$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D14,BU$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BV14" s="1">
-        <f>IF(AND(BV$3&gt;=$D14,BV$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D14,BV$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BW14" s="1">
-        <f>IF(AND(BW$3&gt;=$D14,BW$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D14,BW$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BX14" s="1">
-        <f>IF(AND(BX$3&gt;=$D14,BX$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D14,BX$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BY14" s="1">
-        <f>IF(AND(BY$3&gt;=$D14,BY$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D14,BY$1&lt;=$E14),"█","")</f>
       </c>
       <c r="BZ14" s="1">
-        <f>IF(AND(BZ$3&gt;=$D14,BZ$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D14,BZ$1&lt;=$E14),"█","")</f>
       </c>
       <c r="CA14" s="1">
-        <f>IF(AND(CA$3&gt;=$D14,CA$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D14,CA$1&lt;=$E14),"█","")</f>
       </c>
       <c r="CB14" s="1">
-        <f>IF(AND(CB$3&gt;=$D14,CB$3&lt;=$E14),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D14,CB$1&lt;=$E14),"█","")</f>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.3">
@@ -3808,229 +3956,229 @@
         <v>46250</v>
       </c>
       <c r="F15" s="1">
-        <f>IF(AND(F$3&gt;=$D15,F$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D15,F$1&lt;=$E15),"█","")</f>
       </c>
       <c r="G15" s="1">
-        <f>IF(AND(G$3&gt;=$D15,G$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D15,G$1&lt;=$E15),"█","")</f>
       </c>
       <c r="H15" s="1">
-        <f>IF(AND(H$3&gt;=$D15,H$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D15,H$1&lt;=$E15),"█","")</f>
       </c>
       <c r="I15" s="1">
-        <f>IF(AND(I$3&gt;=$D15,I$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D15,I$1&lt;=$E15),"█","")</f>
       </c>
       <c r="J15" s="1">
-        <f>IF(AND(J$3&gt;=$D15,J$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D15,J$1&lt;=$E15),"█","")</f>
       </c>
       <c r="K15" s="1">
-        <f>IF(AND(K$3&gt;=$D15,K$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D15,K$1&lt;=$E15),"█","")</f>
       </c>
       <c r="L15" s="1">
-        <f>IF(AND(L$3&gt;=$D15,L$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D15,L$1&lt;=$E15),"█","")</f>
       </c>
       <c r="M15" s="1">
-        <f>IF(AND(M$3&gt;=$D15,M$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D15,M$1&lt;=$E15),"█","")</f>
       </c>
       <c r="N15" s="1">
-        <f>IF(AND(N$3&gt;=$D15,N$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D15,N$1&lt;=$E15),"█","")</f>
       </c>
       <c r="O15" s="1">
-        <f>IF(AND(O$3&gt;=$D15,O$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D15,O$1&lt;=$E15),"█","")</f>
       </c>
       <c r="P15" s="1">
-        <f>IF(AND(P$3&gt;=$D15,P$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D15,P$1&lt;=$E15),"█","")</f>
       </c>
       <c r="Q15" s="1">
-        <f>IF(AND(Q$3&gt;=$D15,Q$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D15,Q$1&lt;=$E15),"█","")</f>
       </c>
       <c r="R15" s="1">
-        <f>IF(AND(R$3&gt;=$D15,R$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D15,R$1&lt;=$E15),"█","")</f>
       </c>
       <c r="S15" s="1">
-        <f>IF(AND(S$3&gt;=$D15,S$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D15,S$1&lt;=$E15),"█","")</f>
       </c>
       <c r="T15" s="1">
-        <f>IF(AND(T$3&gt;=$D15,T$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D15,T$1&lt;=$E15),"█","")</f>
       </c>
       <c r="U15" s="1">
-        <f>IF(AND(U$3&gt;=$D15,U$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D15,U$1&lt;=$E15),"█","")</f>
       </c>
       <c r="V15" s="1">
-        <f>IF(AND(V$3&gt;=$D15,V$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D15,V$1&lt;=$E15),"█","")</f>
       </c>
       <c r="W15" s="1">
-        <f>IF(AND(W$3&gt;=$D15,W$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D15,W$1&lt;=$E15),"█","")</f>
       </c>
       <c r="X15" s="1">
-        <f>IF(AND(X$3&gt;=$D15,X$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D15,X$1&lt;=$E15),"█","")</f>
       </c>
       <c r="Y15" s="1">
-        <f>IF(AND(Y$3&gt;=$D15,Y$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D15,Y$1&lt;=$E15),"█","")</f>
       </c>
       <c r="Z15" s="1">
-        <f>IF(AND(Z$3&gt;=$D15,Z$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D15,Z$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AA15" s="1">
-        <f>IF(AND(AA$3&gt;=$D15,AA$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D15,AA$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AB15" s="1">
-        <f>IF(AND(AB$3&gt;=$D15,AB$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D15,AB$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AC15" s="1">
-        <f>IF(AND(AC$3&gt;=$D15,AC$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D15,AC$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AD15" s="1">
-        <f>IF(AND(AD$3&gt;=$D15,AD$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D15,AD$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AE15" s="1">
-        <f>IF(AND(AE$3&gt;=$D15,AE$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D15,AE$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AF15" s="1">
-        <f>IF(AND(AF$3&gt;=$D15,AF$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D15,AF$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AG15" s="1">
-        <f>IF(AND(AG$3&gt;=$D15,AG$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D15,AG$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AH15" s="1">
-        <f>IF(AND(AH$3&gt;=$D15,AH$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D15,AH$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AI15" s="1">
-        <f>IF(AND(AI$3&gt;=$D15,AI$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D15,AI$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AJ15" s="1">
-        <f>IF(AND(AJ$3&gt;=$D15,AJ$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D15,AJ$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AK15" s="1">
-        <f>IF(AND(AK$3&gt;=$D15,AK$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D15,AK$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AL15" s="1">
-        <f>IF(AND(AL$3&gt;=$D15,AL$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D15,AL$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AM15" s="1">
-        <f>IF(AND(AM$3&gt;=$D15,AM$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D15,AM$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AN15" s="1">
-        <f>IF(AND(AN$3&gt;=$D15,AN$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D15,AN$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AO15" s="1">
-        <f>IF(AND(AO$3&gt;=$D15,AO$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D15,AO$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AP15" s="1">
-        <f>IF(AND(AP$3&gt;=$D15,AP$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D15,AP$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AQ15" s="1">
-        <f>IF(AND(AQ$3&gt;=$D15,AQ$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D15,AQ$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AR15" s="1">
-        <f>IF(AND(AR$3&gt;=$D15,AR$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D15,AR$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AS15" s="1">
-        <f>IF(AND(AS$3&gt;=$D15,AS$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D15,AS$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AT15" s="1">
-        <f>IF(AND(AT$3&gt;=$D15,AT$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D15,AT$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AU15" s="1">
-        <f>IF(AND(AU$3&gt;=$D15,AU$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D15,AU$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AV15" s="1">
-        <f>IF(AND(AV$3&gt;=$D15,AV$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D15,AV$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AW15" s="1">
-        <f>IF(AND(AW$3&gt;=$D15,AW$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D15,AW$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AX15" s="1">
-        <f>IF(AND(AX$3&gt;=$D15,AX$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D15,AX$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AY15" s="1">
-        <f>IF(AND(AY$3&gt;=$D15,AY$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D15,AY$1&lt;=$E15),"█","")</f>
       </c>
       <c r="AZ15" s="1">
-        <f>IF(AND(AZ$3&gt;=$D15,AZ$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D15,AZ$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BA15" s="1">
-        <f>IF(AND(BA$3&gt;=$D15,BA$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D15,BA$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BB15" s="1">
-        <f>IF(AND(BB$3&gt;=$D15,BB$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D15,BB$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BC15" s="1">
-        <f>IF(AND(BC$3&gt;=$D15,BC$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D15,BC$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BD15" s="1">
-        <f>IF(AND(BD$3&gt;=$D15,BD$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D15,BD$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BE15" s="1">
-        <f>IF(AND(BE$3&gt;=$D15,BE$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D15,BE$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BF15" s="1">
-        <f>IF(AND(BF$3&gt;=$D15,BF$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D15,BF$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BG15" s="1">
-        <f>IF(AND(BG$3&gt;=$D15,BG$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D15,BG$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BH15" s="1">
-        <f>IF(AND(BH$3&gt;=$D15,BH$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D15,BH$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BI15" s="1">
-        <f>IF(AND(BI$3&gt;=$D15,BI$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D15,BI$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BJ15" s="1">
-        <f>IF(AND(BJ$3&gt;=$D15,BJ$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D15,BJ$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BK15" s="1">
-        <f>IF(AND(BK$3&gt;=$D15,BK$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D15,BK$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BL15" s="1">
-        <f>IF(AND(BL$3&gt;=$D15,BL$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D15,BL$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BM15" s="1">
-        <f>IF(AND(BM$3&gt;=$D15,BM$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D15,BM$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BN15" s="1">
-        <f>IF(AND(BN$3&gt;=$D15,BN$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D15,BN$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BO15" s="1">
-        <f>IF(AND(BO$3&gt;=$D15,BO$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D15,BO$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BP15" s="1">
-        <f>IF(AND(BP$3&gt;=$D15,BP$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D15,BP$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BQ15" s="1">
-        <f>IF(AND(BQ$3&gt;=$D15,BQ$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D15,BQ$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BR15" s="1">
-        <f>IF(AND(BR$3&gt;=$D15,BR$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D15,BR$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BS15" s="1">
-        <f>IF(AND(BS$3&gt;=$D15,BS$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D15,BS$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BT15" s="1">
-        <f>IF(AND(BT$3&gt;=$D15,BT$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D15,BT$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BU15" s="1">
-        <f>IF(AND(BU$3&gt;=$D15,BU$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D15,BU$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BV15" s="1">
-        <f>IF(AND(BV$3&gt;=$D15,BV$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D15,BV$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BW15" s="1">
-        <f>IF(AND(BW$3&gt;=$D15,BW$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D15,BW$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BX15" s="1">
-        <f>IF(AND(BX$3&gt;=$D15,BX$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D15,BX$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BY15" s="1">
-        <f>IF(AND(BY$3&gt;=$D15,BY$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D15,BY$1&lt;=$E15),"█","")</f>
       </c>
       <c r="BZ15" s="1">
-        <f>IF(AND(BZ$3&gt;=$D15,BZ$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D15,BZ$1&lt;=$E15),"█","")</f>
       </c>
       <c r="CA15" s="1">
-        <f>IF(AND(CA$3&gt;=$D15,CA$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D15,CA$1&lt;=$E15),"█","")</f>
       </c>
       <c r="CB15" s="1">
-        <f>IF(AND(CB$3&gt;=$D15,CB$3&lt;=$E15),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D15,CB$1&lt;=$E15),"█","")</f>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.3">
@@ -4044,236 +4192,235 @@
         <v>3</v>
       </c>
       <c r="D16" s="7">
-        <v>46223</v>
+        <f>E14+1</f>
       </c>
       <c r="E16" s="7">
         <f>D16+C16</f>
-        <v>46226</v>
       </c>
       <c r="F16" s="1">
-        <f>IF(AND(F$3&gt;=$D16,F$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D16,F$1&lt;=$E16),"█","")</f>
       </c>
       <c r="G16" s="1">
-        <f>IF(AND(G$3&gt;=$D16,G$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D16,G$1&lt;=$E16),"█","")</f>
       </c>
       <c r="H16" s="1">
-        <f>IF(AND(H$3&gt;=$D16,H$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D16,H$1&lt;=$E16),"█","")</f>
       </c>
       <c r="I16" s="1">
-        <f>IF(AND(I$3&gt;=$D16,I$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D16,I$1&lt;=$E16),"█","")</f>
       </c>
       <c r="J16" s="1">
-        <f>IF(AND(J$3&gt;=$D16,J$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D16,J$1&lt;=$E16),"█","")</f>
       </c>
       <c r="K16" s="1">
-        <f>IF(AND(K$3&gt;=$D16,K$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D16,K$1&lt;=$E16),"█","")</f>
       </c>
       <c r="L16" s="1">
-        <f>IF(AND(L$3&gt;=$D16,L$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D16,L$1&lt;=$E16),"█","")</f>
       </c>
       <c r="M16" s="1">
-        <f>IF(AND(M$3&gt;=$D16,M$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D16,M$1&lt;=$E16),"█","")</f>
       </c>
       <c r="N16" s="1">
-        <f>IF(AND(N$3&gt;=$D16,N$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D16,N$1&lt;=$E16),"█","")</f>
       </c>
       <c r="O16" s="1">
-        <f>IF(AND(O$3&gt;=$D16,O$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D16,O$1&lt;=$E16),"█","")</f>
       </c>
       <c r="P16" s="1">
-        <f>IF(AND(P$3&gt;=$D16,P$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D16,P$1&lt;=$E16),"█","")</f>
       </c>
       <c r="Q16" s="1">
-        <f>IF(AND(Q$3&gt;=$D16,Q$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D16,Q$1&lt;=$E16),"█","")</f>
       </c>
       <c r="R16" s="1">
-        <f>IF(AND(R$3&gt;=$D16,R$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D16,R$1&lt;=$E16),"█","")</f>
       </c>
       <c r="S16" s="1">
-        <f>IF(AND(S$3&gt;=$D16,S$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D16,S$1&lt;=$E16),"█","")</f>
       </c>
       <c r="T16" s="1">
-        <f>IF(AND(T$3&gt;=$D16,T$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D16,T$1&lt;=$E16),"█","")</f>
       </c>
       <c r="U16" s="1">
-        <f>IF(AND(U$3&gt;=$D16,U$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D16,U$1&lt;=$E16),"█","")</f>
       </c>
       <c r="V16" s="1">
-        <f>IF(AND(V$3&gt;=$D16,V$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D16,V$1&lt;=$E16),"█","")</f>
       </c>
       <c r="W16" s="1">
-        <f>IF(AND(W$3&gt;=$D16,W$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D16,W$1&lt;=$E16),"█","")</f>
       </c>
       <c r="X16" s="1">
-        <f>IF(AND(X$3&gt;=$D16,X$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D16,X$1&lt;=$E16),"█","")</f>
       </c>
       <c r="Y16" s="1">
-        <f>IF(AND(Y$3&gt;=$D16,Y$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D16,Y$1&lt;=$E16),"█","")</f>
       </c>
       <c r="Z16" s="1">
-        <f>IF(AND(Z$3&gt;=$D16,Z$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D16,Z$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AA16" s="1">
-        <f>IF(AND(AA$3&gt;=$D16,AA$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D16,AA$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AB16" s="1">
-        <f>IF(AND(AB$3&gt;=$D16,AB$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D16,AB$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AC16" s="1">
-        <f>IF(AND(AC$3&gt;=$D16,AC$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D16,AC$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AD16" s="1">
-        <f>IF(AND(AD$3&gt;=$D16,AD$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D16,AD$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AE16" s="1">
-        <f>IF(AND(AE$3&gt;=$D16,AE$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D16,AE$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AF16" s="1">
-        <f>IF(AND(AF$3&gt;=$D16,AF$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D16,AF$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AG16" s="1">
-        <f>IF(AND(AG$3&gt;=$D16,AG$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D16,AG$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AH16" s="1">
-        <f>IF(AND(AH$3&gt;=$D16,AH$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D16,AH$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AI16" s="1">
-        <f>IF(AND(AI$3&gt;=$D16,AI$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D16,AI$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AJ16" s="1">
-        <f>IF(AND(AJ$3&gt;=$D16,AJ$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D16,AJ$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AK16" s="1">
-        <f>IF(AND(AK$3&gt;=$D16,AK$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D16,AK$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AL16" s="1">
-        <f>IF(AND(AL$3&gt;=$D16,AL$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D16,AL$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AM16" s="1">
-        <f>IF(AND(AM$3&gt;=$D16,AM$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D16,AM$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AN16" s="1">
-        <f>IF(AND(AN$3&gt;=$D16,AN$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D16,AN$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AO16" s="1">
-        <f>IF(AND(AO$3&gt;=$D16,AO$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D16,AO$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AP16" s="1">
-        <f>IF(AND(AP$3&gt;=$D16,AP$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D16,AP$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AQ16" s="1">
-        <f>IF(AND(AQ$3&gt;=$D16,AQ$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D16,AQ$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AR16" s="1">
-        <f>IF(AND(AR$3&gt;=$D16,AR$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D16,AR$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AS16" s="1">
-        <f>IF(AND(AS$3&gt;=$D16,AS$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D16,AS$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AT16" s="1">
-        <f>IF(AND(AT$3&gt;=$D16,AT$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D16,AT$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AU16" s="1">
-        <f>IF(AND(AU$3&gt;=$D16,AU$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D16,AU$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AV16" s="1">
-        <f>IF(AND(AV$3&gt;=$D16,AV$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D16,AV$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AW16" s="1">
-        <f>IF(AND(AW$3&gt;=$D16,AW$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D16,AW$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AX16" s="1">
-        <f>IF(AND(AX$3&gt;=$D16,AX$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D16,AX$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AY16" s="1">
-        <f>IF(AND(AY$3&gt;=$D16,AY$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D16,AY$1&lt;=$E16),"█","")</f>
       </c>
       <c r="AZ16" s="1">
-        <f>IF(AND(AZ$3&gt;=$D16,AZ$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D16,AZ$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BA16" s="1">
-        <f>IF(AND(BA$3&gt;=$D16,BA$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D16,BA$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BB16" s="1">
-        <f>IF(AND(BB$3&gt;=$D16,BB$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D16,BB$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BC16" s="1">
-        <f>IF(AND(BC$3&gt;=$D16,BC$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D16,BC$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BD16" s="1">
-        <f>IF(AND(BD$3&gt;=$D16,BD$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D16,BD$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BE16" s="1">
-        <f>IF(AND(BE$3&gt;=$D16,BE$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D16,BE$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BF16" s="1">
-        <f>IF(AND(BF$3&gt;=$D16,BF$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D16,BF$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BG16" s="1">
-        <f>IF(AND(BG$3&gt;=$D16,BG$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D16,BG$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BH16" s="1">
-        <f>IF(AND(BH$3&gt;=$D16,BH$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D16,BH$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BI16" s="1">
-        <f>IF(AND(BI$3&gt;=$D16,BI$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D16,BI$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BJ16" s="1">
-        <f>IF(AND(BJ$3&gt;=$D16,BJ$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D16,BJ$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BK16" s="1">
-        <f>IF(AND(BK$3&gt;=$D16,BK$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D16,BK$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BL16" s="1">
-        <f>IF(AND(BL$3&gt;=$D16,BL$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D16,BL$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BM16" s="1">
-        <f>IF(AND(BM$3&gt;=$D16,BM$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D16,BM$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BN16" s="1">
-        <f>IF(AND(BN$3&gt;=$D16,BN$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D16,BN$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BO16" s="1">
-        <f>IF(AND(BO$3&gt;=$D16,BO$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D16,BO$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BP16" s="1">
-        <f>IF(AND(BP$3&gt;=$D16,BP$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D16,BP$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BQ16" s="1">
-        <f>IF(AND(BQ$3&gt;=$D16,BQ$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D16,BQ$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BR16" s="1">
-        <f>IF(AND(BR$3&gt;=$D16,BR$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D16,BR$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BS16" s="1">
-        <f>IF(AND(BS$3&gt;=$D16,BS$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D16,BS$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BT16" s="1">
-        <f>IF(AND(BT$3&gt;=$D16,BT$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D16,BT$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BU16" s="1">
-        <f>IF(AND(BU$3&gt;=$D16,BU$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D16,BU$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BV16" s="1">
-        <f>IF(AND(BV$3&gt;=$D16,BV$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D16,BV$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BW16" s="1">
-        <f>IF(AND(BW$3&gt;=$D16,BW$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D16,BW$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BX16" s="1">
-        <f>IF(AND(BX$3&gt;=$D16,BX$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D16,BX$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BY16" s="1">
-        <f>IF(AND(BY$3&gt;=$D16,BY$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D16,BY$1&lt;=$E16),"█","")</f>
       </c>
       <c r="BZ16" s="1">
-        <f>IF(AND(BZ$3&gt;=$D16,BZ$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D16,BZ$1&lt;=$E16),"█","")</f>
       </c>
       <c r="CA16" s="1">
-        <f>IF(AND(CA$3&gt;=$D16,CA$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D16,CA$1&lt;=$E16),"█","")</f>
       </c>
       <c r="CB16" s="1">
-        <f>IF(AND(CB$3&gt;=$D16,CB$3&lt;=$E16),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D16,CB$1&lt;=$E16),"█","")</f>
       </c>
     </row>
     <row r="17" spans="1:35" x14ac:dyDescent="0.3">
@@ -4287,236 +4434,235 @@
         <v>2</v>
       </c>
       <c r="D17" s="7">
-        <v>46226</v>
+        <f>E16+1</f>
       </c>
       <c r="E17" s="7">
         <f>D17+C17</f>
-        <v>46228</v>
       </c>
       <c r="F17" s="1">
-        <f>IF(AND(F$3&gt;=$D17,F$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D17,F$1&lt;=$E17),"█","")</f>
       </c>
       <c r="G17" s="1">
-        <f>IF(AND(G$3&gt;=$D17,G$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D17,G$1&lt;=$E17),"█","")</f>
       </c>
       <c r="H17" s="1">
-        <f>IF(AND(H$3&gt;=$D17,H$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D17,H$1&lt;=$E17),"█","")</f>
       </c>
       <c r="I17" s="1">
-        <f>IF(AND(I$3&gt;=$D17,I$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D17,I$1&lt;=$E17),"█","")</f>
       </c>
       <c r="J17" s="1">
-        <f>IF(AND(J$3&gt;=$D17,J$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D17,J$1&lt;=$E17),"█","")</f>
       </c>
       <c r="K17" s="1">
-        <f>IF(AND(K$3&gt;=$D17,K$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D17,K$1&lt;=$E17),"█","")</f>
       </c>
       <c r="L17" s="1">
-        <f>IF(AND(L$3&gt;=$D17,L$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D17,L$1&lt;=$E17),"█","")</f>
       </c>
       <c r="M17" s="1">
-        <f>IF(AND(M$3&gt;=$D17,M$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D17,M$1&lt;=$E17),"█","")</f>
       </c>
       <c r="N17" s="1">
-        <f>IF(AND(N$3&gt;=$D17,N$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D17,N$1&lt;=$E17),"█","")</f>
       </c>
       <c r="O17" s="1">
-        <f>IF(AND(O$3&gt;=$D17,O$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D17,O$1&lt;=$E17),"█","")</f>
       </c>
       <c r="P17" s="1">
-        <f>IF(AND(P$3&gt;=$D17,P$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D17,P$1&lt;=$E17),"█","")</f>
       </c>
       <c r="Q17" s="1">
-        <f>IF(AND(Q$3&gt;=$D17,Q$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D17,Q$1&lt;=$E17),"█","")</f>
       </c>
       <c r="R17" s="1">
-        <f>IF(AND(R$3&gt;=$D17,R$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D17,R$1&lt;=$E17),"█","")</f>
       </c>
       <c r="S17" s="1">
-        <f>IF(AND(S$3&gt;=$D17,S$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D17,S$1&lt;=$E17),"█","")</f>
       </c>
       <c r="T17" s="1">
-        <f>IF(AND(T$3&gt;=$D17,T$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D17,T$1&lt;=$E17),"█","")</f>
       </c>
       <c r="U17" s="1">
-        <f>IF(AND(U$3&gt;=$D17,U$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D17,U$1&lt;=$E17),"█","")</f>
       </c>
       <c r="V17" s="1">
-        <f>IF(AND(V$3&gt;=$D17,V$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D17,V$1&lt;=$E17),"█","")</f>
       </c>
       <c r="W17" s="1">
-        <f>IF(AND(W$3&gt;=$D17,W$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D17,W$1&lt;=$E17),"█","")</f>
       </c>
       <c r="X17" s="1">
-        <f>IF(AND(X$3&gt;=$D17,X$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D17,X$1&lt;=$E17),"█","")</f>
       </c>
       <c r="Y17" s="1">
-        <f>IF(AND(Y$3&gt;=$D17,Y$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D17,Y$1&lt;=$E17),"█","")</f>
       </c>
       <c r="Z17" s="1">
-        <f>IF(AND(Z$3&gt;=$D17,Z$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D17,Z$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AA17" s="1">
-        <f>IF(AND(AA$3&gt;=$D17,AA$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D17,AA$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AB17" s="1">
-        <f>IF(AND(AB$3&gt;=$D17,AB$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D17,AB$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AC17" s="1">
-        <f>IF(AND(AC$3&gt;=$D17,AC$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D17,AC$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AD17" s="1">
-        <f>IF(AND(AD$3&gt;=$D17,AD$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D17,AD$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AE17" s="1">
-        <f>IF(AND(AE$3&gt;=$D17,AE$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D17,AE$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AF17" s="1">
-        <f>IF(AND(AF$3&gt;=$D17,AF$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D17,AF$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AG17" s="1">
-        <f>IF(AND(AG$3&gt;=$D17,AG$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D17,AG$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AH17" s="1">
-        <f>IF(AND(AH$3&gt;=$D17,AH$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D17,AH$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AI17" s="1">
-        <f>IF(AND(AI$3&gt;=$D17,AI$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D17,AI$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AJ17" s="1">
-        <f>IF(AND(AJ$3&gt;=$D17,AJ$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D17,AJ$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AK17" s="1">
-        <f>IF(AND(AK$3&gt;=$D17,AK$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D17,AK$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AL17" s="1">
-        <f>IF(AND(AL$3&gt;=$D17,AL$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D17,AL$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AM17" s="1">
-        <f>IF(AND(AM$3&gt;=$D17,AM$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D17,AM$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AN17" s="1">
-        <f>IF(AND(AN$3&gt;=$D17,AN$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D17,AN$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AO17" s="1">
-        <f>IF(AND(AO$3&gt;=$D17,AO$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D17,AO$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AP17" s="1">
-        <f>IF(AND(AP$3&gt;=$D17,AP$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D17,AP$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AQ17" s="1">
-        <f>IF(AND(AQ$3&gt;=$D17,AQ$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D17,AQ$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AR17" s="1">
-        <f>IF(AND(AR$3&gt;=$D17,AR$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D17,AR$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AS17" s="1">
-        <f>IF(AND(AS$3&gt;=$D17,AS$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D17,AS$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AT17" s="1">
-        <f>IF(AND(AT$3&gt;=$D17,AT$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D17,AT$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AU17" s="1">
-        <f>IF(AND(AU$3&gt;=$D17,AU$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D17,AU$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AV17" s="1">
-        <f>IF(AND(AV$3&gt;=$D17,AV$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D17,AV$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AW17" s="1">
-        <f>IF(AND(AW$3&gt;=$D17,AW$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D17,AW$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AX17" s="1">
-        <f>IF(AND(AX$3&gt;=$D17,AX$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D17,AX$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AY17" s="1">
-        <f>IF(AND(AY$3&gt;=$D17,AY$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D17,AY$1&lt;=$E17),"█","")</f>
       </c>
       <c r="AZ17" s="1">
-        <f>IF(AND(AZ$3&gt;=$D17,AZ$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D17,AZ$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BA17" s="1">
-        <f>IF(AND(BA$3&gt;=$D17,BA$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D17,BA$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BB17" s="1">
-        <f>IF(AND(BB$3&gt;=$D17,BB$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D17,BB$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BC17" s="1">
-        <f>IF(AND(BC$3&gt;=$D17,BC$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D17,BC$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BD17" s="1">
-        <f>IF(AND(BD$3&gt;=$D17,BD$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D17,BD$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BE17" s="1">
-        <f>IF(AND(BE$3&gt;=$D17,BE$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D17,BE$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BF17" s="1">
-        <f>IF(AND(BF$3&gt;=$D17,BF$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D17,BF$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BG17" s="1">
-        <f>IF(AND(BG$3&gt;=$D17,BG$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D17,BG$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BH17" s="1">
-        <f>IF(AND(BH$3&gt;=$D17,BH$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D17,BH$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BI17" s="1">
-        <f>IF(AND(BI$3&gt;=$D17,BI$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D17,BI$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BJ17" s="1">
-        <f>IF(AND(BJ$3&gt;=$D17,BJ$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D17,BJ$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BK17" s="1">
-        <f>IF(AND(BK$3&gt;=$D17,BK$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D17,BK$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BL17" s="1">
-        <f>IF(AND(BL$3&gt;=$D17,BL$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D17,BL$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BM17" s="1">
-        <f>IF(AND(BM$3&gt;=$D17,BM$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D17,BM$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BN17" s="1">
-        <f>IF(AND(BN$3&gt;=$D17,BN$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D17,BN$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BO17" s="1">
-        <f>IF(AND(BO$3&gt;=$D17,BO$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D17,BO$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BP17" s="1">
-        <f>IF(AND(BP$3&gt;=$D17,BP$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D17,BP$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BQ17" s="1">
-        <f>IF(AND(BQ$3&gt;=$D17,BQ$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D17,BQ$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BR17" s="1">
-        <f>IF(AND(BR$3&gt;=$D17,BR$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D17,BR$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BS17" s="1">
-        <f>IF(AND(BS$3&gt;=$D17,BS$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D17,BS$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BT17" s="1">
-        <f>IF(AND(BT$3&gt;=$D17,BT$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D17,BT$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BU17" s="1">
-        <f>IF(AND(BU$3&gt;=$D17,BU$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D17,BU$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BV17" s="1">
-        <f>IF(AND(BV$3&gt;=$D17,BV$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D17,BV$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BW17" s="1">
-        <f>IF(AND(BW$3&gt;=$D17,BW$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D17,BW$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BX17" s="1">
-        <f>IF(AND(BX$3&gt;=$D17,BX$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D17,BX$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BY17" s="1">
-        <f>IF(AND(BY$3&gt;=$D17,BY$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D17,BY$1&lt;=$E17),"█","")</f>
       </c>
       <c r="BZ17" s="1">
-        <f>IF(AND(BZ$3&gt;=$D17,BZ$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D17,BZ$1&lt;=$E17),"█","")</f>
       </c>
       <c r="CA17" s="1">
-        <f>IF(AND(CA$3&gt;=$D17,CA$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D17,CA$1&lt;=$E17),"█","")</f>
       </c>
       <c r="CB17" s="1">
-        <f>IF(AND(CB$3&gt;=$D17,CB$3&lt;=$E17),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D17,CB$1&lt;=$E17),"█","")</f>
       </c>
     </row>
     <row r="18" spans="1:35" x14ac:dyDescent="0.3">
@@ -4530,236 +4676,235 @@
         <v>4</v>
       </c>
       <c r="D18" s="7">
-        <v>46228</v>
+        <f>E17+1</f>
       </c>
       <c r="E18" s="7">
         <f>D18+C18</f>
-        <v>46232</v>
       </c>
       <c r="F18" s="1">
-        <f>IF(AND(F$3&gt;=$D18,F$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D18,F$1&lt;=$E18),"█","")</f>
       </c>
       <c r="G18" s="1">
-        <f>IF(AND(G$3&gt;=$D18,G$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D18,G$1&lt;=$E18),"█","")</f>
       </c>
       <c r="H18" s="1">
-        <f>IF(AND(H$3&gt;=$D18,H$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D18,H$1&lt;=$E18),"█","")</f>
       </c>
       <c r="I18" s="1">
-        <f>IF(AND(I$3&gt;=$D18,I$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D18,I$1&lt;=$E18),"█","")</f>
       </c>
       <c r="J18" s="1">
-        <f>IF(AND(J$3&gt;=$D18,J$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D18,J$1&lt;=$E18),"█","")</f>
       </c>
       <c r="K18" s="1">
-        <f>IF(AND(K$3&gt;=$D18,K$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D18,K$1&lt;=$E18),"█","")</f>
       </c>
       <c r="L18" s="1">
-        <f>IF(AND(L$3&gt;=$D18,L$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D18,L$1&lt;=$E18),"█","")</f>
       </c>
       <c r="M18" s="1">
-        <f>IF(AND(M$3&gt;=$D18,M$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D18,M$1&lt;=$E18),"█","")</f>
       </c>
       <c r="N18" s="1">
-        <f>IF(AND(N$3&gt;=$D18,N$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D18,N$1&lt;=$E18),"█","")</f>
       </c>
       <c r="O18" s="1">
-        <f>IF(AND(O$3&gt;=$D18,O$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D18,O$1&lt;=$E18),"█","")</f>
       </c>
       <c r="P18" s="1">
-        <f>IF(AND(P$3&gt;=$D18,P$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D18,P$1&lt;=$E18),"█","")</f>
       </c>
       <c r="Q18" s="1">
-        <f>IF(AND(Q$3&gt;=$D18,Q$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D18,Q$1&lt;=$E18),"█","")</f>
       </c>
       <c r="R18" s="1">
-        <f>IF(AND(R$3&gt;=$D18,R$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D18,R$1&lt;=$E18),"█","")</f>
       </c>
       <c r="S18" s="1">
-        <f>IF(AND(S$3&gt;=$D18,S$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D18,S$1&lt;=$E18),"█","")</f>
       </c>
       <c r="T18" s="1">
-        <f>IF(AND(T$3&gt;=$D18,T$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D18,T$1&lt;=$E18),"█","")</f>
       </c>
       <c r="U18" s="1">
-        <f>IF(AND(U$3&gt;=$D18,U$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D18,U$1&lt;=$E18),"█","")</f>
       </c>
       <c r="V18" s="1">
-        <f>IF(AND(V$3&gt;=$D18,V$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D18,V$1&lt;=$E18),"█","")</f>
       </c>
       <c r="W18" s="1">
-        <f>IF(AND(W$3&gt;=$D18,W$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D18,W$1&lt;=$E18),"█","")</f>
       </c>
       <c r="X18" s="1">
-        <f>IF(AND(X$3&gt;=$D18,X$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D18,X$1&lt;=$E18),"█","")</f>
       </c>
       <c r="Y18" s="1">
-        <f>IF(AND(Y$3&gt;=$D18,Y$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D18,Y$1&lt;=$E18),"█","")</f>
       </c>
       <c r="Z18" s="1">
-        <f>IF(AND(Z$3&gt;=$D18,Z$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D18,Z$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AA18" s="1">
-        <f>IF(AND(AA$3&gt;=$D18,AA$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D18,AA$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AB18" s="1">
-        <f>IF(AND(AB$3&gt;=$D18,AB$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D18,AB$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AC18" s="1">
-        <f>IF(AND(AC$3&gt;=$D18,AC$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D18,AC$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AD18" s="1">
-        <f>IF(AND(AD$3&gt;=$D18,AD$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D18,AD$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AE18" s="1">
-        <f>IF(AND(AE$3&gt;=$D18,AE$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D18,AE$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AF18" s="1">
-        <f>IF(AND(AF$3&gt;=$D18,AF$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D18,AF$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AG18" s="1">
-        <f>IF(AND(AG$3&gt;=$D18,AG$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D18,AG$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AH18" s="1">
-        <f>IF(AND(AH$3&gt;=$D18,AH$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D18,AH$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AI18" s="1">
-        <f>IF(AND(AI$3&gt;=$D18,AI$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D18,AI$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AJ18" s="1">
-        <f>IF(AND(AJ$3&gt;=$D18,AJ$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D18,AJ$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AK18" s="1">
-        <f>IF(AND(AK$3&gt;=$D18,AK$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D18,AK$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AL18" s="1">
-        <f>IF(AND(AL$3&gt;=$D18,AL$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D18,AL$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AM18" s="1">
-        <f>IF(AND(AM$3&gt;=$D18,AM$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D18,AM$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AN18" s="1">
-        <f>IF(AND(AN$3&gt;=$D18,AN$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D18,AN$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AO18" s="1">
-        <f>IF(AND(AO$3&gt;=$D18,AO$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D18,AO$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AP18" s="1">
-        <f>IF(AND(AP$3&gt;=$D18,AP$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D18,AP$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AQ18" s="1">
-        <f>IF(AND(AQ$3&gt;=$D18,AQ$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D18,AQ$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AR18" s="1">
-        <f>IF(AND(AR$3&gt;=$D18,AR$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D18,AR$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AS18" s="1">
-        <f>IF(AND(AS$3&gt;=$D18,AS$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D18,AS$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AT18" s="1">
-        <f>IF(AND(AT$3&gt;=$D18,AT$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D18,AT$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AU18" s="1">
-        <f>IF(AND(AU$3&gt;=$D18,AU$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D18,AU$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AV18" s="1">
-        <f>IF(AND(AV$3&gt;=$D18,AV$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D18,AV$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AW18" s="1">
-        <f>IF(AND(AW$3&gt;=$D18,AW$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D18,AW$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AX18" s="1">
-        <f>IF(AND(AX$3&gt;=$D18,AX$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D18,AX$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AY18" s="1">
-        <f>IF(AND(AY$3&gt;=$D18,AY$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D18,AY$1&lt;=$E18),"█","")</f>
       </c>
       <c r="AZ18" s="1">
-        <f>IF(AND(AZ$3&gt;=$D18,AZ$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D18,AZ$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BA18" s="1">
-        <f>IF(AND(BA$3&gt;=$D18,BA$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D18,BA$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BB18" s="1">
-        <f>IF(AND(BB$3&gt;=$D18,BB$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D18,BB$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BC18" s="1">
-        <f>IF(AND(BC$3&gt;=$D18,BC$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D18,BC$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BD18" s="1">
-        <f>IF(AND(BD$3&gt;=$D18,BD$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D18,BD$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BE18" s="1">
-        <f>IF(AND(BE$3&gt;=$D18,BE$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D18,BE$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BF18" s="1">
-        <f>IF(AND(BF$3&gt;=$D18,BF$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D18,BF$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BG18" s="1">
-        <f>IF(AND(BG$3&gt;=$D18,BG$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D18,BG$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BH18" s="1">
-        <f>IF(AND(BH$3&gt;=$D18,BH$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D18,BH$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BI18" s="1">
-        <f>IF(AND(BI$3&gt;=$D18,BI$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D18,BI$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BJ18" s="1">
-        <f>IF(AND(BJ$3&gt;=$D18,BJ$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D18,BJ$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BK18" s="1">
-        <f>IF(AND(BK$3&gt;=$D18,BK$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D18,BK$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BL18" s="1">
-        <f>IF(AND(BL$3&gt;=$D18,BL$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D18,BL$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BM18" s="1">
-        <f>IF(AND(BM$3&gt;=$D18,BM$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D18,BM$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BN18" s="1">
-        <f>IF(AND(BN$3&gt;=$D18,BN$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D18,BN$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BO18" s="1">
-        <f>IF(AND(BO$3&gt;=$D18,BO$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D18,BO$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BP18" s="1">
-        <f>IF(AND(BP$3&gt;=$D18,BP$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D18,BP$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BQ18" s="1">
-        <f>IF(AND(BQ$3&gt;=$D18,BQ$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D18,BQ$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BR18" s="1">
-        <f>IF(AND(BR$3&gt;=$D18,BR$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D18,BR$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BS18" s="1">
-        <f>IF(AND(BS$3&gt;=$D18,BS$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D18,BS$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BT18" s="1">
-        <f>IF(AND(BT$3&gt;=$D18,BT$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D18,BT$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BU18" s="1">
-        <f>IF(AND(BU$3&gt;=$D18,BU$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D18,BU$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BV18" s="1">
-        <f>IF(AND(BV$3&gt;=$D18,BV$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D18,BV$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BW18" s="1">
-        <f>IF(AND(BW$3&gt;=$D18,BW$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D18,BW$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BX18" s="1">
-        <f>IF(AND(BX$3&gt;=$D18,BX$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D18,BX$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BY18" s="1">
-        <f>IF(AND(BY$3&gt;=$D18,BY$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D18,BY$1&lt;=$E18),"█","")</f>
       </c>
       <c r="BZ18" s="1">
-        <f>IF(AND(BZ$3&gt;=$D18,BZ$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D18,BZ$1&lt;=$E18),"█","")</f>
       </c>
       <c r="CA18" s="1">
-        <f>IF(AND(CA$3&gt;=$D18,CA$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D18,CA$1&lt;=$E18),"█","")</f>
       </c>
       <c r="CB18" s="1">
-        <f>IF(AND(CB$3&gt;=$D18,CB$3&lt;=$E18),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D18,CB$1&lt;=$E18),"█","")</f>
       </c>
     </row>
     <row r="19" spans="1:35" x14ac:dyDescent="0.3">
@@ -4773,236 +4918,235 @@
         <v>5</v>
       </c>
       <c r="D19" s="7">
-        <v>46228</v>
+        <f>E17+1</f>
       </c>
       <c r="E19" s="7">
         <f>D19+C19</f>
-        <v>46233</v>
       </c>
       <c r="F19" s="1">
-        <f>IF(AND(F$3&gt;=$D19,F$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D19,F$1&lt;=$E19),"█","")</f>
       </c>
       <c r="G19" s="1">
-        <f>IF(AND(G$3&gt;=$D19,G$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D19,G$1&lt;=$E19),"█","")</f>
       </c>
       <c r="H19" s="1">
-        <f>IF(AND(H$3&gt;=$D19,H$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D19,H$1&lt;=$E19),"█","")</f>
       </c>
       <c r="I19" s="1">
-        <f>IF(AND(I$3&gt;=$D19,I$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D19,I$1&lt;=$E19),"█","")</f>
       </c>
       <c r="J19" s="1">
-        <f>IF(AND(J$3&gt;=$D19,J$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D19,J$1&lt;=$E19),"█","")</f>
       </c>
       <c r="K19" s="1">
-        <f>IF(AND(K$3&gt;=$D19,K$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D19,K$1&lt;=$E19),"█","")</f>
       </c>
       <c r="L19" s="1">
-        <f>IF(AND(L$3&gt;=$D19,L$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D19,L$1&lt;=$E19),"█","")</f>
       </c>
       <c r="M19" s="1">
-        <f>IF(AND(M$3&gt;=$D19,M$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D19,M$1&lt;=$E19),"█","")</f>
       </c>
       <c r="N19" s="1">
-        <f>IF(AND(N$3&gt;=$D19,N$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D19,N$1&lt;=$E19),"█","")</f>
       </c>
       <c r="O19" s="1">
-        <f>IF(AND(O$3&gt;=$D19,O$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D19,O$1&lt;=$E19),"█","")</f>
       </c>
       <c r="P19" s="1">
-        <f>IF(AND(P$3&gt;=$D19,P$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D19,P$1&lt;=$E19),"█","")</f>
       </c>
       <c r="Q19" s="1">
-        <f>IF(AND(Q$3&gt;=$D19,Q$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D19,Q$1&lt;=$E19),"█","")</f>
       </c>
       <c r="R19" s="1">
-        <f>IF(AND(R$3&gt;=$D19,R$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D19,R$1&lt;=$E19),"█","")</f>
       </c>
       <c r="S19" s="1">
-        <f>IF(AND(S$3&gt;=$D19,S$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D19,S$1&lt;=$E19),"█","")</f>
       </c>
       <c r="T19" s="1">
-        <f>IF(AND(T$3&gt;=$D19,T$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D19,T$1&lt;=$E19),"█","")</f>
       </c>
       <c r="U19" s="1">
-        <f>IF(AND(U$3&gt;=$D19,U$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D19,U$1&lt;=$E19),"█","")</f>
       </c>
       <c r="V19" s="1">
-        <f>IF(AND(V$3&gt;=$D19,V$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D19,V$1&lt;=$E19),"█","")</f>
       </c>
       <c r="W19" s="1">
-        <f>IF(AND(W$3&gt;=$D19,W$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D19,W$1&lt;=$E19),"█","")</f>
       </c>
       <c r="X19" s="1">
-        <f>IF(AND(X$3&gt;=$D19,X$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D19,X$1&lt;=$E19),"█","")</f>
       </c>
       <c r="Y19" s="1">
-        <f>IF(AND(Y$3&gt;=$D19,Y$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D19,Y$1&lt;=$E19),"█","")</f>
       </c>
       <c r="Z19" s="1">
-        <f>IF(AND(Z$3&gt;=$D19,Z$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D19,Z$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AA19" s="1">
-        <f>IF(AND(AA$3&gt;=$D19,AA$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D19,AA$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AB19" s="1">
-        <f>IF(AND(AB$3&gt;=$D19,AB$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D19,AB$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AC19" s="1">
-        <f>IF(AND(AC$3&gt;=$D19,AC$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D19,AC$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AD19" s="1">
-        <f>IF(AND(AD$3&gt;=$D19,AD$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D19,AD$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AE19" s="1">
-        <f>IF(AND(AE$3&gt;=$D19,AE$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D19,AE$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AF19" s="1">
-        <f>IF(AND(AF$3&gt;=$D19,AF$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D19,AF$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AG19" s="1">
-        <f>IF(AND(AG$3&gt;=$D19,AG$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D19,AG$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AH19" s="1">
-        <f>IF(AND(AH$3&gt;=$D19,AH$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D19,AH$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AI19" s="1">
-        <f>IF(AND(AI$3&gt;=$D19,AI$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D19,AI$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AJ19" s="1">
-        <f>IF(AND(AJ$3&gt;=$D19,AJ$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D19,AJ$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AK19" s="1">
-        <f>IF(AND(AK$3&gt;=$D19,AK$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D19,AK$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AL19" s="1">
-        <f>IF(AND(AL$3&gt;=$D19,AL$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D19,AL$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AM19" s="1">
-        <f>IF(AND(AM$3&gt;=$D19,AM$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D19,AM$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AN19" s="1">
-        <f>IF(AND(AN$3&gt;=$D19,AN$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D19,AN$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AO19" s="1">
-        <f>IF(AND(AO$3&gt;=$D19,AO$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D19,AO$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AP19" s="1">
-        <f>IF(AND(AP$3&gt;=$D19,AP$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D19,AP$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AQ19" s="1">
-        <f>IF(AND(AQ$3&gt;=$D19,AQ$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D19,AQ$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AR19" s="1">
-        <f>IF(AND(AR$3&gt;=$D19,AR$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D19,AR$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AS19" s="1">
-        <f>IF(AND(AS$3&gt;=$D19,AS$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D19,AS$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AT19" s="1">
-        <f>IF(AND(AT$3&gt;=$D19,AT$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D19,AT$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AU19" s="1">
-        <f>IF(AND(AU$3&gt;=$D19,AU$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D19,AU$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AV19" s="1">
-        <f>IF(AND(AV$3&gt;=$D19,AV$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D19,AV$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AW19" s="1">
-        <f>IF(AND(AW$3&gt;=$D19,AW$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D19,AW$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AX19" s="1">
-        <f>IF(AND(AX$3&gt;=$D19,AX$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D19,AX$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AY19" s="1">
-        <f>IF(AND(AY$3&gt;=$D19,AY$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D19,AY$1&lt;=$E19),"█","")</f>
       </c>
       <c r="AZ19" s="1">
-        <f>IF(AND(AZ$3&gt;=$D19,AZ$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D19,AZ$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BA19" s="1">
-        <f>IF(AND(BA$3&gt;=$D19,BA$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D19,BA$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BB19" s="1">
-        <f>IF(AND(BB$3&gt;=$D19,BB$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D19,BB$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BC19" s="1">
-        <f>IF(AND(BC$3&gt;=$D19,BC$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D19,BC$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BD19" s="1">
-        <f>IF(AND(BD$3&gt;=$D19,BD$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D19,BD$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BE19" s="1">
-        <f>IF(AND(BE$3&gt;=$D19,BE$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D19,BE$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BF19" s="1">
-        <f>IF(AND(BF$3&gt;=$D19,BF$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D19,BF$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BG19" s="1">
-        <f>IF(AND(BG$3&gt;=$D19,BG$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D19,BG$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BH19" s="1">
-        <f>IF(AND(BH$3&gt;=$D19,BH$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D19,BH$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BI19" s="1">
-        <f>IF(AND(BI$3&gt;=$D19,BI$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D19,BI$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BJ19" s="1">
-        <f>IF(AND(BJ$3&gt;=$D19,BJ$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D19,BJ$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BK19" s="1">
-        <f>IF(AND(BK$3&gt;=$D19,BK$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D19,BK$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BL19" s="1">
-        <f>IF(AND(BL$3&gt;=$D19,BL$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D19,BL$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BM19" s="1">
-        <f>IF(AND(BM$3&gt;=$D19,BM$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D19,BM$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BN19" s="1">
-        <f>IF(AND(BN$3&gt;=$D19,BN$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D19,BN$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BO19" s="1">
-        <f>IF(AND(BO$3&gt;=$D19,BO$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D19,BO$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BP19" s="1">
-        <f>IF(AND(BP$3&gt;=$D19,BP$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D19,BP$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BQ19" s="1">
-        <f>IF(AND(BQ$3&gt;=$D19,BQ$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D19,BQ$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BR19" s="1">
-        <f>IF(AND(BR$3&gt;=$D19,BR$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D19,BR$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BS19" s="1">
-        <f>IF(AND(BS$3&gt;=$D19,BS$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D19,BS$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BT19" s="1">
-        <f>IF(AND(BT$3&gt;=$D19,BT$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D19,BT$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BU19" s="1">
-        <f>IF(AND(BU$3&gt;=$D19,BU$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D19,BU$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BV19" s="1">
-        <f>IF(AND(BV$3&gt;=$D19,BV$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D19,BV$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BW19" s="1">
-        <f>IF(AND(BW$3&gt;=$D19,BW$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D19,BW$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BX19" s="1">
-        <f>IF(AND(BX$3&gt;=$D19,BX$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D19,BX$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BY19" s="1">
-        <f>IF(AND(BY$3&gt;=$D19,BY$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D19,BY$1&lt;=$E19),"█","")</f>
       </c>
       <c r="BZ19" s="1">
-        <f>IF(AND(BZ$3&gt;=$D19,BZ$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D19,BZ$1&lt;=$E19),"█","")</f>
       </c>
       <c r="CA19" s="1">
-        <f>IF(AND(CA$3&gt;=$D19,CA$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D19,CA$1&lt;=$E19),"█","")</f>
       </c>
       <c r="CB19" s="1">
-        <f>IF(AND(CB$3&gt;=$D19,CB$3&lt;=$E19),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D19,CB$1&lt;=$E19),"█","")</f>
       </c>
     </row>
     <row r="20" spans="1:35" x14ac:dyDescent="0.3">
@@ -5016,236 +5160,235 @@
         <v>11</v>
       </c>
       <c r="D20" s="7">
-        <v>46233</v>
+        <f>E19+1</f>
       </c>
       <c r="E20" s="7">
         <f>D20+C20</f>
-        <v>46244</v>
       </c>
       <c r="F20" s="1">
-        <f>IF(AND(F$3&gt;=$D20,F$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D20,F$1&lt;=$E20),"█","")</f>
       </c>
       <c r="G20" s="1">
-        <f>IF(AND(G$3&gt;=$D20,G$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D20,G$1&lt;=$E20),"█","")</f>
       </c>
       <c r="H20" s="1">
-        <f>IF(AND(H$3&gt;=$D20,H$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D20,H$1&lt;=$E20),"█","")</f>
       </c>
       <c r="I20" s="1">
-        <f>IF(AND(I$3&gt;=$D20,I$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D20,I$1&lt;=$E20),"█","")</f>
       </c>
       <c r="J20" s="1">
-        <f>IF(AND(J$3&gt;=$D20,J$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D20,J$1&lt;=$E20),"█","")</f>
       </c>
       <c r="K20" s="1">
-        <f>IF(AND(K$3&gt;=$D20,K$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D20,K$1&lt;=$E20),"█","")</f>
       </c>
       <c r="L20" s="1">
-        <f>IF(AND(L$3&gt;=$D20,L$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D20,L$1&lt;=$E20),"█","")</f>
       </c>
       <c r="M20" s="1">
-        <f>IF(AND(M$3&gt;=$D20,M$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D20,M$1&lt;=$E20),"█","")</f>
       </c>
       <c r="N20" s="1">
-        <f>IF(AND(N$3&gt;=$D20,N$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D20,N$1&lt;=$E20),"█","")</f>
       </c>
       <c r="O20" s="1">
-        <f>IF(AND(O$3&gt;=$D20,O$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D20,O$1&lt;=$E20),"█","")</f>
       </c>
       <c r="P20" s="1">
-        <f>IF(AND(P$3&gt;=$D20,P$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D20,P$1&lt;=$E20),"█","")</f>
       </c>
       <c r="Q20" s="1">
-        <f>IF(AND(Q$3&gt;=$D20,Q$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D20,Q$1&lt;=$E20),"█","")</f>
       </c>
       <c r="R20" s="1">
-        <f>IF(AND(R$3&gt;=$D20,R$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D20,R$1&lt;=$E20),"█","")</f>
       </c>
       <c r="S20" s="1">
-        <f>IF(AND(S$3&gt;=$D20,S$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D20,S$1&lt;=$E20),"█","")</f>
       </c>
       <c r="T20" s="1">
-        <f>IF(AND(T$3&gt;=$D20,T$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D20,T$1&lt;=$E20),"█","")</f>
       </c>
       <c r="U20" s="1">
-        <f>IF(AND(U$3&gt;=$D20,U$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D20,U$1&lt;=$E20),"█","")</f>
       </c>
       <c r="V20" s="1">
-        <f>IF(AND(V$3&gt;=$D20,V$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D20,V$1&lt;=$E20),"█","")</f>
       </c>
       <c r="W20" s="1">
-        <f>IF(AND(W$3&gt;=$D20,W$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D20,W$1&lt;=$E20),"█","")</f>
       </c>
       <c r="X20" s="1">
-        <f>IF(AND(X$3&gt;=$D20,X$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D20,X$1&lt;=$E20),"█","")</f>
       </c>
       <c r="Y20" s="1">
-        <f>IF(AND(Y$3&gt;=$D20,Y$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D20,Y$1&lt;=$E20),"█","")</f>
       </c>
       <c r="Z20" s="1">
-        <f>IF(AND(Z$3&gt;=$D20,Z$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D20,Z$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AA20" s="1">
-        <f>IF(AND(AA$3&gt;=$D20,AA$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D20,AA$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AB20" s="1">
-        <f>IF(AND(AB$3&gt;=$D20,AB$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D20,AB$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AC20" s="1">
-        <f>IF(AND(AC$3&gt;=$D20,AC$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D20,AC$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AD20" s="1">
-        <f>IF(AND(AD$3&gt;=$D20,AD$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D20,AD$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AE20" s="1">
-        <f>IF(AND(AE$3&gt;=$D20,AE$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D20,AE$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AF20" s="1">
-        <f>IF(AND(AF$3&gt;=$D20,AF$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D20,AF$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AG20" s="1">
-        <f>IF(AND(AG$3&gt;=$D20,AG$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D20,AG$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AH20" s="1">
-        <f>IF(AND(AH$3&gt;=$D20,AH$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D20,AH$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AI20" s="1">
-        <f>IF(AND(AI$3&gt;=$D20,AI$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D20,AI$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AJ20" s="1">
-        <f>IF(AND(AJ$3&gt;=$D20,AJ$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D20,AJ$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AK20" s="1">
-        <f>IF(AND(AK$3&gt;=$D20,AK$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D20,AK$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AL20" s="1">
-        <f>IF(AND(AL$3&gt;=$D20,AL$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D20,AL$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AM20" s="1">
-        <f>IF(AND(AM$3&gt;=$D20,AM$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D20,AM$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AN20" s="1">
-        <f>IF(AND(AN$3&gt;=$D20,AN$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D20,AN$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AO20" s="1">
-        <f>IF(AND(AO$3&gt;=$D20,AO$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D20,AO$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AP20" s="1">
-        <f>IF(AND(AP$3&gt;=$D20,AP$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D20,AP$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AQ20" s="1">
-        <f>IF(AND(AQ$3&gt;=$D20,AQ$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D20,AQ$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AR20" s="1">
-        <f>IF(AND(AR$3&gt;=$D20,AR$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D20,AR$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AS20" s="1">
-        <f>IF(AND(AS$3&gt;=$D20,AS$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D20,AS$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AT20" s="1">
-        <f>IF(AND(AT$3&gt;=$D20,AT$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D20,AT$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AU20" s="1">
-        <f>IF(AND(AU$3&gt;=$D20,AU$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D20,AU$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AV20" s="1">
-        <f>IF(AND(AV$3&gt;=$D20,AV$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D20,AV$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AW20" s="1">
-        <f>IF(AND(AW$3&gt;=$D20,AW$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D20,AW$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AX20" s="1">
-        <f>IF(AND(AX$3&gt;=$D20,AX$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D20,AX$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AY20" s="1">
-        <f>IF(AND(AY$3&gt;=$D20,AY$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D20,AY$1&lt;=$E20),"█","")</f>
       </c>
       <c r="AZ20" s="1">
-        <f>IF(AND(AZ$3&gt;=$D20,AZ$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D20,AZ$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BA20" s="1">
-        <f>IF(AND(BA$3&gt;=$D20,BA$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D20,BA$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BB20" s="1">
-        <f>IF(AND(BB$3&gt;=$D20,BB$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D20,BB$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BC20" s="1">
-        <f>IF(AND(BC$3&gt;=$D20,BC$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D20,BC$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BD20" s="1">
-        <f>IF(AND(BD$3&gt;=$D20,BD$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D20,BD$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BE20" s="1">
-        <f>IF(AND(BE$3&gt;=$D20,BE$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D20,BE$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BF20" s="1">
-        <f>IF(AND(BF$3&gt;=$D20,BF$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D20,BF$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BG20" s="1">
-        <f>IF(AND(BG$3&gt;=$D20,BG$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D20,BG$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BH20" s="1">
-        <f>IF(AND(BH$3&gt;=$D20,BH$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D20,BH$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BI20" s="1">
-        <f>IF(AND(BI$3&gt;=$D20,BI$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D20,BI$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BJ20" s="1">
-        <f>IF(AND(BJ$3&gt;=$D20,BJ$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D20,BJ$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BK20" s="1">
-        <f>IF(AND(BK$3&gt;=$D20,BK$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D20,BK$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BL20" s="1">
-        <f>IF(AND(BL$3&gt;=$D20,BL$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D20,BL$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BM20" s="1">
-        <f>IF(AND(BM$3&gt;=$D20,BM$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D20,BM$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BN20" s="1">
-        <f>IF(AND(BN$3&gt;=$D20,BN$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D20,BN$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BO20" s="1">
-        <f>IF(AND(BO$3&gt;=$D20,BO$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D20,BO$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BP20" s="1">
-        <f>IF(AND(BP$3&gt;=$D20,BP$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D20,BP$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BQ20" s="1">
-        <f>IF(AND(BQ$3&gt;=$D20,BQ$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D20,BQ$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BR20" s="1">
-        <f>IF(AND(BR$3&gt;=$D20,BR$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D20,BR$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BS20" s="1">
-        <f>IF(AND(BS$3&gt;=$D20,BS$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D20,BS$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BT20" s="1">
-        <f>IF(AND(BT$3&gt;=$D20,BT$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D20,BT$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BU20" s="1">
-        <f>IF(AND(BU$3&gt;=$D20,BU$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D20,BU$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BV20" s="1">
-        <f>IF(AND(BV$3&gt;=$D20,BV$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D20,BV$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BW20" s="1">
-        <f>IF(AND(BW$3&gt;=$D20,BW$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D20,BW$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BX20" s="1">
-        <f>IF(AND(BX$3&gt;=$D20,BX$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D20,BX$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BY20" s="1">
-        <f>IF(AND(BY$3&gt;=$D20,BY$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D20,BY$1&lt;=$E20),"█","")</f>
       </c>
       <c r="BZ20" s="1">
-        <f>IF(AND(BZ$3&gt;=$D20,BZ$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D20,BZ$1&lt;=$E20),"█","")</f>
       </c>
       <c r="CA20" s="1">
-        <f>IF(AND(CA$3&gt;=$D20,CA$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D20,CA$1&lt;=$E20),"█","")</f>
       </c>
       <c r="CB20" s="1">
-        <f>IF(AND(CB$3&gt;=$D20,CB$3&lt;=$E20),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D20,CB$1&lt;=$E20),"█","")</f>
       </c>
     </row>
     <row r="21" spans="1:35" x14ac:dyDescent="0.3">
@@ -5259,236 +5402,235 @@
         <v>4</v>
       </c>
       <c r="D21" s="7">
-        <v>46244</v>
+        <f>E20+1</f>
       </c>
       <c r="E21" s="7">
         <f>D21+C21</f>
-        <v>46248</v>
       </c>
       <c r="F21" s="1">
-        <f>IF(AND(F$3&gt;=$D21,F$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D21,F$1&lt;=$E21),"█","")</f>
       </c>
       <c r="G21" s="1">
-        <f>IF(AND(G$3&gt;=$D21,G$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D21,G$1&lt;=$E21),"█","")</f>
       </c>
       <c r="H21" s="1">
-        <f>IF(AND(H$3&gt;=$D21,H$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D21,H$1&lt;=$E21),"█","")</f>
       </c>
       <c r="I21" s="1">
-        <f>IF(AND(I$3&gt;=$D21,I$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D21,I$1&lt;=$E21),"█","")</f>
       </c>
       <c r="J21" s="1">
-        <f>IF(AND(J$3&gt;=$D21,J$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D21,J$1&lt;=$E21),"█","")</f>
       </c>
       <c r="K21" s="1">
-        <f>IF(AND(K$3&gt;=$D21,K$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D21,K$1&lt;=$E21),"█","")</f>
       </c>
       <c r="L21" s="1">
-        <f>IF(AND(L$3&gt;=$D21,L$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D21,L$1&lt;=$E21),"█","")</f>
       </c>
       <c r="M21" s="1">
-        <f>IF(AND(M$3&gt;=$D21,M$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D21,M$1&lt;=$E21),"█","")</f>
       </c>
       <c r="N21" s="1">
-        <f>IF(AND(N$3&gt;=$D21,N$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D21,N$1&lt;=$E21),"█","")</f>
       </c>
       <c r="O21" s="1">
-        <f>IF(AND(O$3&gt;=$D21,O$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D21,O$1&lt;=$E21),"█","")</f>
       </c>
       <c r="P21" s="1">
-        <f>IF(AND(P$3&gt;=$D21,P$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D21,P$1&lt;=$E21),"█","")</f>
       </c>
       <c r="Q21" s="1">
-        <f>IF(AND(Q$3&gt;=$D21,Q$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D21,Q$1&lt;=$E21),"█","")</f>
       </c>
       <c r="R21" s="1">
-        <f>IF(AND(R$3&gt;=$D21,R$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D21,R$1&lt;=$E21),"█","")</f>
       </c>
       <c r="S21" s="1">
-        <f>IF(AND(S$3&gt;=$D21,S$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D21,S$1&lt;=$E21),"█","")</f>
       </c>
       <c r="T21" s="1">
-        <f>IF(AND(T$3&gt;=$D21,T$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D21,T$1&lt;=$E21),"█","")</f>
       </c>
       <c r="U21" s="1">
-        <f>IF(AND(U$3&gt;=$D21,U$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D21,U$1&lt;=$E21),"█","")</f>
       </c>
       <c r="V21" s="1">
-        <f>IF(AND(V$3&gt;=$D21,V$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D21,V$1&lt;=$E21),"█","")</f>
       </c>
       <c r="W21" s="1">
-        <f>IF(AND(W$3&gt;=$D21,W$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D21,W$1&lt;=$E21),"█","")</f>
       </c>
       <c r="X21" s="1">
-        <f>IF(AND(X$3&gt;=$D21,X$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D21,X$1&lt;=$E21),"█","")</f>
       </c>
       <c r="Y21" s="1">
-        <f>IF(AND(Y$3&gt;=$D21,Y$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D21,Y$1&lt;=$E21),"█","")</f>
       </c>
       <c r="Z21" s="1">
-        <f>IF(AND(Z$3&gt;=$D21,Z$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D21,Z$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AA21" s="1">
-        <f>IF(AND(AA$3&gt;=$D21,AA$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D21,AA$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AB21" s="1">
-        <f>IF(AND(AB$3&gt;=$D21,AB$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D21,AB$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AC21" s="1">
-        <f>IF(AND(AC$3&gt;=$D21,AC$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D21,AC$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AD21" s="1">
-        <f>IF(AND(AD$3&gt;=$D21,AD$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D21,AD$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AE21" s="1">
-        <f>IF(AND(AE$3&gt;=$D21,AE$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D21,AE$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AF21" s="1">
-        <f>IF(AND(AF$3&gt;=$D21,AF$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D21,AF$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AG21" s="1">
-        <f>IF(AND(AG$3&gt;=$D21,AG$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D21,AG$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AH21" s="1">
-        <f>IF(AND(AH$3&gt;=$D21,AH$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D21,AH$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AI21" s="1">
-        <f>IF(AND(AI$3&gt;=$D21,AI$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D21,AI$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AJ21" s="1">
-        <f>IF(AND(AJ$3&gt;=$D21,AJ$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D21,AJ$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AK21" s="1">
-        <f>IF(AND(AK$3&gt;=$D21,AK$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D21,AK$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AL21" s="1">
-        <f>IF(AND(AL$3&gt;=$D21,AL$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D21,AL$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AM21" s="1">
-        <f>IF(AND(AM$3&gt;=$D21,AM$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D21,AM$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AN21" s="1">
-        <f>IF(AND(AN$3&gt;=$D21,AN$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D21,AN$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AO21" s="1">
-        <f>IF(AND(AO$3&gt;=$D21,AO$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D21,AO$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AP21" s="1">
-        <f>IF(AND(AP$3&gt;=$D21,AP$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D21,AP$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AQ21" s="1">
-        <f>IF(AND(AQ$3&gt;=$D21,AQ$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D21,AQ$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AR21" s="1">
-        <f>IF(AND(AR$3&gt;=$D21,AR$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D21,AR$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AS21" s="1">
-        <f>IF(AND(AS$3&gt;=$D21,AS$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D21,AS$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AT21" s="1">
-        <f>IF(AND(AT$3&gt;=$D21,AT$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D21,AT$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AU21" s="1">
-        <f>IF(AND(AU$3&gt;=$D21,AU$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D21,AU$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AV21" s="1">
-        <f>IF(AND(AV$3&gt;=$D21,AV$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D21,AV$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AW21" s="1">
-        <f>IF(AND(AW$3&gt;=$D21,AW$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D21,AW$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AX21" s="1">
-        <f>IF(AND(AX$3&gt;=$D21,AX$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D21,AX$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AY21" s="1">
-        <f>IF(AND(AY$3&gt;=$D21,AY$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D21,AY$1&lt;=$E21),"█","")</f>
       </c>
       <c r="AZ21" s="1">
-        <f>IF(AND(AZ$3&gt;=$D21,AZ$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D21,AZ$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BA21" s="1">
-        <f>IF(AND(BA$3&gt;=$D21,BA$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D21,BA$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BB21" s="1">
-        <f>IF(AND(BB$3&gt;=$D21,BB$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D21,BB$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BC21" s="1">
-        <f>IF(AND(BC$3&gt;=$D21,BC$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D21,BC$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BD21" s="1">
-        <f>IF(AND(BD$3&gt;=$D21,BD$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D21,BD$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BE21" s="1">
-        <f>IF(AND(BE$3&gt;=$D21,BE$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D21,BE$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BF21" s="1">
-        <f>IF(AND(BF$3&gt;=$D21,BF$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D21,BF$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BG21" s="1">
-        <f>IF(AND(BG$3&gt;=$D21,BG$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D21,BG$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BH21" s="1">
-        <f>IF(AND(BH$3&gt;=$D21,BH$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D21,BH$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BI21" s="1">
-        <f>IF(AND(BI$3&gt;=$D21,BI$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D21,BI$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BJ21" s="1">
-        <f>IF(AND(BJ$3&gt;=$D21,BJ$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D21,BJ$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BK21" s="1">
-        <f>IF(AND(BK$3&gt;=$D21,BK$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D21,BK$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BL21" s="1">
-        <f>IF(AND(BL$3&gt;=$D21,BL$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D21,BL$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BM21" s="1">
-        <f>IF(AND(BM$3&gt;=$D21,BM$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D21,BM$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BN21" s="1">
-        <f>IF(AND(BN$3&gt;=$D21,BN$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D21,BN$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BO21" s="1">
-        <f>IF(AND(BO$3&gt;=$D21,BO$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D21,BO$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BP21" s="1">
-        <f>IF(AND(BP$3&gt;=$D21,BP$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D21,BP$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BQ21" s="1">
-        <f>IF(AND(BQ$3&gt;=$D21,BQ$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D21,BQ$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BR21" s="1">
-        <f>IF(AND(BR$3&gt;=$D21,BR$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D21,BR$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BS21" s="1">
-        <f>IF(AND(BS$3&gt;=$D21,BS$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D21,BS$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BT21" s="1">
-        <f>IF(AND(BT$3&gt;=$D21,BT$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D21,BT$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BU21" s="1">
-        <f>IF(AND(BU$3&gt;=$D21,BU$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D21,BU$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BV21" s="1">
-        <f>IF(AND(BV$3&gt;=$D21,BV$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D21,BV$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BW21" s="1">
-        <f>IF(AND(BW$3&gt;=$D21,BW$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D21,BW$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BX21" s="1">
-        <f>IF(AND(BX$3&gt;=$D21,BX$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D21,BX$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BY21" s="1">
-        <f>IF(AND(BY$3&gt;=$D21,BY$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D21,BY$1&lt;=$E21),"█","")</f>
       </c>
       <c r="BZ21" s="1">
-        <f>IF(AND(BZ$3&gt;=$D21,BZ$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D21,BZ$1&lt;=$E21),"█","")</f>
       </c>
       <c r="CA21" s="1">
-        <f>IF(AND(CA$3&gt;=$D21,CA$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D21,CA$1&lt;=$E21),"█","")</f>
       </c>
       <c r="CB21" s="1">
-        <f>IF(AND(CB$3&gt;=$D21,CB$3&lt;=$E21),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D21,CB$1&lt;=$E21),"█","")</f>
       </c>
     </row>
     <row r="22" spans="1:35" x14ac:dyDescent="0.3">
@@ -5502,236 +5644,235 @@
         <v>3</v>
       </c>
       <c r="D22" s="7">
-        <v>46245</v>
+        <f>E21+1</f>
       </c>
       <c r="E22" s="7">
         <f>D22+C22</f>
-        <v>46248</v>
       </c>
       <c r="F22" s="1">
-        <f>IF(AND(F$3&gt;=$D22,F$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D22,F$1&lt;=$E22),"█","")</f>
       </c>
       <c r="G22" s="1">
-        <f>IF(AND(G$3&gt;=$D22,G$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D22,G$1&lt;=$E22),"█","")</f>
       </c>
       <c r="H22" s="1">
-        <f>IF(AND(H$3&gt;=$D22,H$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D22,H$1&lt;=$E22),"█","")</f>
       </c>
       <c r="I22" s="1">
-        <f>IF(AND(I$3&gt;=$D22,I$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D22,I$1&lt;=$E22),"█","")</f>
       </c>
       <c r="J22" s="1">
-        <f>IF(AND(J$3&gt;=$D22,J$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D22,J$1&lt;=$E22),"█","")</f>
       </c>
       <c r="K22" s="1">
-        <f>IF(AND(K$3&gt;=$D22,K$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D22,K$1&lt;=$E22),"█","")</f>
       </c>
       <c r="L22" s="1">
-        <f>IF(AND(L$3&gt;=$D22,L$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D22,L$1&lt;=$E22),"█","")</f>
       </c>
       <c r="M22" s="1">
-        <f>IF(AND(M$3&gt;=$D22,M$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D22,M$1&lt;=$E22),"█","")</f>
       </c>
       <c r="N22" s="1">
-        <f>IF(AND(N$3&gt;=$D22,N$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D22,N$1&lt;=$E22),"█","")</f>
       </c>
       <c r="O22" s="1">
-        <f>IF(AND(O$3&gt;=$D22,O$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D22,O$1&lt;=$E22),"█","")</f>
       </c>
       <c r="P22" s="1">
-        <f>IF(AND(P$3&gt;=$D22,P$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D22,P$1&lt;=$E22),"█","")</f>
       </c>
       <c r="Q22" s="1">
-        <f>IF(AND(Q$3&gt;=$D22,Q$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D22,Q$1&lt;=$E22),"█","")</f>
       </c>
       <c r="R22" s="1">
-        <f>IF(AND(R$3&gt;=$D22,R$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D22,R$1&lt;=$E22),"█","")</f>
       </c>
       <c r="S22" s="1">
-        <f>IF(AND(S$3&gt;=$D22,S$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D22,S$1&lt;=$E22),"█","")</f>
       </c>
       <c r="T22" s="1">
-        <f>IF(AND(T$3&gt;=$D22,T$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D22,T$1&lt;=$E22),"█","")</f>
       </c>
       <c r="U22" s="1">
-        <f>IF(AND(U$3&gt;=$D22,U$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D22,U$1&lt;=$E22),"█","")</f>
       </c>
       <c r="V22" s="1">
-        <f>IF(AND(V$3&gt;=$D22,V$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D22,V$1&lt;=$E22),"█","")</f>
       </c>
       <c r="W22" s="1">
-        <f>IF(AND(W$3&gt;=$D22,W$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D22,W$1&lt;=$E22),"█","")</f>
       </c>
       <c r="X22" s="1">
-        <f>IF(AND(X$3&gt;=$D22,X$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D22,X$1&lt;=$E22),"█","")</f>
       </c>
       <c r="Y22" s="1">
-        <f>IF(AND(Y$3&gt;=$D22,Y$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D22,Y$1&lt;=$E22),"█","")</f>
       </c>
       <c r="Z22" s="1">
-        <f>IF(AND(Z$3&gt;=$D22,Z$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D22,Z$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AA22" s="1">
-        <f>IF(AND(AA$3&gt;=$D22,AA$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D22,AA$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AB22" s="1">
-        <f>IF(AND(AB$3&gt;=$D22,AB$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D22,AB$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AC22" s="1">
-        <f>IF(AND(AC$3&gt;=$D22,AC$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D22,AC$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AD22" s="1">
-        <f>IF(AND(AD$3&gt;=$D22,AD$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D22,AD$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AE22" s="1">
-        <f>IF(AND(AE$3&gt;=$D22,AE$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D22,AE$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AF22" s="1">
-        <f>IF(AND(AF$3&gt;=$D22,AF$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D22,AF$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AG22" s="1">
-        <f>IF(AND(AG$3&gt;=$D22,AG$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D22,AG$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AH22" s="1">
-        <f>IF(AND(AH$3&gt;=$D22,AH$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D22,AH$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AI22" s="1">
-        <f>IF(AND(AI$3&gt;=$D22,AI$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D22,AI$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AJ22" s="1">
-        <f>IF(AND(AJ$3&gt;=$D22,AJ$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D22,AJ$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AK22" s="1">
-        <f>IF(AND(AK$3&gt;=$D22,AK$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D22,AK$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AL22" s="1">
-        <f>IF(AND(AL$3&gt;=$D22,AL$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D22,AL$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AM22" s="1">
-        <f>IF(AND(AM$3&gt;=$D22,AM$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D22,AM$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AN22" s="1">
-        <f>IF(AND(AN$3&gt;=$D22,AN$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D22,AN$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AO22" s="1">
-        <f>IF(AND(AO$3&gt;=$D22,AO$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D22,AO$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AP22" s="1">
-        <f>IF(AND(AP$3&gt;=$D22,AP$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D22,AP$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AQ22" s="1">
-        <f>IF(AND(AQ$3&gt;=$D22,AQ$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D22,AQ$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AR22" s="1">
-        <f>IF(AND(AR$3&gt;=$D22,AR$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D22,AR$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AS22" s="1">
-        <f>IF(AND(AS$3&gt;=$D22,AS$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D22,AS$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AT22" s="1">
-        <f>IF(AND(AT$3&gt;=$D22,AT$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D22,AT$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AU22" s="1">
-        <f>IF(AND(AU$3&gt;=$D22,AU$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D22,AU$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AV22" s="1">
-        <f>IF(AND(AV$3&gt;=$D22,AV$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D22,AV$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AW22" s="1">
-        <f>IF(AND(AW$3&gt;=$D22,AW$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D22,AW$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AX22" s="1">
-        <f>IF(AND(AX$3&gt;=$D22,AX$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D22,AX$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AY22" s="1">
-        <f>IF(AND(AY$3&gt;=$D22,AY$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D22,AY$1&lt;=$E22),"█","")</f>
       </c>
       <c r="AZ22" s="1">
-        <f>IF(AND(AZ$3&gt;=$D22,AZ$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D22,AZ$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BA22" s="1">
-        <f>IF(AND(BA$3&gt;=$D22,BA$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D22,BA$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BB22" s="1">
-        <f>IF(AND(BB$3&gt;=$D22,BB$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D22,BB$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BC22" s="1">
-        <f>IF(AND(BC$3&gt;=$D22,BC$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D22,BC$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BD22" s="1">
-        <f>IF(AND(BD$3&gt;=$D22,BD$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D22,BD$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BE22" s="1">
-        <f>IF(AND(BE$3&gt;=$D22,BE$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D22,BE$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BF22" s="1">
-        <f>IF(AND(BF$3&gt;=$D22,BF$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D22,BF$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BG22" s="1">
-        <f>IF(AND(BG$3&gt;=$D22,BG$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D22,BG$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BH22" s="1">
-        <f>IF(AND(BH$3&gt;=$D22,BH$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D22,BH$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BI22" s="1">
-        <f>IF(AND(BI$3&gt;=$D22,BI$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D22,BI$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BJ22" s="1">
-        <f>IF(AND(BJ$3&gt;=$D22,BJ$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D22,BJ$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BK22" s="1">
-        <f>IF(AND(BK$3&gt;=$D22,BK$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D22,BK$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BL22" s="1">
-        <f>IF(AND(BL$3&gt;=$D22,BL$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D22,BL$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BM22" s="1">
-        <f>IF(AND(BM$3&gt;=$D22,BM$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D22,BM$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BN22" s="1">
-        <f>IF(AND(BN$3&gt;=$D22,BN$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D22,BN$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BO22" s="1">
-        <f>IF(AND(BO$3&gt;=$D22,BO$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D22,BO$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BP22" s="1">
-        <f>IF(AND(BP$3&gt;=$D22,BP$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D22,BP$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BQ22" s="1">
-        <f>IF(AND(BQ$3&gt;=$D22,BQ$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D22,BQ$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BR22" s="1">
-        <f>IF(AND(BR$3&gt;=$D22,BR$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D22,BR$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BS22" s="1">
-        <f>IF(AND(BS$3&gt;=$D22,BS$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D22,BS$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BT22" s="1">
-        <f>IF(AND(BT$3&gt;=$D22,BT$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D22,BT$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BU22" s="1">
-        <f>IF(AND(BU$3&gt;=$D22,BU$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D22,BU$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BV22" s="1">
-        <f>IF(AND(BV$3&gt;=$D22,BV$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D22,BV$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BW22" s="1">
-        <f>IF(AND(BW$3&gt;=$D22,BW$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D22,BW$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BX22" s="1">
-        <f>IF(AND(BX$3&gt;=$D22,BX$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D22,BX$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BY22" s="1">
-        <f>IF(AND(BY$3&gt;=$D22,BY$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D22,BY$1&lt;=$E22),"█","")</f>
       </c>
       <c r="BZ22" s="1">
-        <f>IF(AND(BZ$3&gt;=$D22,BZ$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D22,BZ$1&lt;=$E22),"█","")</f>
       </c>
       <c r="CA22" s="1">
-        <f>IF(AND(CA$3&gt;=$D22,CA$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D22,CA$1&lt;=$E22),"█","")</f>
       </c>
       <c r="CB22" s="1">
-        <f>IF(AND(CB$3&gt;=$D22,CB$3&lt;=$E22),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D22,CB$1&lt;=$E22),"█","")</f>
       </c>
     </row>
     <row r="23" spans="1:35" x14ac:dyDescent="0.3">
@@ -5745,236 +5886,235 @@
         <v>2</v>
       </c>
       <c r="D23" s="7">
-        <v>46248</v>
+        <f>E22+1</f>
       </c>
       <c r="E23" s="7">
         <f>D23+C23</f>
-        <v>46250</v>
       </c>
       <c r="F23" s="1">
-        <f>IF(AND(F$3&gt;=$D23,F$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D23,F$1&lt;=$E23),"█","")</f>
       </c>
       <c r="G23" s="1">
-        <f>IF(AND(G$3&gt;=$D23,G$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D23,G$1&lt;=$E23),"█","")</f>
       </c>
       <c r="H23" s="1">
-        <f>IF(AND(H$3&gt;=$D23,H$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D23,H$1&lt;=$E23),"█","")</f>
       </c>
       <c r="I23" s="1">
-        <f>IF(AND(I$3&gt;=$D23,I$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D23,I$1&lt;=$E23),"█","")</f>
       </c>
       <c r="J23" s="1">
-        <f>IF(AND(J$3&gt;=$D23,J$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D23,J$1&lt;=$E23),"█","")</f>
       </c>
       <c r="K23" s="1">
-        <f>IF(AND(K$3&gt;=$D23,K$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D23,K$1&lt;=$E23),"█","")</f>
       </c>
       <c r="L23" s="1">
-        <f>IF(AND(L$3&gt;=$D23,L$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D23,L$1&lt;=$E23),"█","")</f>
       </c>
       <c r="M23" s="1">
-        <f>IF(AND(M$3&gt;=$D23,M$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D23,M$1&lt;=$E23),"█","")</f>
       </c>
       <c r="N23" s="1">
-        <f>IF(AND(N$3&gt;=$D23,N$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D23,N$1&lt;=$E23),"█","")</f>
       </c>
       <c r="O23" s="1">
-        <f>IF(AND(O$3&gt;=$D23,O$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D23,O$1&lt;=$E23),"█","")</f>
       </c>
       <c r="P23" s="1">
-        <f>IF(AND(P$3&gt;=$D23,P$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D23,P$1&lt;=$E23),"█","")</f>
       </c>
       <c r="Q23" s="1">
-        <f>IF(AND(Q$3&gt;=$D23,Q$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D23,Q$1&lt;=$E23),"█","")</f>
       </c>
       <c r="R23" s="1">
-        <f>IF(AND(R$3&gt;=$D23,R$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D23,R$1&lt;=$E23),"█","")</f>
       </c>
       <c r="S23" s="1">
-        <f>IF(AND(S$3&gt;=$D23,S$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D23,S$1&lt;=$E23),"█","")</f>
       </c>
       <c r="T23" s="1">
-        <f>IF(AND(T$3&gt;=$D23,T$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D23,T$1&lt;=$E23),"█","")</f>
       </c>
       <c r="U23" s="1">
-        <f>IF(AND(U$3&gt;=$D23,U$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D23,U$1&lt;=$E23),"█","")</f>
       </c>
       <c r="V23" s="1">
-        <f>IF(AND(V$3&gt;=$D23,V$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D23,V$1&lt;=$E23),"█","")</f>
       </c>
       <c r="W23" s="1">
-        <f>IF(AND(W$3&gt;=$D23,W$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D23,W$1&lt;=$E23),"█","")</f>
       </c>
       <c r="X23" s="1">
-        <f>IF(AND(X$3&gt;=$D23,X$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D23,X$1&lt;=$E23),"█","")</f>
       </c>
       <c r="Y23" s="1">
-        <f>IF(AND(Y$3&gt;=$D23,Y$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D23,Y$1&lt;=$E23),"█","")</f>
       </c>
       <c r="Z23" s="1">
-        <f>IF(AND(Z$3&gt;=$D23,Z$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D23,Z$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AA23" s="1">
-        <f>IF(AND(AA$3&gt;=$D23,AA$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D23,AA$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AB23" s="1">
-        <f>IF(AND(AB$3&gt;=$D23,AB$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D23,AB$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AC23" s="1">
-        <f>IF(AND(AC$3&gt;=$D23,AC$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D23,AC$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AD23" s="1">
-        <f>IF(AND(AD$3&gt;=$D23,AD$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D23,AD$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AE23" s="1">
-        <f>IF(AND(AE$3&gt;=$D23,AE$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D23,AE$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AF23" s="1">
-        <f>IF(AND(AF$3&gt;=$D23,AF$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D23,AF$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AG23" s="1">
-        <f>IF(AND(AG$3&gt;=$D23,AG$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D23,AG$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AH23" s="1">
-        <f>IF(AND(AH$3&gt;=$D23,AH$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D23,AH$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AI23" s="1">
-        <f>IF(AND(AI$3&gt;=$D23,AI$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D23,AI$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AJ23" s="1">
-        <f>IF(AND(AJ$3&gt;=$D23,AJ$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D23,AJ$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AK23" s="1">
-        <f>IF(AND(AK$3&gt;=$D23,AK$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D23,AK$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AL23" s="1">
-        <f>IF(AND(AL$3&gt;=$D23,AL$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D23,AL$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AM23" s="1">
-        <f>IF(AND(AM$3&gt;=$D23,AM$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D23,AM$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AN23" s="1">
-        <f>IF(AND(AN$3&gt;=$D23,AN$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D23,AN$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AO23" s="1">
-        <f>IF(AND(AO$3&gt;=$D23,AO$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D23,AO$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AP23" s="1">
-        <f>IF(AND(AP$3&gt;=$D23,AP$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D23,AP$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AQ23" s="1">
-        <f>IF(AND(AQ$3&gt;=$D23,AQ$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D23,AQ$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AR23" s="1">
-        <f>IF(AND(AR$3&gt;=$D23,AR$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D23,AR$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AS23" s="1">
-        <f>IF(AND(AS$3&gt;=$D23,AS$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D23,AS$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AT23" s="1">
-        <f>IF(AND(AT$3&gt;=$D23,AT$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D23,AT$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AU23" s="1">
-        <f>IF(AND(AU$3&gt;=$D23,AU$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D23,AU$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AV23" s="1">
-        <f>IF(AND(AV$3&gt;=$D23,AV$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D23,AV$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AW23" s="1">
-        <f>IF(AND(AW$3&gt;=$D23,AW$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D23,AW$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AX23" s="1">
-        <f>IF(AND(AX$3&gt;=$D23,AX$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D23,AX$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AY23" s="1">
-        <f>IF(AND(AY$3&gt;=$D23,AY$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D23,AY$1&lt;=$E23),"█","")</f>
       </c>
       <c r="AZ23" s="1">
-        <f>IF(AND(AZ$3&gt;=$D23,AZ$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D23,AZ$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BA23" s="1">
-        <f>IF(AND(BA$3&gt;=$D23,BA$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D23,BA$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BB23" s="1">
-        <f>IF(AND(BB$3&gt;=$D23,BB$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D23,BB$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BC23" s="1">
-        <f>IF(AND(BC$3&gt;=$D23,BC$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D23,BC$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BD23" s="1">
-        <f>IF(AND(BD$3&gt;=$D23,BD$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D23,BD$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BE23" s="1">
-        <f>IF(AND(BE$3&gt;=$D23,BE$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D23,BE$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BF23" s="1">
-        <f>IF(AND(BF$3&gt;=$D23,BF$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D23,BF$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BG23" s="1">
-        <f>IF(AND(BG$3&gt;=$D23,BG$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D23,BG$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BH23" s="1">
-        <f>IF(AND(BH$3&gt;=$D23,BH$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D23,BH$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BI23" s="1">
-        <f>IF(AND(BI$3&gt;=$D23,BI$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D23,BI$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BJ23" s="1">
-        <f>IF(AND(BJ$3&gt;=$D23,BJ$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D23,BJ$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BK23" s="1">
-        <f>IF(AND(BK$3&gt;=$D23,BK$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D23,BK$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BL23" s="1">
-        <f>IF(AND(BL$3&gt;=$D23,BL$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D23,BL$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BM23" s="1">
-        <f>IF(AND(BM$3&gt;=$D23,BM$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D23,BM$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BN23" s="1">
-        <f>IF(AND(BN$3&gt;=$D23,BN$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D23,BN$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BO23" s="1">
-        <f>IF(AND(BO$3&gt;=$D23,BO$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D23,BO$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BP23" s="1">
-        <f>IF(AND(BP$3&gt;=$D23,BP$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D23,BP$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BQ23" s="1">
-        <f>IF(AND(BQ$3&gt;=$D23,BQ$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D23,BQ$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BR23" s="1">
-        <f>IF(AND(BR$3&gt;=$D23,BR$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D23,BR$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BS23" s="1">
-        <f>IF(AND(BS$3&gt;=$D23,BS$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D23,BS$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BT23" s="1">
-        <f>IF(AND(BT$3&gt;=$D23,BT$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D23,BT$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BU23" s="1">
-        <f>IF(AND(BU$3&gt;=$D23,BU$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D23,BU$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BV23" s="1">
-        <f>IF(AND(BV$3&gt;=$D23,BV$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D23,BV$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BW23" s="1">
-        <f>IF(AND(BW$3&gt;=$D23,BW$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D23,BW$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BX23" s="1">
-        <f>IF(AND(BX$3&gt;=$D23,BX$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D23,BX$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BY23" s="1">
-        <f>IF(AND(BY$3&gt;=$D23,BY$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D23,BY$1&lt;=$E23),"█","")</f>
       </c>
       <c r="BZ23" s="1">
-        <f>IF(AND(BZ$3&gt;=$D23,BZ$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D23,BZ$1&lt;=$E23),"█","")</f>
       </c>
       <c r="CA23" s="1">
-        <f>IF(AND(CA$3&gt;=$D23,CA$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D23,CA$1&lt;=$E23),"█","")</f>
       </c>
       <c r="CB23" s="1">
-        <f>IF(AND(CB$3&gt;=$D23,CB$3&lt;=$E23),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D23,CB$1&lt;=$E23),"█","")</f>
       </c>
     </row>
     <row r="24" spans="1:35" x14ac:dyDescent="0.3">
@@ -5992,232 +6132,231 @@
       </c>
       <c r="E24" s="7">
         <f>D24+C24</f>
-        <v>46250</v>
       </c>
       <c r="F24" s="1">
-        <f>IF(AND(F$3&gt;=$D24,F$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D24,F$1&lt;=$E24),"█","")</f>
       </c>
       <c r="G24" s="1">
-        <f>IF(AND(G$3&gt;=$D24,G$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D24,G$1&lt;=$E24),"█","")</f>
       </c>
       <c r="H24" s="1">
-        <f>IF(AND(H$3&gt;=$D24,H$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D24,H$1&lt;=$E24),"█","")</f>
       </c>
       <c r="I24" s="1">
-        <f>IF(AND(I$3&gt;=$D24,I$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D24,I$1&lt;=$E24),"█","")</f>
       </c>
       <c r="J24" s="1">
-        <f>IF(AND(J$3&gt;=$D24,J$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D24,J$1&lt;=$E24),"█","")</f>
       </c>
       <c r="K24" s="1">
-        <f>IF(AND(K$3&gt;=$D24,K$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D24,K$1&lt;=$E24),"█","")</f>
       </c>
       <c r="L24" s="1">
-        <f>IF(AND(L$3&gt;=$D24,L$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D24,L$1&lt;=$E24),"█","")</f>
       </c>
       <c r="M24" s="1">
-        <f>IF(AND(M$3&gt;=$D24,M$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D24,M$1&lt;=$E24),"█","")</f>
       </c>
       <c r="N24" s="1">
-        <f>IF(AND(N$3&gt;=$D24,N$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D24,N$1&lt;=$E24),"█","")</f>
       </c>
       <c r="O24" s="1">
-        <f>IF(AND(O$3&gt;=$D24,O$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D24,O$1&lt;=$E24),"█","")</f>
       </c>
       <c r="P24" s="1">
-        <f>IF(AND(P$3&gt;=$D24,P$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D24,P$1&lt;=$E24),"█","")</f>
       </c>
       <c r="Q24" s="1">
-        <f>IF(AND(Q$3&gt;=$D24,Q$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D24,Q$1&lt;=$E24),"█","")</f>
       </c>
       <c r="R24" s="1">
-        <f>IF(AND(R$3&gt;=$D24,R$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D24,R$1&lt;=$E24),"█","")</f>
       </c>
       <c r="S24" s="1">
-        <f>IF(AND(S$3&gt;=$D24,S$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D24,S$1&lt;=$E24),"█","")</f>
       </c>
       <c r="T24" s="1">
-        <f>IF(AND(T$3&gt;=$D24,T$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D24,T$1&lt;=$E24),"█","")</f>
       </c>
       <c r="U24" s="1">
-        <f>IF(AND(U$3&gt;=$D24,U$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D24,U$1&lt;=$E24),"█","")</f>
       </c>
       <c r="V24" s="1">
-        <f>IF(AND(V$3&gt;=$D24,V$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D24,V$1&lt;=$E24),"█","")</f>
       </c>
       <c r="W24" s="1">
-        <f>IF(AND(W$3&gt;=$D24,W$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D24,W$1&lt;=$E24),"█","")</f>
       </c>
       <c r="X24" s="1">
-        <f>IF(AND(X$3&gt;=$D24,X$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D24,X$1&lt;=$E24),"█","")</f>
       </c>
       <c r="Y24" s="1">
-        <f>IF(AND(Y$3&gt;=$D24,Y$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D24,Y$1&lt;=$E24),"█","")</f>
       </c>
       <c r="Z24" s="1">
-        <f>IF(AND(Z$3&gt;=$D24,Z$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D24,Z$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AA24" s="1">
-        <f>IF(AND(AA$3&gt;=$D24,AA$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D24,AA$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AB24" s="1">
-        <f>IF(AND(AB$3&gt;=$D24,AB$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D24,AB$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AC24" s="1">
-        <f>IF(AND(AC$3&gt;=$D24,AC$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D24,AC$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AD24" s="1">
-        <f>IF(AND(AD$3&gt;=$D24,AD$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D24,AD$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AE24" s="1">
-        <f>IF(AND(AE$3&gt;=$D24,AE$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D24,AE$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AF24" s="1">
-        <f>IF(AND(AF$3&gt;=$D24,AF$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D24,AF$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AG24" s="1">
-        <f>IF(AND(AG$3&gt;=$D24,AG$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D24,AG$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AH24" s="1">
-        <f>IF(AND(AH$3&gt;=$D24,AH$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D24,AH$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AI24" s="1">
-        <f>IF(AND(AI$3&gt;=$D24,AI$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D24,AI$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AJ24" s="1">
-        <f>IF(AND(AJ$3&gt;=$D24,AJ$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D24,AJ$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AK24" s="1">
-        <f>IF(AND(AK$3&gt;=$D24,AK$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D24,AK$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AL24" s="1">
-        <f>IF(AND(AL$3&gt;=$D24,AL$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D24,AL$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AM24" s="1">
-        <f>IF(AND(AM$3&gt;=$D24,AM$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D24,AM$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AN24" s="1">
-        <f>IF(AND(AN$3&gt;=$D24,AN$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D24,AN$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AO24" s="1">
-        <f>IF(AND(AO$3&gt;=$D24,AO$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D24,AO$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AP24" s="1">
-        <f>IF(AND(AP$3&gt;=$D24,AP$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D24,AP$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AQ24" s="1">
-        <f>IF(AND(AQ$3&gt;=$D24,AQ$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D24,AQ$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AR24" s="1">
-        <f>IF(AND(AR$3&gt;=$D24,AR$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D24,AR$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AS24" s="1">
-        <f>IF(AND(AS$3&gt;=$D24,AS$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D24,AS$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AT24" s="1">
-        <f>IF(AND(AT$3&gt;=$D24,AT$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D24,AT$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AU24" s="1">
-        <f>IF(AND(AU$3&gt;=$D24,AU$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D24,AU$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AV24" s="1">
-        <f>IF(AND(AV$3&gt;=$D24,AV$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D24,AV$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AW24" s="1">
-        <f>IF(AND(AW$3&gt;=$D24,AW$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D24,AW$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AX24" s="1">
-        <f>IF(AND(AX$3&gt;=$D24,AX$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D24,AX$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AY24" s="1">
-        <f>IF(AND(AY$3&gt;=$D24,AY$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D24,AY$1&lt;=$E24),"█","")</f>
       </c>
       <c r="AZ24" s="1">
-        <f>IF(AND(AZ$3&gt;=$D24,AZ$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D24,AZ$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BA24" s="1">
-        <f>IF(AND(BA$3&gt;=$D24,BA$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D24,BA$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BB24" s="1">
-        <f>IF(AND(BB$3&gt;=$D24,BB$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D24,BB$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BC24" s="1">
-        <f>IF(AND(BC$3&gt;=$D24,BC$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D24,BC$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BD24" s="1">
-        <f>IF(AND(BD$3&gt;=$D24,BD$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D24,BD$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BE24" s="1">
-        <f>IF(AND(BE$3&gt;=$D24,BE$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D24,BE$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BF24" s="1">
-        <f>IF(AND(BF$3&gt;=$D24,BF$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D24,BF$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BG24" s="1">
-        <f>IF(AND(BG$3&gt;=$D24,BG$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D24,BG$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BH24" s="1">
-        <f>IF(AND(BH$3&gt;=$D24,BH$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D24,BH$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BI24" s="1">
-        <f>IF(AND(BI$3&gt;=$D24,BI$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D24,BI$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BJ24" s="1">
-        <f>IF(AND(BJ$3&gt;=$D24,BJ$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D24,BJ$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BK24" s="1">
-        <f>IF(AND(BK$3&gt;=$D24,BK$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D24,BK$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BL24" s="1">
-        <f>IF(AND(BL$3&gt;=$D24,BL$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D24,BL$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BM24" s="1">
-        <f>IF(AND(BM$3&gt;=$D24,BM$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D24,BM$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BN24" s="1">
-        <f>IF(AND(BN$3&gt;=$D24,BN$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D24,BN$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BO24" s="1">
-        <f>IF(AND(BO$3&gt;=$D24,BO$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D24,BO$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BP24" s="1">
-        <f>IF(AND(BP$3&gt;=$D24,BP$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D24,BP$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BQ24" s="1">
-        <f>IF(AND(BQ$3&gt;=$D24,BQ$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D24,BQ$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BR24" s="1">
-        <f>IF(AND(BR$3&gt;=$D24,BR$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D24,BR$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BS24" s="1">
-        <f>IF(AND(BS$3&gt;=$D24,BS$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D24,BS$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BT24" s="1">
-        <f>IF(AND(BT$3&gt;=$D24,BT$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D24,BT$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BU24" s="1">
-        <f>IF(AND(BU$3&gt;=$D24,BU$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D24,BU$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BV24" s="1">
-        <f>IF(AND(BV$3&gt;=$D24,BV$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D24,BV$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BW24" s="1">
-        <f>IF(AND(BW$3&gt;=$D24,BW$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D24,BW$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BX24" s="1">
-        <f>IF(AND(BX$3&gt;=$D24,BX$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D24,BX$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BY24" s="1">
-        <f>IF(AND(BY$3&gt;=$D24,BY$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D24,BY$1&lt;=$E24),"█","")</f>
       </c>
       <c r="BZ24" s="1">
-        <f>IF(AND(BZ$3&gt;=$D24,BZ$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D24,BZ$1&lt;=$E24),"█","")</f>
       </c>
       <c r="CA24" s="1">
-        <f>IF(AND(CA$3&gt;=$D24,CA$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D24,CA$1&lt;=$E24),"█","")</f>
       </c>
       <c r="CB24" s="1">
-        <f>IF(AND(CB$3&gt;=$D24,CB$3&lt;=$E24),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D24,CB$1&lt;=$E24),"█","")</f>
       </c>
     </row>
     <row r="25" spans="1:35" x14ac:dyDescent="0.3">
@@ -6231,236 +6370,235 @@
         <v>3</v>
       </c>
       <c r="D25" s="7">
-        <v>46247</v>
+        <f>E22</f>
       </c>
       <c r="E25" s="7">
         <f>D25+C25</f>
-        <v>46250</v>
       </c>
       <c r="F25" s="1">
-        <f>IF(AND(F$3&gt;=$D25,F$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(F$1&gt;=$D25,F$1&lt;=$E25),"█","")</f>
       </c>
       <c r="G25" s="1">
-        <f>IF(AND(G$3&gt;=$D25,G$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(G$1&gt;=$D25,G$1&lt;=$E25),"█","")</f>
       </c>
       <c r="H25" s="1">
-        <f>IF(AND(H$3&gt;=$D25,H$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(H$1&gt;=$D25,H$1&lt;=$E25),"█","")</f>
       </c>
       <c r="I25" s="1">
-        <f>IF(AND(I$3&gt;=$D25,I$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(I$1&gt;=$D25,I$1&lt;=$E25),"█","")</f>
       </c>
       <c r="J25" s="1">
-        <f>IF(AND(J$3&gt;=$D25,J$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(J$1&gt;=$D25,J$1&lt;=$E25),"█","")</f>
       </c>
       <c r="K25" s="1">
-        <f>IF(AND(K$3&gt;=$D25,K$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(K$1&gt;=$D25,K$1&lt;=$E25),"█","")</f>
       </c>
       <c r="L25" s="1">
-        <f>IF(AND(L$3&gt;=$D25,L$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(L$1&gt;=$D25,L$1&lt;=$E25),"█","")</f>
       </c>
       <c r="M25" s="1">
-        <f>IF(AND(M$3&gt;=$D25,M$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(M$1&gt;=$D25,M$1&lt;=$E25),"█","")</f>
       </c>
       <c r="N25" s="1">
-        <f>IF(AND(N$3&gt;=$D25,N$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(N$1&gt;=$D25,N$1&lt;=$E25),"█","")</f>
       </c>
       <c r="O25" s="1">
-        <f>IF(AND(O$3&gt;=$D25,O$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(O$1&gt;=$D25,O$1&lt;=$E25),"█","")</f>
       </c>
       <c r="P25" s="1">
-        <f>IF(AND(P$3&gt;=$D25,P$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(P$1&gt;=$D25,P$1&lt;=$E25),"█","")</f>
       </c>
       <c r="Q25" s="1">
-        <f>IF(AND(Q$3&gt;=$D25,Q$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(Q$1&gt;=$D25,Q$1&lt;=$E25),"█","")</f>
       </c>
       <c r="R25" s="1">
-        <f>IF(AND(R$3&gt;=$D25,R$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(R$1&gt;=$D25,R$1&lt;=$E25),"█","")</f>
       </c>
       <c r="S25" s="1">
-        <f>IF(AND(S$3&gt;=$D25,S$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(S$1&gt;=$D25,S$1&lt;=$E25),"█","")</f>
       </c>
       <c r="T25" s="1">
-        <f>IF(AND(T$3&gt;=$D25,T$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(T$1&gt;=$D25,T$1&lt;=$E25),"█","")</f>
       </c>
       <c r="U25" s="1">
-        <f>IF(AND(U$3&gt;=$D25,U$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(U$1&gt;=$D25,U$1&lt;=$E25),"█","")</f>
       </c>
       <c r="V25" s="1">
-        <f>IF(AND(V$3&gt;=$D25,V$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(V$1&gt;=$D25,V$1&lt;=$E25),"█","")</f>
       </c>
       <c r="W25" s="1">
-        <f>IF(AND(W$3&gt;=$D25,W$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(W$1&gt;=$D25,W$1&lt;=$E25),"█","")</f>
       </c>
       <c r="X25" s="1">
-        <f>IF(AND(X$3&gt;=$D25,X$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(X$1&gt;=$D25,X$1&lt;=$E25),"█","")</f>
       </c>
       <c r="Y25" s="1">
-        <f>IF(AND(Y$3&gt;=$D25,Y$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(Y$1&gt;=$D25,Y$1&lt;=$E25),"█","")</f>
       </c>
       <c r="Z25" s="1">
-        <f>IF(AND(Z$3&gt;=$D25,Z$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(Z$1&gt;=$D25,Z$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AA25" s="1">
-        <f>IF(AND(AA$3&gt;=$D25,AA$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AA$1&gt;=$D25,AA$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AB25" s="1">
-        <f>IF(AND(AB$3&gt;=$D25,AB$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AB$1&gt;=$D25,AB$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AC25" s="1">
-        <f>IF(AND(AC$3&gt;=$D25,AC$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AC$1&gt;=$D25,AC$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AD25" s="1">
-        <f>IF(AND(AD$3&gt;=$D25,AD$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AD$1&gt;=$D25,AD$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AE25" s="1">
-        <f>IF(AND(AE$3&gt;=$D25,AE$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AE$1&gt;=$D25,AE$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AF25" s="1">
-        <f>IF(AND(AF$3&gt;=$D25,AF$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AF$1&gt;=$D25,AF$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AG25" s="1">
-        <f>IF(AND(AG$3&gt;=$D25,AG$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AG$1&gt;=$D25,AG$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AH25" s="1">
-        <f>IF(AND(AH$3&gt;=$D25,AH$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AH$1&gt;=$D25,AH$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AI25" s="1">
-        <f>IF(AND(AI$3&gt;=$D25,AI$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AI$1&gt;=$D25,AI$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AJ25" s="1">
-        <f>IF(AND(AJ$3&gt;=$D25,AJ$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AJ$1&gt;=$D25,AJ$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AK25" s="1">
-        <f>IF(AND(AK$3&gt;=$D25,AK$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AK$1&gt;=$D25,AK$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AL25" s="1">
-        <f>IF(AND(AL$3&gt;=$D25,AL$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AL$1&gt;=$D25,AL$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AM25" s="1">
-        <f>IF(AND(AM$3&gt;=$D25,AM$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AM$1&gt;=$D25,AM$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AN25" s="1">
-        <f>IF(AND(AN$3&gt;=$D25,AN$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AN$1&gt;=$D25,AN$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AO25" s="1">
-        <f>IF(AND(AO$3&gt;=$D25,AO$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AO$1&gt;=$D25,AO$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AP25" s="1">
-        <f>IF(AND(AP$3&gt;=$D25,AP$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AP$1&gt;=$D25,AP$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AQ25" s="1">
-        <f>IF(AND(AQ$3&gt;=$D25,AQ$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AQ$1&gt;=$D25,AQ$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AR25" s="1">
-        <f>IF(AND(AR$3&gt;=$D25,AR$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AR$1&gt;=$D25,AR$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AS25" s="1">
-        <f>IF(AND(AS$3&gt;=$D25,AS$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AS$1&gt;=$D25,AS$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AT25" s="1">
-        <f>IF(AND(AT$3&gt;=$D25,AT$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AT$1&gt;=$D25,AT$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AU25" s="1">
-        <f>IF(AND(AU$3&gt;=$D25,AU$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AU$1&gt;=$D25,AU$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AV25" s="1">
-        <f>IF(AND(AV$3&gt;=$D25,AV$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AV$1&gt;=$D25,AV$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AW25" s="1">
-        <f>IF(AND(AW$3&gt;=$D25,AW$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AW$1&gt;=$D25,AW$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AX25" s="1">
-        <f>IF(AND(AX$3&gt;=$D25,AX$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AX$1&gt;=$D25,AX$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AY25" s="1">
-        <f>IF(AND(AY$3&gt;=$D25,AY$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AY$1&gt;=$D25,AY$1&lt;=$E25),"█","")</f>
       </c>
       <c r="AZ25" s="1">
-        <f>IF(AND(AZ$3&gt;=$D25,AZ$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(AZ$1&gt;=$D25,AZ$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BA25" s="1">
-        <f>IF(AND(BA$3&gt;=$D25,BA$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BA$1&gt;=$D25,BA$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BB25" s="1">
-        <f>IF(AND(BB$3&gt;=$D25,BB$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BB$1&gt;=$D25,BB$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BC25" s="1">
-        <f>IF(AND(BC$3&gt;=$D25,BC$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BC$1&gt;=$D25,BC$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BD25" s="1">
-        <f>IF(AND(BD$3&gt;=$D25,BD$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BD$1&gt;=$D25,BD$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BE25" s="1">
-        <f>IF(AND(BE$3&gt;=$D25,BE$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BE$1&gt;=$D25,BE$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BF25" s="1">
-        <f>IF(AND(BF$3&gt;=$D25,BF$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BF$1&gt;=$D25,BF$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BG25" s="1">
-        <f>IF(AND(BG$3&gt;=$D25,BG$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BG$1&gt;=$D25,BG$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BH25" s="1">
-        <f>IF(AND(BH$3&gt;=$D25,BH$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BH$1&gt;=$D25,BH$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BI25" s="1">
-        <f>IF(AND(BI$3&gt;=$D25,BI$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BI$1&gt;=$D25,BI$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BJ25" s="1">
-        <f>IF(AND(BJ$3&gt;=$D25,BJ$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BJ$1&gt;=$D25,BJ$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BK25" s="1">
-        <f>IF(AND(BK$3&gt;=$D25,BK$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BK$1&gt;=$D25,BK$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BL25" s="1">
-        <f>IF(AND(BL$3&gt;=$D25,BL$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BL$1&gt;=$D25,BL$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BM25" s="1">
-        <f>IF(AND(BM$3&gt;=$D25,BM$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BM$1&gt;=$D25,BM$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BN25" s="1">
-        <f>IF(AND(BN$3&gt;=$D25,BN$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BN$1&gt;=$D25,BN$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BO25" s="1">
-        <f>IF(AND(BO$3&gt;=$D25,BO$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BO$1&gt;=$D25,BO$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BP25" s="1">
-        <f>IF(AND(BP$3&gt;=$D25,BP$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BP$1&gt;=$D25,BP$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BQ25" s="1">
-        <f>IF(AND(BQ$3&gt;=$D25,BQ$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BQ$1&gt;=$D25,BQ$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BR25" s="1">
-        <f>IF(AND(BR$3&gt;=$D25,BR$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BR$1&gt;=$D25,BR$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BS25" s="1">
-        <f>IF(AND(BS$3&gt;=$D25,BS$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BS$1&gt;=$D25,BS$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BT25" s="1">
-        <f>IF(AND(BT$3&gt;=$D25,BT$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BT$1&gt;=$D25,BT$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BU25" s="1">
-        <f>IF(AND(BU$3&gt;=$D25,BU$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BU$1&gt;=$D25,BU$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BV25" s="1">
-        <f>IF(AND(BV$3&gt;=$D25,BV$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BV$1&gt;=$D25,BV$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BW25" s="1">
-        <f>IF(AND(BW$3&gt;=$D25,BW$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BW$1&gt;=$D25,BW$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BX25" s="1">
-        <f>IF(AND(BX$3&gt;=$D25,BX$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BX$1&gt;=$D25,BX$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BY25" s="1">
-        <f>IF(AND(BY$3&gt;=$D25,BY$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BY$1&gt;=$D25,BY$1&lt;=$E25),"█","")</f>
       </c>
       <c r="BZ25" s="1">
-        <f>IF(AND(BZ$3&gt;=$D25,BZ$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(BZ$1&gt;=$D25,BZ$1&lt;=$E25),"█","")</f>
       </c>
       <c r="CA25" s="1">
-        <f>IF(AND(CA$3&gt;=$D25,CA$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(CA$1&gt;=$D25,CA$1&lt;=$E25),"█","")</f>
       </c>
       <c r="CB25" s="1">
-        <f>IF(AND(CB$3&gt;=$D25,CB$3&lt;=$E25),"█","")</f>
+        <f>IF(AND(CB$1&gt;=$D25,CB$1&lt;=$E25),"█","")</f>
       </c>
     </row>
   </sheetData>

--- a/Ebooks/Plan.xlsx
+++ b/Ebooks/Plan.xlsx
@@ -1521,10 +1521,10 @@
         <f>COUNTIF(F5:CB5,"█")</f>
       </c>
       <c r="D5" s="11">
-        <f>IF(C5&gt;0,MINIFS(F$1:CB$1,F5:CB5,"█"),"")</f>
+        <f>IF(C5&gt;0,INDEX(F$1:CB$1,MATCH("█",F5:CB5,0)),"")</f>
       </c>
       <c r="E5" s="11">
-        <f>IF(C5&gt;0,MAXIFS(F$1:CB$1,F5:CB5,"█"),"")</f>
+        <f>IF(C5&gt;0,LOOKUP(2,1/(F5:CB5="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
@@ -1613,10 +1613,10 @@
         <f>COUNTIF(F6:CB6,"█")</f>
       </c>
       <c r="D6" s="11">
-        <f>IF(C6&gt;0,MINIFS(F$1:CB$1,F6:CB6,"█"),"")</f>
+        <f>IF(C6&gt;0,INDEX(F$1:CB$1,MATCH("█",F6:CB6,0)),"")</f>
       </c>
       <c r="E6" s="11">
-        <f>IF(C6&gt;0,MAXIFS(F$1:CB$1,F6:CB6,"█"),"")</f>
+        <f>IF(C6&gt;0,LOOKUP(2,1/(F6:CB6="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F6" s="2" t="s">
         <v>28</v>
@@ -1709,10 +1709,10 @@
         <f>COUNTIF(F7:CB7,"█")</f>
       </c>
       <c r="D7" s="11">
-        <f>IF(C7&gt;0,MINIFS(F$1:CB$1,F7:CB7,"█"),"")</f>
+        <f>IF(C7&gt;0,INDEX(F$1:CB$1,MATCH("█",F7:CB7,0)),"")</f>
       </c>
       <c r="E7" s="11">
-        <f>IF(C7&gt;0,MAXIFS(F$1:CB$1,F7:CB7,"█"),"")</f>
+        <f>IF(C7&gt;0,LOOKUP(2,1/(F7:CB7="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
@@ -1807,10 +1807,10 @@
         <f>COUNTIF(F8:CB8,"█")</f>
       </c>
       <c r="D8" s="11">
-        <f>IF(C8&gt;0,MINIFS(F$1:CB$1,F8:CB8,"█"),"")</f>
+        <f>IF(C8&gt;0,INDEX(F$1:CB$1,MATCH("█",F8:CB8,0)),"")</f>
       </c>
       <c r="E8" s="11">
-        <f>IF(C8&gt;0,MAXIFS(F$1:CB$1,F8:CB8,"█"),"")</f>
+        <f>IF(C8&gt;0,LOOKUP(2,1/(F8:CB8="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
@@ -1899,10 +1899,10 @@
         <f>COUNTIF(F9:CB9,"█")</f>
       </c>
       <c r="D9" s="11">
-        <f>IF(C9&gt;0,MINIFS(F$1:CB$1,F9:CB9,"█"),"")</f>
+        <f>IF(C9&gt;0,INDEX(F$1:CB$1,MATCH("█",F9:CB9,0)),"")</f>
       </c>
       <c r="E9" s="11">
-        <f>IF(C9&gt;0,MAXIFS(F$1:CB$1,F9:CB9,"█"),"")</f>
+        <f>IF(C9&gt;0,LOOKUP(2,1/(F9:CB9="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
@@ -2239,10 +2239,10 @@
         <f>COUNTIF(F11:CB11,"█")</f>
       </c>
       <c r="D11" s="11">
-        <f>IF(C11&gt;0,MINIFS(F$1:CB$1,F11:CB11,"█"),"")</f>
+        <f>IF(C11&gt;0,INDEX(F$1:CB$1,MATCH("█",F11:CB11,0)),"")</f>
       </c>
       <c r="E11" s="11">
-        <f>IF(C11&gt;0,MAXIFS(F$1:CB$1,F11:CB11,"█"),"")</f>
+        <f>IF(C11&gt;0,LOOKUP(2,1/(F11:CB11="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F11" s="2" t="s">
         <v>28</v>
@@ -2333,10 +2333,10 @@
         <f>COUNTIF(F12:CB12,"█")</f>
       </c>
       <c r="D12" s="11">
-        <f>IF(C12&gt;0,MINIFS(F$1:CB$1,F12:CB12,"█"),"")</f>
+        <f>IF(C12&gt;0,INDEX(F$1:CB$1,MATCH("█",F12:CB12,0)),"")</f>
       </c>
       <c r="E12" s="11">
-        <f>IF(C12&gt;0,MAXIFS(F$1:CB$1,F12:CB12,"█"),"")</f>
+        <f>IF(C12&gt;0,LOOKUP(2,1/(F12:CB12="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2" t="s">
@@ -2431,10 +2431,10 @@
         <f>COUNTIF(F13:CB13,"█")</f>
       </c>
       <c r="D13" s="11">
-        <f>IF(C13&gt;0,MINIFS(F$1:CB$1,F13:CB13,"█"),"")</f>
+        <f>IF(C13&gt;0,INDEX(F$1:CB$1,MATCH("█",F13:CB13,0)),"")</f>
       </c>
       <c r="E13" s="11">
-        <f>IF(C13&gt;0,MAXIFS(F$1:CB$1,F13:CB13,"█"),"")</f>
+        <f>IF(C13&gt;0,LOOKUP(2,1/(F13:CB13="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -2525,10 +2525,10 @@
         <f>COUNTIF(F14:CB14,"█")</f>
       </c>
       <c r="D14" s="11">
-        <f>IF(C14&gt;0,MINIFS(F$1:CB$1,F14:CB14,"█"),"")</f>
+        <f>IF(C14&gt;0,INDEX(F$1:CB$1,MATCH("█",F14:CB14,0)),"")</f>
       </c>
       <c r="E14" s="11">
-        <f>IF(C14&gt;0,MAXIFS(F$1:CB$1,F14:CB14,"█"),"")</f>
+        <f>IF(C14&gt;0,LOOKUP(2,1/(F14:CB14="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F14" s="2" t="s">
         <v>28</v>
@@ -2883,10 +2883,10 @@
         <f>COUNTIF(F16:CB16,"█")</f>
       </c>
       <c r="D16" s="11">
-        <f>IF(C16&gt;0,MINIFS(F$1:CB$1,F16:CB16,"█"),"")</f>
+        <f>IF(C16&gt;0,INDEX(F$1:CB$1,MATCH("█",F16:CB16,0)),"")</f>
       </c>
       <c r="E16" s="11">
-        <f>IF(C16&gt;0,MAXIFS(F$1:CB$1,F16:CB16,"█"),"")</f>
+        <f>IF(C16&gt;0,LOOKUP(2,1/(F16:CB16="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
@@ -2979,10 +2979,10 @@
         <f>COUNTIF(F17:CB17,"█")</f>
       </c>
       <c r="D17" s="11">
-        <f>IF(C17&gt;0,MINIFS(F$1:CB$1,F17:CB17,"█"),"")</f>
+        <f>IF(C17&gt;0,INDEX(F$1:CB$1,MATCH("█",F17:CB17,0)),"")</f>
       </c>
       <c r="E17" s="11">
-        <f>IF(C17&gt;0,MAXIFS(F$1:CB$1,F17:CB17,"█"),"")</f>
+        <f>IF(C17&gt;0,LOOKUP(2,1/(F17:CB17="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
@@ -3077,10 +3077,10 @@
         <f>COUNTIF(F18:CB18,"█")</f>
       </c>
       <c r="D18" s="11">
-        <f>IF(C18&gt;0,MINIFS(F$1:CB$1,F18:CB18,"█"),"")</f>
+        <f>IF(C18&gt;0,INDEX(F$1:CB$1,MATCH("█",F18:CB18,0)),"")</f>
       </c>
       <c r="E18" s="11">
-        <f>IF(C18&gt;0,MAXIFS(F$1:CB$1,F18:CB18,"█"),"")</f>
+        <f>IF(C18&gt;0,LOOKUP(2,1/(F18:CB18="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
@@ -3175,10 +3175,10 @@
         <f>COUNTIF(F19:CB19,"█")</f>
       </c>
       <c r="D19" s="11">
-        <f>IF(C19&gt;0,MINIFS(F$1:CB$1,F19:CB19,"█"),"")</f>
+        <f>IF(C19&gt;0,INDEX(F$1:CB$1,MATCH("█",F19:CB19,0)),"")</f>
       </c>
       <c r="E19" s="11">
-        <f>IF(C19&gt;0,MAXIFS(F$1:CB$1,F19:CB19,"█"),"")</f>
+        <f>IF(C19&gt;0,LOOKUP(2,1/(F19:CB19="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
@@ -3275,10 +3275,10 @@
         <f>COUNTIF(F20:CB20,"█")</f>
       </c>
       <c r="D20" s="11">
-        <f>IF(C20&gt;0,MINIFS(F$1:CB$1,F20:CB20,"█"),"")</f>
+        <f>IF(C20&gt;0,INDEX(F$1:CB$1,MATCH("█",F20:CB20,0)),"")</f>
       </c>
       <c r="E20" s="11">
-        <f>IF(C20&gt;0,MAXIFS(F$1:CB$1,F20:CB20,"█"),"")</f>
+        <f>IF(C20&gt;0,LOOKUP(2,1/(F20:CB20="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -3383,10 +3383,10 @@
         <f>COUNTIF(F21:CB21,"█")</f>
       </c>
       <c r="D21" s="11">
-        <f>IF(C21&gt;0,MINIFS(F$1:CB$1,F21:CB21,"█"),"")</f>
+        <f>IF(C21&gt;0,INDEX(F$1:CB$1,MATCH("█",F21:CB21,0)),"")</f>
       </c>
       <c r="E21" s="11">
-        <f>IF(C21&gt;0,MAXIFS(F$1:CB$1,F21:CB21,"█"),"")</f>
+        <f>IF(C21&gt;0,LOOKUP(2,1/(F21:CB21="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -3481,10 +3481,10 @@
         <f>COUNTIF(F22:CB22,"█")</f>
       </c>
       <c r="D22" s="11">
-        <f>IF(C22&gt;0,MINIFS(F$1:CB$1,F22:CB22,"█"),"")</f>
+        <f>IF(C22&gt;0,INDEX(F$1:CB$1,MATCH("█",F22:CB22,0)),"")</f>
       </c>
       <c r="E22" s="11">
-        <f>IF(C22&gt;0,MAXIFS(F$1:CB$1,F22:CB22,"█"),"")</f>
+        <f>IF(C22&gt;0,LOOKUP(2,1/(F22:CB22="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -3581,10 +3581,10 @@
         <f>COUNTIF(F23:CB23,"█")</f>
       </c>
       <c r="D23" s="11">
-        <f>IF(C23&gt;0,MINIFS(F$1:CB$1,F23:CB23,"█"),"")</f>
+        <f>IF(C23&gt;0,INDEX(F$1:CB$1,MATCH("█",F23:CB23,0)),"")</f>
       </c>
       <c r="E23" s="11">
-        <f>IF(C23&gt;0,MAXIFS(F$1:CB$1,F23:CB23,"█"),"")</f>
+        <f>IF(C23&gt;0,LOOKUP(2,1/(F23:CB23="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -3675,10 +3675,10 @@
         <f>COUNTIF(F24:CB24,"█")</f>
       </c>
       <c r="D24" s="11">
-        <f>IF(C24&gt;0,MINIFS(F$1:CB$1,F24:CB24,"█"),"")</f>
+        <f>IF(C24&gt;0,INDEX(F$1:CB$1,MATCH("█",F24:CB24,0)),"")</f>
       </c>
       <c r="E24" s="11">
-        <f>IF(C24&gt;0,MAXIFS(F$1:CB$1,F24:CB24,"█"),"")</f>
+        <f>IF(C24&gt;0,LOOKUP(2,1/(F24:CB24="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F24" s="2" t="s">
         <v>28</v>
@@ -3817,10 +3817,10 @@
         <f>COUNTIF(F25:CB25,"█")</f>
       </c>
       <c r="D25" s="11">
-        <f>IF(C25&gt;0,MINIFS(F$1:CB$1,F25:CB25,"█"),"")</f>
+        <f>IF(C25&gt;0,INDEX(F$1:CB$1,MATCH("█",F25:CB25,0)),"")</f>
       </c>
       <c r="E25" s="11">
-        <f>IF(C25&gt;0,MAXIFS(F$1:CB$1,F25:CB25,"█"),"")</f>
+        <f>IF(C25&gt;0,LOOKUP(2,1/(F25:CB25="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>

--- a/Ebooks/Plan.xlsx
+++ b/Ebooks/Plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="48">
   <si>
     <t>WBS</t>
   </si>
@@ -97,10 +97,10 @@
     <t>Project Introduction</t>
   </si>
   <si>
-    <t>Business objective</t>
+    <t>█</t>
   </si>
   <si>
-    <t>█</t>
+    <t>Business objective</t>
   </si>
   <si>
     <t>SWOT Analysis</t>
@@ -1526,88 +1526,238 @@
       <c r="E5" s="11">
         <f>IF(C5&gt;0,LOOKUP(2,1/(F5:CB5="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
-      <c r="AR5" s="2"/>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2"/>
-      <c r="BD5" s="2"/>
-      <c r="BE5" s="2"/>
-      <c r="BF5" s="2"/>
-      <c r="BG5" s="2"/>
-      <c r="BH5" s="2"/>
-      <c r="BI5" s="2"/>
-      <c r="BJ5" s="2"/>
-      <c r="BK5" s="2"/>
-      <c r="BL5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="BN5" s="2"/>
-      <c r="BO5" s="2"/>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2"/>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2"/>
-      <c r="BU5" s="2"/>
-      <c r="BV5" s="2"/>
-      <c r="BW5" s="2"/>
-      <c r="BX5" s="2"/>
-      <c r="BY5" s="2"/>
-      <c r="BZ5" s="2"/>
-      <c r="CA5" s="2"/>
-      <c r="CB5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB5" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>1.2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="10">
         <f>COUNTIF(F6:CB6,"█")</f>
@@ -1619,84 +1769,230 @@
         <f>IF(C6&gt;0,LOOKUP(2,1/(F6:CB6="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2"/>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2"/>
-      <c r="BF6" s="2"/>
-      <c r="BG6" s="2"/>
-      <c r="BH6" s="2"/>
-      <c r="BI6" s="2"/>
-      <c r="BJ6" s="2"/>
-      <c r="BK6" s="2"/>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2"/>
-      <c r="BO6" s="2"/>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2"/>
-      <c r="BU6" s="2"/>
-      <c r="BV6" s="2"/>
-      <c r="BW6" s="2"/>
-      <c r="BX6" s="2"/>
-      <c r="BY6" s="2"/>
-      <c r="BZ6" s="2"/>
-      <c r="CA6" s="2"/>
-      <c r="CB6" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -1714,87 +2010,231 @@
       <c r="E7" s="11">
         <f>IF(C7&gt;0,LOOKUP(2,1/(F7:CB7="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="H7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="2"/>
-      <c r="AL7" s="2"/>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2"/>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2"/>
-      <c r="BD7" s="2"/>
-      <c r="BE7" s="2"/>
-      <c r="BF7" s="2"/>
-      <c r="BG7" s="2"/>
-      <c r="BH7" s="2"/>
-      <c r="BI7" s="2"/>
-      <c r="BJ7" s="2"/>
-      <c r="BK7" s="2"/>
-      <c r="BL7" s="2"/>
-      <c r="BM7" s="2"/>
-      <c r="BN7" s="2"/>
-      <c r="BO7" s="2"/>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2"/>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2"/>
-      <c r="BU7" s="2"/>
-      <c r="BV7" s="2"/>
-      <c r="BW7" s="2"/>
-      <c r="BX7" s="2"/>
-      <c r="BY7" s="2"/>
-      <c r="BZ7" s="2"/>
-      <c r="CA7" s="2"/>
-      <c r="CB7" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB7" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -1812,81 +2252,231 @@
       <c r="E8" s="11">
         <f>IF(C8&gt;0,LOOKUP(2,1/(F8:CB8="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2"/>
-      <c r="AE8" s="2"/>
-      <c r="AF8" s="2"/>
-      <c r="AG8" s="2"/>
-      <c r="AH8" s="2"/>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2"/>
-      <c r="AR8" s="2"/>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2"/>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="AY8" s="2"/>
-      <c r="AZ8" s="2"/>
-      <c r="BA8" s="2"/>
-      <c r="BB8" s="2"/>
-      <c r="BC8" s="2"/>
-      <c r="BD8" s="2"/>
-      <c r="BE8" s="2"/>
-      <c r="BF8" s="2"/>
-      <c r="BG8" s="2"/>
-      <c r="BH8" s="2"/>
-      <c r="BI8" s="2"/>
-      <c r="BJ8" s="2"/>
-      <c r="BK8" s="2"/>
-      <c r="BL8" s="2"/>
-      <c r="BM8" s="2"/>
-      <c r="BN8" s="2"/>
-      <c r="BO8" s="2"/>
-      <c r="BP8" s="2"/>
-      <c r="BQ8" s="2"/>
-      <c r="BR8" s="2"/>
-      <c r="BS8" s="2"/>
-      <c r="BT8" s="2"/>
-      <c r="BU8" s="2"/>
-      <c r="BV8" s="2"/>
-      <c r="BW8" s="2"/>
-      <c r="BX8" s="2"/>
-      <c r="BY8" s="2"/>
-      <c r="BZ8" s="2"/>
-      <c r="CA8" s="2"/>
-      <c r="CB8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB8" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -1904,87 +2494,231 @@
       <c r="E9" s="11">
         <f>IF(C9&gt;0,LOOKUP(2,1/(F9:CB9="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-      <c r="AG9" s="2"/>
-      <c r="AH9" s="2"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2"/>
-      <c r="AR9" s="2"/>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2"/>
-      <c r="AU9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AX9" s="2"/>
-      <c r="AY9" s="2"/>
-      <c r="AZ9" s="2"/>
-      <c r="BA9" s="2"/>
-      <c r="BB9" s="2"/>
-      <c r="BC9" s="2"/>
-      <c r="BD9" s="2"/>
-      <c r="BE9" s="2"/>
-      <c r="BF9" s="2"/>
-      <c r="BG9" s="2"/>
-      <c r="BH9" s="2"/>
-      <c r="BI9" s="2"/>
-      <c r="BJ9" s="2"/>
-      <c r="BK9" s="2"/>
-      <c r="BL9" s="2"/>
-      <c r="BM9" s="2"/>
-      <c r="BN9" s="2"/>
-      <c r="BO9" s="2"/>
-      <c r="BP9" s="2"/>
-      <c r="BQ9" s="2"/>
-      <c r="BR9" s="2"/>
-      <c r="BS9" s="2"/>
-      <c r="BT9" s="2"/>
-      <c r="BU9" s="2"/>
-      <c r="BV9" s="2"/>
-      <c r="BW9" s="2"/>
-      <c r="BX9" s="2"/>
-      <c r="BY9" s="2"/>
-      <c r="BZ9" s="2"/>
-      <c r="CA9" s="2"/>
-      <c r="CB9" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB9" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
@@ -2245,82 +2979,230 @@
         <f>IF(C11&gt;0,LOOKUP(2,1/(F11:CB11="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
-      <c r="AG11" s="2"/>
-      <c r="AH11" s="2"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
-      <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
-      <c r="AP11" s="2"/>
-      <c r="AQ11" s="2"/>
-      <c r="AR11" s="2"/>
-      <c r="AS11" s="2"/>
-      <c r="AT11" s="2"/>
-      <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AX11" s="2"/>
-      <c r="AY11" s="2"/>
-      <c r="AZ11" s="2"/>
-      <c r="BA11" s="2"/>
-      <c r="BB11" s="2"/>
-      <c r="BC11" s="2"/>
-      <c r="BD11" s="2"/>
-      <c r="BE11" s="2"/>
-      <c r="BF11" s="2"/>
-      <c r="BG11" s="2"/>
-      <c r="BH11" s="2"/>
-      <c r="BI11" s="2"/>
-      <c r="BJ11" s="2"/>
-      <c r="BK11" s="2"/>
-      <c r="BL11" s="2"/>
-      <c r="BM11" s="2"/>
-      <c r="BN11" s="2"/>
-      <c r="BO11" s="2"/>
-      <c r="BP11" s="2"/>
-      <c r="BQ11" s="2"/>
-      <c r="BR11" s="2"/>
-      <c r="BS11" s="2"/>
-      <c r="BT11" s="2"/>
-      <c r="BU11" s="2"/>
-      <c r="BV11" s="2"/>
-      <c r="BW11" s="2"/>
-      <c r="BX11" s="2"/>
-      <c r="BY11" s="2"/>
-      <c r="BZ11" s="2"/>
-      <c r="CA11" s="2"/>
-      <c r="CB11" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB11" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -2338,87 +3220,231 @@
       <c r="E12" s="11">
         <f>IF(C12&gt;0,LOOKUP(2,1/(F12:CB12="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2"/>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2"/>
-      <c r="AG12" s="2"/>
-      <c r="AH12" s="2"/>
-      <c r="AI12" s="2"/>
-      <c r="AJ12" s="2"/>
-      <c r="AK12" s="2"/>
-      <c r="AL12" s="2"/>
-      <c r="AM12" s="2"/>
-      <c r="AN12" s="2"/>
-      <c r="AO12" s="2"/>
-      <c r="AP12" s="2"/>
-      <c r="AQ12" s="2"/>
-      <c r="AR12" s="2"/>
-      <c r="AS12" s="2"/>
-      <c r="AT12" s="2"/>
-      <c r="AU12" s="2"/>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
-      <c r="AX12" s="2"/>
-      <c r="AY12" s="2"/>
-      <c r="AZ12" s="2"/>
-      <c r="BA12" s="2"/>
-      <c r="BB12" s="2"/>
-      <c r="BC12" s="2"/>
-      <c r="BD12" s="2"/>
-      <c r="BE12" s="2"/>
-      <c r="BF12" s="2"/>
-      <c r="BG12" s="2"/>
-      <c r="BH12" s="2"/>
-      <c r="BI12" s="2"/>
-      <c r="BJ12" s="2"/>
-      <c r="BK12" s="2"/>
-      <c r="BL12" s="2"/>
-      <c r="BM12" s="2"/>
-      <c r="BN12" s="2"/>
-      <c r="BO12" s="2"/>
-      <c r="BP12" s="2"/>
-      <c r="BQ12" s="2"/>
-      <c r="BR12" s="2"/>
-      <c r="BS12" s="2"/>
-      <c r="BT12" s="2"/>
-      <c r="BU12" s="2"/>
-      <c r="BV12" s="2"/>
-      <c r="BW12" s="2"/>
-      <c r="BX12" s="2"/>
-      <c r="BY12" s="2"/>
-      <c r="BZ12" s="2"/>
-      <c r="CA12" s="2"/>
-      <c r="CB12" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB12" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
@@ -2436,83 +3462,231 @@
       <c r="E13" s="11">
         <f>IF(C13&gt;0,LOOKUP(2,1/(F13:CB13="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="J13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2"/>
-      <c r="AE13" s="2"/>
-      <c r="AF13" s="2"/>
-      <c r="AG13" s="2"/>
-      <c r="AH13" s="2"/>
-      <c r="AI13" s="2"/>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="2"/>
-      <c r="AL13" s="2"/>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="2"/>
-      <c r="AP13" s="2"/>
-      <c r="AQ13" s="2"/>
-      <c r="AR13" s="2"/>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2"/>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
-      <c r="AX13" s="2"/>
-      <c r="AY13" s="2"/>
-      <c r="AZ13" s="2"/>
-      <c r="BA13" s="2"/>
-      <c r="BB13" s="2"/>
-      <c r="BC13" s="2"/>
-      <c r="BD13" s="2"/>
-      <c r="BE13" s="2"/>
-      <c r="BF13" s="2"/>
-      <c r="BG13" s="2"/>
-      <c r="BH13" s="2"/>
-      <c r="BI13" s="2"/>
-      <c r="BJ13" s="2"/>
-      <c r="BK13" s="2"/>
-      <c r="BL13" s="2"/>
-      <c r="BM13" s="2"/>
-      <c r="BN13" s="2"/>
-      <c r="BO13" s="2"/>
-      <c r="BP13" s="2"/>
-      <c r="BQ13" s="2"/>
-      <c r="BR13" s="2"/>
-      <c r="BS13" s="2"/>
-      <c r="BT13" s="2"/>
-      <c r="BU13" s="2"/>
-      <c r="BV13" s="2"/>
-      <c r="BW13" s="2"/>
-      <c r="BX13" s="2"/>
-      <c r="BY13" s="2"/>
-      <c r="BZ13" s="2"/>
-      <c r="CA13" s="2"/>
-      <c r="CB13" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB13" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
@@ -2531,104 +3705,230 @@
         <f>IF(C14&gt;0,LOOKUP(2,1/(F14:CB14="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="K14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="Z14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AJ14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK14" s="2"/>
-      <c r="AL14" s="2"/>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2"/>
-      <c r="AP14" s="2"/>
-      <c r="AQ14" s="2"/>
-      <c r="AR14" s="2"/>
-      <c r="AS14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AT14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AU14" s="2"/>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
-      <c r="AX14" s="2"/>
-      <c r="AY14" s="2"/>
-      <c r="AZ14" s="2"/>
-      <c r="BA14" s="2"/>
-      <c r="BB14" s="2"/>
-      <c r="BC14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AU14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="BD14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="BE14" s="2"/>
-      <c r="BF14" s="2"/>
-      <c r="BG14" s="2"/>
-      <c r="BH14" s="2"/>
-      <c r="BI14" s="2"/>
-      <c r="BJ14" s="2"/>
-      <c r="BK14" s="2"/>
-      <c r="BL14" s="2"/>
-      <c r="BM14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="BE14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="BN14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="BO14" s="2"/>
-      <c r="BP14" s="2"/>
-      <c r="BQ14" s="2"/>
-      <c r="BR14" s="2"/>
-      <c r="BS14" s="2"/>
-      <c r="BT14" s="2"/>
-      <c r="BU14" s="2"/>
-      <c r="BV14" s="2"/>
-      <c r="BW14" s="2"/>
-      <c r="BX14" s="2"/>
-      <c r="BY14" s="2"/>
-      <c r="BZ14" s="2"/>
-      <c r="CA14" s="2"/>
-      <c r="CB14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="BO14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB14" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
@@ -2888,85 +4188,231 @@
       <c r="E16" s="11">
         <f>IF(C16&gt;0,LOOKUP(2,1/(F16:CB16="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="P16" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="2"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="2"/>
-      <c r="AE16" s="2"/>
-      <c r="AF16" s="2"/>
-      <c r="AG16" s="2"/>
-      <c r="AH16" s="2"/>
-      <c r="AI16" s="2"/>
-      <c r="AJ16" s="2"/>
-      <c r="AK16" s="2"/>
-      <c r="AL16" s="2"/>
-      <c r="AM16" s="2"/>
-      <c r="AN16" s="2"/>
-      <c r="AO16" s="2"/>
-      <c r="AP16" s="2"/>
-      <c r="AQ16" s="2"/>
-      <c r="AR16" s="2"/>
-      <c r="AS16" s="2"/>
-      <c r="AT16" s="2"/>
-      <c r="AU16" s="2"/>
-      <c r="AV16" s="2"/>
-      <c r="AW16" s="2"/>
-      <c r="AX16" s="2"/>
-      <c r="AY16" s="2"/>
-      <c r="AZ16" s="2"/>
-      <c r="BA16" s="2"/>
-      <c r="BB16" s="2"/>
-      <c r="BC16" s="2"/>
-      <c r="BD16" s="2"/>
-      <c r="BE16" s="2"/>
-      <c r="BF16" s="2"/>
-      <c r="BG16" s="2"/>
-      <c r="BH16" s="2"/>
-      <c r="BI16" s="2"/>
-      <c r="BJ16" s="2"/>
-      <c r="BK16" s="2"/>
-      <c r="BL16" s="2"/>
-      <c r="BM16" s="2"/>
-      <c r="BN16" s="2"/>
-      <c r="BO16" s="2"/>
-      <c r="BP16" s="2"/>
-      <c r="BQ16" s="2"/>
-      <c r="BR16" s="2"/>
-      <c r="BS16" s="2"/>
-      <c r="BT16" s="2"/>
-      <c r="BU16" s="2"/>
-      <c r="BV16" s="2"/>
-      <c r="BW16" s="2"/>
-      <c r="BX16" s="2"/>
-      <c r="BY16" s="2"/>
-      <c r="BZ16" s="2"/>
-      <c r="CA16" s="2"/>
-      <c r="CB16" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB16" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -2984,87 +4430,231 @@
       <c r="E17" s="11">
         <f>IF(C17&gt;0,LOOKUP(2,1/(F17:CB17="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="R17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2"/>
-      <c r="AE17" s="2"/>
-      <c r="AF17" s="2"/>
-      <c r="AG17" s="2"/>
-      <c r="AH17" s="2"/>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="2"/>
-      <c r="AL17" s="2"/>
-      <c r="AM17" s="2"/>
-      <c r="AN17" s="2"/>
-      <c r="AO17" s="2"/>
-      <c r="AP17" s="2"/>
-      <c r="AQ17" s="2"/>
-      <c r="AR17" s="2"/>
-      <c r="AS17" s="2"/>
-      <c r="AT17" s="2"/>
-      <c r="AU17" s="2"/>
-      <c r="AV17" s="2"/>
-      <c r="AW17" s="2"/>
-      <c r="AX17" s="2"/>
-      <c r="AY17" s="2"/>
-      <c r="AZ17" s="2"/>
-      <c r="BA17" s="2"/>
-      <c r="BB17" s="2"/>
-      <c r="BC17" s="2"/>
-      <c r="BD17" s="2"/>
-      <c r="BE17" s="2"/>
-      <c r="BF17" s="2"/>
-      <c r="BG17" s="2"/>
-      <c r="BH17" s="2"/>
-      <c r="BI17" s="2"/>
-      <c r="BJ17" s="2"/>
-      <c r="BK17" s="2"/>
-      <c r="BL17" s="2"/>
-      <c r="BM17" s="2"/>
-      <c r="BN17" s="2"/>
-      <c r="BO17" s="2"/>
-      <c r="BP17" s="2"/>
-      <c r="BQ17" s="2"/>
-      <c r="BR17" s="2"/>
-      <c r="BS17" s="2"/>
-      <c r="BT17" s="2"/>
-      <c r="BU17" s="2"/>
-      <c r="BV17" s="2"/>
-      <c r="BW17" s="2"/>
-      <c r="BX17" s="2"/>
-      <c r="BY17" s="2"/>
-      <c r="BZ17" s="2"/>
-      <c r="CA17" s="2"/>
-      <c r="CB17" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB17" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
@@ -3082,87 +4672,231 @@
       <c r="E18" s="11">
         <f>IF(C18&gt;0,LOOKUP(2,1/(F18:CB18="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="U18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
-      <c r="AD18" s="2"/>
-      <c r="AE18" s="2"/>
-      <c r="AF18" s="2"/>
-      <c r="AG18" s="2"/>
-      <c r="AH18" s="2"/>
-      <c r="AI18" s="2"/>
-      <c r="AJ18" s="2"/>
-      <c r="AK18" s="2"/>
-      <c r="AL18" s="2"/>
-      <c r="AM18" s="2"/>
-      <c r="AN18" s="2"/>
-      <c r="AO18" s="2"/>
-      <c r="AP18" s="2"/>
-      <c r="AQ18" s="2"/>
-      <c r="AR18" s="2"/>
-      <c r="AS18" s="2"/>
-      <c r="AT18" s="2"/>
-      <c r="AU18" s="2"/>
-      <c r="AV18" s="2"/>
-      <c r="AW18" s="2"/>
-      <c r="AX18" s="2"/>
-      <c r="AY18" s="2"/>
-      <c r="AZ18" s="2"/>
-      <c r="BA18" s="2"/>
-      <c r="BB18" s="2"/>
-      <c r="BC18" s="2"/>
-      <c r="BD18" s="2"/>
-      <c r="BE18" s="2"/>
-      <c r="BF18" s="2"/>
-      <c r="BG18" s="2"/>
-      <c r="BH18" s="2"/>
-      <c r="BI18" s="2"/>
-      <c r="BJ18" s="2"/>
-      <c r="BK18" s="2"/>
-      <c r="BL18" s="2"/>
-      <c r="BM18" s="2"/>
-      <c r="BN18" s="2"/>
-      <c r="BO18" s="2"/>
-      <c r="BP18" s="2"/>
-      <c r="BQ18" s="2"/>
-      <c r="BR18" s="2"/>
-      <c r="BS18" s="2"/>
-      <c r="BT18" s="2"/>
-      <c r="BU18" s="2"/>
-      <c r="BV18" s="2"/>
-      <c r="BW18" s="2"/>
-      <c r="BX18" s="2"/>
-      <c r="BY18" s="2"/>
-      <c r="BZ18" s="2"/>
-      <c r="CA18" s="2"/>
-      <c r="CB18" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB18" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
@@ -3180,89 +4914,231 @@
       <c r="E19" s="11">
         <f>IF(C19&gt;0,LOOKUP(2,1/(F19:CB19="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="U19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
-      <c r="AH19" s="2"/>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="2"/>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="2"/>
-      <c r="AO19" s="2"/>
-      <c r="AP19" s="2"/>
-      <c r="AQ19" s="2"/>
-      <c r="AR19" s="2"/>
-      <c r="AS19" s="2"/>
-      <c r="AT19" s="2"/>
-      <c r="AU19" s="2"/>
-      <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
-      <c r="AX19" s="2"/>
-      <c r="AY19" s="2"/>
-      <c r="AZ19" s="2"/>
-      <c r="BA19" s="2"/>
-      <c r="BB19" s="2"/>
-      <c r="BC19" s="2"/>
-      <c r="BD19" s="2"/>
-      <c r="BE19" s="2"/>
-      <c r="BF19" s="2"/>
-      <c r="BG19" s="2"/>
-      <c r="BH19" s="2"/>
-      <c r="BI19" s="2"/>
-      <c r="BJ19" s="2"/>
-      <c r="BK19" s="2"/>
-      <c r="BL19" s="2"/>
-      <c r="BM19" s="2"/>
-      <c r="BN19" s="2"/>
-      <c r="BO19" s="2"/>
-      <c r="BP19" s="2"/>
-      <c r="BQ19" s="2"/>
-      <c r="BR19" s="2"/>
-      <c r="BS19" s="2"/>
-      <c r="BT19" s="2"/>
-      <c r="BU19" s="2"/>
-      <c r="BV19" s="2"/>
-      <c r="BW19" s="2"/>
-      <c r="BX19" s="2"/>
-      <c r="BY19" s="2"/>
-      <c r="BZ19" s="2"/>
-      <c r="CA19" s="2"/>
-      <c r="CB19" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB19" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
@@ -3280,97 +5156,231 @@
       <c r="E20" s="11">
         <f>IF(C20&gt;0,LOOKUP(2,1/(F20:CB20="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="Y20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AG20" s="2"/>
-      <c r="AH20" s="2"/>
-      <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="2"/>
-      <c r="AL20" s="2"/>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2"/>
-      <c r="AO20" s="2"/>
-      <c r="AP20" s="2"/>
-      <c r="AQ20" s="2"/>
-      <c r="AR20" s="2"/>
-      <c r="AS20" s="2"/>
-      <c r="AT20" s="2"/>
-      <c r="AU20" s="2"/>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
-      <c r="AX20" s="2"/>
-      <c r="AY20" s="2"/>
-      <c r="AZ20" s="2"/>
-      <c r="BA20" s="2"/>
-      <c r="BB20" s="2"/>
-      <c r="BC20" s="2"/>
-      <c r="BD20" s="2"/>
-      <c r="BE20" s="2"/>
-      <c r="BF20" s="2"/>
-      <c r="BG20" s="2"/>
-      <c r="BH20" s="2"/>
-      <c r="BI20" s="2"/>
-      <c r="BJ20" s="2"/>
-      <c r="BK20" s="2"/>
-      <c r="BL20" s="2"/>
-      <c r="BM20" s="2"/>
-      <c r="BN20" s="2"/>
-      <c r="BO20" s="2"/>
-      <c r="BP20" s="2"/>
-      <c r="BQ20" s="2"/>
-      <c r="BR20" s="2"/>
-      <c r="BS20" s="2"/>
-      <c r="BT20" s="2"/>
-      <c r="BU20" s="2"/>
-      <c r="BV20" s="2"/>
-      <c r="BW20" s="2"/>
-      <c r="BX20" s="2"/>
-      <c r="BY20" s="2"/>
-      <c r="BZ20" s="2"/>
-      <c r="CA20" s="2"/>
-      <c r="CB20" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB20" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="21" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
@@ -3388,87 +5398,231 @@
       <c r="E21" s="11">
         <f>IF(C21&gt;0,LOOKUP(2,1/(F21:CB21="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF21" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AG21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH21" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AI21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
-      <c r="AL21" s="2"/>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2"/>
-      <c r="AO21" s="2"/>
-      <c r="AP21" s="2"/>
-      <c r="AQ21" s="2"/>
-      <c r="AR21" s="2"/>
-      <c r="AS21" s="2"/>
-      <c r="AT21" s="2"/>
-      <c r="AU21" s="2"/>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
-      <c r="AX21" s="2"/>
-      <c r="AY21" s="2"/>
-      <c r="AZ21" s="2"/>
-      <c r="BA21" s="2"/>
-      <c r="BB21" s="2"/>
-      <c r="BC21" s="2"/>
-      <c r="BD21" s="2"/>
-      <c r="BE21" s="2"/>
-      <c r="BF21" s="2"/>
-      <c r="BG21" s="2"/>
-      <c r="BH21" s="2"/>
-      <c r="BI21" s="2"/>
-      <c r="BJ21" s="2"/>
-      <c r="BK21" s="2"/>
-      <c r="BL21" s="2"/>
-      <c r="BM21" s="2"/>
-      <c r="BN21" s="2"/>
-      <c r="BO21" s="2"/>
-      <c r="BP21" s="2"/>
-      <c r="BQ21" s="2"/>
-      <c r="BR21" s="2"/>
-      <c r="BS21" s="2"/>
-      <c r="BT21" s="2"/>
-      <c r="BU21" s="2"/>
-      <c r="BV21" s="2"/>
-      <c r="BW21" s="2"/>
-      <c r="BX21" s="2"/>
-      <c r="BY21" s="2"/>
-      <c r="BZ21" s="2"/>
-      <c r="CA21" s="2"/>
-      <c r="CB21" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB21" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
@@ -3486,89 +5640,231 @@
       <c r="E22" s="11">
         <f>IF(C22&gt;0,LOOKUP(2,1/(F22:CB22="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-      <c r="AC22" s="2"/>
-      <c r="AD22" s="2"/>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="2"/>
-      <c r="AG22" s="2"/>
-      <c r="AH22" s="2"/>
-      <c r="AI22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AJ22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL22" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN22" s="2"/>
-      <c r="AO22" s="2"/>
-      <c r="AP22" s="2"/>
-      <c r="AQ22" s="2"/>
-      <c r="AR22" s="2"/>
-      <c r="AS22" s="2"/>
-      <c r="AT22" s="2"/>
-      <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
-      <c r="AX22" s="2"/>
-      <c r="AY22" s="2"/>
-      <c r="AZ22" s="2"/>
-      <c r="BA22" s="2"/>
-      <c r="BB22" s="2"/>
-      <c r="BC22" s="2"/>
-      <c r="BD22" s="2"/>
-      <c r="BE22" s="2"/>
-      <c r="BF22" s="2"/>
-      <c r="BG22" s="2"/>
-      <c r="BH22" s="2"/>
-      <c r="BI22" s="2"/>
-      <c r="BJ22" s="2"/>
-      <c r="BK22" s="2"/>
-      <c r="BL22" s="2"/>
-      <c r="BM22" s="2"/>
-      <c r="BN22" s="2"/>
-      <c r="BO22" s="2"/>
-      <c r="BP22" s="2"/>
-      <c r="BQ22" s="2"/>
-      <c r="BR22" s="2"/>
-      <c r="BS22" s="2"/>
-      <c r="BT22" s="2"/>
-      <c r="BU22" s="2"/>
-      <c r="BV22" s="2"/>
-      <c r="BW22" s="2"/>
-      <c r="BX22" s="2"/>
-      <c r="BY22" s="2"/>
-      <c r="BZ22" s="2"/>
-      <c r="CA22" s="2"/>
-      <c r="CB22" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AN22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB22" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="23" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
@@ -3586,83 +5882,231 @@
       <c r="E23" s="11">
         <f>IF(C23&gt;0,LOOKUP(2,1/(F23:CB23="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
-      <c r="AC23" s="2"/>
-      <c r="AD23" s="2"/>
-      <c r="AE23" s="2"/>
-      <c r="AF23" s="2"/>
-      <c r="AG23" s="2"/>
-      <c r="AH23" s="2"/>
-      <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
-      <c r="AL23" s="2"/>
-      <c r="AM23" s="2"/>
+      <c r="F23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM23" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AN23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AO23" s="2"/>
-      <c r="AP23" s="2"/>
-      <c r="AQ23" s="2"/>
-      <c r="AR23" s="2"/>
-      <c r="AS23" s="2"/>
-      <c r="AT23" s="2"/>
-      <c r="AU23" s="2"/>
-      <c r="AV23" s="2"/>
-      <c r="AW23" s="2"/>
-      <c r="AX23" s="2"/>
-      <c r="AY23" s="2"/>
-      <c r="AZ23" s="2"/>
-      <c r="BA23" s="2"/>
-      <c r="BB23" s="2"/>
-      <c r="BC23" s="2"/>
-      <c r="BD23" s="2"/>
-      <c r="BE23" s="2"/>
-      <c r="BF23" s="2"/>
-      <c r="BG23" s="2"/>
-      <c r="BH23" s="2"/>
-      <c r="BI23" s="2"/>
-      <c r="BJ23" s="2"/>
-      <c r="BK23" s="2"/>
-      <c r="BL23" s="2"/>
-      <c r="BM23" s="2"/>
-      <c r="BN23" s="2"/>
-      <c r="BO23" s="2"/>
-      <c r="BP23" s="2"/>
-      <c r="BQ23" s="2"/>
-      <c r="BR23" s="2"/>
-      <c r="BS23" s="2"/>
-      <c r="BT23" s="2"/>
-      <c r="BU23" s="2"/>
-      <c r="BV23" s="2"/>
-      <c r="BW23" s="2"/>
-      <c r="BX23" s="2"/>
-      <c r="BY23" s="2"/>
-      <c r="BZ23" s="2"/>
-      <c r="CA23" s="2"/>
-      <c r="CB23" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AO23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB23" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
@@ -3681,130 +6125,230 @@
         <f>IF(C24&gt;0,LOOKUP(2,1/(F24:CB24="█"),F$1:CB$1),"")</f>
       </c>
       <c r="F24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="X24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AC24" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AD24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
-      <c r="AO24" s="2"/>
-      <c r="AP24" s="2"/>
-      <c r="AQ24" s="2"/>
-      <c r="AR24" s="2"/>
-      <c r="AS24" s="2"/>
-      <c r="AT24" s="2"/>
-      <c r="AU24" s="2"/>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
-      <c r="AX24" s="2"/>
-      <c r="AY24" s="2"/>
-      <c r="AZ24" s="2"/>
-      <c r="BA24" s="2"/>
-      <c r="BB24" s="2"/>
-      <c r="BC24" s="2"/>
-      <c r="BD24" s="2"/>
-      <c r="BE24" s="2"/>
-      <c r="BF24" s="2"/>
-      <c r="BG24" s="2"/>
-      <c r="BH24" s="2"/>
-      <c r="BI24" s="2"/>
-      <c r="BJ24" s="2"/>
-      <c r="BK24" s="2"/>
-      <c r="BL24" s="2"/>
-      <c r="BM24" s="2"/>
-      <c r="BN24" s="2"/>
-      <c r="BO24" s="2"/>
-      <c r="BP24" s="2"/>
-      <c r="BQ24" s="2"/>
-      <c r="BR24" s="2"/>
-      <c r="BS24" s="2"/>
-      <c r="BT24" s="2"/>
-      <c r="BU24" s="2"/>
-      <c r="BV24" s="2"/>
-      <c r="BW24" s="2"/>
-      <c r="BX24" s="2"/>
-      <c r="BY24" s="2"/>
-      <c r="BZ24" s="2"/>
-      <c r="CA24" s="2"/>
-      <c r="CB24" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB24" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
@@ -3822,85 +6366,231 @@
       <c r="E25" s="11">
         <f>IF(C25&gt;0,LOOKUP(2,1/(F25:CB25="█"),F$1:CB$1),"")</f>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="2"/>
-      <c r="AD25" s="2"/>
-      <c r="AE25" s="2"/>
-      <c r="AF25" s="2"/>
-      <c r="AG25" s="2"/>
-      <c r="AH25" s="2"/>
-      <c r="AI25" s="2"/>
-      <c r="AJ25" s="2"/>
-      <c r="AK25" s="2"/>
-      <c r="AL25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL25" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AM25" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AO25" s="2"/>
-      <c r="AP25" s="2"/>
-      <c r="AQ25" s="2"/>
-      <c r="AR25" s="2"/>
-      <c r="AS25" s="2"/>
-      <c r="AT25" s="2"/>
-      <c r="AU25" s="2"/>
-      <c r="AV25" s="2"/>
-      <c r="AW25" s="2"/>
-      <c r="AX25" s="2"/>
-      <c r="AY25" s="2"/>
-      <c r="AZ25" s="2"/>
-      <c r="BA25" s="2"/>
-      <c r="BB25" s="2"/>
-      <c r="BC25" s="2"/>
-      <c r="BD25" s="2"/>
-      <c r="BE25" s="2"/>
-      <c r="BF25" s="2"/>
-      <c r="BG25" s="2"/>
-      <c r="BH25" s="2"/>
-      <c r="BI25" s="2"/>
-      <c r="BJ25" s="2"/>
-      <c r="BK25" s="2"/>
-      <c r="BL25" s="2"/>
-      <c r="BM25" s="2"/>
-      <c r="BN25" s="2"/>
-      <c r="BO25" s="2"/>
-      <c r="BP25" s="2"/>
-      <c r="BQ25" s="2"/>
-      <c r="BR25" s="2"/>
-      <c r="BS25" s="2"/>
-      <c r="BT25" s="2"/>
-      <c r="BU25" s="2"/>
-      <c r="BV25" s="2"/>
-      <c r="BW25" s="2"/>
-      <c r="BX25" s="2"/>
-      <c r="BY25" s="2"/>
-      <c r="BZ25" s="2"/>
-      <c r="CA25" s="2"/>
-      <c r="CB25" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AO25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB25" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/Ebooks/Plan.xlsx
+++ b/Ebooks/Plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="48">
   <si>
     <t>WBS</t>
   </si>
@@ -97,10 +97,10 @@
     <t>Project Introduction</t>
   </si>
   <si>
-    <t>Business objective</t>
+    <t>█</t>
   </si>
   <si>
-    <t>█</t>
+    <t>Business objective</t>
   </si>
   <si>
     <t>SWOT Analysis</t>
@@ -615,7 +615,7 @@
   <sheetData>
     <row r="1" spans="6:80" x14ac:dyDescent="0.25">
       <c r="F1" s="2">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="G1" s="2">
         <f>F1+1</f>
@@ -1526,88 +1526,238 @@
       <c r="E5" s="11">
         <f>IF(C5&gt;0,INDEX(F$1:CB$1,MATCH("█",F5:CB5,0)+C5-1),"")</f>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
-      <c r="AA5" s="2"/>
-      <c r="AB5" s="2"/>
-      <c r="AC5" s="2"/>
-      <c r="AD5" s="2"/>
-      <c r="AE5" s="2"/>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
-      <c r="AI5" s="2"/>
-      <c r="AJ5" s="2"/>
-      <c r="AK5" s="2"/>
-      <c r="AL5" s="2"/>
-      <c r="AM5" s="2"/>
-      <c r="AN5" s="2"/>
-      <c r="AO5" s="2"/>
-      <c r="AP5" s="2"/>
-      <c r="AQ5" s="2"/>
-      <c r="AR5" s="2"/>
-      <c r="AS5" s="2"/>
-      <c r="AT5" s="2"/>
-      <c r="AU5" s="2"/>
-      <c r="AV5" s="2"/>
-      <c r="AW5" s="2"/>
-      <c r="AX5" s="2"/>
-      <c r="AY5" s="2"/>
-      <c r="AZ5" s="2"/>
-      <c r="BA5" s="2"/>
-      <c r="BB5" s="2"/>
-      <c r="BC5" s="2"/>
-      <c r="BD5" s="2"/>
-      <c r="BE5" s="2"/>
-      <c r="BF5" s="2"/>
-      <c r="BG5" s="2"/>
-      <c r="BH5" s="2"/>
-      <c r="BI5" s="2"/>
-      <c r="BJ5" s="2"/>
-      <c r="BK5" s="2"/>
-      <c r="BL5" s="2"/>
-      <c r="BM5" s="2"/>
-      <c r="BN5" s="2"/>
-      <c r="BO5" s="2"/>
-      <c r="BP5" s="2"/>
-      <c r="BQ5" s="2"/>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2"/>
-      <c r="BT5" s="2"/>
-      <c r="BU5" s="2"/>
-      <c r="BV5" s="2"/>
-      <c r="BW5" s="2"/>
-      <c r="BX5" s="2"/>
-      <c r="BY5" s="2"/>
-      <c r="BZ5" s="2"/>
-      <c r="CA5" s="2"/>
-      <c r="CB5" s="2"/>
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB5" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A6" s="9">
         <v>1.2</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C6" s="10">
         <f>COUNTIF(F6:CB6,"█")</f>
@@ -1619,82 +1769,230 @@
         <f>IF(C6&gt;0,INDEX(F$1:CB$1,MATCH("█",F6:CB6,0)+C6-1),"")</f>
       </c>
       <c r="F6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
-      <c r="AA6" s="2"/>
-      <c r="AB6" s="2"/>
-      <c r="AC6" s="2"/>
-      <c r="AD6" s="2"/>
-      <c r="AE6" s="2"/>
-      <c r="AF6" s="2"/>
-      <c r="AG6" s="2"/>
-      <c r="AH6" s="2"/>
-      <c r="AI6" s="2"/>
-      <c r="AJ6" s="2"/>
-      <c r="AK6" s="2"/>
-      <c r="AL6" s="2"/>
-      <c r="AM6" s="2"/>
-      <c r="AN6" s="2"/>
-      <c r="AO6" s="2"/>
-      <c r="AP6" s="2"/>
-      <c r="AQ6" s="2"/>
-      <c r="AR6" s="2"/>
-      <c r="AS6" s="2"/>
-      <c r="AT6" s="2"/>
-      <c r="AU6" s="2"/>
-      <c r="AV6" s="2"/>
-      <c r="AW6" s="2"/>
-      <c r="AX6" s="2"/>
-      <c r="AY6" s="2"/>
-      <c r="AZ6" s="2"/>
-      <c r="BA6" s="2"/>
-      <c r="BB6" s="2"/>
-      <c r="BC6" s="2"/>
-      <c r="BD6" s="2"/>
-      <c r="BE6" s="2"/>
-      <c r="BF6" s="2"/>
-      <c r="BG6" s="2"/>
-      <c r="BH6" s="2"/>
-      <c r="BI6" s="2"/>
-      <c r="BJ6" s="2"/>
-      <c r="BK6" s="2"/>
-      <c r="BL6" s="2"/>
-      <c r="BM6" s="2"/>
-      <c r="BN6" s="2"/>
-      <c r="BO6" s="2"/>
-      <c r="BP6" s="2"/>
-      <c r="BQ6" s="2"/>
-      <c r="BR6" s="2"/>
-      <c r="BS6" s="2"/>
-      <c r="BT6" s="2"/>
-      <c r="BU6" s="2"/>
-      <c r="BV6" s="2"/>
-      <c r="BW6" s="2"/>
-      <c r="BX6" s="2"/>
-      <c r="BY6" s="2"/>
-      <c r="BZ6" s="2"/>
-      <c r="CA6" s="2"/>
-      <c r="CB6" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB6" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A7" s="9">
@@ -1712,83 +2010,231 @@
       <c r="E7" s="11">
         <f>IF(C7&gt;0,INDEX(F$1:CB$1,MATCH("█",F7:CB7,0)+C7-1),"")</f>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="H7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
-      <c r="AA7" s="2"/>
-      <c r="AB7" s="2"/>
-      <c r="AC7" s="2"/>
-      <c r="AD7" s="2"/>
-      <c r="AE7" s="2"/>
-      <c r="AF7" s="2"/>
-      <c r="AG7" s="2"/>
-      <c r="AH7" s="2"/>
-      <c r="AI7" s="2"/>
-      <c r="AJ7" s="2"/>
-      <c r="AK7" s="2"/>
-      <c r="AL7" s="2"/>
-      <c r="AM7" s="2"/>
-      <c r="AN7" s="2"/>
-      <c r="AO7" s="2"/>
-      <c r="AP7" s="2"/>
-      <c r="AQ7" s="2"/>
-      <c r="AR7" s="2"/>
-      <c r="AS7" s="2"/>
-      <c r="AT7" s="2"/>
-      <c r="AU7" s="2"/>
-      <c r="AV7" s="2"/>
-      <c r="AW7" s="2"/>
-      <c r="AX7" s="2"/>
-      <c r="AY7" s="2"/>
-      <c r="AZ7" s="2"/>
-      <c r="BA7" s="2"/>
-      <c r="BB7" s="2"/>
-      <c r="BC7" s="2"/>
-      <c r="BD7" s="2"/>
-      <c r="BE7" s="2"/>
-      <c r="BF7" s="2"/>
-      <c r="BG7" s="2"/>
-      <c r="BH7" s="2"/>
-      <c r="BI7" s="2"/>
-      <c r="BJ7" s="2"/>
-      <c r="BK7" s="2"/>
-      <c r="BL7" s="2"/>
-      <c r="BM7" s="2"/>
-      <c r="BN7" s="2"/>
-      <c r="BO7" s="2"/>
-      <c r="BP7" s="2"/>
-      <c r="BQ7" s="2"/>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2"/>
-      <c r="BT7" s="2"/>
-      <c r="BU7" s="2"/>
-      <c r="BV7" s="2"/>
-      <c r="BW7" s="2"/>
-      <c r="BX7" s="2"/>
-      <c r="BY7" s="2"/>
-      <c r="BZ7" s="2"/>
-      <c r="CA7" s="2"/>
-      <c r="CB7" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB7" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="8" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A8" s="9">
@@ -1806,81 +2252,231 @@
       <c r="E8" s="11">
         <f>IF(C8&gt;0,INDEX(F$1:CB$1,MATCH("█",F8:CB8,0)+C8-1),"")</f>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
-      <c r="AA8" s="2"/>
-      <c r="AB8" s="2"/>
-      <c r="AC8" s="2"/>
-      <c r="AD8" s="2"/>
-      <c r="AE8" s="2"/>
-      <c r="AF8" s="2"/>
-      <c r="AG8" s="2"/>
-      <c r="AH8" s="2"/>
-      <c r="AI8" s="2"/>
-      <c r="AJ8" s="2"/>
-      <c r="AK8" s="2"/>
-      <c r="AL8" s="2"/>
-      <c r="AM8" s="2"/>
-      <c r="AN8" s="2"/>
-      <c r="AO8" s="2"/>
-      <c r="AP8" s="2"/>
-      <c r="AQ8" s="2"/>
-      <c r="AR8" s="2"/>
-      <c r="AS8" s="2"/>
-      <c r="AT8" s="2"/>
-      <c r="AU8" s="2"/>
-      <c r="AV8" s="2"/>
-      <c r="AW8" s="2"/>
-      <c r="AX8" s="2"/>
-      <c r="AY8" s="2"/>
-      <c r="AZ8" s="2"/>
-      <c r="BA8" s="2"/>
-      <c r="BB8" s="2"/>
-      <c r="BC8" s="2"/>
-      <c r="BD8" s="2"/>
-      <c r="BE8" s="2"/>
-      <c r="BF8" s="2"/>
-      <c r="BG8" s="2"/>
-      <c r="BH8" s="2"/>
-      <c r="BI8" s="2"/>
-      <c r="BJ8" s="2"/>
-      <c r="BK8" s="2"/>
-      <c r="BL8" s="2"/>
-      <c r="BM8" s="2"/>
-      <c r="BN8" s="2"/>
-      <c r="BO8" s="2"/>
-      <c r="BP8" s="2"/>
-      <c r="BQ8" s="2"/>
-      <c r="BR8" s="2"/>
-      <c r="BS8" s="2"/>
-      <c r="BT8" s="2"/>
-      <c r="BU8" s="2"/>
-      <c r="BV8" s="2"/>
-      <c r="BW8" s="2"/>
-      <c r="BX8" s="2"/>
-      <c r="BY8" s="2"/>
-      <c r="BZ8" s="2"/>
-      <c r="CA8" s="2"/>
-      <c r="CB8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB8" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="9" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A9" s="9">
@@ -1898,83 +2494,231 @@
       <c r="E9" s="11">
         <f>IF(C9&gt;0,INDEX(F$1:CB$1,MATCH("█",F9:CB9,0)+C9-1),"")</f>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="H9" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
-      <c r="AA9" s="2"/>
-      <c r="AB9" s="2"/>
-      <c r="AC9" s="2"/>
-      <c r="AD9" s="2"/>
-      <c r="AE9" s="2"/>
-      <c r="AF9" s="2"/>
-      <c r="AG9" s="2"/>
-      <c r="AH9" s="2"/>
-      <c r="AI9" s="2"/>
-      <c r="AJ9" s="2"/>
-      <c r="AK9" s="2"/>
-      <c r="AL9" s="2"/>
-      <c r="AM9" s="2"/>
-      <c r="AN9" s="2"/>
-      <c r="AO9" s="2"/>
-      <c r="AP9" s="2"/>
-      <c r="AQ9" s="2"/>
-      <c r="AR9" s="2"/>
-      <c r="AS9" s="2"/>
-      <c r="AT9" s="2"/>
-      <c r="AU9" s="2"/>
-      <c r="AV9" s="2"/>
-      <c r="AW9" s="2"/>
-      <c r="AX9" s="2"/>
-      <c r="AY9" s="2"/>
-      <c r="AZ9" s="2"/>
-      <c r="BA9" s="2"/>
-      <c r="BB9" s="2"/>
-      <c r="BC9" s="2"/>
-      <c r="BD9" s="2"/>
-      <c r="BE9" s="2"/>
-      <c r="BF9" s="2"/>
-      <c r="BG9" s="2"/>
-      <c r="BH9" s="2"/>
-      <c r="BI9" s="2"/>
-      <c r="BJ9" s="2"/>
-      <c r="BK9" s="2"/>
-      <c r="BL9" s="2"/>
-      <c r="BM9" s="2"/>
-      <c r="BN9" s="2"/>
-      <c r="BO9" s="2"/>
-      <c r="BP9" s="2"/>
-      <c r="BQ9" s="2"/>
-      <c r="BR9" s="2"/>
-      <c r="BS9" s="2"/>
-      <c r="BT9" s="2"/>
-      <c r="BU9" s="2"/>
-      <c r="BV9" s="2"/>
-      <c r="BW9" s="2"/>
-      <c r="BX9" s="2"/>
-      <c r="BY9" s="2"/>
-      <c r="BZ9" s="2"/>
-      <c r="CA9" s="2"/>
-      <c r="CB9" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB9" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="10" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
@@ -2235,82 +2979,230 @@
         <f>IF(C11&gt;0,INDEX(F$1:CB$1,MATCH("█",F11:CB11,0)+C11-1),"")</f>
       </c>
       <c r="F11" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
-      <c r="AA11" s="2"/>
-      <c r="AB11" s="2"/>
-      <c r="AC11" s="2"/>
-      <c r="AD11" s="2"/>
-      <c r="AE11" s="2"/>
-      <c r="AF11" s="2"/>
-      <c r="AG11" s="2"/>
-      <c r="AH11" s="2"/>
-      <c r="AI11" s="2"/>
-      <c r="AJ11" s="2"/>
-      <c r="AK11" s="2"/>
-      <c r="AL11" s="2"/>
-      <c r="AM11" s="2"/>
-      <c r="AN11" s="2"/>
-      <c r="AO11" s="2"/>
-      <c r="AP11" s="2"/>
-      <c r="AQ11" s="2"/>
-      <c r="AR11" s="2"/>
-      <c r="AS11" s="2"/>
-      <c r="AT11" s="2"/>
-      <c r="AU11" s="2"/>
-      <c r="AV11" s="2"/>
-      <c r="AW11" s="2"/>
-      <c r="AX11" s="2"/>
-      <c r="AY11" s="2"/>
-      <c r="AZ11" s="2"/>
-      <c r="BA11" s="2"/>
-      <c r="BB11" s="2"/>
-      <c r="BC11" s="2"/>
-      <c r="BD11" s="2"/>
-      <c r="BE11" s="2"/>
-      <c r="BF11" s="2"/>
-      <c r="BG11" s="2"/>
-      <c r="BH11" s="2"/>
-      <c r="BI11" s="2"/>
-      <c r="BJ11" s="2"/>
-      <c r="BK11" s="2"/>
-      <c r="BL11" s="2"/>
-      <c r="BM11" s="2"/>
-      <c r="BN11" s="2"/>
-      <c r="BO11" s="2"/>
-      <c r="BP11" s="2"/>
-      <c r="BQ11" s="2"/>
-      <c r="BR11" s="2"/>
-      <c r="BS11" s="2"/>
-      <c r="BT11" s="2"/>
-      <c r="BU11" s="2"/>
-      <c r="BV11" s="2"/>
-      <c r="BW11" s="2"/>
-      <c r="BX11" s="2"/>
-      <c r="BY11" s="2"/>
-      <c r="BZ11" s="2"/>
-      <c r="CA11" s="2"/>
-      <c r="CB11" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB11" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="12" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A12" s="9">
@@ -2328,83 +3220,231 @@
       <c r="E12" s="11">
         <f>IF(C12&gt;0,INDEX(F$1:CB$1,MATCH("█",F12:CB12,0)+C12-1),"")</f>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
-      <c r="AA12" s="2"/>
-      <c r="AB12" s="2"/>
-      <c r="AC12" s="2"/>
-      <c r="AD12" s="2"/>
-      <c r="AE12" s="2"/>
-      <c r="AF12" s="2"/>
-      <c r="AG12" s="2"/>
-      <c r="AH12" s="2"/>
-      <c r="AI12" s="2"/>
-      <c r="AJ12" s="2"/>
-      <c r="AK12" s="2"/>
-      <c r="AL12" s="2"/>
-      <c r="AM12" s="2"/>
-      <c r="AN12" s="2"/>
-      <c r="AO12" s="2"/>
-      <c r="AP12" s="2"/>
-      <c r="AQ12" s="2"/>
-      <c r="AR12" s="2"/>
-      <c r="AS12" s="2"/>
-      <c r="AT12" s="2"/>
-      <c r="AU12" s="2"/>
-      <c r="AV12" s="2"/>
-      <c r="AW12" s="2"/>
-      <c r="AX12" s="2"/>
-      <c r="AY12" s="2"/>
-      <c r="AZ12" s="2"/>
-      <c r="BA12" s="2"/>
-      <c r="BB12" s="2"/>
-      <c r="BC12" s="2"/>
-      <c r="BD12" s="2"/>
-      <c r="BE12" s="2"/>
-      <c r="BF12" s="2"/>
-      <c r="BG12" s="2"/>
-      <c r="BH12" s="2"/>
-      <c r="BI12" s="2"/>
-      <c r="BJ12" s="2"/>
-      <c r="BK12" s="2"/>
-      <c r="BL12" s="2"/>
-      <c r="BM12" s="2"/>
-      <c r="BN12" s="2"/>
-      <c r="BO12" s="2"/>
-      <c r="BP12" s="2"/>
-      <c r="BQ12" s="2"/>
-      <c r="BR12" s="2"/>
-      <c r="BS12" s="2"/>
-      <c r="BT12" s="2"/>
-      <c r="BU12" s="2"/>
-      <c r="BV12" s="2"/>
-      <c r="BW12" s="2"/>
-      <c r="BX12" s="2"/>
-      <c r="BY12" s="2"/>
-      <c r="BZ12" s="2"/>
-      <c r="CA12" s="2"/>
-      <c r="CB12" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB12" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
@@ -2422,83 +3462,231 @@
       <c r="E13" s="11">
         <f>IF(C13&gt;0,INDEX(F$1:CB$1,MATCH("█",F13:CB13,0)+C13-1),"")</f>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="J13" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="2"/>
-      <c r="AB13" s="2"/>
-      <c r="AC13" s="2"/>
-      <c r="AD13" s="2"/>
-      <c r="AE13" s="2"/>
-      <c r="AF13" s="2"/>
-      <c r="AG13" s="2"/>
-      <c r="AH13" s="2"/>
-      <c r="AI13" s="2"/>
-      <c r="AJ13" s="2"/>
-      <c r="AK13" s="2"/>
-      <c r="AL13" s="2"/>
-      <c r="AM13" s="2"/>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="2"/>
-      <c r="AP13" s="2"/>
-      <c r="AQ13" s="2"/>
-      <c r="AR13" s="2"/>
-      <c r="AS13" s="2"/>
-      <c r="AT13" s="2"/>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="2"/>
-      <c r="AW13" s="2"/>
-      <c r="AX13" s="2"/>
-      <c r="AY13" s="2"/>
-      <c r="AZ13" s="2"/>
-      <c r="BA13" s="2"/>
-      <c r="BB13" s="2"/>
-      <c r="BC13" s="2"/>
-      <c r="BD13" s="2"/>
-      <c r="BE13" s="2"/>
-      <c r="BF13" s="2"/>
-      <c r="BG13" s="2"/>
-      <c r="BH13" s="2"/>
-      <c r="BI13" s="2"/>
-      <c r="BJ13" s="2"/>
-      <c r="BK13" s="2"/>
-      <c r="BL13" s="2"/>
-      <c r="BM13" s="2"/>
-      <c r="BN13" s="2"/>
-      <c r="BO13" s="2"/>
-      <c r="BP13" s="2"/>
-      <c r="BQ13" s="2"/>
-      <c r="BR13" s="2"/>
-      <c r="BS13" s="2"/>
-      <c r="BT13" s="2"/>
-      <c r="BU13" s="2"/>
-      <c r="BV13" s="2"/>
-      <c r="BW13" s="2"/>
-      <c r="BX13" s="2"/>
-      <c r="BY13" s="2"/>
-      <c r="BZ13" s="2"/>
-      <c r="CA13" s="2"/>
-      <c r="CB13" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB13" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
@@ -2517,82 +3705,230 @@
         <f>IF(C14&gt;0,INDEX(F$1:CB$1,MATCH("█",F14:CB14,0)+C14-1),"")</f>
       </c>
       <c r="F14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
-      <c r="AA14" s="2"/>
-      <c r="AB14" s="2"/>
-      <c r="AC14" s="2"/>
-      <c r="AD14" s="2"/>
-      <c r="AE14" s="2"/>
-      <c r="AF14" s="2"/>
-      <c r="AG14" s="2"/>
-      <c r="AH14" s="2"/>
-      <c r="AI14" s="2"/>
-      <c r="AJ14" s="2"/>
-      <c r="AK14" s="2"/>
-      <c r="AL14" s="2"/>
-      <c r="AM14" s="2"/>
-      <c r="AN14" s="2"/>
-      <c r="AO14" s="2"/>
-      <c r="AP14" s="2"/>
-      <c r="AQ14" s="2"/>
-      <c r="AR14" s="2"/>
-      <c r="AS14" s="2"/>
-      <c r="AT14" s="2"/>
-      <c r="AU14" s="2"/>
-      <c r="AV14" s="2"/>
-      <c r="AW14" s="2"/>
-      <c r="AX14" s="2"/>
-      <c r="AY14" s="2"/>
-      <c r="AZ14" s="2"/>
-      <c r="BA14" s="2"/>
-      <c r="BB14" s="2"/>
-      <c r="BC14" s="2"/>
-      <c r="BD14" s="2"/>
-      <c r="BE14" s="2"/>
-      <c r="BF14" s="2"/>
-      <c r="BG14" s="2"/>
-      <c r="BH14" s="2"/>
-      <c r="BI14" s="2"/>
-      <c r="BJ14" s="2"/>
-      <c r="BK14" s="2"/>
-      <c r="BL14" s="2"/>
-      <c r="BM14" s="2"/>
-      <c r="BN14" s="2"/>
-      <c r="BO14" s="2"/>
-      <c r="BP14" s="2"/>
-      <c r="BQ14" s="2"/>
-      <c r="BR14" s="2"/>
-      <c r="BS14" s="2"/>
-      <c r="BT14" s="2"/>
-      <c r="BU14" s="2"/>
-      <c r="BV14" s="2"/>
-      <c r="BW14" s="2"/>
-      <c r="BX14" s="2"/>
-      <c r="BY14" s="2"/>
-      <c r="BZ14" s="2"/>
-      <c r="CA14" s="2"/>
-      <c r="CB14" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB14" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="15" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
@@ -2852,83 +4188,231 @@
       <c r="E16" s="11">
         <f>IF(C16&gt;0,INDEX(F$1:CB$1,MATCH("█",F16:CB16,0)+C16-1),"")</f>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="P16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
-      <c r="AA16" s="2"/>
-      <c r="AB16" s="2"/>
-      <c r="AC16" s="2"/>
-      <c r="AD16" s="2"/>
-      <c r="AE16" s="2"/>
-      <c r="AF16" s="2"/>
-      <c r="AG16" s="2"/>
-      <c r="AH16" s="2"/>
-      <c r="AI16" s="2"/>
-      <c r="AJ16" s="2"/>
-      <c r="AK16" s="2"/>
-      <c r="AL16" s="2"/>
-      <c r="AM16" s="2"/>
-      <c r="AN16" s="2"/>
-      <c r="AO16" s="2"/>
-      <c r="AP16" s="2"/>
-      <c r="AQ16" s="2"/>
-      <c r="AR16" s="2"/>
-      <c r="AS16" s="2"/>
-      <c r="AT16" s="2"/>
-      <c r="AU16" s="2"/>
-      <c r="AV16" s="2"/>
-      <c r="AW16" s="2"/>
-      <c r="AX16" s="2"/>
-      <c r="AY16" s="2"/>
-      <c r="AZ16" s="2"/>
-      <c r="BA16" s="2"/>
-      <c r="BB16" s="2"/>
-      <c r="BC16" s="2"/>
-      <c r="BD16" s="2"/>
-      <c r="BE16" s="2"/>
-      <c r="BF16" s="2"/>
-      <c r="BG16" s="2"/>
-      <c r="BH16" s="2"/>
-      <c r="BI16" s="2"/>
-      <c r="BJ16" s="2"/>
-      <c r="BK16" s="2"/>
-      <c r="BL16" s="2"/>
-      <c r="BM16" s="2"/>
-      <c r="BN16" s="2"/>
-      <c r="BO16" s="2"/>
-      <c r="BP16" s="2"/>
-      <c r="BQ16" s="2"/>
-      <c r="BR16" s="2"/>
-      <c r="BS16" s="2"/>
-      <c r="BT16" s="2"/>
-      <c r="BU16" s="2"/>
-      <c r="BV16" s="2"/>
-      <c r="BW16" s="2"/>
-      <c r="BX16" s="2"/>
-      <c r="BY16" s="2"/>
-      <c r="BZ16" s="2"/>
-      <c r="CA16" s="2"/>
-      <c r="CB16" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB16" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="17" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A17" s="9">
@@ -2946,83 +4430,231 @@
       <c r="E17" s="11">
         <f>IF(C17&gt;0,INDEX(F$1:CB$1,MATCH("█",F17:CB17,0)+C17-1),"")</f>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="R17" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
-      <c r="AA17" s="2"/>
-      <c r="AB17" s="2"/>
-      <c r="AC17" s="2"/>
-      <c r="AD17" s="2"/>
-      <c r="AE17" s="2"/>
-      <c r="AF17" s="2"/>
-      <c r="AG17" s="2"/>
-      <c r="AH17" s="2"/>
-      <c r="AI17" s="2"/>
-      <c r="AJ17" s="2"/>
-      <c r="AK17" s="2"/>
-      <c r="AL17" s="2"/>
-      <c r="AM17" s="2"/>
-      <c r="AN17" s="2"/>
-      <c r="AO17" s="2"/>
-      <c r="AP17" s="2"/>
-      <c r="AQ17" s="2"/>
-      <c r="AR17" s="2"/>
-      <c r="AS17" s="2"/>
-      <c r="AT17" s="2"/>
-      <c r="AU17" s="2"/>
-      <c r="AV17" s="2"/>
-      <c r="AW17" s="2"/>
-      <c r="AX17" s="2"/>
-      <c r="AY17" s="2"/>
-      <c r="AZ17" s="2"/>
-      <c r="BA17" s="2"/>
-      <c r="BB17" s="2"/>
-      <c r="BC17" s="2"/>
-      <c r="BD17" s="2"/>
-      <c r="BE17" s="2"/>
-      <c r="BF17" s="2"/>
-      <c r="BG17" s="2"/>
-      <c r="BH17" s="2"/>
-      <c r="BI17" s="2"/>
-      <c r="BJ17" s="2"/>
-      <c r="BK17" s="2"/>
-      <c r="BL17" s="2"/>
-      <c r="BM17" s="2"/>
-      <c r="BN17" s="2"/>
-      <c r="BO17" s="2"/>
-      <c r="BP17" s="2"/>
-      <c r="BQ17" s="2"/>
-      <c r="BR17" s="2"/>
-      <c r="BS17" s="2"/>
-      <c r="BT17" s="2"/>
-      <c r="BU17" s="2"/>
-      <c r="BV17" s="2"/>
-      <c r="BW17" s="2"/>
-      <c r="BX17" s="2"/>
-      <c r="BY17" s="2"/>
-      <c r="BZ17" s="2"/>
-      <c r="CA17" s="2"/>
-      <c r="CB17" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB17" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="18" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A18" s="9">
@@ -3040,83 +4672,231 @@
       <c r="E18" s="11">
         <f>IF(C18&gt;0,INDEX(F$1:CB$1,MATCH("█",F18:CB18,0)+C18-1),"")</f>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="U18" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
-      <c r="AD18" s="2"/>
-      <c r="AE18" s="2"/>
-      <c r="AF18" s="2"/>
-      <c r="AG18" s="2"/>
-      <c r="AH18" s="2"/>
-      <c r="AI18" s="2"/>
-      <c r="AJ18" s="2"/>
-      <c r="AK18" s="2"/>
-      <c r="AL18" s="2"/>
-      <c r="AM18" s="2"/>
-      <c r="AN18" s="2"/>
-      <c r="AO18" s="2"/>
-      <c r="AP18" s="2"/>
-      <c r="AQ18" s="2"/>
-      <c r="AR18" s="2"/>
-      <c r="AS18" s="2"/>
-      <c r="AT18" s="2"/>
-      <c r="AU18" s="2"/>
-      <c r="AV18" s="2"/>
-      <c r="AW18" s="2"/>
-      <c r="AX18" s="2"/>
-      <c r="AY18" s="2"/>
-      <c r="AZ18" s="2"/>
-      <c r="BA18" s="2"/>
-      <c r="BB18" s="2"/>
-      <c r="BC18" s="2"/>
-      <c r="BD18" s="2"/>
-      <c r="BE18" s="2"/>
-      <c r="BF18" s="2"/>
-      <c r="BG18" s="2"/>
-      <c r="BH18" s="2"/>
-      <c r="BI18" s="2"/>
-      <c r="BJ18" s="2"/>
-      <c r="BK18" s="2"/>
-      <c r="BL18" s="2"/>
-      <c r="BM18" s="2"/>
-      <c r="BN18" s="2"/>
-      <c r="BO18" s="2"/>
-      <c r="BP18" s="2"/>
-      <c r="BQ18" s="2"/>
-      <c r="BR18" s="2"/>
-      <c r="BS18" s="2"/>
-      <c r="BT18" s="2"/>
-      <c r="BU18" s="2"/>
-      <c r="BV18" s="2"/>
-      <c r="BW18" s="2"/>
-      <c r="BX18" s="2"/>
-      <c r="BY18" s="2"/>
-      <c r="BZ18" s="2"/>
-      <c r="CA18" s="2"/>
-      <c r="CB18" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="V18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB18" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="19" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A19" s="9">
@@ -3134,83 +4914,231 @@
       <c r="E19" s="11">
         <f>IF(C19&gt;0,INDEX(F$1:CB$1,MATCH("█",F19:CB19,0)+C19-1),"")</f>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
+      <c r="F19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="U19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
-      <c r="AE19" s="2"/>
-      <c r="AF19" s="2"/>
-      <c r="AG19" s="2"/>
-      <c r="AH19" s="2"/>
-      <c r="AI19" s="2"/>
-      <c r="AJ19" s="2"/>
-      <c r="AK19" s="2"/>
-      <c r="AL19" s="2"/>
-      <c r="AM19" s="2"/>
-      <c r="AN19" s="2"/>
-      <c r="AO19" s="2"/>
-      <c r="AP19" s="2"/>
-      <c r="AQ19" s="2"/>
-      <c r="AR19" s="2"/>
-      <c r="AS19" s="2"/>
-      <c r="AT19" s="2"/>
-      <c r="AU19" s="2"/>
-      <c r="AV19" s="2"/>
-      <c r="AW19" s="2"/>
-      <c r="AX19" s="2"/>
-      <c r="AY19" s="2"/>
-      <c r="AZ19" s="2"/>
-      <c r="BA19" s="2"/>
-      <c r="BB19" s="2"/>
-      <c r="BC19" s="2"/>
-      <c r="BD19" s="2"/>
-      <c r="BE19" s="2"/>
-      <c r="BF19" s="2"/>
-      <c r="BG19" s="2"/>
-      <c r="BH19" s="2"/>
-      <c r="BI19" s="2"/>
-      <c r="BJ19" s="2"/>
-      <c r="BK19" s="2"/>
-      <c r="BL19" s="2"/>
-      <c r="BM19" s="2"/>
-      <c r="BN19" s="2"/>
-      <c r="BO19" s="2"/>
-      <c r="BP19" s="2"/>
-      <c r="BQ19" s="2"/>
-      <c r="BR19" s="2"/>
-      <c r="BS19" s="2"/>
-      <c r="BT19" s="2"/>
-      <c r="BU19" s="2"/>
-      <c r="BV19" s="2"/>
-      <c r="BW19" s="2"/>
-      <c r="BX19" s="2"/>
-      <c r="BY19" s="2"/>
-      <c r="BZ19" s="2"/>
-      <c r="CA19" s="2"/>
-      <c r="CB19" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB19" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="20" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
@@ -3228,83 +5156,231 @@
       <c r="E20" s="11">
         <f>IF(C20&gt;0,INDEX(F$1:CB$1,MATCH("█",F20:CB20,0)+C20-1),"")</f>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
+      <c r="F20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X20" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="Y20" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z20" s="2"/>
-      <c r="AA20" s="2"/>
-      <c r="AB20" s="2"/>
-      <c r="AC20" s="2"/>
-      <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="2"/>
-      <c r="AG20" s="2"/>
-      <c r="AH20" s="2"/>
-      <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="2"/>
-      <c r="AL20" s="2"/>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2"/>
-      <c r="AO20" s="2"/>
-      <c r="AP20" s="2"/>
-      <c r="AQ20" s="2"/>
-      <c r="AR20" s="2"/>
-      <c r="AS20" s="2"/>
-      <c r="AT20" s="2"/>
-      <c r="AU20" s="2"/>
-      <c r="AV20" s="2"/>
-      <c r="AW20" s="2"/>
-      <c r="AX20" s="2"/>
-      <c r="AY20" s="2"/>
-      <c r="AZ20" s="2"/>
-      <c r="BA20" s="2"/>
-      <c r="BB20" s="2"/>
-      <c r="BC20" s="2"/>
-      <c r="BD20" s="2"/>
-      <c r="BE20" s="2"/>
-      <c r="BF20" s="2"/>
-      <c r="BG20" s="2"/>
-      <c r="BH20" s="2"/>
-      <c r="BI20" s="2"/>
-      <c r="BJ20" s="2"/>
-      <c r="BK20" s="2"/>
-      <c r="BL20" s="2"/>
-      <c r="BM20" s="2"/>
-      <c r="BN20" s="2"/>
-      <c r="BO20" s="2"/>
-      <c r="BP20" s="2"/>
-      <c r="BQ20" s="2"/>
-      <c r="BR20" s="2"/>
-      <c r="BS20" s="2"/>
-      <c r="BT20" s="2"/>
-      <c r="BU20" s="2"/>
-      <c r="BV20" s="2"/>
-      <c r="BW20" s="2"/>
-      <c r="BX20" s="2"/>
-      <c r="BY20" s="2"/>
-      <c r="BZ20" s="2"/>
-      <c r="CA20" s="2"/>
-      <c r="CB20" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="Z20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB20" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="21" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A21" s="9">
@@ -3322,83 +5398,231 @@
       <c r="E21" s="11">
         <f>IF(C21&gt;0,INDEX(F$1:CB$1,MATCH("█",F21:CB21,0)+C21-1),"")</f>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
-      <c r="AA21" s="2"/>
-      <c r="AB21" s="2"/>
-      <c r="AC21" s="2"/>
-      <c r="AD21" s="2"/>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
+      <c r="F21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF21" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AG21" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AH21" s="2"/>
-      <c r="AI21" s="2"/>
-      <c r="AJ21" s="2"/>
-      <c r="AK21" s="2"/>
-      <c r="AL21" s="2"/>
-      <c r="AM21" s="2"/>
-      <c r="AN21" s="2"/>
-      <c r="AO21" s="2"/>
-      <c r="AP21" s="2"/>
-      <c r="AQ21" s="2"/>
-      <c r="AR21" s="2"/>
-      <c r="AS21" s="2"/>
-      <c r="AT21" s="2"/>
-      <c r="AU21" s="2"/>
-      <c r="AV21" s="2"/>
-      <c r="AW21" s="2"/>
-      <c r="AX21" s="2"/>
-      <c r="AY21" s="2"/>
-      <c r="AZ21" s="2"/>
-      <c r="BA21" s="2"/>
-      <c r="BB21" s="2"/>
-      <c r="BC21" s="2"/>
-      <c r="BD21" s="2"/>
-      <c r="BE21" s="2"/>
-      <c r="BF21" s="2"/>
-      <c r="BG21" s="2"/>
-      <c r="BH21" s="2"/>
-      <c r="BI21" s="2"/>
-      <c r="BJ21" s="2"/>
-      <c r="BK21" s="2"/>
-      <c r="BL21" s="2"/>
-      <c r="BM21" s="2"/>
-      <c r="BN21" s="2"/>
-      <c r="BO21" s="2"/>
-      <c r="BP21" s="2"/>
-      <c r="BQ21" s="2"/>
-      <c r="BR21" s="2"/>
-      <c r="BS21" s="2"/>
-      <c r="BT21" s="2"/>
-      <c r="BU21" s="2"/>
-      <c r="BV21" s="2"/>
-      <c r="BW21" s="2"/>
-      <c r="BX21" s="2"/>
-      <c r="BY21" s="2"/>
-      <c r="BZ21" s="2"/>
-      <c r="CA21" s="2"/>
-      <c r="CB21" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AH21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB21" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="22" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A22" s="9">
@@ -3416,83 +5640,231 @@
       <c r="E22" s="11">
         <f>IF(C22&gt;0,INDEX(F$1:CB$1,MATCH("█",F22:CB22,0)+C22-1),"")</f>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
-      <c r="AA22" s="2"/>
-      <c r="AB22" s="2"/>
-      <c r="AC22" s="2"/>
-      <c r="AD22" s="2"/>
-      <c r="AE22" s="2"/>
-      <c r="AF22" s="2"/>
-      <c r="AG22" s="2"/>
-      <c r="AH22" s="2"/>
-      <c r="AI22" s="2"/>
+      <c r="F22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI22" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AJ22" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AK22" s="2"/>
-      <c r="AL22" s="2"/>
-      <c r="AM22" s="2"/>
-      <c r="AN22" s="2"/>
-      <c r="AO22" s="2"/>
-      <c r="AP22" s="2"/>
-      <c r="AQ22" s="2"/>
-      <c r="AR22" s="2"/>
-      <c r="AS22" s="2"/>
-      <c r="AT22" s="2"/>
-      <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
-      <c r="AW22" s="2"/>
-      <c r="AX22" s="2"/>
-      <c r="AY22" s="2"/>
-      <c r="AZ22" s="2"/>
-      <c r="BA22" s="2"/>
-      <c r="BB22" s="2"/>
-      <c r="BC22" s="2"/>
-      <c r="BD22" s="2"/>
-      <c r="BE22" s="2"/>
-      <c r="BF22" s="2"/>
-      <c r="BG22" s="2"/>
-      <c r="BH22" s="2"/>
-      <c r="BI22" s="2"/>
-      <c r="BJ22" s="2"/>
-      <c r="BK22" s="2"/>
-      <c r="BL22" s="2"/>
-      <c r="BM22" s="2"/>
-      <c r="BN22" s="2"/>
-      <c r="BO22" s="2"/>
-      <c r="BP22" s="2"/>
-      <c r="BQ22" s="2"/>
-      <c r="BR22" s="2"/>
-      <c r="BS22" s="2"/>
-      <c r="BT22" s="2"/>
-      <c r="BU22" s="2"/>
-      <c r="BV22" s="2"/>
-      <c r="BW22" s="2"/>
-      <c r="BX22" s="2"/>
-      <c r="BY22" s="2"/>
-      <c r="BZ22" s="2"/>
-      <c r="CA22" s="2"/>
-      <c r="CB22" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AK22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB22" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="23" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A23" s="9">
@@ -3510,83 +5882,231 @@
       <c r="E23" s="11">
         <f>IF(C23&gt;0,INDEX(F$1:CB$1,MATCH("█",F23:CB23,0)+C23-1),"")</f>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
-      <c r="AA23" s="2"/>
-      <c r="AB23" s="2"/>
-      <c r="AC23" s="2"/>
-      <c r="AD23" s="2"/>
-      <c r="AE23" s="2"/>
-      <c r="AF23" s="2"/>
-      <c r="AG23" s="2"/>
-      <c r="AH23" s="2"/>
-      <c r="AI23" s="2"/>
-      <c r="AJ23" s="2"/>
-      <c r="AK23" s="2"/>
-      <c r="AL23" s="2"/>
-      <c r="AM23" s="2"/>
+      <c r="F23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM23" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AN23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AO23" s="2"/>
-      <c r="AP23" s="2"/>
-      <c r="AQ23" s="2"/>
-      <c r="AR23" s="2"/>
-      <c r="AS23" s="2"/>
-      <c r="AT23" s="2"/>
-      <c r="AU23" s="2"/>
-      <c r="AV23" s="2"/>
-      <c r="AW23" s="2"/>
-      <c r="AX23" s="2"/>
-      <c r="AY23" s="2"/>
-      <c r="AZ23" s="2"/>
-      <c r="BA23" s="2"/>
-      <c r="BB23" s="2"/>
-      <c r="BC23" s="2"/>
-      <c r="BD23" s="2"/>
-      <c r="BE23" s="2"/>
-      <c r="BF23" s="2"/>
-      <c r="BG23" s="2"/>
-      <c r="BH23" s="2"/>
-      <c r="BI23" s="2"/>
-      <c r="BJ23" s="2"/>
-      <c r="BK23" s="2"/>
-      <c r="BL23" s="2"/>
-      <c r="BM23" s="2"/>
-      <c r="BN23" s="2"/>
-      <c r="BO23" s="2"/>
-      <c r="BP23" s="2"/>
-      <c r="BQ23" s="2"/>
-      <c r="BR23" s="2"/>
-      <c r="BS23" s="2"/>
-      <c r="BT23" s="2"/>
-      <c r="BU23" s="2"/>
-      <c r="BV23" s="2"/>
-      <c r="BW23" s="2"/>
-      <c r="BX23" s="2"/>
-      <c r="BY23" s="2"/>
-      <c r="BZ23" s="2"/>
-      <c r="CA23" s="2"/>
-      <c r="CB23" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AO23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB23" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
@@ -3605,82 +6125,230 @@
         <f>IF(C24&gt;0,INDEX(F$1:CB$1,MATCH("█",F24:CB24,0)+C24-1),"")</f>
       </c>
       <c r="F24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
-      <c r="AO24" s="2"/>
-      <c r="AP24" s="2"/>
-      <c r="AQ24" s="2"/>
-      <c r="AR24" s="2"/>
-      <c r="AS24" s="2"/>
-      <c r="AT24" s="2"/>
-      <c r="AU24" s="2"/>
-      <c r="AV24" s="2"/>
-      <c r="AW24" s="2"/>
-      <c r="AX24" s="2"/>
-      <c r="AY24" s="2"/>
-      <c r="AZ24" s="2"/>
-      <c r="BA24" s="2"/>
-      <c r="BB24" s="2"/>
-      <c r="BC24" s="2"/>
-      <c r="BD24" s="2"/>
-      <c r="BE24" s="2"/>
-      <c r="BF24" s="2"/>
-      <c r="BG24" s="2"/>
-      <c r="BH24" s="2"/>
-      <c r="BI24" s="2"/>
-      <c r="BJ24" s="2"/>
-      <c r="BK24" s="2"/>
-      <c r="BL24" s="2"/>
-      <c r="BM24" s="2"/>
-      <c r="BN24" s="2"/>
-      <c r="BO24" s="2"/>
-      <c r="BP24" s="2"/>
-      <c r="BQ24" s="2"/>
-      <c r="BR24" s="2"/>
-      <c r="BS24" s="2"/>
-      <c r="BT24" s="2"/>
-      <c r="BU24" s="2"/>
-      <c r="BV24" s="2"/>
-      <c r="BW24" s="2"/>
-      <c r="BX24" s="2"/>
-      <c r="BY24" s="2"/>
-      <c r="BZ24" s="2"/>
-      <c r="CA24" s="2"/>
-      <c r="CB24" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB24" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="25" spans="1:80" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
@@ -3698,83 +6366,231 @@
       <c r="E25" s="11">
         <f>IF(C25&gt;0,INDEX(F$1:CB$1,MATCH("█",F25:CB25,0)+C25-1),"")</f>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="2"/>
-      <c r="T25" s="2"/>
-      <c r="U25" s="2"/>
-      <c r="V25" s="2"/>
-      <c r="W25" s="2"/>
-      <c r="X25" s="2"/>
-      <c r="Y25" s="2"/>
-      <c r="Z25" s="2"/>
-      <c r="AA25" s="2"/>
-      <c r="AB25" s="2"/>
-      <c r="AC25" s="2"/>
-      <c r="AD25" s="2"/>
-      <c r="AE25" s="2"/>
-      <c r="AF25" s="2"/>
-      <c r="AG25" s="2"/>
-      <c r="AH25" s="2"/>
-      <c r="AI25" s="2"/>
-      <c r="AJ25" s="2"/>
-      <c r="AK25" s="2"/>
-      <c r="AL25" s="2"/>
+      <c r="F25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL25" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AM25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="AN25" s="2"/>
-      <c r="AO25" s="2"/>
-      <c r="AP25" s="2"/>
-      <c r="AQ25" s="2"/>
-      <c r="AR25" s="2"/>
-      <c r="AS25" s="2"/>
-      <c r="AT25" s="2"/>
-      <c r="AU25" s="2"/>
-      <c r="AV25" s="2"/>
-      <c r="AW25" s="2"/>
-      <c r="AX25" s="2"/>
-      <c r="AY25" s="2"/>
-      <c r="AZ25" s="2"/>
-      <c r="BA25" s="2"/>
-      <c r="BB25" s="2"/>
-      <c r="BC25" s="2"/>
-      <c r="BD25" s="2"/>
-      <c r="BE25" s="2"/>
-      <c r="BF25" s="2"/>
-      <c r="BG25" s="2"/>
-      <c r="BH25" s="2"/>
-      <c r="BI25" s="2"/>
-      <c r="BJ25" s="2"/>
-      <c r="BK25" s="2"/>
-      <c r="BL25" s="2"/>
-      <c r="BM25" s="2"/>
-      <c r="BN25" s="2"/>
-      <c r="BO25" s="2"/>
-      <c r="BP25" s="2"/>
-      <c r="BQ25" s="2"/>
-      <c r="BR25" s="2"/>
-      <c r="BS25" s="2"/>
-      <c r="BT25" s="2"/>
-      <c r="BU25" s="2"/>
-      <c r="BV25" s="2"/>
-      <c r="BW25" s="2"/>
-      <c r="BX25" s="2"/>
-      <c r="BY25" s="2"/>
-      <c r="BZ25" s="2"/>
-      <c r="CA25" s="2"/>
-      <c r="CB25" s="2"/>
+        <v>27</v>
+      </c>
+      <c r="AN25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AW25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AY25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BB25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BC25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BD25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BE25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BF25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BG25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BH25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BI25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BJ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BK25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BL25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BM25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BN25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BO25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BP25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BQ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BR25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BS25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BT25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BU25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BV25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BW25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BX25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BY25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BZ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CA25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="CB25" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">

--- a/Ebooks/Plan.xlsx
+++ b/Ebooks/Plan.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="48">
   <si>
     <t>WBS</t>
   </si>
@@ -1529,7 +1529,9 @@
       <c r="F5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
@@ -1620,11 +1622,11 @@
       <c r="E6" s="11">
         <f>IF(C6&gt;0,INDEX(F$1:CB$1,MATCH("█",F6:CB6,0)+C6-1),"")</f>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F6" s="2"/>
       <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="H6" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1714,13 +1716,15 @@
       <c r="E7" s="11">
         <f>IF(C7&gt;0,INDEX(F$1:CB$1,MATCH("█",F7:CB7,0)+C7-1),"")</f>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1808,14 +1812,14 @@
       <c r="E8" s="11">
         <f>IF(C8&gt;0,INDEX(F$1:CB$1,MATCH("█",F8:CB8,0)+C8-1),"")</f>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="K8" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
@@ -1902,14 +1906,18 @@
       <c r="E9" s="11">
         <f>IF(C9&gt;0,INDEX(F$1:CB$1,MATCH("█",F9:CB9,0)+C9-1),"")</f>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="I9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
@@ -2238,15 +2246,15 @@
       <c r="E11" s="11">
         <f>IF(C11&gt;0,INDEX(F$1:CB$1,MATCH("█",F11:CB11,0)+C11-1),"")</f>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2332,17 +2340,19 @@
       <c r="E12" s="11">
         <f>IF(C12&gt;0,INDEX(F$1:CB$1,MATCH("█",F12:CB12,0)+C12-1),"")</f>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="O12" s="2"/>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -2426,9 +2436,7 @@
       <c r="E13" s="11">
         <f>IF(C13&gt;0,INDEX(F$1:CB$1,MATCH("█",F13:CB13,0)+C13-1),"")</f>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -2437,7 +2445,9 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
@@ -2520,9 +2530,7 @@
       <c r="E14" s="11">
         <f>IF(C14&gt;0,INDEX(F$1:CB$1,MATCH("█",F14:CB14,0)+C14-1),"")</f>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -2532,11 +2540,21 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
+      <c r="P14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2"/>
       <c r="W14" s="2"/>
@@ -2856,9 +2874,7 @@
       <c r="E16" s="11">
         <f>IF(C16&gt;0,INDEX(F$1:CB$1,MATCH("█",F16:CB16,0)+C16-1),"")</f>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -2873,9 +2889,15 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
+      <c r="U16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
@@ -2950,9 +2972,7 @@
       <c r="E17" s="11">
         <f>IF(C17&gt;0,INDEX(F$1:CB$1,MATCH("█",F17:CB17,0)+C17-1),"")</f>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F17" s="2"/>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -2970,8 +2990,12 @@
       <c r="U17" s="2"/>
       <c r="V17" s="2"/>
       <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
+      <c r="X17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y17" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="Z17" s="2"/>
       <c r="AA17" s="2"/>
       <c r="AB17" s="2"/>
@@ -3044,9 +3068,7 @@
       <c r="E18" s="11">
         <f>IF(C18&gt;0,INDEX(F$1:CB$1,MATCH("█",F18:CB18,0)+C18-1),"")</f>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F18" s="2"/>
       <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -3066,10 +3088,18 @@
       <c r="W18" s="2"/>
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
-      <c r="AA18" s="2"/>
-      <c r="AB18" s="2"/>
-      <c r="AC18" s="2"/>
+      <c r="Z18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC18" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AD18" s="2"/>
       <c r="AE18" s="2"/>
       <c r="AF18" s="2"/>
@@ -3138,9 +3168,7 @@
       <c r="E19" s="11">
         <f>IF(C19&gt;0,INDEX(F$1:CB$1,MATCH("█",F19:CB19,0)+C19-1),"")</f>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F19" s="2"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -3160,11 +3188,21 @@
       <c r="W19" s="2"/>
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
-      <c r="AA19" s="2"/>
-      <c r="AB19" s="2"/>
-      <c r="AC19" s="2"/>
-      <c r="AD19" s="2"/>
+      <c r="Z19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD19" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AE19" s="2"/>
       <c r="AF19" s="2"/>
       <c r="AG19" s="2"/>
@@ -3232,9 +3270,7 @@
       <c r="E20" s="11">
         <f>IF(C20&gt;0,INDEX(F$1:CB$1,MATCH("█",F20:CB20,0)+C20-1),"")</f>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -3259,17 +3295,39 @@
       <c r="AB20" s="2"/>
       <c r="AC20" s="2"/>
       <c r="AD20" s="2"/>
-      <c r="AE20" s="2"/>
-      <c r="AF20" s="2"/>
-      <c r="AG20" s="2"/>
-      <c r="AH20" s="2"/>
-      <c r="AI20" s="2"/>
-      <c r="AJ20" s="2"/>
-      <c r="AK20" s="2"/>
-      <c r="AL20" s="2"/>
-      <c r="AM20" s="2"/>
-      <c r="AN20" s="2"/>
-      <c r="AO20" s="2"/>
+      <c r="AE20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO20" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2"/>
       <c r="AR20" s="2"/>
@@ -3326,9 +3384,7 @@
       <c r="E21" s="11">
         <f>IF(C21&gt;0,INDEX(F$1:CB$1,MATCH("█",F21:CB21,0)+C21-1),"")</f>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -3364,10 +3420,18 @@
       <c r="AM21" s="2"/>
       <c r="AN21" s="2"/>
       <c r="AO21" s="2"/>
-      <c r="AP21" s="2"/>
-      <c r="AQ21" s="2"/>
-      <c r="AR21" s="2"/>
-      <c r="AS21" s="2"/>
+      <c r="AP21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS21" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AT21" s="2"/>
       <c r="AU21" s="2"/>
       <c r="AV21" s="2"/>
@@ -3420,9 +3484,7 @@
       <c r="E22" s="11">
         <f>IF(C22&gt;0,INDEX(F$1:CB$1,MATCH("█",F22:CB22,0)+C22-1),"")</f>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -3462,9 +3524,15 @@
       <c r="AQ22" s="2"/>
       <c r="AR22" s="2"/>
       <c r="AS22" s="2"/>
-      <c r="AT22" s="2"/>
-      <c r="AU22" s="2"/>
-      <c r="AV22" s="2"/>
+      <c r="AT22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AV22" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AW22" s="2"/>
       <c r="AX22" s="2"/>
       <c r="AY22" s="2"/>
@@ -3514,9 +3582,7 @@
       <c r="E23" s="11">
         <f>IF(C23&gt;0,INDEX(F$1:CB$1,MATCH("█",F23:CB23,0)+C23-1),"")</f>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F23" s="2"/>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -3559,8 +3625,12 @@
       <c r="AT23" s="2"/>
       <c r="AU23" s="2"/>
       <c r="AV23" s="2"/>
-      <c r="AW23" s="2"/>
-      <c r="AX23" s="2"/>
+      <c r="AW23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AX23" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AY23" s="2"/>
       <c r="AZ23" s="2"/>
       <c r="BA23" s="2"/>
@@ -3608,49 +3678,117 @@
       <c r="E24" s="11">
         <f>IF(C24&gt;0,INDEX(F$1:CB$1,MATCH("█",F24:CB24,0)+C24-1),"")</f>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F24" s="2"/>
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
-      <c r="AA24" s="2"/>
-      <c r="AB24" s="2"/>
-      <c r="AC24" s="2"/>
-      <c r="AD24" s="2"/>
-      <c r="AE24" s="2"/>
-      <c r="AF24" s="2"/>
-      <c r="AG24" s="2"/>
-      <c r="AH24" s="2"/>
-      <c r="AI24" s="2"/>
-      <c r="AJ24" s="2"/>
-      <c r="AK24" s="2"/>
-      <c r="AL24" s="2"/>
-      <c r="AM24" s="2"/>
-      <c r="AN24" s="2"/>
-      <c r="AO24" s="2"/>
-      <c r="AP24" s="2"/>
-      <c r="AQ24" s="2"/>
-      <c r="AR24" s="2"/>
-      <c r="AS24" s="2"/>
-      <c r="AT24" s="2"/>
+      <c r="L24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="X24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AB24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AH24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AK24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AN24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AO24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AP24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AQ24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AR24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AS24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AT24" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="AU24" s="2"/>
       <c r="AV24" s="2"/>
       <c r="AW24" s="2"/>
@@ -3702,9 +3840,7 @@
       <c r="E25" s="11">
         <f>IF(C25&gt;0,INDEX(F$1:CB$1,MATCH("█",F25:CB25,0)+C25-1),"")</f>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>27</v>
-      </c>
+      <c r="F25" s="2"/>
       <c r="G25" s="2"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -3749,9 +3885,15 @@
       <c r="AV25" s="2"/>
       <c r="AW25" s="2"/>
       <c r="AX25" s="2"/>
-      <c r="AY25" s="2"/>
-      <c r="AZ25" s="2"/>
-      <c r="BA25" s="2"/>
+      <c r="AY25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="AZ25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA25" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="BB25" s="2"/>
       <c r="BC25" s="2"/>
       <c r="BD25" s="2"/>
